--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\Mott's Wrecker Service\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19EA8FE4-08F8-45D6-B774-2551B6A6F074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="2340" yWindow="1665" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId4"/>
+    <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="183">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -569,23 +574,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -620,22 +617,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -925,2056 +929,2039 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M59"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="true" style="1"/>
-    <col min="2" max="2" width="15" customWidth="true" style="1"/>
-    <col min="3" max="3" width="15" customWidth="true" style="1"/>
-    <col min="4" max="4" width="15" customWidth="true" style="1"/>
-    <col min="5" max="5" width="15" customWidth="true" style="1"/>
-    <col min="6" max="6" width="15" customWidth="true" style="1"/>
-    <col min="7" max="7" width="15" customWidth="true" style="1"/>
-    <col min="8" max="8" width="15" customWidth="true" style="1"/>
-    <col min="9" max="9" width="15" customWidth="true" style="1"/>
-    <col min="10" max="10" width="15" customWidth="true" style="1"/>
-    <col min="11" max="11" width="15" customWidth="true" style="1"/>
-    <col min="12" max="12" width="15" customWidth="true" style="1"/>
-    <col min="13" max="13" width="15" customWidth="true" style="1"/>
+    <col min="1" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>111</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>5001912988</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="4" t="s">
+      <c r="G4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="4" t="s">
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>110</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>5012724655</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="4" t="s">
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>111</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>5014045676</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="4" t="s">
+      <c r="G6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>301</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>5018915355</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="4" t="s">
+      <c r="G7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>111</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>5019699676</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="4" t="s">
+      <c r="G8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>110</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>5021015870</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="4" t="s">
+      <c r="G9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>112</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>5021546241</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="4" t="s">
+      <c r="G10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>112</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>5023845243</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="4" t="s">
+      <c r="G11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>111</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>5025459813</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="4" t="s">
+      <c r="G12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="4" t="s">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>301</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>5027410344</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="4" t="s">
+      <c r="G13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="4" t="s">
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>112</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>5028822223</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="4" t="s">
+      <c r="G14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="4" t="s">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>112</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>5033153504</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="4" t="s">
+      <c r="G15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="4" t="s">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>110</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>5034518310</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="4" t="s">
+      <c r="G16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="4" t="s">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>112</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>5042484121</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="4" t="s">
+      <c r="G17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="4" t="s">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="3">
         <v>112</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>5048577916</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="4" t="s">
+      <c r="G18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="4" t="s">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="3">
         <v>301</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>5060271507</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="4" t="s">
+      <c r="G19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="4" t="s">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <v>112</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>5065583844</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="4" t="s">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="4" t="s">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>110</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>5100237567</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="4" t="s">
+      <c r="G21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="4" t="s">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>112</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>5101465304</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="4" t="s">
+      <c r="G22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="4" t="s">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>112</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>5106751495</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="4" t="s">
+      <c r="G23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="4" t="s">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>112</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>5107862306</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="4" t="s">
+      <c r="G24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="M24" s="4"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="4" t="s">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>111</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>5114256434</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="4" t="s">
+      <c r="G25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="M25" s="4"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="4" t="s">
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>112</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>5121665545</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" s="4" t="s">
+      <c r="G26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="4" t="s">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <v>301</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>5133605271</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" s="4" t="s">
+      <c r="G27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M27" s="4"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="4" t="s">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <v>113</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>5134154922</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" s="4" t="s">
+      <c r="G28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="M28" s="4"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="4" t="s">
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3">
         <v>110</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>5160042047</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" s="4" t="s">
+      <c r="G29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="M29" s="4"/>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="4" t="s">
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3">
         <v>301</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>5161466800</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="4" t="s">
+      <c r="G30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="M30" s="4"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="4" t="s">
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3">
         <v>112</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>5168199288</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="4" t="s">
+      <c r="G31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="M31" s="4"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="4" t="s">
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3">
         <v>301</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>5170090230</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" s="4" t="s">
+      <c r="G32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="M32" s="4"/>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="4" t="s">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>110</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>5174829578</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="4" t="s">
+      <c r="G33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M33" s="4"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="4" t="s">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>110</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>5180830801</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L34" s="4" t="s">
+      <c r="G34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="4" t="s">
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <v>110</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>5203835458</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L35" s="4" t="s">
+      <c r="G35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="M35" s="4"/>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="4" t="s">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>112</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>5206231644</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L36" s="4" t="s">
+      <c r="G36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="M36" s="4"/>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="4" t="s">
+      <c r="M36" s="3"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="3">
         <v>112</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>5206259061</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L37" s="4" t="s">
+      <c r="G37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="4" t="s">
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="3">
         <v>111</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>5211779691</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L38" s="4" t="s">
+      <c r="G38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="4" t="s">
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="3">
         <v>301</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>5212121113</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L39" s="4" t="s">
+      <c r="G39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="4" t="s">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="3">
         <v>110</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>5220297071</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="4" t="s">
+      <c r="G40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="4" t="s">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="3">
         <v>110</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>5238353442</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L41" s="4" t="s">
+      <c r="G41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="M41" s="4"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="4" t="s">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="3">
         <v>112</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>5254543722</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L42" s="4" t="s">
+      <c r="G42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="M42" s="4"/>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="4" t="s">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="3">
         <v>112</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>5262654432</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L43" s="4" t="s">
+      <c r="G43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="M43" s="4"/>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="4" t="s">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="3">
         <v>110</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>5265044352</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L44" s="4" t="s">
+      <c r="G44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="M44" s="4"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="4" t="s">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="3">
         <v>112</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="3">
         <v>5267281540</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L45" s="4" t="s">
+      <c r="G45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="M45" s="4"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="4" t="s">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="3">
         <v>111</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="3">
         <v>5268658556</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L46" s="4" t="s">
+      <c r="G46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="4" t="s">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="3">
         <v>112</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="3">
         <v>5272725026</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L47" s="4" t="s">
+      <c r="G47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="M47" s="4"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="4" t="s">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="3">
         <v>112</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>5291991975</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L48" s="4" t="s">
+      <c r="G48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="M48" s="4" t="s">
+      <c r="M48" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="3">
         <v>110</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="3">
         <v>5296674307</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L49" s="4" t="s">
+      <c r="G49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="M49" s="4" t="s">
+      <c r="M49" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="4" t="s">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="3">
         <v>111</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="3">
         <v>5299186078</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L50" s="4" t="s">
+      <c r="G50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="4" t="s">
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="3">
         <v>112</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="3">
         <v>5302786279</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L51" s="4" t="s">
+      <c r="G51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="M51" s="4"/>
-    </row>
-    <row r="52" spans="1:13">
-      <c r="A52" s="4" t="s">
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="3">
         <v>110</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="3">
         <v>5304829908</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L52" s="4" t="s">
+      <c r="G52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="M52" s="4" t="s">
+      <c r="M52" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
-      <c r="A53" s="4" t="s">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="3">
         <v>112</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="3">
         <v>5307546103</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G53" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L53" s="4" t="s">
+      <c r="G53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="M53" s="4" t="s">
+      <c r="M53" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="4" t="s">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="3">
         <v>110</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="3">
         <v>5313359492</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L54" s="4" t="s">
+      <c r="G54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="M54" s="4" t="s">
+      <c r="M54" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="3">
         <v>111</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="3">
         <v>5316784489</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L55" s="4" t="s">
+      <c r="G55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="M55" s="4"/>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="4" t="s">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>110</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="3">
         <v>5328380737</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G56" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L56" s="4" t="s">
+      <c r="G56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="M56" s="4" t="s">
+      <c r="M56" s="3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
-      <c r="A57" s="4" t="s">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="3">
         <v>112</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="3">
         <v>5341988170</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G57" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L57" s="4" t="s">
+      <c r="G57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="M57" s="4" t="s">
+      <c r="M57" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="4" t="s">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="3">
         <v>111</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="3">
         <v>5349375228</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L58" s="4" t="s">
+      <c r="G58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="M58" s="4"/>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="4" t="s">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="3">
         <v>112</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="3">
         <v>5371436091</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L59" s="4" t="s">
+      <c r="G59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="M59" s="4" t="s">
+      <c r="M59" s="3" t="s">
         <v>182</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\Mott's Wrecker Service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19EA8FE4-08F8-45D6-B774-2551B6A6F074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54055A7F-7F0B-4560-81FF-9F101C539FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1665" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="198">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -569,6 +569,51 @@
   </si>
   <si>
     <t>03/10/26 09:34 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 10:01 EDT</t>
+  </si>
+  <si>
+    <t>30.5mi W of Uvalde TX</t>
+  </si>
+  <si>
+    <t>03/18/26 10:16 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 10:34 EDT</t>
+  </si>
+  <si>
+    <t>CAMERA-OBSTRUCTION</t>
+  </si>
+  <si>
+    <t>2.2mi E of Del Rio TX</t>
+  </si>
+  <si>
+    <t>03/18/26 10:14 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 15:26 EDT</t>
+  </si>
+  <si>
+    <t>Jacky  Messer</t>
+  </si>
+  <si>
+    <t>5mi S of Cibolo TX</t>
+  </si>
+  <si>
+    <t>03/19/26 08:21 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 13:32 EDT</t>
+  </si>
+  <si>
+    <t>6mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>03/20/26 07:53 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 08:46 EDT</t>
   </si>
 </sst>
 </file>
@@ -930,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -2961,6 +3006,148 @@
         <v>182</v>
       </c>
     </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="3">
+        <v>113</v>
+      </c>
+      <c r="D60" s="3">
+        <v>5418546440</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="3">
+        <v>113</v>
+      </c>
+      <c r="D61" s="3">
+        <v>5418729285</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C62" s="3">
+        <v>110</v>
+      </c>
+      <c r="D62" s="3">
+        <v>5427300085</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C63" s="3">
+        <v>110</v>
+      </c>
+      <c r="D63" s="3">
+        <v>5432585895</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50D0A103-ED97-4682-A246-680B6F9E4651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3ABE08D-68D9-43E4-AB4C-E3AEF9665D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3306" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3577" uniqueCount="1295">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -3614,6 +3614,297 @@
   </si>
   <si>
     <t>3.7mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>04/06/26 10:22 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi N of Windcrest TX</t>
+  </si>
+  <si>
+    <t>04/06/26 10:47 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi NW of Selma TX</t>
+  </si>
+  <si>
+    <t>04/06/26 19:03 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 10:49 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi NW of Selma TX</t>
+  </si>
+  <si>
+    <t>04/06/26 12:06 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 19:28 EDT</t>
+  </si>
+  <si>
+    <t>10mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>04/07/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi SW of Kirby TX</t>
+  </si>
+  <si>
+    <t>04/08/26 10:57 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 16:12 EDT</t>
+  </si>
+  <si>
+    <t>14.7mi SW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>04/08/26 10:59 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 14:34 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 16:20 EDT</t>
+  </si>
+  <si>
+    <t>7mi S of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>04/08/26 08:11 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 11:03 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:17 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 11:01 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:19 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:21 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:22 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:25 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:26 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:40 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 09:19 EDT</t>
+  </si>
+  <si>
+    <t>4mi NE of Leon Valley TX</t>
+  </si>
+  <si>
+    <t>04/08/26 09:30 EDT</t>
+  </si>
+  <si>
+    <t>1mi E of Scenic Oaks TX</t>
+  </si>
+  <si>
+    <t>04/08/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi NW of Boerne TX</t>
+  </si>
+  <si>
+    <t>04/08/26 11:19 EDT</t>
+  </si>
+  <si>
+    <t>8.1mi NW of Boerne TX</t>
+  </si>
+  <si>
+    <t>04/08/26 11:32 EDT</t>
+  </si>
+  <si>
+    <t>4.4mi NW of Boerne TX</t>
+  </si>
+  <si>
+    <t>04/08/26 11:59 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi NW of Boerne TX</t>
+  </si>
+  <si>
+    <t>04/08/26 12:31 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi S of San Antonio TX</t>
+  </si>
+  <si>
+    <t>04/08/26 12:32 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi S of San Antonio TX</t>
+  </si>
+  <si>
+    <t>04/08/26 12:36 EDT</t>
+  </si>
+  <si>
+    <t>5.3mi S of Terrell Hills TX</t>
+  </si>
+  <si>
+    <t>04/08/26 12:38 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi SW of Kirby TX</t>
+  </si>
+  <si>
+    <t>04/08/26 12:43 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi E of Kirby TX</t>
+  </si>
+  <si>
+    <t>04/08/26 12:46 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 12:50 EDT</t>
+  </si>
+  <si>
+    <t>6.5mi S of Canyon Lake TX</t>
+  </si>
+  <si>
+    <t>04/09/26 10:52 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 13:29 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 20:31 EDT</t>
+  </si>
+  <si>
+    <t>7.9mi S of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>04/09/26 09:41 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 10:20 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 10:24 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 10:28 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 11:24 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 07:44 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 11:50 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi NW of Live Oak TX</t>
+  </si>
+  <si>
+    <t>04/10/26 07:43 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 07:45 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 12:05 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 13:57 EDT</t>
+  </si>
+  <si>
+    <t>5.2mi NW of Live Oak TX</t>
+  </si>
+  <si>
+    <t>04/09/26 15:37 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 15:40 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 17:16 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi NE of Northlake TX</t>
+  </si>
+  <si>
+    <t>04/09/26 19:55 EDT</t>
+  </si>
+  <si>
+    <t>6.4mi NW of Pauls Valley OK</t>
+  </si>
+  <si>
+    <t>04/10/26 00:08 EDT</t>
+  </si>
+  <si>
+    <t>18.4mi W of El Reno OK</t>
+  </si>
+  <si>
+    <t>04/10/26 08:44 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 13:38 EDT</t>
+  </si>
+  <si>
+    <t>4.2mi N of Sanger TX</t>
+  </si>
+  <si>
+    <t>04/10/26 18:04 EDT</t>
+  </si>
+  <si>
+    <t>8.7mi SW of Belton TX</t>
+  </si>
+  <si>
+    <t>04/10/26 18:10 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi N of Sonterra TX</t>
+  </si>
+  <si>
+    <t>04/10/26 18:18 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi SW of Sonterra TX</t>
+  </si>
+  <si>
+    <t>04/10/26 19:33 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 19:54 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 08:59 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 16:34 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi NE of San Marcos TX</t>
+  </si>
+  <si>
+    <t>04/12/26 17:25 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi W of Windcrest TX</t>
   </si>
 </sst>
 </file>
@@ -3975,7 +4266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M656"/>
+  <dimension ref="A1:M713"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -23021,6 +23312,1631 @@
       <c r="L656" s="3"/>
       <c r="M656" s="3"/>
     </row>
+    <row r="657" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A657" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B657" s="3"/>
+      <c r="C657" s="3">
+        <v>112</v>
+      </c>
+      <c r="D657" s="3">
+        <v>5529768263</v>
+      </c>
+      <c r="E657" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F657" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G657" s="3"/>
+      <c r="H657" s="3"/>
+      <c r="I657" s="3"/>
+      <c r="J657" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K657" s="3"/>
+      <c r="L657" s="3"/>
+      <c r="M657" s="3"/>
+    </row>
+    <row r="658" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A658" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B658" s="3"/>
+      <c r="C658" s="3">
+        <v>112</v>
+      </c>
+      <c r="D658" s="3">
+        <v>5529907646</v>
+      </c>
+      <c r="E658" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F658" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G658" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H658" s="3"/>
+      <c r="I658" s="3"/>
+      <c r="J658" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K658" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L658" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="M658" s="3"/>
+    </row>
+    <row r="659" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A659" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B659" s="3"/>
+      <c r="C659" s="3">
+        <v>112</v>
+      </c>
+      <c r="D659" s="3">
+        <v>5529919178</v>
+      </c>
+      <c r="E659" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H659" s="3"/>
+      <c r="I659" s="3"/>
+      <c r="J659" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K659" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L659" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="M659" s="3"/>
+    </row>
+    <row r="660" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A660" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B660" s="3"/>
+      <c r="C660" s="3">
+        <v>112</v>
+      </c>
+      <c r="D660" s="3">
+        <v>5530437204</v>
+      </c>
+      <c r="E660" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G660" s="3"/>
+      <c r="H660" s="3"/>
+      <c r="I660" s="3"/>
+      <c r="J660" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K660" s="3"/>
+      <c r="L660" s="3"/>
+      <c r="M660" s="3"/>
+    </row>
+    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A661" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B661" s="3"/>
+      <c r="C661" s="3">
+        <v>111</v>
+      </c>
+      <c r="D661" s="3">
+        <v>5533565542</v>
+      </c>
+      <c r="E661" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G661" s="3"/>
+      <c r="H661" s="3"/>
+      <c r="I661" s="3"/>
+      <c r="J661" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K661" s="3"/>
+      <c r="L661" s="3"/>
+      <c r="M661" s="3"/>
+    </row>
+    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A662" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B662" s="3"/>
+      <c r="C662" s="3">
+        <v>110</v>
+      </c>
+      <c r="D662" s="3">
+        <v>5536628411</v>
+      </c>
+      <c r="E662" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H662" s="3"/>
+      <c r="I662" s="3"/>
+      <c r="J662" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K662" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L662" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="M662" s="3"/>
+    </row>
+    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A663" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C663" s="3">
+        <v>112</v>
+      </c>
+      <c r="D663" s="3">
+        <v>5538641628</v>
+      </c>
+      <c r="E663" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H663" s="3"/>
+      <c r="I663" s="3"/>
+      <c r="J663" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K663" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L663" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="M663" s="3" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A664" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B664" s="3"/>
+      <c r="C664" s="3">
+        <v>112</v>
+      </c>
+      <c r="D664" s="3">
+        <v>5538711556</v>
+      </c>
+      <c r="E664" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G664" s="3"/>
+      <c r="H664" s="3"/>
+      <c r="I664" s="3"/>
+      <c r="J664" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K664" s="3"/>
+      <c r="L664" s="3"/>
+      <c r="M664" s="3"/>
+    </row>
+    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A665" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C665" s="3">
+        <v>110</v>
+      </c>
+      <c r="D665" s="3">
+        <v>5541680581</v>
+      </c>
+      <c r="E665" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H665" s="3"/>
+      <c r="I665" s="3"/>
+      <c r="J665" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K665" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L665" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M665" s="3" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A666" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B666" s="3"/>
+      <c r="C666" s="3">
+        <v>110</v>
+      </c>
+      <c r="D666" s="3">
+        <v>5541705791</v>
+      </c>
+      <c r="E666" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H666" s="3"/>
+      <c r="I666" s="3"/>
+      <c r="J666" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K666" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L666" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="M666" s="3"/>
+    </row>
+    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A667" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B667" s="3"/>
+      <c r="C667" s="3">
+        <v>110</v>
+      </c>
+      <c r="D667" s="3">
+        <v>5541715801</v>
+      </c>
+      <c r="E667" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="G667" s="3"/>
+      <c r="H667" s="3"/>
+      <c r="I667" s="3"/>
+      <c r="J667" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K667" s="3"/>
+      <c r="L667" s="3"/>
+      <c r="M667" s="3"/>
+    </row>
+    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A668" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B668" s="3"/>
+      <c r="C668" s="3">
+        <v>110</v>
+      </c>
+      <c r="D668" s="3">
+        <v>5541724879</v>
+      </c>
+      <c r="E668" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G668" s="3"/>
+      <c r="H668" s="3"/>
+      <c r="I668" s="3"/>
+      <c r="J668" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K668" s="3"/>
+      <c r="L668" s="3"/>
+      <c r="M668" s="3"/>
+    </row>
+    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A669" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B669" s="3"/>
+      <c r="C669" s="3">
+        <v>110</v>
+      </c>
+      <c r="D669" s="3">
+        <v>5541729765</v>
+      </c>
+      <c r="E669" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="G669" s="3"/>
+      <c r="H669" s="3"/>
+      <c r="I669" s="3"/>
+      <c r="J669" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K669" s="3"/>
+      <c r="L669" s="3"/>
+      <c r="M669" s="3"/>
+    </row>
+    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A670" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B670" s="3"/>
+      <c r="C670" s="3">
+        <v>110</v>
+      </c>
+      <c r="D670" s="3">
+        <v>5541749226</v>
+      </c>
+      <c r="E670" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="G670" s="3"/>
+      <c r="H670" s="3"/>
+      <c r="I670" s="3"/>
+      <c r="J670" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K670" s="3"/>
+      <c r="L670" s="3"/>
+      <c r="M670" s="3"/>
+    </row>
+    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A671" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B671" s="3"/>
+      <c r="C671" s="3">
+        <v>110</v>
+      </c>
+      <c r="D671" s="3">
+        <v>5541754423</v>
+      </c>
+      <c r="E671" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="G671" s="3"/>
+      <c r="H671" s="3"/>
+      <c r="I671" s="3"/>
+      <c r="J671" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K671" s="3"/>
+      <c r="L671" s="3"/>
+      <c r="M671" s="3"/>
+    </row>
+    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A672" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B672" s="3"/>
+      <c r="C672" s="3">
+        <v>112</v>
+      </c>
+      <c r="D672" s="3">
+        <v>5541816431</v>
+      </c>
+      <c r="E672" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G672" s="3"/>
+      <c r="H672" s="3"/>
+      <c r="I672" s="3"/>
+      <c r="J672" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K672" s="3"/>
+      <c r="L672" s="3"/>
+      <c r="M672" s="3"/>
+    </row>
+    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A673" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B673" s="3"/>
+      <c r="C673" s="3">
+        <v>112</v>
+      </c>
+      <c r="D673" s="3">
+        <v>5542010934</v>
+      </c>
+      <c r="E673" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G673" s="3"/>
+      <c r="H673" s="3"/>
+      <c r="I673" s="3"/>
+      <c r="J673" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K673" s="3"/>
+      <c r="L673" s="3"/>
+      <c r="M673" s="3"/>
+    </row>
+    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A674" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B674" s="3"/>
+      <c r="C674" s="3">
+        <v>110</v>
+      </c>
+      <c r="D674" s="3">
+        <v>5542066946</v>
+      </c>
+      <c r="E674" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G674" s="3"/>
+      <c r="H674" s="3"/>
+      <c r="I674" s="3"/>
+      <c r="J674" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K674" s="3"/>
+      <c r="L674" s="3"/>
+      <c r="M674" s="3"/>
+    </row>
+    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A675" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B675" s="3"/>
+      <c r="C675" s="3">
+        <v>110</v>
+      </c>
+      <c r="D675" s="3">
+        <v>5542109417</v>
+      </c>
+      <c r="E675" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G675" s="3"/>
+      <c r="H675" s="3"/>
+      <c r="I675" s="3"/>
+      <c r="J675" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K675" s="3"/>
+      <c r="L675" s="3"/>
+      <c r="M675" s="3"/>
+    </row>
+    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A676" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B676" s="3"/>
+      <c r="C676" s="3">
+        <v>110</v>
+      </c>
+      <c r="D676" s="3">
+        <v>5542729907</v>
+      </c>
+      <c r="E676" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G676" s="3"/>
+      <c r="H676" s="3"/>
+      <c r="I676" s="3"/>
+      <c r="J676" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K676" s="3"/>
+      <c r="L676" s="3"/>
+      <c r="M676" s="3"/>
+    </row>
+    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A677" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B677" s="3"/>
+      <c r="C677" s="3">
+        <v>112</v>
+      </c>
+      <c r="D677" s="3">
+        <v>5542825172</v>
+      </c>
+      <c r="E677" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G677" s="3"/>
+      <c r="H677" s="3"/>
+      <c r="I677" s="3"/>
+      <c r="J677" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K677" s="3"/>
+      <c r="L677" s="3"/>
+      <c r="M677" s="3"/>
+    </row>
+    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A678" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B678" s="3"/>
+      <c r="C678" s="3">
+        <v>110</v>
+      </c>
+      <c r="D678" s="3">
+        <v>5543036016</v>
+      </c>
+      <c r="E678" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G678" s="3"/>
+      <c r="H678" s="3"/>
+      <c r="I678" s="3"/>
+      <c r="J678" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K678" s="3"/>
+      <c r="L678" s="3"/>
+      <c r="M678" s="3"/>
+    </row>
+    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A679" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B679" s="3"/>
+      <c r="C679" s="3">
+        <v>110</v>
+      </c>
+      <c r="D679" s="3">
+        <v>5543296985</v>
+      </c>
+      <c r="E679" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G679" s="3"/>
+      <c r="H679" s="3"/>
+      <c r="I679" s="3"/>
+      <c r="J679" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K679" s="3"/>
+      <c r="L679" s="3"/>
+      <c r="M679" s="3"/>
+    </row>
+    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A680" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B680" s="3"/>
+      <c r="C680" s="3">
+        <v>110</v>
+      </c>
+      <c r="D680" s="3">
+        <v>5543305791</v>
+      </c>
+      <c r="E680" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G680" s="3"/>
+      <c r="H680" s="3"/>
+      <c r="I680" s="3"/>
+      <c r="J680" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K680" s="3"/>
+      <c r="L680" s="3"/>
+      <c r="M680" s="3"/>
+    </row>
+    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A681" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B681" s="3"/>
+      <c r="C681" s="3">
+        <v>110</v>
+      </c>
+      <c r="D681" s="3">
+        <v>5543344665</v>
+      </c>
+      <c r="E681" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G681" s="3"/>
+      <c r="H681" s="3"/>
+      <c r="I681" s="3"/>
+      <c r="J681" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K681" s="3"/>
+      <c r="L681" s="3"/>
+      <c r="M681" s="3"/>
+    </row>
+    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A682" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B682" s="3"/>
+      <c r="C682" s="3">
+        <v>110</v>
+      </c>
+      <c r="D682" s="3">
+        <v>5543352896</v>
+      </c>
+      <c r="E682" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F682" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G682" s="3"/>
+      <c r="H682" s="3"/>
+      <c r="I682" s="3"/>
+      <c r="J682" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K682" s="3"/>
+      <c r="L682" s="3"/>
+      <c r="M682" s="3"/>
+    </row>
+    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A683" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B683" s="3"/>
+      <c r="C683" s="3">
+        <v>110</v>
+      </c>
+      <c r="D683" s="3">
+        <v>5543402637</v>
+      </c>
+      <c r="E683" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F683" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G683" s="3"/>
+      <c r="H683" s="3"/>
+      <c r="I683" s="3"/>
+      <c r="J683" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K683" s="3"/>
+      <c r="L683" s="3"/>
+      <c r="M683" s="3"/>
+    </row>
+    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A684" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B684" s="3"/>
+      <c r="C684" s="3">
+        <v>110</v>
+      </c>
+      <c r="D684" s="3">
+        <v>5543419437</v>
+      </c>
+      <c r="E684" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F684" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G684" s="3"/>
+      <c r="H684" s="3"/>
+      <c r="I684" s="3"/>
+      <c r="J684" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K684" s="3"/>
+      <c r="L684" s="3"/>
+      <c r="M684" s="3"/>
+    </row>
+    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A685" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B685" s="3"/>
+      <c r="C685" s="3">
+        <v>111</v>
+      </c>
+      <c r="D685" s="3">
+        <v>5543449251</v>
+      </c>
+      <c r="E685" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H685" s="3"/>
+      <c r="I685" s="3"/>
+      <c r="J685" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K685" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L685" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M685" s="3"/>
+    </row>
+    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A686" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B686" s="3"/>
+      <c r="C686" s="3">
+        <v>112</v>
+      </c>
+      <c r="D686" s="3">
+        <v>5553811372</v>
+      </c>
+      <c r="E686" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G686" s="3"/>
+      <c r="H686" s="3"/>
+      <c r="I686" s="3"/>
+      <c r="J686" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K686" s="3"/>
+      <c r="L686" s="3"/>
+      <c r="M686" s="3"/>
+    </row>
+    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A687" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B687" s="3"/>
+      <c r="C687" s="3">
+        <v>111</v>
+      </c>
+      <c r="D687" s="3">
+        <v>5543786620</v>
+      </c>
+      <c r="E687" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G687" s="3"/>
+      <c r="H687" s="3"/>
+      <c r="I687" s="3"/>
+      <c r="J687" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K687" s="3"/>
+      <c r="L687" s="3"/>
+      <c r="M687" s="3"/>
+    </row>
+    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A688" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B688" s="3"/>
+      <c r="C688" s="3">
+        <v>111</v>
+      </c>
+      <c r="D688" s="3">
+        <v>5546710164</v>
+      </c>
+      <c r="E688" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G688" s="3"/>
+      <c r="H688" s="3"/>
+      <c r="I688" s="3"/>
+      <c r="J688" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K688" s="3"/>
+      <c r="L688" s="3"/>
+      <c r="M688" s="3"/>
+    </row>
+    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A689" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B689" s="3"/>
+      <c r="C689" s="3">
+        <v>112</v>
+      </c>
+      <c r="D689" s="3">
+        <v>5548669240</v>
+      </c>
+      <c r="E689" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G689" s="3"/>
+      <c r="H689" s="3"/>
+      <c r="I689" s="3"/>
+      <c r="J689" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K689" s="3"/>
+      <c r="L689" s="3"/>
+      <c r="M689" s="3"/>
+    </row>
+    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A690" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B690" s="3"/>
+      <c r="C690" s="3">
+        <v>112</v>
+      </c>
+      <c r="D690" s="3">
+        <v>5548887132</v>
+      </c>
+      <c r="E690" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H690" s="3"/>
+      <c r="I690" s="3"/>
+      <c r="J690" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K690" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L690" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M690" s="3"/>
+    </row>
+    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A691" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B691" s="3"/>
+      <c r="C691" s="3">
+        <v>112</v>
+      </c>
+      <c r="D691" s="3">
+        <v>5548909928</v>
+      </c>
+      <c r="E691" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H691" s="3"/>
+      <c r="I691" s="3"/>
+      <c r="J691" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K691" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L691" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M691" s="3"/>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A692" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B692" s="3"/>
+      <c r="C692" s="3">
+        <v>112</v>
+      </c>
+      <c r="D692" s="3">
+        <v>5548934742</v>
+      </c>
+      <c r="E692" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G692" s="3"/>
+      <c r="H692" s="3"/>
+      <c r="I692" s="3"/>
+      <c r="J692" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K692" s="3"/>
+      <c r="L692" s="3"/>
+      <c r="M692" s="3"/>
+    </row>
+    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A693" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B693" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C693" s="3">
+        <v>110</v>
+      </c>
+      <c r="D693" s="3">
+        <v>5549311845</v>
+      </c>
+      <c r="E693" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H693" s="3"/>
+      <c r="I693" s="3"/>
+      <c r="J693" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K693" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L693" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M693" s="3"/>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A694" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B694" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C694" s="3">
+        <v>110</v>
+      </c>
+      <c r="D694" s="3">
+        <v>5549507929</v>
+      </c>
+      <c r="E694" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H694" s="3"/>
+      <c r="I694" s="3"/>
+      <c r="J694" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K694" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L694" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="M694" s="3" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A695" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B695" s="3"/>
+      <c r="C695" s="3">
+        <v>110</v>
+      </c>
+      <c r="D695" s="3">
+        <v>5549620087</v>
+      </c>
+      <c r="E695" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G695" s="3"/>
+      <c r="H695" s="3"/>
+      <c r="I695" s="3"/>
+      <c r="J695" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K695" s="3"/>
+      <c r="L695" s="3"/>
+      <c r="M695" s="3"/>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A696" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B696" s="3"/>
+      <c r="C696" s="3">
+        <v>110</v>
+      </c>
+      <c r="D696" s="3">
+        <v>5549629236</v>
+      </c>
+      <c r="E696" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G696" s="3"/>
+      <c r="H696" s="3"/>
+      <c r="I696" s="3"/>
+      <c r="J696" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K696" s="3"/>
+      <c r="L696" s="3"/>
+      <c r="M696" s="3"/>
+    </row>
+    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A697" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B697" s="3"/>
+      <c r="C697" s="3">
+        <v>110</v>
+      </c>
+      <c r="D697" s="3">
+        <v>5550528759</v>
+      </c>
+      <c r="E697" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G697" s="3"/>
+      <c r="H697" s="3"/>
+      <c r="I697" s="3"/>
+      <c r="J697" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K697" s="3"/>
+      <c r="L697" s="3"/>
+      <c r="M697" s="3"/>
+    </row>
+    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A698" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B698" s="3"/>
+      <c r="C698" s="3">
+        <v>110</v>
+      </c>
+      <c r="D698" s="3">
+        <v>5550561967</v>
+      </c>
+      <c r="E698" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G698" s="3"/>
+      <c r="H698" s="3"/>
+      <c r="I698" s="3"/>
+      <c r="J698" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K698" s="3"/>
+      <c r="L698" s="3"/>
+      <c r="M698" s="3"/>
+    </row>
+    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A699" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B699" s="3"/>
+      <c r="C699" s="3">
+        <v>110</v>
+      </c>
+      <c r="D699" s="3">
+        <v>5551407891</v>
+      </c>
+      <c r="E699" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G699" s="3"/>
+      <c r="H699" s="3"/>
+      <c r="I699" s="3"/>
+      <c r="J699" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K699" s="3"/>
+      <c r="L699" s="3"/>
+      <c r="M699" s="3"/>
+    </row>
+    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A700" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B700" s="3"/>
+      <c r="C700" s="3">
+        <v>110</v>
+      </c>
+      <c r="D700" s="3">
+        <v>5551431111</v>
+      </c>
+      <c r="E700" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G700" s="3"/>
+      <c r="H700" s="3"/>
+      <c r="I700" s="3"/>
+      <c r="J700" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K700" s="3"/>
+      <c r="L700" s="3"/>
+      <c r="M700" s="3"/>
+    </row>
+    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A701" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B701" s="3"/>
+      <c r="C701" s="3">
+        <v>111</v>
+      </c>
+      <c r="D701" s="3">
+        <v>5552159212</v>
+      </c>
+      <c r="E701" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G701" s="3"/>
+      <c r="H701" s="3"/>
+      <c r="I701" s="3"/>
+      <c r="J701" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K701" s="3"/>
+      <c r="L701" s="3"/>
+      <c r="M701" s="3"/>
+    </row>
+    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A702" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B702" s="3"/>
+      <c r="C702" s="3">
+        <v>111</v>
+      </c>
+      <c r="D702" s="3">
+        <v>5553120303</v>
+      </c>
+      <c r="E702" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H702" s="3"/>
+      <c r="I702" s="3"/>
+      <c r="J702" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K702" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L702" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="M702" s="3"/>
+    </row>
+    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A703" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B703" s="3"/>
+      <c r="C703" s="3">
+        <v>111</v>
+      </c>
+      <c r="D703" s="3">
+        <v>5553731244</v>
+      </c>
+      <c r="E703" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G703" s="3"/>
+      <c r="H703" s="3"/>
+      <c r="I703" s="3"/>
+      <c r="J703" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K703" s="3"/>
+      <c r="L703" s="3"/>
+      <c r="M703" s="3"/>
+    </row>
+    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A704" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B704" s="3"/>
+      <c r="C704" s="3">
+        <v>112</v>
+      </c>
+      <c r="D704" s="3">
+        <v>5554911730</v>
+      </c>
+      <c r="E704" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G704" s="3"/>
+      <c r="H704" s="3"/>
+      <c r="I704" s="3"/>
+      <c r="J704" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K704" s="3"/>
+      <c r="L704" s="3"/>
+      <c r="M704" s="3"/>
+    </row>
+    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A705" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B705" s="3"/>
+      <c r="C705" s="3">
+        <v>111</v>
+      </c>
+      <c r="D705" s="3">
+        <v>5556878601</v>
+      </c>
+      <c r="E705" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G705" s="3"/>
+      <c r="H705" s="3"/>
+      <c r="I705" s="3"/>
+      <c r="J705" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K705" s="3"/>
+      <c r="L705" s="3"/>
+      <c r="M705" s="3"/>
+    </row>
+    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A706" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B706" s="3"/>
+      <c r="C706" s="3">
+        <v>111</v>
+      </c>
+      <c r="D706" s="3">
+        <v>5558850537</v>
+      </c>
+      <c r="E706" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G706" s="3"/>
+      <c r="H706" s="3"/>
+      <c r="I706" s="3"/>
+      <c r="J706" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K706" s="3"/>
+      <c r="L706" s="3"/>
+      <c r="M706" s="3"/>
+    </row>
+    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A707" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B707" s="3"/>
+      <c r="C707" s="3">
+        <v>111</v>
+      </c>
+      <c r="D707" s="3">
+        <v>5558888737</v>
+      </c>
+      <c r="E707" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G707" s="3"/>
+      <c r="H707" s="3"/>
+      <c r="I707" s="3"/>
+      <c r="J707" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K707" s="3"/>
+      <c r="L707" s="3"/>
+      <c r="M707" s="3"/>
+    </row>
+    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A708" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B708" s="3"/>
+      <c r="C708" s="3">
+        <v>111</v>
+      </c>
+      <c r="D708" s="3">
+        <v>5558936957</v>
+      </c>
+      <c r="E708" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G708" s="3"/>
+      <c r="H708" s="3"/>
+      <c r="I708" s="3"/>
+      <c r="J708" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K708" s="3"/>
+      <c r="L708" s="3"/>
+      <c r="M708" s="3"/>
+    </row>
+    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A709" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B709" s="3"/>
+      <c r="C709" s="3">
+        <v>110</v>
+      </c>
+      <c r="D709" s="3">
+        <v>5559355573</v>
+      </c>
+      <c r="E709" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F709" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="G709" s="3"/>
+      <c r="H709" s="3"/>
+      <c r="I709" s="3"/>
+      <c r="J709" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K709" s="3"/>
+      <c r="L709" s="3"/>
+      <c r="M709" s="3"/>
+    </row>
+    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A710" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B710" s="3"/>
+      <c r="C710" s="3">
+        <v>111</v>
+      </c>
+      <c r="D710" s="3">
+        <v>5559448882</v>
+      </c>
+      <c r="E710" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F710" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="G710" s="3"/>
+      <c r="H710" s="3"/>
+      <c r="I710" s="3"/>
+      <c r="J710" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K710" s="3"/>
+      <c r="L710" s="3"/>
+      <c r="M710" s="3"/>
+    </row>
+    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A711" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B711" s="3"/>
+      <c r="C711" s="3">
+        <v>113</v>
+      </c>
+      <c r="D711" s="3">
+        <v>5560761237</v>
+      </c>
+      <c r="E711" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="G711" s="3"/>
+      <c r="H711" s="3"/>
+      <c r="I711" s="3"/>
+      <c r="J711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K711" s="3"/>
+      <c r="L711" s="3"/>
+      <c r="M711" s="3"/>
+    </row>
+    <row r="712" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A712" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B712" s="3"/>
+      <c r="C712" s="3">
+        <v>112</v>
+      </c>
+      <c r="D712" s="3">
+        <v>5566527912</v>
+      </c>
+      <c r="E712" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G712" s="3"/>
+      <c r="H712" s="3"/>
+      <c r="I712" s="3"/>
+      <c r="J712" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K712" s="3"/>
+      <c r="L712" s="3"/>
+      <c r="M712" s="3"/>
+    </row>
+    <row r="713" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A713" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B713" s="3"/>
+      <c r="C713" s="3">
+        <v>112</v>
+      </c>
+      <c r="D713" s="3">
+        <v>5566765278</v>
+      </c>
+      <c r="E713" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G713" s="3"/>
+      <c r="H713" s="3"/>
+      <c r="I713" s="3"/>
+      <c r="J713" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K713" s="3"/>
+      <c r="L713" s="3"/>
+      <c r="M713" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3ABE08D-68D9-43E4-AB4C-E3AEF9665D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83DAA01C-AB0A-43D5-8F54-679862BE8A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3577" uniqueCount="1295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3736" uniqueCount="1352">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -3277,7 +3277,10 @@
     <t>2.2mi E of Del Rio TX</t>
   </si>
   <si>
-    <t>03/18/26 10:14 EDT</t>
+    <t>Non-Coachable</t>
+  </si>
+  <si>
+    <t>04/15/26 09:06 EDT</t>
   </si>
   <si>
     <t>03/17/26 14:44 EDT</t>
@@ -3859,6 +3862,9 @@
     <t>18.4mi W of El Reno OK</t>
   </si>
   <si>
+    <t>04/13/26 10:16 EDT</t>
+  </si>
+  <si>
     <t>04/10/26 08:44 EDT</t>
   </si>
   <si>
@@ -3905,6 +3911,171 @@
   </si>
   <si>
     <t>1.4mi W of Windcrest TX</t>
+  </si>
+  <si>
+    <t>04/13/26 09:54 EDT</t>
+  </si>
+  <si>
+    <t>5.1mi N of Cibolo TX</t>
+  </si>
+  <si>
+    <t>04/14/26 11:45 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:55 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 15:44 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi S of Converse TX</t>
+  </si>
+  <si>
+    <t>04/13/26 15:46 EDT</t>
+  </si>
+  <si>
+    <t>6.7mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>04/13/26 17:11 EDT</t>
+  </si>
+  <si>
+    <t>11.9mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>04/13/26 20:24 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 08:52 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi S of San Antonio TX</t>
+  </si>
+  <si>
+    <t>04/14/26 11:46 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:48 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:59 EDT</t>
+  </si>
+  <si>
+    <t>4.4mi NE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>04/14/26 12:09 EDT</t>
+  </si>
+  <si>
+    <t>5.1mi SW of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>04/14/26 12:19 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi W of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>04/15/26 08:28 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 12:04 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 12:42 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi W of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>04/15/26 08:29 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 12:43 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 12:47 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi W of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>04/14/26 13:39 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 16:54 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>6mi NE of Seguin TX</t>
+  </si>
+  <si>
+    <t>04/14/26 19:27 EDT</t>
+  </si>
+  <si>
+    <t>9.9mi SW of Lockhart TX</t>
+  </si>
+  <si>
+    <t>04/15/26 12:25 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:55 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 15:23 EDT</t>
+  </si>
+  <si>
+    <t>20.6mi NE of Pearsall TX</t>
+  </si>
+  <si>
+    <t>04/15/26 16:11 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi NW of Windcrest TX</t>
+  </si>
+  <si>
+    <t>04/16/26 10:03 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi S of Terrell Hills TX</t>
+  </si>
+  <si>
+    <t>04/16/26 10:05 EDT</t>
+  </si>
+  <si>
+    <t>4.8mi S of San Antonio TX</t>
+  </si>
+  <si>
+    <t>04/16/26 17:08 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 04:49 EDT</t>
+  </si>
+  <si>
+    <t>7.3mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>04/17/26 09:25 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi SW of Converse TX</t>
+  </si>
+  <si>
+    <t>04/17/26 16:02 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi W of Hornsby Bend TX</t>
+  </si>
+  <si>
+    <t>04/17/26 18:02 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi E of Selma TX</t>
   </si>
 </sst>
 </file>
@@ -4266,7 +4437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M713"/>
+  <dimension ref="A1:M741"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -21498,7 +21669,7 @@
         <v>1084</v>
       </c>
       <c r="G595" s="3" t="s">
-        <v>30</v>
+        <v>1085</v>
       </c>
       <c r="H595" s="3"/>
       <c r="I595" s="3"/>
@@ -21509,13 +21680,13 @@
         <v>32</v>
       </c>
       <c r="L595" s="3" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="M595" s="3"/>
     </row>
     <row r="596" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A596" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B596" s="3"/>
       <c r="C596" s="3">
@@ -21528,7 +21699,7 @@
         <v>28</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G596" s="3" t="s">
         <v>80</v>
@@ -21542,13 +21713,13 @@
         <v>32</v>
       </c>
       <c r="L596" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="M596" s="3"/>
     </row>
     <row r="597" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A597" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B597" s="3"/>
       <c r="C597" s="3">
@@ -21575,7 +21746,7 @@
     </row>
     <row r="598" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A598" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B598" s="3"/>
       <c r="C598" s="3">
@@ -21588,7 +21759,7 @@
         <v>116</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G598" s="3" t="s">
         <v>80</v>
@@ -21602,13 +21773,13 @@
         <v>32</v>
       </c>
       <c r="L598" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="M598" s="3"/>
     </row>
     <row r="599" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A599" s="3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B599" s="3"/>
       <c r="C599" s="3">
@@ -21621,7 +21792,7 @@
         <v>43</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G599" s="3"/>
       <c r="H599" s="3"/>
@@ -21635,7 +21806,7 @@
     </row>
     <row r="600" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A600" s="3" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B600" s="3"/>
       <c r="C600" s="3">
@@ -21662,13 +21833,13 @@
         <v>32</v>
       </c>
       <c r="L600" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="M600" s="3"/>
     </row>
     <row r="601" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A601" s="3" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B601" s="3"/>
       <c r="C601" s="3">
@@ -21681,7 +21852,7 @@
         <v>55</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G601" s="3"/>
       <c r="H601" s="3"/>
@@ -21695,7 +21866,7 @@
     </row>
     <row r="602" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A602" s="3" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B602" s="3" t="s">
         <v>49</v>
@@ -21710,7 +21881,7 @@
         <v>61</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="G602" s="3" t="s">
         <v>30</v>
@@ -21724,13 +21895,13 @@
         <v>32</v>
       </c>
       <c r="L602" s="3" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="M602" s="3"/>
     </row>
     <row r="603" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A603" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B603" s="3" t="s">
         <v>49</v>
@@ -21759,13 +21930,13 @@
         <v>32</v>
       </c>
       <c r="L603" s="3" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="M603" s="3"/>
     </row>
     <row r="604" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A604" s="3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B604" s="3"/>
       <c r="C604" s="3">
@@ -21778,7 +21949,7 @@
         <v>43</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G604" s="3"/>
       <c r="H604" s="3"/>
@@ -21792,7 +21963,7 @@
     </row>
     <row r="605" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A605" s="3" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B605" s="3"/>
       <c r="C605" s="3">
@@ -21805,7 +21976,7 @@
         <v>61</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G605" s="3"/>
       <c r="H605" s="3"/>
@@ -21819,7 +21990,7 @@
     </row>
     <row r="606" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A606" s="3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B606" s="3"/>
       <c r="C606" s="3">
@@ -21832,7 +22003,7 @@
         <v>43</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="G606" s="3"/>
       <c r="H606" s="3"/>
@@ -21846,7 +22017,7 @@
     </row>
     <row r="607" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A607" s="3" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B607" s="3"/>
       <c r="C607" s="3">
@@ -21859,7 +22030,7 @@
         <v>55</v>
       </c>
       <c r="F607" s="3" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G607" s="3"/>
       <c r="H607" s="3"/>
@@ -21873,7 +22044,7 @@
     </row>
     <row r="608" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A608" s="3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B608" s="3"/>
       <c r="C608" s="3">
@@ -21900,13 +22071,13 @@
         <v>32</v>
       </c>
       <c r="L608" s="3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="M608" s="3"/>
     </row>
     <row r="609" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A609" s="3" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B609" s="3"/>
       <c r="C609" s="3">
@@ -21933,7 +22104,7 @@
     </row>
     <row r="610" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A610" s="3" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B610" s="3" t="s">
         <v>49</v>
@@ -21948,7 +22119,7 @@
         <v>61</v>
       </c>
       <c r="F610" s="3" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G610" s="3" t="s">
         <v>30</v>
@@ -21962,15 +22133,15 @@
         <v>32</v>
       </c>
       <c r="L610" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="M610" s="3" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="611" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A611" s="3" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B611" s="3"/>
       <c r="C611" s="3">
@@ -21983,7 +22154,7 @@
         <v>61</v>
       </c>
       <c r="F611" s="3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G611" s="3" t="s">
         <v>80</v>
@@ -21997,13 +22168,13 @@
         <v>32</v>
       </c>
       <c r="L611" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="M611" s="3"/>
     </row>
     <row r="612" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A612" s="3" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B612" s="3"/>
       <c r="C612" s="3">
@@ -22016,7 +22187,7 @@
         <v>61</v>
       </c>
       <c r="F612" s="3" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G612" s="3"/>
       <c r="H612" s="3"/>
@@ -22030,7 +22201,7 @@
     </row>
     <row r="613" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A613" s="3" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B613" s="3"/>
       <c r="C613" s="3">
@@ -22043,7 +22214,7 @@
         <v>61</v>
       </c>
       <c r="F613" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G613" s="3"/>
       <c r="H613" s="3"/>
@@ -22057,7 +22228,7 @@
     </row>
     <row r="614" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A614" s="3" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B614" s="3"/>
       <c r="C614" s="3">
@@ -22070,7 +22241,7 @@
         <v>16</v>
       </c>
       <c r="F614" s="3" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="G614" s="3"/>
       <c r="H614" s="3"/>
@@ -22084,7 +22255,7 @@
     </row>
     <row r="615" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A615" s="3" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B615" s="3"/>
       <c r="C615" s="3">
@@ -22111,7 +22282,7 @@
     </row>
     <row r="616" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A616" s="3" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B616" s="3"/>
       <c r="C616" s="3">
@@ -22124,7 +22295,7 @@
         <v>61</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="G616" s="3" t="s">
         <v>80</v>
@@ -22138,13 +22309,13 @@
         <v>32</v>
       </c>
       <c r="L616" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="M616" s="3"/>
     </row>
     <row r="617" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A617" s="3" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B617" s="3"/>
       <c r="C617" s="3">
@@ -22157,7 +22328,7 @@
         <v>28</v>
       </c>
       <c r="F617" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G617" s="3"/>
       <c r="H617" s="3"/>
@@ -22171,7 +22342,7 @@
     </row>
     <row r="618" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A618" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B618" s="3"/>
       <c r="C618" s="3">
@@ -22198,7 +22369,7 @@
     </row>
     <row r="619" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A619" s="3" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B619" s="3"/>
       <c r="C619" s="3">
@@ -22225,13 +22396,13 @@
         <v>32</v>
       </c>
       <c r="L619" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="M619" s="3"/>
     </row>
     <row r="620" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A620" s="3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B620" s="3"/>
       <c r="C620" s="3">
@@ -22244,7 +22415,7 @@
         <v>43</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="G620" s="3"/>
       <c r="H620" s="3"/>
@@ -22258,7 +22429,7 @@
     </row>
     <row r="621" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A621" s="3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B621" s="3"/>
       <c r="C621" s="3">
@@ -22285,13 +22456,13 @@
         <v>32</v>
       </c>
       <c r="L621" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="M621" s="3"/>
     </row>
     <row r="622" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A622" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B622" s="3"/>
       <c r="C622" s="3">
@@ -22304,7 +22475,7 @@
         <v>28</v>
       </c>
       <c r="F622" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G622" s="3"/>
       <c r="H622" s="3"/>
@@ -22318,7 +22489,7 @@
     </row>
     <row r="623" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A623" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B623" s="3"/>
       <c r="C623" s="3">
@@ -22331,7 +22502,7 @@
         <v>28</v>
       </c>
       <c r="F623" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G623" s="3" t="s">
         <v>80</v>
@@ -22345,13 +22516,13 @@
         <v>32</v>
       </c>
       <c r="L623" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="M623" s="3"/>
     </row>
     <row r="624" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A624" s="3" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B624" s="3"/>
       <c r="C624" s="3">
@@ -22378,7 +22549,7 @@
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A625" s="3" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B625" s="3"/>
       <c r="C625" s="3">
@@ -22405,7 +22576,7 @@
     </row>
     <row r="626" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A626" s="3" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B626" s="3"/>
       <c r="C626" s="3">
@@ -22418,7 +22589,7 @@
         <v>55</v>
       </c>
       <c r="F626" s="3" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="G626" s="3"/>
       <c r="H626" s="3"/>
@@ -22432,7 +22603,7 @@
     </row>
     <row r="627" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A627" s="3" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B627" s="3"/>
       <c r="C627" s="3">
@@ -22445,7 +22616,7 @@
         <v>55</v>
       </c>
       <c r="F627" s="3" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="G627" s="3"/>
       <c r="H627" s="3"/>
@@ -22459,7 +22630,7 @@
     </row>
     <row r="628" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A628" s="3" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B628" s="3"/>
       <c r="C628" s="3">
@@ -22486,7 +22657,7 @@
     </row>
     <row r="629" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A629" s="3" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B629" s="3"/>
       <c r="C629" s="3">
@@ -22513,7 +22684,7 @@
     </row>
     <row r="630" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A630" s="3" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B630" s="3"/>
       <c r="C630" s="3">
@@ -22540,13 +22711,13 @@
         <v>32</v>
       </c>
       <c r="L630" s="3" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="M630" s="3"/>
     </row>
     <row r="631" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A631" s="3" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B631" s="3" t="s">
         <v>27</v>
@@ -22561,7 +22732,7 @@
         <v>38</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="G631" s="3" t="s">
         <v>30</v>
@@ -22575,15 +22746,15 @@
         <v>32</v>
       </c>
       <c r="L631" s="3" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="M631" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="632" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A632" s="3" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B632" s="3"/>
       <c r="C632" s="3">
@@ -22596,7 +22767,7 @@
         <v>43</v>
       </c>
       <c r="F632" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G632" s="3"/>
       <c r="H632" s="3"/>
@@ -22610,7 +22781,7 @@
     </row>
     <row r="633" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A633" s="3" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B633" s="3"/>
       <c r="C633" s="3">
@@ -22637,7 +22808,7 @@
     </row>
     <row r="634" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A634" s="3" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B634" s="3"/>
       <c r="C634" s="3">
@@ -22650,7 +22821,7 @@
         <v>61</v>
       </c>
       <c r="F634" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G634" s="3" t="s">
         <v>80</v>
@@ -22664,7 +22835,7 @@
         <v>32</v>
       </c>
       <c r="L634" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="M634" s="3"/>
     </row>
@@ -22699,7 +22870,7 @@
     </row>
     <row r="636" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A636" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B636" s="3" t="s">
         <v>1079</v>
@@ -22728,13 +22899,13 @@
         <v>32</v>
       </c>
       <c r="L636" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="M636" s="3"/>
     </row>
     <row r="637" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A637" s="3" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B637" s="3"/>
       <c r="C637" s="3">
@@ -22761,13 +22932,13 @@
         <v>32</v>
       </c>
       <c r="L637" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="M637" s="3"/>
     </row>
     <row r="638" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A638" s="3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B638" s="3"/>
       <c r="C638" s="3">
@@ -22780,7 +22951,7 @@
         <v>61</v>
       </c>
       <c r="F638" s="3" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G638" s="3"/>
       <c r="H638" s="3"/>
@@ -22794,7 +22965,7 @@
     </row>
     <row r="639" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A639" s="3" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B639" s="3"/>
       <c r="C639" s="3">
@@ -22807,7 +22978,7 @@
         <v>43</v>
       </c>
       <c r="F639" s="3" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="G639" s="3"/>
       <c r="H639" s="3"/>
@@ -22821,7 +22992,7 @@
     </row>
     <row r="640" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A640" s="3" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B640" s="3"/>
       <c r="C640" s="3">
@@ -22848,7 +23019,7 @@
     </row>
     <row r="641" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A641" s="3" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B641" s="3"/>
       <c r="C641" s="3">
@@ -22875,13 +23046,13 @@
         <v>32</v>
       </c>
       <c r="L641" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="M641" s="3"/>
     </row>
     <row r="642" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A642" s="3" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B642" s="3" t="s">
         <v>1079</v>
@@ -22896,7 +23067,7 @@
         <v>28</v>
       </c>
       <c r="F642" s="3" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="G642" s="3"/>
       <c r="H642" s="3"/>
@@ -22910,7 +23081,7 @@
     </row>
     <row r="643" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A643" s="3" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B643" s="3"/>
       <c r="C643" s="3">
@@ -22923,7 +23094,7 @@
         <v>28</v>
       </c>
       <c r="F643" s="3" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="G643" s="3"/>
       <c r="H643" s="3"/>
@@ -22937,7 +23108,7 @@
     </row>
     <row r="644" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A644" s="3" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B644" s="3"/>
       <c r="C644" s="3">
@@ -22964,7 +23135,7 @@
     </row>
     <row r="645" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A645" s="3" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B645" s="3"/>
       <c r="C645" s="3">
@@ -22977,7 +23148,7 @@
         <v>38</v>
       </c>
       <c r="F645" s="3" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G645" s="3" t="s">
         <v>80</v>
@@ -22991,13 +23162,13 @@
         <v>32</v>
       </c>
       <c r="L645" s="3" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="M645" s="3"/>
     </row>
     <row r="646" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A646" s="3" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B646" s="3"/>
       <c r="C646" s="3">
@@ -23010,7 +23181,7 @@
         <v>55</v>
       </c>
       <c r="F646" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G646" s="3"/>
       <c r="H646" s="3"/>
@@ -23024,7 +23195,7 @@
     </row>
     <row r="647" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A647" s="3" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B647" s="3"/>
       <c r="C647" s="3">
@@ -23037,7 +23208,7 @@
         <v>43</v>
       </c>
       <c r="F647" s="3" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="G647" s="3"/>
       <c r="H647" s="3"/>
@@ -23051,7 +23222,7 @@
     </row>
     <row r="648" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A648" s="3" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B648" s="3"/>
       <c r="C648" s="3">
@@ -23064,7 +23235,7 @@
         <v>43</v>
       </c>
       <c r="F648" s="3" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="G648" s="3"/>
       <c r="H648" s="3"/>
@@ -23078,7 +23249,7 @@
     </row>
     <row r="649" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A649" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B649" s="3" t="s">
         <v>1079</v>
@@ -23107,13 +23278,13 @@
         <v>32</v>
       </c>
       <c r="L649" s="3" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="M649" s="3"/>
     </row>
     <row r="650" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A650" s="3" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B650" s="3"/>
       <c r="C650" s="3">
@@ -23126,7 +23297,7 @@
         <v>38</v>
       </c>
       <c r="F650" s="3" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G650" s="3" t="s">
         <v>80</v>
@@ -23140,13 +23311,13 @@
         <v>32</v>
       </c>
       <c r="L650" s="3" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="M650" s="3"/>
     </row>
     <row r="651" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A651" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B651" s="3"/>
       <c r="C651" s="3">
@@ -23159,7 +23330,7 @@
         <v>55</v>
       </c>
       <c r="F651" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G651" s="3"/>
       <c r="H651" s="3"/>
@@ -23173,7 +23344,7 @@
     </row>
     <row r="652" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A652" s="3" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B652" s="3"/>
       <c r="C652" s="3">
@@ -23186,7 +23357,7 @@
         <v>38</v>
       </c>
       <c r="F652" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="G652" s="3" t="s">
         <v>80</v>
@@ -23200,13 +23371,13 @@
         <v>32</v>
       </c>
       <c r="L652" s="3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="M652" s="3"/>
     </row>
     <row r="653" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A653" s="3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B653" s="3"/>
       <c r="C653" s="3">
@@ -23219,7 +23390,7 @@
         <v>38</v>
       </c>
       <c r="F653" s="3" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G653" s="3"/>
       <c r="H653" s="3"/>
@@ -23233,7 +23404,7 @@
     </row>
     <row r="654" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A654" s="3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B654" s="3"/>
       <c r="C654" s="3">
@@ -23260,7 +23431,7 @@
     </row>
     <row r="655" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A655" s="3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B655" s="3"/>
       <c r="C655" s="3">
@@ -23273,7 +23444,7 @@
         <v>38</v>
       </c>
       <c r="F655" s="3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G655" s="3"/>
       <c r="H655" s="3"/>
@@ -23287,7 +23458,7 @@
     </row>
     <row r="656" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A656" s="3" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B656" s="3"/>
       <c r="C656" s="3">
@@ -23300,7 +23471,7 @@
         <v>43</v>
       </c>
       <c r="F656" s="3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="G656" s="3"/>
       <c r="H656" s="3"/>
@@ -23314,7 +23485,7 @@
     </row>
     <row r="657" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A657" s="3" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B657" s="3"/>
       <c r="C657" s="3">
@@ -23327,7 +23498,7 @@
         <v>55</v>
       </c>
       <c r="F657" s="3" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G657" s="3"/>
       <c r="H657" s="3"/>
@@ -23341,7 +23512,7 @@
     </row>
     <row r="658" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A658" s="3" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B658" s="3"/>
       <c r="C658" s="3">
@@ -23354,7 +23525,7 @@
         <v>61</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G658" s="3" t="s">
         <v>80</v>
@@ -23368,13 +23539,13 @@
         <v>32</v>
       </c>
       <c r="L658" s="3" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="M658" s="3"/>
     </row>
     <row r="659" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A659" s="3" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B659" s="3"/>
       <c r="C659" s="3">
@@ -23387,7 +23558,7 @@
         <v>61</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="G659" s="3" t="s">
         <v>80</v>
@@ -23401,13 +23572,13 @@
         <v>32</v>
       </c>
       <c r="L659" s="3" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="M659" s="3"/>
     </row>
     <row r="660" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A660" s="3" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B660" s="3"/>
       <c r="C660" s="3">
@@ -23434,7 +23605,7 @@
     </row>
     <row r="661" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A661" s="3" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B661" s="3"/>
       <c r="C661" s="3">
@@ -23447,7 +23618,7 @@
         <v>43</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="G661" s="3"/>
       <c r="H661" s="3"/>
@@ -23461,7 +23632,7 @@
     </row>
     <row r="662" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A662" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B662" s="3"/>
       <c r="C662" s="3">
@@ -23474,7 +23645,7 @@
         <v>61</v>
       </c>
       <c r="F662" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="G662" s="3" t="s">
         <v>80</v>
@@ -23488,13 +23659,13 @@
         <v>32</v>
       </c>
       <c r="L662" s="3" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="M662" s="3"/>
     </row>
     <row r="663" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A663" s="3" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B663" s="3" t="s">
         <v>27</v>
@@ -23509,7 +23680,7 @@
         <v>61</v>
       </c>
       <c r="F663" s="3" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="G663" s="3" t="s">
         <v>30</v>
@@ -23523,15 +23694,15 @@
         <v>32</v>
       </c>
       <c r="L663" s="3" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="M663" s="3" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="664" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A664" s="3" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B664" s="3"/>
       <c r="C664" s="3">
@@ -23544,7 +23715,7 @@
         <v>43</v>
       </c>
       <c r="F664" s="3" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="G664" s="3"/>
       <c r="H664" s="3"/>
@@ -23558,7 +23729,7 @@
     </row>
     <row r="665" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A665" s="3" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B665" s="3" t="s">
         <v>49</v>
@@ -23587,15 +23758,15 @@
         <v>32</v>
       </c>
       <c r="L665" s="3" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="M665" s="3" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="666" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A666" s="3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B666" s="3"/>
       <c r="C666" s="3">
@@ -23622,13 +23793,13 @@
         <v>32</v>
       </c>
       <c r="L666" s="3" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="M666" s="3"/>
     </row>
     <row r="667" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A667" s="3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B667" s="3"/>
       <c r="C667" s="3">
@@ -23655,7 +23826,7 @@
     </row>
     <row r="668" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A668" s="3" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B668" s="3"/>
       <c r="C668" s="3">
@@ -23682,7 +23853,7 @@
     </row>
     <row r="669" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A669" s="3" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B669" s="3"/>
       <c r="C669" s="3">
@@ -23709,7 +23880,7 @@
     </row>
     <row r="670" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A670" s="3" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B670" s="3"/>
       <c r="C670" s="3">
@@ -23736,7 +23907,7 @@
     </row>
     <row r="671" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A671" s="3" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B671" s="3"/>
       <c r="C671" s="3">
@@ -23763,7 +23934,7 @@
     </row>
     <row r="672" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A672" s="3" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B672" s="3"/>
       <c r="C672" s="3">
@@ -23790,7 +23961,7 @@
     </row>
     <row r="673" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A673" s="3" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B673" s="3"/>
       <c r="C673" s="3">
@@ -23803,7 +23974,7 @@
         <v>43</v>
       </c>
       <c r="F673" s="3" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G673" s="3"/>
       <c r="H673" s="3"/>
@@ -23817,7 +23988,7 @@
     </row>
     <row r="674" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A674" s="3" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B674" s="3"/>
       <c r="C674" s="3">
@@ -23830,7 +24001,7 @@
         <v>61</v>
       </c>
       <c r="F674" s="3" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="G674" s="3"/>
       <c r="H674" s="3"/>
@@ -23844,7 +24015,7 @@
     </row>
     <row r="675" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A675" s="3" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B675" s="3"/>
       <c r="C675" s="3">
@@ -23857,7 +24028,7 @@
         <v>61</v>
       </c>
       <c r="F675" s="3" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="G675" s="3"/>
       <c r="H675" s="3"/>
@@ -23871,7 +24042,7 @@
     </row>
     <row r="676" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A676" s="3" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B676" s="3"/>
       <c r="C676" s="3">
@@ -23884,7 +24055,7 @@
         <v>16</v>
       </c>
       <c r="F676" s="3" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="G676" s="3"/>
       <c r="H676" s="3"/>
@@ -23898,7 +24069,7 @@
     </row>
     <row r="677" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A677" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B677" s="3"/>
       <c r="C677" s="3">
@@ -23911,7 +24082,7 @@
         <v>55</v>
       </c>
       <c r="F677" s="3" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="G677" s="3"/>
       <c r="H677" s="3"/>
@@ -23925,7 +24096,7 @@
     </row>
     <row r="678" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A678" s="3" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B678" s="3"/>
       <c r="C678" s="3">
@@ -23938,7 +24109,7 @@
         <v>61</v>
       </c>
       <c r="F678" s="3" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G678" s="3"/>
       <c r="H678" s="3"/>
@@ -23952,7 +24123,7 @@
     </row>
     <row r="679" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A679" s="3" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B679" s="3"/>
       <c r="C679" s="3">
@@ -23965,7 +24136,7 @@
         <v>61</v>
       </c>
       <c r="F679" s="3" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="G679" s="3"/>
       <c r="H679" s="3"/>
@@ -23979,7 +24150,7 @@
     </row>
     <row r="680" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A680" s="3" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B680" s="3"/>
       <c r="C680" s="3">
@@ -23992,7 +24163,7 @@
         <v>61</v>
       </c>
       <c r="F680" s="3" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="G680" s="3"/>
       <c r="H680" s="3"/>
@@ -24006,7 +24177,7 @@
     </row>
     <row r="681" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A681" s="3" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B681" s="3"/>
       <c r="C681" s="3">
@@ -24019,7 +24190,7 @@
         <v>61</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="G681" s="3"/>
       <c r="H681" s="3"/>
@@ -24033,7 +24204,7 @@
     </row>
     <row r="682" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A682" s="3" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B682" s="3"/>
       <c r="C682" s="3">
@@ -24046,7 +24217,7 @@
         <v>61</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="G682" s="3"/>
       <c r="H682" s="3"/>
@@ -24060,7 +24231,7 @@
     </row>
     <row r="683" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A683" s="3" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B683" s="3"/>
       <c r="C683" s="3">
@@ -24073,7 +24244,7 @@
         <v>61</v>
       </c>
       <c r="F683" s="3" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="G683" s="3"/>
       <c r="H683" s="3"/>
@@ -24087,7 +24258,7 @@
     </row>
     <row r="684" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A684" s="3" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B684" s="3"/>
       <c r="C684" s="3">
@@ -24114,7 +24285,7 @@
     </row>
     <row r="685" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A685" s="3" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B685" s="3"/>
       <c r="C685" s="3">
@@ -24127,7 +24298,7 @@
         <v>61</v>
       </c>
       <c r="F685" s="3" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="G685" s="3" t="s">
         <v>80</v>
@@ -24141,13 +24312,13 @@
         <v>32</v>
       </c>
       <c r="L685" s="3" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="M685" s="3"/>
     </row>
     <row r="686" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A686" s="3" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B686" s="3"/>
       <c r="C686" s="3">
@@ -24174,7 +24345,7 @@
     </row>
     <row r="687" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A687" s="3" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B687" s="3"/>
       <c r="C687" s="3">
@@ -24201,7 +24372,7 @@
     </row>
     <row r="688" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A688" s="3" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B688" s="3"/>
       <c r="C688" s="3">
@@ -24214,7 +24385,7 @@
         <v>28</v>
       </c>
       <c r="F688" s="3" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="G688" s="3"/>
       <c r="H688" s="3"/>
@@ -24228,7 +24399,7 @@
     </row>
     <row r="689" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A689" s="3" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B689" s="3"/>
       <c r="C689" s="3">
@@ -24255,7 +24426,7 @@
     </row>
     <row r="690" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A690" s="3" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B690" s="3"/>
       <c r="C690" s="3">
@@ -24282,13 +24453,13 @@
         <v>32</v>
       </c>
       <c r="L690" s="3" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="M690" s="3"/>
     </row>
     <row r="691" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A691" s="3" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B691" s="3"/>
       <c r="C691" s="3">
@@ -24315,13 +24486,13 @@
         <v>32</v>
       </c>
       <c r="L691" s="3" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="M691" s="3"/>
     </row>
     <row r="692" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A692" s="3" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B692" s="3"/>
       <c r="C692" s="3">
@@ -24348,7 +24519,7 @@
     </row>
     <row r="693" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A693" s="3" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B693" s="3" t="s">
         <v>49</v>
@@ -24377,13 +24548,13 @@
         <v>32</v>
       </c>
       <c r="L693" s="3" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="M693" s="3"/>
     </row>
     <row r="694" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A694" s="3" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B694" s="3" t="s">
         <v>49</v>
@@ -24398,7 +24569,7 @@
         <v>61</v>
       </c>
       <c r="F694" s="3" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G694" s="3" t="s">
         <v>30</v>
@@ -24412,15 +24583,15 @@
         <v>32</v>
       </c>
       <c r="L694" s="3" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="M694" s="3" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="695" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A695" s="3" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B695" s="3"/>
       <c r="C695" s="3">
@@ -24447,7 +24618,7 @@
     </row>
     <row r="696" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A696" s="3" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B696" s="3"/>
       <c r="C696" s="3">
@@ -24474,7 +24645,7 @@
     </row>
     <row r="697" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A697" s="3" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B697" s="3"/>
       <c r="C697" s="3">
@@ -24501,7 +24672,7 @@
     </row>
     <row r="698" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A698" s="3" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B698" s="3"/>
       <c r="C698" s="3">
@@ -24514,7 +24685,7 @@
         <v>61</v>
       </c>
       <c r="F698" s="3" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G698" s="3"/>
       <c r="H698" s="3"/>
@@ -24528,7 +24699,7 @@
     </row>
     <row r="699" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A699" s="3" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B699" s="3"/>
       <c r="C699" s="3">
@@ -24555,7 +24726,7 @@
     </row>
     <row r="700" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A700" s="3" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B700" s="3"/>
       <c r="C700" s="3">
@@ -24582,7 +24753,7 @@
     </row>
     <row r="701" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A701" s="3" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B701" s="3"/>
       <c r="C701" s="3">
@@ -24595,7 +24766,7 @@
         <v>43</v>
       </c>
       <c r="F701" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="G701" s="3"/>
       <c r="H701" s="3"/>
@@ -24609,7 +24780,7 @@
     </row>
     <row r="702" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A702" s="3" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B702" s="3"/>
       <c r="C702" s="3">
@@ -24622,7 +24793,7 @@
         <v>61</v>
       </c>
       <c r="F702" s="3" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="G702" s="3" t="s">
         <v>80</v>
@@ -24636,13 +24807,13 @@
         <v>32</v>
       </c>
       <c r="L702" s="3" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="M702" s="3"/>
     </row>
     <row r="703" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A703" s="3" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B703" s="3"/>
       <c r="C703" s="3">
@@ -24655,21 +24826,27 @@
         <v>61</v>
       </c>
       <c r="F703" s="3" t="s">
-        <v>1278</v>
-      </c>
-      <c r="G703" s="3"/>
+        <v>1279</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="H703" s="3"/>
       <c r="I703" s="3"/>
       <c r="J703" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K703" s="3"/>
-      <c r="L703" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="K703" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L703" s="3" t="s">
+        <v>1280</v>
+      </c>
       <c r="M703" s="3"/>
     </row>
     <row r="704" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A704" s="3" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B704" s="3"/>
       <c r="C704" s="3">
@@ -24682,7 +24859,7 @@
         <v>43</v>
       </c>
       <c r="F704" s="3" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G704" s="3"/>
       <c r="H704" s="3"/>
@@ -24696,7 +24873,7 @@
     </row>
     <row r="705" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A705" s="3" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B705" s="3"/>
       <c r="C705" s="3">
@@ -24709,7 +24886,7 @@
         <v>43</v>
       </c>
       <c r="F705" s="3" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="G705" s="3"/>
       <c r="H705" s="3"/>
@@ -24723,7 +24900,7 @@
     </row>
     <row r="706" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A706" s="3" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B706" s="3"/>
       <c r="C706" s="3">
@@ -24736,21 +24913,27 @@
         <v>61</v>
       </c>
       <c r="F706" s="3" t="s">
-        <v>1283</v>
-      </c>
-      <c r="G706" s="3"/>
+        <v>1285</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="H706" s="3"/>
       <c r="I706" s="3"/>
       <c r="J706" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K706" s="3"/>
-      <c r="L706" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="K706" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L706" s="3" t="s">
+        <v>1280</v>
+      </c>
       <c r="M706" s="3"/>
     </row>
     <row r="707" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A707" s="3" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="B707" s="3"/>
       <c r="C707" s="3">
@@ -24763,21 +24946,27 @@
         <v>61</v>
       </c>
       <c r="F707" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="G707" s="3"/>
+        <v>1287</v>
+      </c>
+      <c r="G707" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="H707" s="3"/>
       <c r="I707" s="3"/>
       <c r="J707" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K707" s="3"/>
-      <c r="L707" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="K707" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L707" s="3" t="s">
+        <v>1280</v>
+      </c>
       <c r="M707" s="3"/>
     </row>
     <row r="708" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A708" s="3" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="B708" s="3"/>
       <c r="C708" s="3">
@@ -24790,7 +24979,7 @@
         <v>43</v>
       </c>
       <c r="F708" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G708" s="3"/>
       <c r="H708" s="3"/>
@@ -24804,7 +24993,7 @@
     </row>
     <row r="709" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A709" s="3" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="B709" s="3"/>
       <c r="C709" s="3">
@@ -24819,19 +25008,25 @@
       <c r="F709" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="G709" s="3"/>
+      <c r="G709" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="H709" s="3"/>
       <c r="I709" s="3"/>
       <c r="J709" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K709" s="3"/>
-      <c r="L709" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="K709" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L709" s="3" t="s">
+        <v>1280</v>
+      </c>
       <c r="M709" s="3"/>
     </row>
     <row r="710" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A710" s="3" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="B710" s="3"/>
       <c r="C710" s="3">
@@ -24858,7 +25053,7 @@
     </row>
     <row r="711" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A711" s="3" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B711" s="3"/>
       <c r="C711" s="3">
@@ -24885,7 +25080,7 @@
     </row>
     <row r="712" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A712" s="3" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="B712" s="3"/>
       <c r="C712" s="3">
@@ -24898,7 +25093,7 @@
         <v>55</v>
       </c>
       <c r="F712" s="3" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="G712" s="3"/>
       <c r="H712" s="3"/>
@@ -24912,7 +25107,7 @@
     </row>
     <row r="713" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A713" s="3" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="B713" s="3"/>
       <c r="C713" s="3">
@@ -24925,7 +25120,7 @@
         <v>55</v>
       </c>
       <c r="F713" s="3" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="G713" s="3"/>
       <c r="H713" s="3"/>
@@ -24937,6 +25132,832 @@
       <c r="L713" s="3"/>
       <c r="M713" s="3"/>
     </row>
+    <row r="714" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A714" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C714" s="3">
+        <v>110</v>
+      </c>
+      <c r="D714" s="3">
+        <v>5569343074</v>
+      </c>
+      <c r="E714" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H714" s="3"/>
+      <c r="I714" s="3"/>
+      <c r="J714" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K714" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L714" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M714" s="3" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="715" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A715" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B715" s="3"/>
+      <c r="C715" s="3">
+        <v>110</v>
+      </c>
+      <c r="D715" s="3">
+        <v>5569438030</v>
+      </c>
+      <c r="E715" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G715" s="3"/>
+      <c r="H715" s="3"/>
+      <c r="I715" s="3"/>
+      <c r="J715" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K715" s="3"/>
+      <c r="L715" s="3"/>
+      <c r="M715" s="3"/>
+    </row>
+    <row r="716" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A716" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B716" s="3"/>
+      <c r="C716" s="3">
+        <v>112</v>
+      </c>
+      <c r="D716" s="3">
+        <v>5572067577</v>
+      </c>
+      <c r="E716" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G716" s="3"/>
+      <c r="H716" s="3"/>
+      <c r="I716" s="3"/>
+      <c r="J716" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K716" s="3"/>
+      <c r="L716" s="3"/>
+      <c r="M716" s="3"/>
+    </row>
+    <row r="717" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A717" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B717" s="3"/>
+      <c r="C717" s="3">
+        <v>112</v>
+      </c>
+      <c r="D717" s="3">
+        <v>5572087467</v>
+      </c>
+      <c r="E717" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H717" s="3"/>
+      <c r="I717" s="3"/>
+      <c r="J717" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K717" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L717" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M717" s="3"/>
+    </row>
+    <row r="718" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A718" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B718" s="3"/>
+      <c r="C718" s="3">
+        <v>112</v>
+      </c>
+      <c r="D718" s="3">
+        <v>5572740162</v>
+      </c>
+      <c r="E718" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H718" s="3"/>
+      <c r="I718" s="3"/>
+      <c r="J718" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K718" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L718" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M718" s="3"/>
+    </row>
+    <row r="719" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A719" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B719" s="3"/>
+      <c r="C719" s="3">
+        <v>113</v>
+      </c>
+      <c r="D719" s="3">
+        <v>5573892163</v>
+      </c>
+      <c r="E719" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H719" s="3"/>
+      <c r="I719" s="3"/>
+      <c r="J719" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K719" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L719" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M719" s="3"/>
+    </row>
+    <row r="720" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A720" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B720" s="3"/>
+      <c r="C720" s="3">
+        <v>112</v>
+      </c>
+      <c r="D720" s="3">
+        <v>5575541826</v>
+      </c>
+      <c r="E720" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H720" s="3"/>
+      <c r="I720" s="3"/>
+      <c r="J720" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K720" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L720" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="M720" s="3"/>
+    </row>
+    <row r="721" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A721" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B721" s="3"/>
+      <c r="C721" s="3">
+        <v>301</v>
+      </c>
+      <c r="D721" s="3">
+        <v>5576637888</v>
+      </c>
+      <c r="E721" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="G721" s="3"/>
+      <c r="H721" s="3"/>
+      <c r="I721" s="3"/>
+      <c r="J721" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K721" s="3"/>
+      <c r="L721" s="3"/>
+      <c r="M721" s="3"/>
+    </row>
+    <row r="722" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A722" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B722" s="3"/>
+      <c r="C722" s="3">
+        <v>301</v>
+      </c>
+      <c r="D722" s="3">
+        <v>5576726243</v>
+      </c>
+      <c r="E722" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G722" s="3"/>
+      <c r="H722" s="3"/>
+      <c r="I722" s="3"/>
+      <c r="J722" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K722" s="3"/>
+      <c r="L722" s="3"/>
+      <c r="M722" s="3"/>
+    </row>
+    <row r="723" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A723" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B723" s="3"/>
+      <c r="C723" s="3">
+        <v>301</v>
+      </c>
+      <c r="D723" s="3">
+        <v>5576811029</v>
+      </c>
+      <c r="E723" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G723" s="3"/>
+      <c r="H723" s="3"/>
+      <c r="I723" s="3"/>
+      <c r="J723" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K723" s="3"/>
+      <c r="L723" s="3"/>
+      <c r="M723" s="3"/>
+    </row>
+    <row r="724" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A724" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B724" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C724" s="3">
+        <v>301</v>
+      </c>
+      <c r="D724" s="3">
+        <v>5576884002</v>
+      </c>
+      <c r="E724" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H724" s="3"/>
+      <c r="I724" s="3"/>
+      <c r="J724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K724" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L724" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="M724" s="3" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="725" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A725" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B725" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C725" s="3">
+        <v>301</v>
+      </c>
+      <c r="D725" s="3">
+        <v>5577088802</v>
+      </c>
+      <c r="E725" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H725" s="3"/>
+      <c r="I725" s="3"/>
+      <c r="J725" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K725" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L725" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="M725" s="3"/>
+    </row>
+    <row r="726" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A726" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B726" s="3"/>
+      <c r="C726" s="3">
+        <v>301</v>
+      </c>
+      <c r="D726" s="3">
+        <v>5577097230</v>
+      </c>
+      <c r="E726" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G726" s="3"/>
+      <c r="H726" s="3"/>
+      <c r="I726" s="3"/>
+      <c r="J726" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K726" s="3"/>
+      <c r="L726" s="3"/>
+      <c r="M726" s="3"/>
+    </row>
+    <row r="727" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A727" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B727" s="3"/>
+      <c r="C727" s="3">
+        <v>301</v>
+      </c>
+      <c r="D727" s="3">
+        <v>5577123214</v>
+      </c>
+      <c r="E727" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G727" s="3"/>
+      <c r="H727" s="3"/>
+      <c r="I727" s="3"/>
+      <c r="J727" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K727" s="3"/>
+      <c r="L727" s="3"/>
+      <c r="M727" s="3"/>
+    </row>
+    <row r="728" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A728" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B728" s="3"/>
+      <c r="C728" s="3">
+        <v>301</v>
+      </c>
+      <c r="D728" s="3">
+        <v>5577587922</v>
+      </c>
+      <c r="E728" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="G728" s="3"/>
+      <c r="H728" s="3"/>
+      <c r="I728" s="3"/>
+      <c r="J728" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K728" s="3"/>
+      <c r="L728" s="3"/>
+      <c r="M728" s="3"/>
+    </row>
+    <row r="729" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A729" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B729" s="3"/>
+      <c r="C729" s="3">
+        <v>111</v>
+      </c>
+      <c r="D729" s="3">
+        <v>5579254828</v>
+      </c>
+      <c r="E729" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G729" s="3"/>
+      <c r="H729" s="3"/>
+      <c r="I729" s="3"/>
+      <c r="J729" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K729" s="3"/>
+      <c r="L729" s="3"/>
+      <c r="M729" s="3"/>
+    </row>
+    <row r="730" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A730" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B730" s="3"/>
+      <c r="C730" s="3">
+        <v>111</v>
+      </c>
+      <c r="D730" s="3">
+        <v>5579374266</v>
+      </c>
+      <c r="E730" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H730" s="3"/>
+      <c r="I730" s="3"/>
+      <c r="J730" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K730" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L730" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="M730" s="3"/>
+    </row>
+    <row r="731" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A731" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B731" s="3"/>
+      <c r="C731" s="3">
+        <v>111</v>
+      </c>
+      <c r="D731" s="3">
+        <v>5580290039</v>
+      </c>
+      <c r="E731" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H731" s="3"/>
+      <c r="I731" s="3"/>
+      <c r="J731" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K731" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L731" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="M731" s="3"/>
+    </row>
+    <row r="732" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A732" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B732" s="3"/>
+      <c r="C732" s="3">
+        <v>113</v>
+      </c>
+      <c r="D732" s="3">
+        <v>5583727371</v>
+      </c>
+      <c r="E732" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H732" s="3"/>
+      <c r="I732" s="3"/>
+      <c r="J732" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K732" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L732" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="M732" s="3"/>
+    </row>
+    <row r="733" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A733" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B733" s="3"/>
+      <c r="C733" s="3">
+        <v>113</v>
+      </c>
+      <c r="D733" s="3">
+        <v>5585278460</v>
+      </c>
+      <c r="E733" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G733" s="3"/>
+      <c r="H733" s="3"/>
+      <c r="I733" s="3"/>
+      <c r="J733" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K733" s="3"/>
+      <c r="L733" s="3"/>
+      <c r="M733" s="3"/>
+    </row>
+    <row r="734" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A734" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B734" s="3"/>
+      <c r="C734" s="3">
+        <v>111</v>
+      </c>
+      <c r="D734" s="3">
+        <v>5585692272</v>
+      </c>
+      <c r="E734" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F734" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G734" s="3"/>
+      <c r="H734" s="3"/>
+      <c r="I734" s="3"/>
+      <c r="J734" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K734" s="3"/>
+      <c r="L734" s="3"/>
+      <c r="M734" s="3"/>
+    </row>
+    <row r="735" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A735" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B735" s="3"/>
+      <c r="C735" s="3">
+        <v>111</v>
+      </c>
+      <c r="D735" s="3">
+        <v>5589492959</v>
+      </c>
+      <c r="E735" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F735" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G735" s="3"/>
+      <c r="H735" s="3"/>
+      <c r="I735" s="3"/>
+      <c r="J735" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K735" s="3"/>
+      <c r="L735" s="3"/>
+      <c r="M735" s="3"/>
+    </row>
+    <row r="736" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A736" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B736" s="3"/>
+      <c r="C736" s="3">
+        <v>111</v>
+      </c>
+      <c r="D736" s="3">
+        <v>5589504517</v>
+      </c>
+      <c r="E736" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F736" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G736" s="3"/>
+      <c r="H736" s="3"/>
+      <c r="I736" s="3"/>
+      <c r="J736" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K736" s="3"/>
+      <c r="L736" s="3"/>
+      <c r="M736" s="3"/>
+    </row>
+    <row r="737" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A737" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B737" s="3"/>
+      <c r="C737" s="3">
+        <v>111</v>
+      </c>
+      <c r="D737" s="3">
+        <v>5592917017</v>
+      </c>
+      <c r="E737" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G737" s="3"/>
+      <c r="H737" s="3"/>
+      <c r="I737" s="3"/>
+      <c r="J737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K737" s="3"/>
+      <c r="L737" s="3"/>
+      <c r="M737" s="3"/>
+    </row>
+    <row r="738" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A738" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B738" s="3"/>
+      <c r="C738" s="3">
+        <v>112</v>
+      </c>
+      <c r="D738" s="3">
+        <v>5595024776</v>
+      </c>
+      <c r="E738" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G738" s="3"/>
+      <c r="H738" s="3"/>
+      <c r="I738" s="3"/>
+      <c r="J738" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K738" s="3"/>
+      <c r="L738" s="3"/>
+      <c r="M738" s="3"/>
+    </row>
+    <row r="739" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A739" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B739" s="3"/>
+      <c r="C739" s="3">
+        <v>113</v>
+      </c>
+      <c r="D739" s="3">
+        <v>5596004370</v>
+      </c>
+      <c r="E739" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G739" s="3"/>
+      <c r="H739" s="3"/>
+      <c r="I739" s="3"/>
+      <c r="J739" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K739" s="3"/>
+      <c r="L739" s="3"/>
+      <c r="M739" s="3"/>
+    </row>
+    <row r="740" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A740" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B740" s="3"/>
+      <c r="C740" s="3">
+        <v>113</v>
+      </c>
+      <c r="D740" s="3">
+        <v>5598981659</v>
+      </c>
+      <c r="E740" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G740" s="3"/>
+      <c r="H740" s="3"/>
+      <c r="I740" s="3"/>
+      <c r="J740" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K740" s="3"/>
+      <c r="L740" s="3"/>
+      <c r="M740" s="3"/>
+    </row>
+    <row r="741" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A741" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B741" s="3"/>
+      <c r="C741" s="3">
+        <v>113</v>
+      </c>
+      <c r="D741" s="3">
+        <v>5599821712</v>
+      </c>
+      <c r="E741" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G741" s="3"/>
+      <c r="H741" s="3"/>
+      <c r="I741" s="3"/>
+      <c r="J741" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K741" s="3"/>
+      <c r="L741" s="3"/>
+      <c r="M741" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07C5F778-5866-4D60-9DA0-ABB814D79400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2515709-6FBA-4FA0-B95E-D9BA06EEA8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4712" uniqueCount="2203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4926" uniqueCount="2298">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -6547,6 +6547,12 @@
     <t>29.626211, -98.282610</t>
   </si>
   <si>
+    <t>04/27/26 12:10 EDT</t>
+  </si>
+  <si>
+    <t>04/27/26 12:11 EDT</t>
+  </si>
+  <si>
     <t>04/24/26 11:49 EDT</t>
   </si>
   <si>
@@ -6619,6 +6625,12 @@
     <t>29.457766, -98.307780</t>
   </si>
   <si>
+    <t>04/25/26 12:59 EDT</t>
+  </si>
+  <si>
+    <t>29.438023, -98.379780</t>
+  </si>
+  <si>
     <t>04/25/26 13:21 EDT</t>
   </si>
   <si>
@@ -6629,6 +6641,279 @@
   </si>
   <si>
     <t>29.432580, -98.244870</t>
+  </si>
+  <si>
+    <t>04/27/26 12:49 EDT</t>
+  </si>
+  <si>
+    <t>5.2mi E of Converse TX</t>
+  </si>
+  <si>
+    <t>29.487513, -98.225410</t>
+  </si>
+  <si>
+    <t>04/27/26 15:11 EDT</t>
+  </si>
+  <si>
+    <t>29.421139, -98.433556</t>
+  </si>
+  <si>
+    <t>04/27/26 15:48 EDT</t>
+  </si>
+  <si>
+    <t>14.1mi S of Pearsall TX</t>
+  </si>
+  <si>
+    <t>28.696062, -99.165146</t>
+  </si>
+  <si>
+    <t>04/27/26 16:02 EDT</t>
+  </si>
+  <si>
+    <t>0.8mi S of Hondo TX</t>
+  </si>
+  <si>
+    <t>29.341820, -99.166510</t>
+  </si>
+  <si>
+    <t>04/27/26 16:13 EDT</t>
+  </si>
+  <si>
+    <t>12.1mi NE of Pearsall TX</t>
+  </si>
+  <si>
+    <t>29.051727, -99.017110</t>
+  </si>
+  <si>
+    <t>04/27/26 17:44 EDT</t>
+  </si>
+  <si>
+    <t>6.6mi SE of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.320269, -98.538680</t>
+  </si>
+  <si>
+    <t>04/28/26 06:56 EDT</t>
+  </si>
+  <si>
+    <t>04/27/26 19:55 EDT</t>
+  </si>
+  <si>
+    <t>29.582270, -97.999520</t>
+  </si>
+  <si>
+    <t>04/27/26 20:29 EDT</t>
+  </si>
+  <si>
+    <t>29.582737, -97.998630</t>
+  </si>
+  <si>
+    <t>04/27/26 20:43 EDT</t>
+  </si>
+  <si>
+    <t>29.171915, -98.855020</t>
+  </si>
+  <si>
+    <t>04/28/26 06:23 EDT</t>
+  </si>
+  <si>
+    <t>29.613108, -98.284680</t>
+  </si>
+  <si>
+    <t>04/28/26 08:28 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi NE of Universal City TX</t>
+  </si>
+  <si>
+    <t>29.562265, -98.293290</t>
+  </si>
+  <si>
+    <t>04/28/26 08:59 EDT</t>
+  </si>
+  <si>
+    <t>29.489141, -98.224434</t>
+  </si>
+  <si>
+    <t>04/28/26 10:26 EDT</t>
+  </si>
+  <si>
+    <t>29.487606, -98.225040</t>
+  </si>
+  <si>
+    <t>04/28/26 14:16 EDT</t>
+  </si>
+  <si>
+    <t>29.694345, -98.103226</t>
+  </si>
+  <si>
+    <t>04/29/26 10:26 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi NW of Schertz TX</t>
+  </si>
+  <si>
+    <t>29.578938, -98.262840</t>
+  </si>
+  <si>
+    <t>04/30/26 12:52 EDT</t>
+  </si>
+  <si>
+    <t>04/29/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi E of Schertz TX</t>
+  </si>
+  <si>
+    <t>29.560330, -98.239450</t>
+  </si>
+  <si>
+    <t>04/30/26 12:50 EDT</t>
+  </si>
+  <si>
+    <t>04/29/26 11:36 EDT</t>
+  </si>
+  <si>
+    <t>29.487326, -98.104706</t>
+  </si>
+  <si>
+    <t>04/29/26 13:35 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi S of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.510164, -98.209526</t>
+  </si>
+  <si>
+    <t>04/29/26 14:12 EDT</t>
+  </si>
+  <si>
+    <t>29.470125, -98.276920</t>
+  </si>
+  <si>
+    <t>HIGH-G</t>
+  </si>
+  <si>
+    <t>7.3mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.492895, -98.121230</t>
+  </si>
+  <si>
+    <t>04/29/26 18:58 EDT</t>
+  </si>
+  <si>
+    <t>4mi S of San Marcos TX</t>
+  </si>
+  <si>
+    <t>29.816187, -97.943565</t>
+  </si>
+  <si>
+    <t>04/29/26 21:00 EDT</t>
+  </si>
+  <si>
+    <t>6.4mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.529120, -98.113470</t>
+  </si>
+  <si>
+    <t>04/30/26 08:11 EDT</t>
+  </si>
+  <si>
+    <t>5.3mi S of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.487856, -98.222590</t>
+  </si>
+  <si>
+    <t>04/30/26 12:51 EDT</t>
+  </si>
+  <si>
+    <t>04/30/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi E of Sugar Land TX</t>
+  </si>
+  <si>
+    <t>29.592152, -95.630430</t>
+  </si>
+  <si>
+    <t>04/30/26 14:48 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.476665, -98.256900</t>
+  </si>
+  <si>
+    <t>05/01/26 10:44 EDT</t>
+  </si>
+  <si>
+    <t>04/30/26 14:59 EDT</t>
+  </si>
+  <si>
+    <t>29.612005, -98.284700</t>
+  </si>
+  <si>
+    <t>04/30/26 15:22 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi NW of Schertz TX</t>
+  </si>
+  <si>
+    <t>29.582035, -98.265000</t>
+  </si>
+  <si>
+    <t>04/30/26 18:43 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi W of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.581018, -98.023890</t>
+  </si>
+  <si>
+    <t>05/01/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.427942, -98.360695</t>
+  </si>
+  <si>
+    <t>05/01/26 14:42 EDT</t>
+  </si>
+  <si>
+    <t>29.502707, -98.480545</t>
+  </si>
+  <si>
+    <t>05/01/26 15:49 EDT</t>
+  </si>
+  <si>
+    <t>5.2mi SW of Luling TX</t>
+  </si>
+  <si>
+    <t>29.639225, -97.718360</t>
+  </si>
+  <si>
+    <t>05/01/26 17:17 EDT</t>
+  </si>
+  <si>
+    <t>30mi S of Pearsall TX</t>
+  </si>
+  <si>
+    <t>28.473688, -99.229030</t>
+  </si>
+  <si>
+    <t>05/01/26 19:42 EDT</t>
+  </si>
+  <si>
+    <t>29.446413, -98.356384</t>
   </si>
 </sst>
 </file>
@@ -6990,7 +7275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N780"/>
+  <dimension ref="A1:N814"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -31626,7 +31911,9 @@
       <c r="A769" s="3" t="s">
         <v>2172</v>
       </c>
-      <c r="B769" s="3"/>
+      <c r="B769" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="C769" s="3">
         <v>112</v>
       </c>
@@ -31642,19 +31929,27 @@
       <c r="G769" s="3" t="s">
         <v>2174</v>
       </c>
-      <c r="H769" s="3"/>
+      <c r="H769" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I769" s="3"/>
       <c r="J769" s="3"/>
       <c r="K769" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L769" s="3"/>
-      <c r="M769" s="3"/>
-      <c r="N769" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L769" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M769" s="3" t="s">
+        <v>2175</v>
+      </c>
+      <c r="N769" s="3" t="s">
+        <v>2176</v>
+      </c>
     </row>
     <row r="770" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A770" s="3" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="B770" s="3"/>
       <c r="C770" s="3">
@@ -31667,24 +31962,30 @@
         <v>210</v>
       </c>
       <c r="F770" s="3" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="G770" s="3" t="s">
-        <v>2177</v>
-      </c>
-      <c r="H770" s="3"/>
+        <v>2179</v>
+      </c>
+      <c r="H770" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I770" s="3"/>
       <c r="J770" s="3"/>
       <c r="K770" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L770" s="3"/>
-      <c r="M770" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L770" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M770" s="3" t="s">
+        <v>2175</v>
+      </c>
       <c r="N770" s="3"/>
     </row>
     <row r="771" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A771" s="3" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="B771" s="3"/>
       <c r="C771" s="3">
@@ -31697,24 +31998,30 @@
         <v>210</v>
       </c>
       <c r="F771" s="3" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="G771" s="3" t="s">
-        <v>2179</v>
-      </c>
-      <c r="H771" s="3"/>
+        <v>2181</v>
+      </c>
+      <c r="H771" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I771" s="3"/>
       <c r="J771" s="3"/>
       <c r="K771" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L771" s="3"/>
-      <c r="M771" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L771" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M771" s="3" t="s">
+        <v>2175</v>
+      </c>
       <c r="N771" s="3"/>
     </row>
     <row r="772" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A772" s="3" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="B772" s="3"/>
       <c r="C772" s="3">
@@ -31727,10 +32034,10 @@
         <v>53</v>
       </c>
       <c r="F772" s="3" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="G772" s="3" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="H772" s="3"/>
       <c r="I772" s="3"/>
@@ -31744,7 +32051,7 @@
     </row>
     <row r="773" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A773" s="3" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B773" s="3"/>
       <c r="C773" s="3">
@@ -31760,21 +32067,27 @@
         <v>120</v>
       </c>
       <c r="G773" s="3" t="s">
-        <v>2184</v>
-      </c>
-      <c r="H773" s="3"/>
+        <v>2186</v>
+      </c>
+      <c r="H773" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I773" s="3"/>
       <c r="J773" s="3"/>
       <c r="K773" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L773" s="3"/>
-      <c r="M773" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L773" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M773" s="3" t="s">
+        <v>2175</v>
+      </c>
       <c r="N773" s="3"/>
     </row>
     <row r="774" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A774" s="3" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="B774" s="3"/>
       <c r="C774" s="3">
@@ -31787,24 +32100,30 @@
         <v>80</v>
       </c>
       <c r="F774" s="3" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="G774" s="3" t="s">
-        <v>2187</v>
-      </c>
-      <c r="H774" s="3"/>
+        <v>2189</v>
+      </c>
+      <c r="H774" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I774" s="3"/>
       <c r="J774" s="3"/>
       <c r="K774" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L774" s="3"/>
-      <c r="M774" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L774" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M774" s="3" t="s">
+        <v>2175</v>
+      </c>
       <c r="N774" s="3"/>
     </row>
     <row r="775" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A775" s="3" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="B775" s="3"/>
       <c r="C775" s="3">
@@ -31820,7 +32139,7 @@
         <v>1151</v>
       </c>
       <c r="G775" s="3" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="H775" s="3"/>
       <c r="I775" s="3"/>
@@ -31834,7 +32153,7 @@
     </row>
     <row r="776" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A776" s="3" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="B776" s="3"/>
       <c r="C776" s="3">
@@ -31847,24 +32166,30 @@
         <v>80</v>
       </c>
       <c r="F776" s="3" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="G776" s="3" t="s">
-        <v>2192</v>
-      </c>
-      <c r="H776" s="3"/>
+        <v>2194</v>
+      </c>
+      <c r="H776" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I776" s="3"/>
       <c r="J776" s="3"/>
       <c r="K776" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L776" s="3"/>
-      <c r="M776" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L776" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M776" s="3" t="s">
+        <v>2175</v>
+      </c>
       <c r="N776" s="3"/>
     </row>
     <row r="777" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A777" s="3" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="B777" s="3"/>
       <c r="C777" s="3">
@@ -31880,7 +32205,7 @@
         <v>2111</v>
       </c>
       <c r="G777" s="3" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="H777" s="3"/>
       <c r="I777" s="3"/>
@@ -31894,7 +32219,7 @@
     </row>
     <row r="778" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A778" s="3" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="B778" s="3"/>
       <c r="C778" s="3">
@@ -31910,7 +32235,7 @@
         <v>201</v>
       </c>
       <c r="G778" s="3" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="H778" s="3"/>
       <c r="I778" s="3"/>
@@ -31924,7 +32249,7 @@
     </row>
     <row r="779" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A779" s="3" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B779" s="3"/>
       <c r="C779" s="3">
@@ -31940,51 +32265,1123 @@
         <v>201</v>
       </c>
       <c r="G779" s="3" t="s">
-        <v>2198</v>
-      </c>
-      <c r="H779" s="3"/>
+        <v>2200</v>
+      </c>
+      <c r="H779" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I779" s="3"/>
       <c r="J779" s="3"/>
       <c r="K779" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L779" s="3"/>
-      <c r="M779" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L779" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M779" s="3" t="s">
+        <v>2175</v>
+      </c>
       <c r="N779" s="3"/>
     </row>
     <row r="780" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A780" s="3" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="B780" s="3"/>
       <c r="C780" s="3">
         <v>112</v>
       </c>
       <c r="D780" s="3">
-        <v>5643944084</v>
+        <v>5650303542</v>
       </c>
       <c r="E780" s="3" t="s">
-        <v>2200</v>
+        <v>53</v>
       </c>
       <c r="F780" s="3" t="s">
-        <v>2201</v>
+        <v>1071</v>
       </c>
       <c r="G780" s="3" t="s">
         <v>2202</v>
       </c>
       <c r="H780" s="3"/>
-      <c r="I780" s="3">
-        <v>51</v>
-      </c>
-      <c r="J780" s="3">
-        <v>45</v>
-      </c>
+      <c r="I780" s="3"/>
+      <c r="J780" s="3"/>
       <c r="K780" s="3" t="s">
         <v>20</v>
       </c>
       <c r="L780" s="3"/>
       <c r="M780" s="3"/>
       <c r="N780" s="3"/>
+    </row>
+    <row r="781" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A781" s="3" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B781" s="3"/>
+      <c r="C781" s="3">
+        <v>112</v>
+      </c>
+      <c r="D781" s="3">
+        <v>5643944084</v>
+      </c>
+      <c r="E781" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="H781" s="3"/>
+      <c r="I781" s="3">
+        <v>51</v>
+      </c>
+      <c r="J781" s="3">
+        <v>45</v>
+      </c>
+      <c r="K781" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L781" s="3"/>
+      <c r="M781" s="3"/>
+      <c r="N781" s="3"/>
+    </row>
+    <row r="782" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A782" s="3" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B782" s="3"/>
+      <c r="C782" s="3">
+        <v>111</v>
+      </c>
+      <c r="D782" s="3">
+        <v>5652922486</v>
+      </c>
+      <c r="E782" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="H782" s="3"/>
+      <c r="I782" s="3"/>
+      <c r="J782" s="3"/>
+      <c r="K782" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L782" s="3"/>
+      <c r="M782" s="3"/>
+      <c r="N782" s="3"/>
+    </row>
+    <row r="783" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A783" s="3" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B783" s="3"/>
+      <c r="C783" s="3">
+        <v>113</v>
+      </c>
+      <c r="D783" s="3">
+        <v>5654157244</v>
+      </c>
+      <c r="E783" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>2211</v>
+      </c>
+      <c r="H783" s="3"/>
+      <c r="I783" s="3"/>
+      <c r="J783" s="3"/>
+      <c r="K783" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L783" s="3"/>
+      <c r="M783" s="3"/>
+      <c r="N783" s="3"/>
+    </row>
+    <row r="784" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A784" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B784" s="3"/>
+      <c r="C784" s="3">
+        <v>111</v>
+      </c>
+      <c r="D784" s="3">
+        <v>5654459454</v>
+      </c>
+      <c r="E784" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>2213</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>2214</v>
+      </c>
+      <c r="H784" s="3"/>
+      <c r="I784" s="3"/>
+      <c r="J784" s="3"/>
+      <c r="K784" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L784" s="3"/>
+      <c r="M784" s="3"/>
+      <c r="N784" s="3"/>
+    </row>
+    <row r="785" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A785" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B785" s="3"/>
+      <c r="C785" s="3">
+        <v>113</v>
+      </c>
+      <c r="D785" s="3">
+        <v>5654579819</v>
+      </c>
+      <c r="E785" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="G785" s="3" t="s">
+        <v>2217</v>
+      </c>
+      <c r="H785" s="3"/>
+      <c r="I785" s="3">
+        <v>68</v>
+      </c>
+      <c r="J785" s="3">
+        <v>60</v>
+      </c>
+      <c r="K785" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L785" s="3"/>
+      <c r="M785" s="3"/>
+      <c r="N785" s="3"/>
+    </row>
+    <row r="786" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A786" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B786" s="3"/>
+      <c r="C786" s="3">
+        <v>111</v>
+      </c>
+      <c r="D786" s="3">
+        <v>5654660681</v>
+      </c>
+      <c r="E786" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F786" s="3" t="s">
+        <v>2219</v>
+      </c>
+      <c r="G786" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="H786" s="3"/>
+      <c r="I786" s="3"/>
+      <c r="J786" s="3"/>
+      <c r="K786" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L786" s="3"/>
+      <c r="M786" s="3"/>
+      <c r="N786" s="3"/>
+    </row>
+    <row r="787" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A787" s="3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B787" s="3"/>
+      <c r="C787" s="3">
+        <v>111</v>
+      </c>
+      <c r="D787" s="3">
+        <v>5655349708</v>
+      </c>
+      <c r="E787" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F787" s="3" t="s">
+        <v>2222</v>
+      </c>
+      <c r="G787" s="3" t="s">
+        <v>2223</v>
+      </c>
+      <c r="H787" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I787" s="3"/>
+      <c r="J787" s="3"/>
+      <c r="K787" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L787" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M787" s="3" t="s">
+        <v>2224</v>
+      </c>
+      <c r="N787" s="3"/>
+    </row>
+    <row r="788" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A788" s="3" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B788" s="3"/>
+      <c r="C788" s="3">
+        <v>110</v>
+      </c>
+      <c r="D788" s="3">
+        <v>5656141939</v>
+      </c>
+      <c r="E788" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F788" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G788" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H788" s="3"/>
+      <c r="I788" s="3"/>
+      <c r="J788" s="3"/>
+      <c r="K788" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L788" s="3"/>
+      <c r="M788" s="3"/>
+      <c r="N788" s="3"/>
+    </row>
+    <row r="789" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A789" s="3" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B789" s="3"/>
+      <c r="C789" s="3">
+        <v>110</v>
+      </c>
+      <c r="D789" s="3">
+        <v>5663500780</v>
+      </c>
+      <c r="E789" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F789" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G789" s="3" t="s">
+        <v>2228</v>
+      </c>
+      <c r="H789" s="3"/>
+      <c r="I789" s="3"/>
+      <c r="J789" s="3"/>
+      <c r="K789" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L789" s="3"/>
+      <c r="M789" s="3"/>
+      <c r="N789" s="3"/>
+    </row>
+    <row r="790" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A790" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B790" s="3"/>
+      <c r="C790" s="3">
+        <v>111</v>
+      </c>
+      <c r="D790" s="3">
+        <v>5656326962</v>
+      </c>
+      <c r="E790" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>2230</v>
+      </c>
+      <c r="H790" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I790" s="3"/>
+      <c r="J790" s="3"/>
+      <c r="K790" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L790" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M790" s="3" t="s">
+        <v>2224</v>
+      </c>
+      <c r="N790" s="3"/>
+    </row>
+    <row r="791" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A791" s="3" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B791" s="3"/>
+      <c r="C791" s="3">
+        <v>112</v>
+      </c>
+      <c r="D791" s="3">
+        <v>5657375924</v>
+      </c>
+      <c r="E791" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="G791" s="3" t="s">
+        <v>2232</v>
+      </c>
+      <c r="H791" s="3"/>
+      <c r="I791" s="3"/>
+      <c r="J791" s="3"/>
+      <c r="K791" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L791" s="3"/>
+      <c r="M791" s="3"/>
+      <c r="N791" s="3"/>
+    </row>
+    <row r="792" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A792" s="3" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B792" s="3"/>
+      <c r="C792" s="3">
+        <v>112</v>
+      </c>
+      <c r="D792" s="3">
+        <v>5657895977</v>
+      </c>
+      <c r="E792" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="G792" s="3" t="s">
+        <v>2235</v>
+      </c>
+      <c r="H792" s="3"/>
+      <c r="I792" s="3"/>
+      <c r="J792" s="3"/>
+      <c r="K792" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L792" s="3"/>
+      <c r="M792" s="3"/>
+      <c r="N792" s="3"/>
+    </row>
+    <row r="793" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A793" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B793" s="3"/>
+      <c r="C793" s="3">
+        <v>112</v>
+      </c>
+      <c r="D793" s="3">
+        <v>5670374171</v>
+      </c>
+      <c r="E793" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G793" s="3" t="s">
+        <v>2237</v>
+      </c>
+      <c r="H793" s="3"/>
+      <c r="I793" s="3"/>
+      <c r="J793" s="3"/>
+      <c r="K793" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L793" s="3"/>
+      <c r="M793" s="3"/>
+      <c r="N793" s="3"/>
+    </row>
+    <row r="794" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A794" s="3" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B794" s="3"/>
+      <c r="C794" s="3">
+        <v>301</v>
+      </c>
+      <c r="D794" s="3">
+        <v>5658542524</v>
+      </c>
+      <c r="E794" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="G794" s="3" t="s">
+        <v>2239</v>
+      </c>
+      <c r="H794" s="3"/>
+      <c r="I794" s="3"/>
+      <c r="J794" s="3"/>
+      <c r="K794" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L794" s="3"/>
+      <c r="M794" s="3"/>
+      <c r="N794" s="3"/>
+    </row>
+    <row r="795" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A795" s="3" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B795" s="3"/>
+      <c r="C795" s="3">
+        <v>112</v>
+      </c>
+      <c r="D795" s="3">
+        <v>5660392304</v>
+      </c>
+      <c r="E795" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="G795" s="3" t="s">
+        <v>2241</v>
+      </c>
+      <c r="H795" s="3"/>
+      <c r="I795" s="3"/>
+      <c r="J795" s="3"/>
+      <c r="K795" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L795" s="3"/>
+      <c r="M795" s="3"/>
+      <c r="N795" s="3"/>
+    </row>
+    <row r="796" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A796" s="3" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B796" s="3"/>
+      <c r="C796" s="3">
+        <v>301</v>
+      </c>
+      <c r="D796" s="3">
+        <v>5665387657</v>
+      </c>
+      <c r="E796" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>2243</v>
+      </c>
+      <c r="G796" s="3" t="s">
+        <v>2244</v>
+      </c>
+      <c r="H796" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I796" s="3"/>
+      <c r="J796" s="3"/>
+      <c r="K796" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L796" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M796" s="3" t="s">
+        <v>2245</v>
+      </c>
+      <c r="N796" s="3"/>
+    </row>
+    <row r="797" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A797" s="3" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B797" s="3"/>
+      <c r="C797" s="3">
+        <v>301</v>
+      </c>
+      <c r="D797" s="3">
+        <v>5665722177</v>
+      </c>
+      <c r="E797" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>2247</v>
+      </c>
+      <c r="G797" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="H797" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I797" s="3"/>
+      <c r="J797" s="3"/>
+      <c r="K797" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L797" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M797" s="3" t="s">
+        <v>2249</v>
+      </c>
+      <c r="N797" s="3"/>
+    </row>
+    <row r="798" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A798" s="3" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B798" s="3"/>
+      <c r="C798" s="3">
+        <v>301</v>
+      </c>
+      <c r="D798" s="3">
+        <v>5665871324</v>
+      </c>
+      <c r="E798" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="G798" s="3" t="s">
+        <v>2251</v>
+      </c>
+      <c r="H798" s="3"/>
+      <c r="I798" s="3"/>
+      <c r="J798" s="3"/>
+      <c r="K798" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L798" s="3"/>
+      <c r="M798" s="3"/>
+      <c r="N798" s="3"/>
+    </row>
+    <row r="799" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A799" s="3" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B799" s="3"/>
+      <c r="C799" s="3">
+        <v>301</v>
+      </c>
+      <c r="D799" s="3">
+        <v>5666885104</v>
+      </c>
+      <c r="E799" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>2253</v>
+      </c>
+      <c r="G799" s="3" t="s">
+        <v>2254</v>
+      </c>
+      <c r="H799" s="3"/>
+      <c r="I799" s="3"/>
+      <c r="J799" s="3"/>
+      <c r="K799" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L799" s="3"/>
+      <c r="M799" s="3"/>
+      <c r="N799" s="3"/>
+    </row>
+    <row r="800" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A800" s="3" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B800" s="3"/>
+      <c r="C800" s="3">
+        <v>112</v>
+      </c>
+      <c r="D800" s="3">
+        <v>5667219705</v>
+      </c>
+      <c r="E800" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G800" s="3" t="s">
+        <v>2256</v>
+      </c>
+      <c r="H800" s="3"/>
+      <c r="I800" s="3"/>
+      <c r="J800" s="3"/>
+      <c r="K800" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L800" s="3"/>
+      <c r="M800" s="3"/>
+      <c r="N800" s="3"/>
+    </row>
+    <row r="801" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A801" s="3" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B801" s="3"/>
+      <c r="C801" s="3">
+        <v>301</v>
+      </c>
+      <c r="D801" s="3">
+        <v>5667226890</v>
+      </c>
+      <c r="E801" s="3" t="s">
+        <v>2257</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G801" s="3" t="s">
+        <v>2259</v>
+      </c>
+      <c r="H801" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I801" s="3"/>
+      <c r="J801" s="3"/>
+      <c r="K801" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L801" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M801" s="3" t="s">
+        <v>2249</v>
+      </c>
+      <c r="N801" s="3"/>
+    </row>
+    <row r="802" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A802" s="3" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B802" s="3"/>
+      <c r="C802" s="3">
+        <v>113</v>
+      </c>
+      <c r="D802" s="3">
+        <v>5669504791</v>
+      </c>
+      <c r="E802" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="G802" s="3" t="s">
+        <v>2262</v>
+      </c>
+      <c r="H802" s="3"/>
+      <c r="I802" s="3"/>
+      <c r="J802" s="3"/>
+      <c r="K802" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L802" s="3"/>
+      <c r="M802" s="3"/>
+      <c r="N802" s="3"/>
+    </row>
+    <row r="803" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A803" s="3" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B803" s="3"/>
+      <c r="C803" s="3">
+        <v>113</v>
+      </c>
+      <c r="D803" s="3">
+        <v>5670061028</v>
+      </c>
+      <c r="E803" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>2264</v>
+      </c>
+      <c r="G803" s="3" t="s">
+        <v>2265</v>
+      </c>
+      <c r="H803" s="3"/>
+      <c r="I803" s="3"/>
+      <c r="J803" s="3"/>
+      <c r="K803" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L803" s="3"/>
+      <c r="M803" s="3"/>
+      <c r="N803" s="3"/>
+    </row>
+    <row r="804" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A804" s="3" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B804" s="3"/>
+      <c r="C804" s="3">
+        <v>110</v>
+      </c>
+      <c r="D804" s="3">
+        <v>5671537773</v>
+      </c>
+      <c r="E804" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>2267</v>
+      </c>
+      <c r="G804" s="3" t="s">
+        <v>2268</v>
+      </c>
+      <c r="H804" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I804" s="3"/>
+      <c r="J804" s="3"/>
+      <c r="K804" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L804" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M804" s="3" t="s">
+        <v>2269</v>
+      </c>
+      <c r="N804" s="3"/>
+    </row>
+    <row r="805" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A805" s="3" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B805" s="3"/>
+      <c r="C805" s="3">
+        <v>112</v>
+      </c>
+      <c r="D805" s="3">
+        <v>5671921701</v>
+      </c>
+      <c r="E805" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>2271</v>
+      </c>
+      <c r="G805" s="3" t="s">
+        <v>2272</v>
+      </c>
+      <c r="H805" s="3"/>
+      <c r="I805" s="3"/>
+      <c r="J805" s="3"/>
+      <c r="K805" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L805" s="3"/>
+      <c r="M805" s="3"/>
+      <c r="N805" s="3"/>
+    </row>
+    <row r="806" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A806" s="3" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B806" s="3"/>
+      <c r="C806" s="3">
+        <v>113</v>
+      </c>
+      <c r="D806" s="3">
+        <v>5674397842</v>
+      </c>
+      <c r="E806" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G806" s="3" t="s">
+        <v>2275</v>
+      </c>
+      <c r="H806" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I806" s="3"/>
+      <c r="J806" s="3"/>
+      <c r="K806" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L806" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M806" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="N806" s="3"/>
+    </row>
+    <row r="807" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A807" s="3" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B807" s="3"/>
+      <c r="C807" s="3">
+        <v>112</v>
+      </c>
+      <c r="D807" s="3">
+        <v>5683867115</v>
+      </c>
+      <c r="E807" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="G807" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="H807" s="3"/>
+      <c r="I807" s="3"/>
+      <c r="J807" s="3"/>
+      <c r="K807" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L807" s="3"/>
+      <c r="M807" s="3"/>
+      <c r="N807" s="3"/>
+    </row>
+    <row r="808" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A808" s="3" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B808" s="3"/>
+      <c r="C808" s="3">
+        <v>112</v>
+      </c>
+      <c r="D808" s="3">
+        <v>5674698267</v>
+      </c>
+      <c r="E808" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>2280</v>
+      </c>
+      <c r="G808" s="3" t="s">
+        <v>2281</v>
+      </c>
+      <c r="H808" s="3"/>
+      <c r="I808" s="3"/>
+      <c r="J808" s="3"/>
+      <c r="K808" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L808" s="3"/>
+      <c r="M808" s="3"/>
+      <c r="N808" s="3"/>
+    </row>
+    <row r="809" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A809" s="3" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B809" s="3"/>
+      <c r="C809" s="3">
+        <v>113</v>
+      </c>
+      <c r="D809" s="3">
+        <v>5676217376</v>
+      </c>
+      <c r="E809" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="G809" s="3" t="s">
+        <v>2284</v>
+      </c>
+      <c r="H809" s="3"/>
+      <c r="I809" s="3"/>
+      <c r="J809" s="3"/>
+      <c r="K809" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L809" s="3"/>
+      <c r="M809" s="3"/>
+      <c r="N809" s="3"/>
+    </row>
+    <row r="810" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A810" s="3" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B810" s="3"/>
+      <c r="C810" s="3">
+        <v>111</v>
+      </c>
+      <c r="D810" s="3">
+        <v>5678645173</v>
+      </c>
+      <c r="E810" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="G810" s="3" t="s">
+        <v>2287</v>
+      </c>
+      <c r="H810" s="3"/>
+      <c r="I810" s="3"/>
+      <c r="J810" s="3"/>
+      <c r="K810" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L810" s="3"/>
+      <c r="M810" s="3"/>
+      <c r="N810" s="3"/>
+    </row>
+    <row r="811" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A811" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B811" s="3"/>
+      <c r="C811" s="3">
+        <v>111</v>
+      </c>
+      <c r="D811" s="3">
+        <v>5680898510</v>
+      </c>
+      <c r="E811" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="G811" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="H811" s="3"/>
+      <c r="I811" s="3"/>
+      <c r="J811" s="3"/>
+      <c r="K811" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L811" s="3"/>
+      <c r="M811" s="3"/>
+      <c r="N811" s="3"/>
+    </row>
+    <row r="812" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A812" s="3" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B812" s="3"/>
+      <c r="C812" s="3">
+        <v>112</v>
+      </c>
+      <c r="D812" s="3">
+        <v>5681446333</v>
+      </c>
+      <c r="E812" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F812" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="G812" s="3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="H812" s="3"/>
+      <c r="I812" s="3"/>
+      <c r="J812" s="3"/>
+      <c r="K812" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L812" s="3"/>
+      <c r="M812" s="3"/>
+      <c r="N812" s="3"/>
+    </row>
+    <row r="813" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A813" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B813" s="3"/>
+      <c r="C813" s="3">
+        <v>111</v>
+      </c>
+      <c r="D813" s="3">
+        <v>5682075244</v>
+      </c>
+      <c r="E813" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F813" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="G813" s="3" t="s">
+        <v>2295</v>
+      </c>
+      <c r="H813" s="3"/>
+      <c r="I813" s="3"/>
+      <c r="J813" s="3"/>
+      <c r="K813" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L813" s="3"/>
+      <c r="M813" s="3"/>
+      <c r="N813" s="3"/>
+    </row>
+    <row r="814" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A814" s="3" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B814" s="3"/>
+      <c r="C814" s="3">
+        <v>111</v>
+      </c>
+      <c r="D814" s="3">
+        <v>5682949548</v>
+      </c>
+      <c r="E814" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F814" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="G814" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="H814" s="3"/>
+      <c r="I814" s="3"/>
+      <c r="J814" s="3"/>
+      <c r="K814" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L814" s="3"/>
+      <c r="M814" s="3"/>
+      <c r="N814" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2515709-6FBA-4FA0-B95E-D9BA06EEA8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B2EEAA1-CA54-464E-9113-7507A50C3C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4926" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5050" uniqueCount="2359">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -6914,6 +6914,189 @@
   </si>
   <si>
     <t>29.446413, -98.356384</t>
+  </si>
+  <si>
+    <t>05/04/26 11:59 EDT</t>
+  </si>
+  <si>
+    <t>05/04/26 12:20 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi S of Leon Valley TX</t>
+  </si>
+  <si>
+    <t>29.452372, -98.630844</t>
+  </si>
+  <si>
+    <t>05/04/26 12:53 EDT</t>
+  </si>
+  <si>
+    <t>29.582262, -97.999504</t>
+  </si>
+  <si>
+    <t>05/05/26 09:18 EDT</t>
+  </si>
+  <si>
+    <t>29.395767, -98.477190</t>
+  </si>
+  <si>
+    <t>05/05/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>05/05/26 10:11 EDT</t>
+  </si>
+  <si>
+    <t>05/05/26 09:22 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi SE of San Antonio TX</t>
+  </si>
+  <si>
+    <t>29.422876, -98.480870</t>
+  </si>
+  <si>
+    <t>05/05/26 10:35 EDT</t>
+  </si>
+  <si>
+    <t>23.6mi S of Marble Falls TX</t>
+  </si>
+  <si>
+    <t>30.236795, -98.385580</t>
+  </si>
+  <si>
+    <t>05/05/26 11:43 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi NW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.417720, -98.633970</t>
+  </si>
+  <si>
+    <t>05/05/26 11:48 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi NW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.403122, -98.628610</t>
+  </si>
+  <si>
+    <t>05/05/26 13:30 EDT</t>
+  </si>
+  <si>
+    <t>0.6mi E of Bulverde TX</t>
+  </si>
+  <si>
+    <t>29.776878, -98.426470</t>
+  </si>
+  <si>
+    <t>05/06/26 10:21 EDT</t>
+  </si>
+  <si>
+    <t>05/05/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi NE of Live Oak TX</t>
+  </si>
+  <si>
+    <t>29.563375, -98.329420</t>
+  </si>
+  <si>
+    <t>05/05/26 14:00 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.491732, -98.290510</t>
+  </si>
+  <si>
+    <t>05/06/26 10:20 EDT</t>
+  </si>
+  <si>
+    <t>05/06/26 08:32 EDT</t>
+  </si>
+  <si>
+    <t>4mi S of San Antonio TX</t>
+  </si>
+  <si>
+    <t>29.405853, -98.510254</t>
+  </si>
+  <si>
+    <t>05/06/26 09:19 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.477287, -98.254200</t>
+  </si>
+  <si>
+    <t>05/06/26 19:00 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi NE of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.070215, -99.103790</t>
+  </si>
+  <si>
+    <t>05/07/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>05/06/26 19:59 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi S of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.518969, -97.957770</t>
+  </si>
+  <si>
+    <t>05/06/26 20:13 EDT</t>
+  </si>
+  <si>
+    <t>29.582256, -97.999540</t>
+  </si>
+  <si>
+    <t>05/07/26 11:09 EDT</t>
+  </si>
+  <si>
+    <t>29.425335, -98.420290</t>
+  </si>
+  <si>
+    <t>05/08/26 10:09 EDT</t>
+  </si>
+  <si>
+    <t>05/07/26 12:52 EDT</t>
+  </si>
+  <si>
+    <t>29.420110, -98.438515</t>
+  </si>
+  <si>
+    <t>05/08/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>05/08/26 08:30 EDT</t>
+  </si>
+  <si>
+    <t>29.543219, -98.416890</t>
+  </si>
+  <si>
+    <t>05/08/26 10:50 EDT</t>
+  </si>
+  <si>
+    <t>0.5mi SW of Uvalde TX</t>
+  </si>
+  <si>
+    <t>29.210363, -99.783910</t>
+  </si>
+  <si>
+    <t>05/08/26 13:39 EDT</t>
+  </si>
+  <si>
+    <t>29.552715, -98.035780</t>
   </si>
 </sst>
 </file>
@@ -7275,7 +7458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N814"/>
+  <dimension ref="A1:N834"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -33111,7 +33294,9 @@
       <c r="A806" s="3" t="s">
         <v>2273</v>
       </c>
-      <c r="B806" s="3"/>
+      <c r="B806" s="3" t="s">
+        <v>1670</v>
+      </c>
       <c r="C806" s="3">
         <v>113</v>
       </c>
@@ -33373,15 +33558,661 @@
       <c r="G814" s="3" t="s">
         <v>2297</v>
       </c>
-      <c r="H814" s="3"/>
+      <c r="H814" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I814" s="3"/>
       <c r="J814" s="3"/>
       <c r="K814" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L814" s="3"/>
-      <c r="M814" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L814" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M814" s="3" t="s">
+        <v>2298</v>
+      </c>
       <c r="N814" s="3"/>
+    </row>
+    <row r="815" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A815" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B815" s="3"/>
+      <c r="C815" s="3">
+        <v>111</v>
+      </c>
+      <c r="D815" s="3">
+        <v>5694519919</v>
+      </c>
+      <c r="E815" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="G815" s="3" t="s">
+        <v>2301</v>
+      </c>
+      <c r="H815" s="3"/>
+      <c r="I815" s="3"/>
+      <c r="J815" s="3"/>
+      <c r="K815" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L815" s="3"/>
+      <c r="M815" s="3"/>
+      <c r="N815" s="3"/>
+    </row>
+    <row r="816" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A816" s="3" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B816" s="3"/>
+      <c r="C816" s="3">
+        <v>112</v>
+      </c>
+      <c r="D816" s="3">
+        <v>5694720098</v>
+      </c>
+      <c r="E816" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G816" s="3" t="s">
+        <v>2303</v>
+      </c>
+      <c r="H816" s="3"/>
+      <c r="I816" s="3"/>
+      <c r="J816" s="3"/>
+      <c r="K816" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L816" s="3"/>
+      <c r="M816" s="3"/>
+      <c r="N816" s="3"/>
+    </row>
+    <row r="817" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A817" s="3" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B817" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C817" s="3">
+        <v>110</v>
+      </c>
+      <c r="D817" s="3">
+        <v>5700070812</v>
+      </c>
+      <c r="E817" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G817" s="3" t="s">
+        <v>2305</v>
+      </c>
+      <c r="H817" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I817" s="3"/>
+      <c r="J817" s="3"/>
+      <c r="K817" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L817" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M817" s="3" t="s">
+        <v>2306</v>
+      </c>
+      <c r="N817" s="3" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="818" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A818" s="3" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B818" s="3"/>
+      <c r="C818" s="3">
+        <v>112</v>
+      </c>
+      <c r="D818" s="3">
+        <v>5700098209</v>
+      </c>
+      <c r="E818" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>2309</v>
+      </c>
+      <c r="G818" s="3" t="s">
+        <v>2310</v>
+      </c>
+      <c r="H818" s="3"/>
+      <c r="I818" s="3"/>
+      <c r="J818" s="3"/>
+      <c r="K818" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L818" s="3"/>
+      <c r="M818" s="3"/>
+      <c r="N818" s="3"/>
+    </row>
+    <row r="819" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A819" s="3" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B819" s="3"/>
+      <c r="C819" s="3">
+        <v>112</v>
+      </c>
+      <c r="D819" s="3">
+        <v>5700524922</v>
+      </c>
+      <c r="E819" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="G819" s="3" t="s">
+        <v>2313</v>
+      </c>
+      <c r="H819" s="3"/>
+      <c r="I819" s="3"/>
+      <c r="J819" s="3"/>
+      <c r="K819" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L819" s="3"/>
+      <c r="M819" s="3"/>
+      <c r="N819" s="3"/>
+    </row>
+    <row r="820" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A820" s="3" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B820" s="3"/>
+      <c r="C820" s="3">
+        <v>110</v>
+      </c>
+      <c r="D820" s="3">
+        <v>5701024357</v>
+      </c>
+      <c r="E820" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F820" s="3" t="s">
+        <v>2315</v>
+      </c>
+      <c r="G820" s="3" t="s">
+        <v>2316</v>
+      </c>
+      <c r="H820" s="3"/>
+      <c r="I820" s="3"/>
+      <c r="J820" s="3"/>
+      <c r="K820" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L820" s="3"/>
+      <c r="M820" s="3"/>
+      <c r="N820" s="3"/>
+    </row>
+    <row r="821" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A821" s="3" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B821" s="3"/>
+      <c r="C821" s="3">
+        <v>113</v>
+      </c>
+      <c r="D821" s="3">
+        <v>5701066096</v>
+      </c>
+      <c r="E821" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F821" s="3" t="s">
+        <v>2318</v>
+      </c>
+      <c r="G821" s="3" t="s">
+        <v>2319</v>
+      </c>
+      <c r="H821" s="3"/>
+      <c r="I821" s="3"/>
+      <c r="J821" s="3"/>
+      <c r="K821" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L821" s="3"/>
+      <c r="M821" s="3"/>
+      <c r="N821" s="3"/>
+    </row>
+    <row r="822" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A822" s="3" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B822" s="3"/>
+      <c r="C822" s="3">
+        <v>112</v>
+      </c>
+      <c r="D822" s="3">
+        <v>5701961591</v>
+      </c>
+      <c r="E822" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F822" s="3" t="s">
+        <v>2321</v>
+      </c>
+      <c r="G822" s="3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="H822" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I822" s="3"/>
+      <c r="J822" s="3"/>
+      <c r="K822" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L822" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M822" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="N822" s="3"/>
+    </row>
+    <row r="823" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A823" s="3" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B823" s="3"/>
+      <c r="C823" s="3">
+        <v>112</v>
+      </c>
+      <c r="D823" s="3">
+        <v>5702169165</v>
+      </c>
+      <c r="E823" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F823" s="3" t="s">
+        <v>2325</v>
+      </c>
+      <c r="G823" s="3" t="s">
+        <v>2326</v>
+      </c>
+      <c r="H823" s="3"/>
+      <c r="I823" s="3"/>
+      <c r="J823" s="3"/>
+      <c r="K823" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L823" s="3"/>
+      <c r="M823" s="3"/>
+      <c r="N823" s="3"/>
+    </row>
+    <row r="824" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A824" s="3" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B824" s="3"/>
+      <c r="C824" s="3">
+        <v>112</v>
+      </c>
+      <c r="D824" s="3">
+        <v>5702232806</v>
+      </c>
+      <c r="E824" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F824" s="3" t="s">
+        <v>2328</v>
+      </c>
+      <c r="G824" s="3" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H824" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I824" s="3"/>
+      <c r="J824" s="3"/>
+      <c r="K824" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L824" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M824" s="3" t="s">
+        <v>2330</v>
+      </c>
+      <c r="N824" s="3"/>
+    </row>
+    <row r="825" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A825" s="3" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B825" s="3"/>
+      <c r="C825" s="3">
+        <v>112</v>
+      </c>
+      <c r="D825" s="3">
+        <v>5706879874</v>
+      </c>
+      <c r="E825" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F825" s="3" t="s">
+        <v>2332</v>
+      </c>
+      <c r="G825" s="3" t="s">
+        <v>2333</v>
+      </c>
+      <c r="H825" s="3"/>
+      <c r="I825" s="3"/>
+      <c r="J825" s="3"/>
+      <c r="K825" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L825" s="3"/>
+      <c r="M825" s="3"/>
+      <c r="N825" s="3"/>
+    </row>
+    <row r="826" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A826" s="3" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B826" s="3"/>
+      <c r="C826" s="3">
+        <v>113</v>
+      </c>
+      <c r="D826" s="3">
+        <v>5707125309</v>
+      </c>
+      <c r="E826" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F826" s="3" t="s">
+        <v>2335</v>
+      </c>
+      <c r="G826" s="3" t="s">
+        <v>2336</v>
+      </c>
+      <c r="H826" s="3"/>
+      <c r="I826" s="3"/>
+      <c r="J826" s="3"/>
+      <c r="K826" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L826" s="3"/>
+      <c r="M826" s="3"/>
+      <c r="N826" s="3"/>
+    </row>
+    <row r="827" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A827" s="3" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B827" s="3"/>
+      <c r="C827" s="3">
+        <v>111</v>
+      </c>
+      <c r="D827" s="3">
+        <v>5711692700</v>
+      </c>
+      <c r="E827" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F827" s="3" t="s">
+        <v>2338</v>
+      </c>
+      <c r="G827" s="3" t="s">
+        <v>2339</v>
+      </c>
+      <c r="H827" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I827" s="3"/>
+      <c r="J827" s="3"/>
+      <c r="K827" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L827" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M827" s="3" t="s">
+        <v>2340</v>
+      </c>
+      <c r="N827" s="3"/>
+    </row>
+    <row r="828" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A828" s="3" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B828" s="3"/>
+      <c r="C828" s="3">
+        <v>112</v>
+      </c>
+      <c r="D828" s="3">
+        <v>5719694252</v>
+      </c>
+      <c r="E828" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F828" s="3" t="s">
+        <v>2342</v>
+      </c>
+      <c r="G828" s="3" t="s">
+        <v>2343</v>
+      </c>
+      <c r="H828" s="3"/>
+      <c r="I828" s="3"/>
+      <c r="J828" s="3"/>
+      <c r="K828" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L828" s="3"/>
+      <c r="M828" s="3"/>
+      <c r="N828" s="3"/>
+    </row>
+    <row r="829" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A829" s="3" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B829" s="3"/>
+      <c r="C829" s="3">
+        <v>112</v>
+      </c>
+      <c r="D829" s="3">
+        <v>5712088807</v>
+      </c>
+      <c r="E829" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F829" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G829" s="3" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H829" s="3"/>
+      <c r="I829" s="3"/>
+      <c r="J829" s="3"/>
+      <c r="K829" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L829" s="3"/>
+      <c r="M829" s="3"/>
+      <c r="N829" s="3"/>
+    </row>
+    <row r="830" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A830" s="3" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B830" s="3"/>
+      <c r="C830" s="3">
+        <v>111</v>
+      </c>
+      <c r="D830" s="3">
+        <v>5714812744</v>
+      </c>
+      <c r="E830" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F830" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G830" s="3" t="s">
+        <v>2347</v>
+      </c>
+      <c r="H830" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I830" s="3"/>
+      <c r="J830" s="3"/>
+      <c r="K830" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L830" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M830" s="3" t="s">
+        <v>2348</v>
+      </c>
+      <c r="N830" s="3"/>
+    </row>
+    <row r="831" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A831" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B831" s="3"/>
+      <c r="C831" s="3">
+        <v>111</v>
+      </c>
+      <c r="D831" s="3">
+        <v>5715651809</v>
+      </c>
+      <c r="E831" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F831" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G831" s="3" t="s">
+        <v>2350</v>
+      </c>
+      <c r="H831" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I831" s="3"/>
+      <c r="J831" s="3"/>
+      <c r="K831" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L831" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M831" s="3" t="s">
+        <v>2351</v>
+      </c>
+      <c r="N831" s="3"/>
+    </row>
+    <row r="832" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A832" s="3" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B832" s="3"/>
+      <c r="C832" s="3">
+        <v>111</v>
+      </c>
+      <c r="D832" s="3">
+        <v>5720910223</v>
+      </c>
+      <c r="E832" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F832" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G832" s="3" t="s">
+        <v>2353</v>
+      </c>
+      <c r="H832" s="3"/>
+      <c r="I832" s="3"/>
+      <c r="J832" s="3"/>
+      <c r="K832" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L832" s="3"/>
+      <c r="M832" s="3"/>
+      <c r="N832" s="3"/>
+    </row>
+    <row r="833" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A833" s="3" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B833" s="3"/>
+      <c r="C833" s="3">
+        <v>111</v>
+      </c>
+      <c r="D833" s="3">
+        <v>5721696791</v>
+      </c>
+      <c r="E833" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F833" s="3" t="s">
+        <v>2355</v>
+      </c>
+      <c r="G833" s="3" t="s">
+        <v>2356</v>
+      </c>
+      <c r="H833" s="3"/>
+      <c r="I833" s="3"/>
+      <c r="J833" s="3"/>
+      <c r="K833" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L833" s="3"/>
+      <c r="M833" s="3"/>
+      <c r="N833" s="3"/>
+    </row>
+    <row r="834" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A834" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B834" s="3"/>
+      <c r="C834" s="3">
+        <v>112</v>
+      </c>
+      <c r="D834" s="3">
+        <v>5723077123</v>
+      </c>
+      <c r="E834" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F834" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="G834" s="3" t="s">
+        <v>2358</v>
+      </c>
+      <c r="H834" s="3"/>
+      <c r="I834" s="3"/>
+      <c r="J834" s="3"/>
+      <c r="K834" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L834" s="3"/>
+      <c r="M834" s="3"/>
+      <c r="N834" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B2EEAA1-CA54-464E-9113-7507A50C3C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CFCEE20-B3E6-4805-8A93-4D38117A3F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5050" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5374" uniqueCount="2507">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -7093,10 +7093,454 @@
     <t>29.210363, -99.783910</t>
   </si>
   <si>
+    <t>05/11/26 11:56 EDT</t>
+  </si>
+  <si>
     <t>05/08/26 13:39 EDT</t>
   </si>
   <si>
     <t>29.552715, -98.035780</t>
+  </si>
+  <si>
+    <t>05/08/26 15:59 EDT</t>
+  </si>
+  <si>
+    <t>29.506428, -98.132095</t>
+  </si>
+  <si>
+    <t>05/09/26 14:29 EDT</t>
+  </si>
+  <si>
+    <t>29.515743, -98.289370</t>
+  </si>
+  <si>
+    <t>05/09/26 14:30 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi NE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.526680, -98.296570</t>
+  </si>
+  <si>
+    <t>05/09/26 16:20 EDT</t>
+  </si>
+  <si>
+    <t>14.9mi E of Kerrville TX</t>
+  </si>
+  <si>
+    <t>29.974445, -98.894960</t>
+  </si>
+  <si>
+    <t>05/09/26 18:03 EDT</t>
+  </si>
+  <si>
+    <t>U-TURN</t>
+  </si>
+  <si>
+    <t>7.2mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.379068, -98.312225</t>
+  </si>
+  <si>
+    <t>05/11/26 10:54 EDT</t>
+  </si>
+  <si>
+    <t>29.458532, -98.316600</t>
+  </si>
+  <si>
+    <t>05/11/26 11:26 EDT</t>
+  </si>
+  <si>
+    <t>29.465158, -98.294850</t>
+  </si>
+  <si>
+    <t>05/11/26 11:57 EDT</t>
+  </si>
+  <si>
+    <t>05/11/26 12:33 EDT</t>
+  </si>
+  <si>
+    <t>29.570820, -98.233010</t>
+  </si>
+  <si>
+    <t>05/11/26 17:30 EDT</t>
+  </si>
+  <si>
+    <t>05/11/26 13:01 EDT</t>
+  </si>
+  <si>
+    <t>29.582240, -97.999535</t>
+  </si>
+  <si>
+    <t>05/11/26 14:28 EDT</t>
+  </si>
+  <si>
+    <t>29.521297, -98.138870</t>
+  </si>
+  <si>
+    <t>05/11/26 14:52 EDT</t>
+  </si>
+  <si>
+    <t>29.470028, -98.277780</t>
+  </si>
+  <si>
+    <t>05/11/26 14:53 EDT</t>
+  </si>
+  <si>
+    <t>4.8mi N of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.630972, -98.228600</t>
+  </si>
+  <si>
+    <t>05/11/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>29.518278, -98.136880</t>
+  </si>
+  <si>
+    <t>05/11/26 15:04 EDT</t>
+  </si>
+  <si>
+    <t>29.519634, -98.137760</t>
+  </si>
+  <si>
+    <t>05/11/26 15:11 EDT</t>
+  </si>
+  <si>
+    <t>4mi N of Schertz TX</t>
+  </si>
+  <si>
+    <t>29.622494, -98.246250</t>
+  </si>
+  <si>
+    <t>05/12/26 14:24 EDT</t>
+  </si>
+  <si>
+    <t>29.550690, -98.098320</t>
+  </si>
+  <si>
+    <t>05/12/26 14:34 EDT</t>
+  </si>
+  <si>
+    <t>5.5mi E of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.608444, -97.878100</t>
+  </si>
+  <si>
+    <t>05/13/26 09:43 EDT</t>
+  </si>
+  <si>
+    <t>05/13/26 09:50 EDT</t>
+  </si>
+  <si>
+    <t>05/12/26 14:36 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi E of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.603935, -97.897640</t>
+  </si>
+  <si>
+    <t>05/13/26 09:44 EDT</t>
+  </si>
+  <si>
+    <t>05/12/26 15:50 EDT</t>
+  </si>
+  <si>
+    <t>7.4mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.534548, -98.093000</t>
+  </si>
+  <si>
+    <t>05/12/26 15:53 EDT</t>
+  </si>
+  <si>
+    <t>29.526619, -98.119865</t>
+  </si>
+  <si>
+    <t>05/12/26 15:58 EDT</t>
+  </si>
+  <si>
+    <t>15mi S of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.184513, -98.706566</t>
+  </si>
+  <si>
+    <t>05/12/26 17:24 EDT</t>
+  </si>
+  <si>
+    <t>3mi E of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.385307, -98.568410</t>
+  </si>
+  <si>
+    <t>05/12/26 18:08 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi S of Terrell Hills TX</t>
+  </si>
+  <si>
+    <t>29.438940, -98.460690</t>
+  </si>
+  <si>
+    <t>05/12/26 18:29 EDT</t>
+  </si>
+  <si>
+    <t>24.6mi SE of Floresville TX</t>
+  </si>
+  <si>
+    <t>28.879744, -97.893270</t>
+  </si>
+  <si>
+    <t>05/13/26 10:21 EDT</t>
+  </si>
+  <si>
+    <t>29.471212, -98.274086</t>
+  </si>
+  <si>
+    <t>05/14/26 10:20 EDT</t>
+  </si>
+  <si>
+    <t>05/13/26 11:59 EDT</t>
+  </si>
+  <si>
+    <t>29.503050, -98.181620</t>
+  </si>
+  <si>
+    <t>05/13/26 13:58 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi SW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.347176, -98.660330</t>
+  </si>
+  <si>
+    <t>05/13/26 14:00 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi SW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.346983, -98.653770</t>
+  </si>
+  <si>
+    <t>05/14/26 10:21 EDT</t>
+  </si>
+  <si>
+    <t>05/13/26 14:58 EDT</t>
+  </si>
+  <si>
+    <t>39.7mi N of Laredo TX</t>
+  </si>
+  <si>
+    <t>28.120417, -99.330260</t>
+  </si>
+  <si>
+    <t>05/13/26 15:06 EDT</t>
+  </si>
+  <si>
+    <t>31.2mi N of Laredo TX</t>
+  </si>
+  <si>
+    <t>28.000696, -99.367170</t>
+  </si>
+  <si>
+    <t>05/13/26 15:12 EDT</t>
+  </si>
+  <si>
+    <t>24.7mi N of Laredo TX</t>
+  </si>
+  <si>
+    <t>27.910208, -99.393555</t>
+  </si>
+  <si>
+    <t>05/13/26 15:31 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi N of Laredo TX</t>
+  </si>
+  <si>
+    <t>27.629047, -99.489840</t>
+  </si>
+  <si>
+    <t>05/13/26 16:19 EDT</t>
+  </si>
+  <si>
+    <t>5.5mi NW of Laredo TX</t>
+  </si>
+  <si>
+    <t>27.633259, -99.530080</t>
+  </si>
+  <si>
+    <t>05/13/26 16:29 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi N of Leon Valley TX</t>
+  </si>
+  <si>
+    <t>29.560045, -98.590020</t>
+  </si>
+  <si>
+    <t>05/13/26 16:40 EDT</t>
+  </si>
+  <si>
+    <t>29.540281, -98.072750</t>
+  </si>
+  <si>
+    <t>05/13/26 18:05 EDT</t>
+  </si>
+  <si>
+    <t>29.421415, -98.360770</t>
+  </si>
+  <si>
+    <t>05/13/26 18:13 EDT</t>
+  </si>
+  <si>
+    <t>29.398613, -98.374306</t>
+  </si>
+  <si>
+    <t>05/14/26 10:29 EDT</t>
+  </si>
+  <si>
+    <t>29.562902, -98.034700</t>
+  </si>
+  <si>
+    <t>05/14/26 14:18 EDT</t>
+  </si>
+  <si>
+    <t>8.4mi NW of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.755255, -98.239880</t>
+  </si>
+  <si>
+    <t>05/14/26 14:29 EDT</t>
+  </si>
+  <si>
+    <t>2.8mi W of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.714447, -98.157610</t>
+  </si>
+  <si>
+    <t>05/14/26 15:06 EDT</t>
+  </si>
+  <si>
+    <t>29.582523, -97.998400</t>
+  </si>
+  <si>
+    <t>05/15/26 10:20 EDT</t>
+  </si>
+  <si>
+    <t>05/14/26 17:15 EDT</t>
+  </si>
+  <si>
+    <t>Mark  Franklin</t>
+  </si>
+  <si>
+    <t>29.507807, -98.169590</t>
+  </si>
+  <si>
+    <t>05/15/26 07:37 EDT</t>
+  </si>
+  <si>
+    <t>4.8mi SW of Luling TX</t>
+  </si>
+  <si>
+    <t>29.641094, -97.711280</t>
+  </si>
+  <si>
+    <t>05/15/26 07:52 EDT</t>
+  </si>
+  <si>
+    <t>29.497713, -98.195690</t>
+  </si>
+  <si>
+    <t>05/15/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi S of Schertz TX</t>
+  </si>
+  <si>
+    <t>29.523617, -98.246270</t>
+  </si>
+  <si>
+    <t>05/15/26 10:07 EDT</t>
+  </si>
+  <si>
+    <t>2mi N of Windcrest TX</t>
+  </si>
+  <si>
+    <t>29.542685, -98.374370</t>
+  </si>
+  <si>
+    <t>05/15/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>29.516653, -98.396480</t>
+  </si>
+  <si>
+    <t>05/15/26 14:19 EDT</t>
+  </si>
+  <si>
+    <t>29.460815, -98.311005</t>
+  </si>
+  <si>
+    <t>05/15/26 14:22 EDT</t>
+  </si>
+  <si>
+    <t>29.421198, -98.260710</t>
+  </si>
+  <si>
+    <t>05/15/26 15:19 EDT</t>
+  </si>
+  <si>
+    <t>29.468270, -98.282640</t>
+  </si>
+  <si>
+    <t>05/15/26 16:52 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi SE of Luling TX</t>
+  </si>
+  <si>
+    <t>29.642353, -97.586600</t>
+  </si>
+  <si>
+    <t>05/15/26 17:17 EDT</t>
+  </si>
+  <si>
+    <t>8.5mi SE of Gonzales TX</t>
+  </si>
+  <si>
+    <t>29.408060, -97.373620</t>
+  </si>
+  <si>
+    <t>05/15/26 19:35 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi SW of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.433424, -98.405500</t>
+  </si>
+  <si>
+    <t>05/16/26 16:18 EDT</t>
+  </si>
+  <si>
+    <t>6.1mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.471079, -98.217660</t>
   </si>
 </sst>
 </file>
@@ -7458,23 +7902,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N834"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N888"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -7518,7 +7962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
@@ -7548,7 +7992,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -7578,7 +8022,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -7608,7 +8052,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -7638,7 +8082,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -7668,7 +8112,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -7706,7 +8150,7 @@
       </c>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>41</v>
       </c>
@@ -7736,7 +8180,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
@@ -7766,7 +8210,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>49</v>
       </c>
@@ -7796,7 +8240,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>52</v>
       </c>
@@ -7826,7 +8270,7 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>56</v>
       </c>
@@ -7856,7 +8300,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
@@ -7886,7 +8330,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>59</v>
       </c>
@@ -7924,7 +8368,7 @@
       </c>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>64</v>
       </c>
@@ -7954,7 +8398,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>67</v>
       </c>
@@ -7984,7 +8428,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>70</v>
       </c>
@@ -8014,7 +8458,7 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>70</v>
       </c>
@@ -8044,7 +8488,7 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>76</v>
       </c>
@@ -8074,7 +8518,7 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
@@ -8112,7 +8556,7 @@
       </c>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>83</v>
       </c>
@@ -8142,7 +8586,7 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>86</v>
       </c>
@@ -8172,7 +8616,7 @@
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>88</v>
       </c>
@@ -8202,7 +8646,7 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>90</v>
       </c>
@@ -8232,7 +8676,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>93</v>
       </c>
@@ -8262,7 +8706,7 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>96</v>
       </c>
@@ -8300,7 +8744,7 @@
       </c>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>100</v>
       </c>
@@ -8330,7 +8774,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>103</v>
       </c>
@@ -8360,7 +8804,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>106</v>
       </c>
@@ -8398,7 +8842,7 @@
       </c>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>108</v>
       </c>
@@ -8434,7 +8878,7 @@
       </c>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>111</v>
       </c>
@@ -8464,7 +8908,7 @@
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>113</v>
       </c>
@@ -8494,7 +8938,7 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>116</v>
       </c>
@@ -8524,7 +8968,7 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>119</v>
       </c>
@@ -8562,7 +9006,7 @@
       </c>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>122</v>
       </c>
@@ -8592,7 +9036,7 @@
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>125</v>
       </c>
@@ -8630,7 +9074,7 @@
       </c>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
@@ -8666,7 +9110,7 @@
       </c>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>131</v>
       </c>
@@ -8696,7 +9140,7 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>135</v>
       </c>
@@ -8726,7 +9170,7 @@
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>138</v>
       </c>
@@ -8756,7 +9200,7 @@
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>141</v>
       </c>
@@ -8786,7 +9230,7 @@
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>144</v>
       </c>
@@ -8824,7 +9268,7 @@
       </c>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>146</v>
       </c>
@@ -8854,7 +9298,7 @@
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>150</v>
       </c>
@@ -8890,7 +9334,7 @@
       </c>
       <c r="N46" s="3"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>150</v>
       </c>
@@ -8928,7 +9372,7 @@
       </c>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>154</v>
       </c>
@@ -8958,7 +9402,7 @@
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>157</v>
       </c>
@@ -8988,7 +9432,7 @@
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>160</v>
       </c>
@@ -9018,7 +9462,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>163</v>
       </c>
@@ -9054,7 +9498,7 @@
       </c>
       <c r="N51" s="3"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>167</v>
       </c>
@@ -9084,7 +9528,7 @@
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>170</v>
       </c>
@@ -9114,7 +9558,7 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>172</v>
       </c>
@@ -9150,7 +9594,7 @@
       </c>
       <c r="N54" s="3"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>175</v>
       </c>
@@ -9186,7 +9630,7 @@
       </c>
       <c r="N55" s="3"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>179</v>
       </c>
@@ -9222,7 +9666,7 @@
       </c>
       <c r="N56" s="3"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>182</v>
       </c>
@@ -9260,7 +9704,7 @@
       </c>
       <c r="N57" s="3"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>186</v>
       </c>
@@ -9290,7 +9734,7 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>188</v>
       </c>
@@ -9320,7 +9764,7 @@
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>191</v>
       </c>
@@ -9350,7 +9794,7 @@
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>194</v>
       </c>
@@ -9388,7 +9832,7 @@
       </c>
       <c r="N61" s="3"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>197</v>
       </c>
@@ -9418,7 +9862,7 @@
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>200</v>
       </c>
@@ -9456,7 +9900,7 @@
       </c>
       <c r="N63" s="3"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>204</v>
       </c>
@@ -9486,7 +9930,7 @@
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>207</v>
       </c>
@@ -9516,7 +9960,7 @@
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>209</v>
       </c>
@@ -9554,7 +9998,7 @@
       </c>
       <c r="N66" s="3"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>213</v>
       </c>
@@ -9584,7 +10028,7 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>215</v>
       </c>
@@ -9614,7 +10058,7 @@
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>217</v>
       </c>
@@ -9652,7 +10096,7 @@
       </c>
       <c r="N69" s="3"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>220</v>
       </c>
@@ -9688,7 +10132,7 @@
       </c>
       <c r="N70" s="3"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>224</v>
       </c>
@@ -9718,7 +10162,7 @@
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>227</v>
       </c>
@@ -9756,7 +10200,7 @@
       </c>
       <c r="N72" s="3"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>229</v>
       </c>
@@ -9794,7 +10238,7 @@
       </c>
       <c r="N73" s="3"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>232</v>
       </c>
@@ -9824,7 +10268,7 @@
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>235</v>
       </c>
@@ -9854,7 +10298,7 @@
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>238</v>
       </c>
@@ -9884,7 +10328,7 @@
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>240</v>
       </c>
@@ -9914,7 +10358,7 @@
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>243</v>
       </c>
@@ -9944,7 +10388,7 @@
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>245</v>
       </c>
@@ -9974,7 +10418,7 @@
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>248</v>
       </c>
@@ -10004,7 +10448,7 @@
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>251</v>
       </c>
@@ -10034,7 +10478,7 @@
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>253</v>
       </c>
@@ -10070,7 +10514,7 @@
       </c>
       <c r="N82" s="3"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>257</v>
       </c>
@@ -10100,7 +10544,7 @@
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>260</v>
       </c>
@@ -10130,7 +10574,7 @@
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>262</v>
       </c>
@@ -10160,7 +10604,7 @@
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>264</v>
       </c>
@@ -10190,7 +10634,7 @@
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>267</v>
       </c>
@@ -10220,7 +10664,7 @@
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>270</v>
       </c>
@@ -10250,7 +10694,7 @@
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>273</v>
       </c>
@@ -10288,7 +10732,7 @@
       </c>
       <c r="N89" s="3"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>277</v>
       </c>
@@ -10318,7 +10762,7 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>280</v>
       </c>
@@ -10354,7 +10798,7 @@
       </c>
       <c r="N91" s="3"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>283</v>
       </c>
@@ -10392,7 +10836,7 @@
       </c>
       <c r="N92" s="3"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>286</v>
       </c>
@@ -10422,7 +10866,7 @@
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>289</v>
       </c>
@@ -10452,7 +10896,7 @@
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>292</v>
       </c>
@@ -10482,7 +10926,7 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>294</v>
       </c>
@@ -10512,7 +10956,7 @@
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>297</v>
       </c>
@@ -10542,7 +10986,7 @@
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>300</v>
       </c>
@@ -10572,7 +11016,7 @@
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>303</v>
       </c>
@@ -10608,7 +11052,7 @@
       </c>
       <c r="N99" s="3"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>306</v>
       </c>
@@ -10638,7 +11082,7 @@
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>308</v>
       </c>
@@ -10668,7 +11112,7 @@
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>311</v>
       </c>
@@ -10704,7 +11148,7 @@
       </c>
       <c r="N102" s="3"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>313</v>
       </c>
@@ -10734,7 +11178,7 @@
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>316</v>
       </c>
@@ -10764,7 +11208,7 @@
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>319</v>
       </c>
@@ -10794,7 +11238,7 @@
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>321</v>
       </c>
@@ -10824,7 +11268,7 @@
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>323</v>
       </c>
@@ -10854,7 +11298,7 @@
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>325</v>
       </c>
@@ -10884,7 +11328,7 @@
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>327</v>
       </c>
@@ -10920,7 +11364,7 @@
       </c>
       <c r="N109" s="3"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>331</v>
       </c>
@@ -10950,7 +11394,7 @@
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>334</v>
       </c>
@@ -10984,7 +11428,7 @@
       </c>
       <c r="N111" s="3"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>337</v>
       </c>
@@ -11014,7 +11458,7 @@
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>340</v>
       </c>
@@ -11050,7 +11494,7 @@
       </c>
       <c r="N113" s="3"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>340</v>
       </c>
@@ -11086,7 +11530,7 @@
       </c>
       <c r="N114" s="3"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>344</v>
       </c>
@@ -11116,7 +11560,7 @@
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>346</v>
       </c>
@@ -11146,7 +11590,7 @@
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>348</v>
       </c>
@@ -11176,7 +11620,7 @@
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>351</v>
       </c>
@@ -11206,7 +11650,7 @@
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>354</v>
       </c>
@@ -11236,7 +11680,7 @@
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>357</v>
       </c>
@@ -11266,7 +11710,7 @@
       <c r="M120" s="3"/>
       <c r="N120" s="3"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>360</v>
       </c>
@@ -11302,7 +11746,7 @@
       </c>
       <c r="N121" s="3"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>364</v>
       </c>
@@ -11332,7 +11776,7 @@
       <c r="M122" s="3"/>
       <c r="N122" s="3"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>367</v>
       </c>
@@ -11362,7 +11806,7 @@
       <c r="M123" s="3"/>
       <c r="N123" s="3"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>370</v>
       </c>
@@ -11392,7 +11836,7 @@
       <c r="M124" s="3"/>
       <c r="N124" s="3"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>373</v>
       </c>
@@ -11422,7 +11866,7 @@
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>375</v>
       </c>
@@ -11452,7 +11896,7 @@
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>378</v>
       </c>
@@ -11482,7 +11926,7 @@
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>381</v>
       </c>
@@ -11512,7 +11956,7 @@
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>383</v>
       </c>
@@ -11542,7 +11986,7 @@
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>386</v>
       </c>
@@ -11572,7 +12016,7 @@
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>388</v>
       </c>
@@ -11602,7 +12046,7 @@
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>391</v>
       </c>
@@ -11632,7 +12076,7 @@
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>393</v>
       </c>
@@ -11662,7 +12106,7 @@
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>395</v>
       </c>
@@ -11692,7 +12136,7 @@
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>398</v>
       </c>
@@ -11728,7 +12172,7 @@
       </c>
       <c r="N135" s="3"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>402</v>
       </c>
@@ -11758,7 +12202,7 @@
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>404</v>
       </c>
@@ -11788,7 +12232,7 @@
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>407</v>
       </c>
@@ -11818,7 +12262,7 @@
       <c r="M138" s="3"/>
       <c r="N138" s="3"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>409</v>
       </c>
@@ -11848,7 +12292,7 @@
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>411</v>
       </c>
@@ -11878,7 +12322,7 @@
       <c r="M140" s="3"/>
       <c r="N140" s="3"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>415</v>
       </c>
@@ -11908,7 +12352,7 @@
       <c r="M141" s="3"/>
       <c r="N141" s="3"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>417</v>
       </c>
@@ -11944,7 +12388,7 @@
       </c>
       <c r="N142" s="3"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>421</v>
       </c>
@@ -11974,7 +12418,7 @@
       <c r="M143" s="3"/>
       <c r="N143" s="3"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>424</v>
       </c>
@@ -12004,7 +12448,7 @@
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>427</v>
       </c>
@@ -12034,7 +12478,7 @@
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>431</v>
       </c>
@@ -12072,7 +12516,7 @@
       </c>
       <c r="N146" s="3"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>435</v>
       </c>
@@ -12102,7 +12546,7 @@
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>438</v>
       </c>
@@ -12140,7 +12584,7 @@
       </c>
       <c r="N148" s="3"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>441</v>
       </c>
@@ -12170,7 +12614,7 @@
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>444</v>
       </c>
@@ -12206,7 +12650,7 @@
       </c>
       <c r="N150" s="3"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>447</v>
       </c>
@@ -12236,7 +12680,7 @@
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>450</v>
       </c>
@@ -12266,7 +12710,7 @@
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>452</v>
       </c>
@@ -12302,7 +12746,7 @@
       </c>
       <c r="N153" s="3"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>456</v>
       </c>
@@ -12332,7 +12776,7 @@
       <c r="M154" s="3"/>
       <c r="N154" s="3"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>459</v>
       </c>
@@ -12362,7 +12806,7 @@
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>462</v>
       </c>
@@ -12398,7 +12842,7 @@
       </c>
       <c r="N156" s="3"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>462</v>
       </c>
@@ -12428,7 +12872,7 @@
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>467</v>
       </c>
@@ -12466,7 +12910,7 @@
       </c>
       <c r="N158" s="3"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>471</v>
       </c>
@@ -12502,7 +12946,7 @@
       </c>
       <c r="N159" s="3"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>474</v>
       </c>
@@ -12532,7 +12976,7 @@
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>477</v>
       </c>
@@ -12562,7 +13006,7 @@
       <c r="M161" s="3"/>
       <c r="N161" s="3"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>480</v>
       </c>
@@ -12592,7 +13036,7 @@
       <c r="M162" s="3"/>
       <c r="N162" s="3"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>482</v>
       </c>
@@ -12630,7 +13074,7 @@
       </c>
       <c r="N163" s="3"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>486</v>
       </c>
@@ -12660,7 +13104,7 @@
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>489</v>
       </c>
@@ -12690,7 +13134,7 @@
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>492</v>
       </c>
@@ -12720,7 +13164,7 @@
       <c r="M166" s="3"/>
       <c r="N166" s="3"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>494</v>
       </c>
@@ -12750,7 +13194,7 @@
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>496</v>
       </c>
@@ -12786,7 +13230,7 @@
       </c>
       <c r="N168" s="3"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>500</v>
       </c>
@@ -12816,7 +13260,7 @@
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>502</v>
       </c>
@@ -12846,7 +13290,7 @@
       <c r="M170" s="3"/>
       <c r="N170" s="3"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>505</v>
       </c>
@@ -12876,7 +13320,7 @@
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>507</v>
       </c>
@@ -12906,7 +13350,7 @@
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>510</v>
       </c>
@@ -12936,7 +13380,7 @@
       <c r="M173" s="3"/>
       <c r="N173" s="3"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>513</v>
       </c>
@@ -12966,7 +13410,7 @@
       <c r="M174" s="3"/>
       <c r="N174" s="3"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>515</v>
       </c>
@@ -13002,7 +13446,7 @@
       </c>
       <c r="N175" s="3"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>518</v>
       </c>
@@ -13040,7 +13484,7 @@
       </c>
       <c r="N176" s="3"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>522</v>
       </c>
@@ -13070,7 +13514,7 @@
       <c r="M177" s="3"/>
       <c r="N177" s="3"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>524</v>
       </c>
@@ -13100,7 +13544,7 @@
       <c r="M178" s="3"/>
       <c r="N178" s="3"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>526</v>
       </c>
@@ -13136,7 +13580,7 @@
       </c>
       <c r="N179" s="3"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>529</v>
       </c>
@@ -13166,7 +13610,7 @@
       <c r="M180" s="3"/>
       <c r="N180" s="3"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>532</v>
       </c>
@@ -13196,7 +13640,7 @@
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>535</v>
       </c>
@@ -13226,7 +13670,7 @@
       <c r="M182" s="3"/>
       <c r="N182" s="3"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>538</v>
       </c>
@@ -13256,7 +13700,7 @@
       <c r="M183" s="3"/>
       <c r="N183" s="3"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>541</v>
       </c>
@@ -13294,7 +13738,7 @@
       </c>
       <c r="N184" s="3"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>545</v>
       </c>
@@ -13324,7 +13768,7 @@
       <c r="M185" s="3"/>
       <c r="N185" s="3"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>548</v>
       </c>
@@ -13360,7 +13804,7 @@
       </c>
       <c r="N186" s="3"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>551</v>
       </c>
@@ -13390,7 +13834,7 @@
       <c r="M187" s="3"/>
       <c r="N187" s="3"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>554</v>
       </c>
@@ -13420,7 +13864,7 @@
       <c r="M188" s="3"/>
       <c r="N188" s="3"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>556</v>
       </c>
@@ -13450,7 +13894,7 @@
       <c r="M189" s="3"/>
       <c r="N189" s="3"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>559</v>
       </c>
@@ -13480,7 +13924,7 @@
       <c r="M190" s="3"/>
       <c r="N190" s="3"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>561</v>
       </c>
@@ -13516,7 +13960,7 @@
       </c>
       <c r="N191" s="3"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>565</v>
       </c>
@@ -13546,7 +13990,7 @@
       <c r="M192" s="3"/>
       <c r="N192" s="3"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>568</v>
       </c>
@@ -13576,7 +14020,7 @@
       <c r="M193" s="3"/>
       <c r="N193" s="3"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>571</v>
       </c>
@@ -13606,7 +14050,7 @@
       <c r="M194" s="3"/>
       <c r="N194" s="3"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>573</v>
       </c>
@@ -13642,7 +14086,7 @@
       </c>
       <c r="N195" s="3"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>575</v>
       </c>
@@ -13672,7 +14116,7 @@
       <c r="M196" s="3"/>
       <c r="N196" s="3"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>578</v>
       </c>
@@ -13702,7 +14146,7 @@
       <c r="M197" s="3"/>
       <c r="N197" s="3"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>581</v>
       </c>
@@ -13732,7 +14176,7 @@
       <c r="M198" s="3"/>
       <c r="N198" s="3"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>584</v>
       </c>
@@ -13770,7 +14214,7 @@
       </c>
       <c r="N199" s="3"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>589</v>
       </c>
@@ -13800,7 +14244,7 @@
       <c r="M200" s="3"/>
       <c r="N200" s="3"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>592</v>
       </c>
@@ -13830,7 +14274,7 @@
       <c r="M201" s="3"/>
       <c r="N201" s="3"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>595</v>
       </c>
@@ -13868,7 +14312,7 @@
       </c>
       <c r="N202" s="3"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>599</v>
       </c>
@@ -13898,7 +14342,7 @@
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>601</v>
       </c>
@@ -13928,7 +14372,7 @@
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>603</v>
       </c>
@@ -13958,7 +14402,7 @@
       <c r="M205" s="3"/>
       <c r="N205" s="3"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>605</v>
       </c>
@@ -13988,7 +14432,7 @@
       <c r="M206" s="3"/>
       <c r="N206" s="3"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>607</v>
       </c>
@@ -14018,7 +14462,7 @@
       <c r="M207" s="3"/>
       <c r="N207" s="3"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>610</v>
       </c>
@@ -14048,7 +14492,7 @@
       <c r="M208" s="3"/>
       <c r="N208" s="3"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>613</v>
       </c>
@@ -14078,7 +14522,7 @@
       <c r="M209" s="3"/>
       <c r="N209" s="3"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>615</v>
       </c>
@@ -14108,7 +14552,7 @@
       <c r="M210" s="3"/>
       <c r="N210" s="3"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>617</v>
       </c>
@@ -14138,7 +14582,7 @@
       <c r="M211" s="3"/>
       <c r="N211" s="3"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>619</v>
       </c>
@@ -14168,7 +14612,7 @@
       <c r="M212" s="3"/>
       <c r="N212" s="3"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>622</v>
       </c>
@@ -14204,7 +14648,7 @@
       </c>
       <c r="N213" s="3"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>625</v>
       </c>
@@ -14234,7 +14678,7 @@
       <c r="M214" s="3"/>
       <c r="N214" s="3"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>628</v>
       </c>
@@ -14264,7 +14708,7 @@
       <c r="M215" s="3"/>
       <c r="N215" s="3"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>631</v>
       </c>
@@ -14294,7 +14738,7 @@
       <c r="M216" s="3"/>
       <c r="N216" s="3"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>634</v>
       </c>
@@ -14324,7 +14768,7 @@
       <c r="M217" s="3"/>
       <c r="N217" s="3"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>636</v>
       </c>
@@ -14360,7 +14804,7 @@
       </c>
       <c r="N218" s="3"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>636</v>
       </c>
@@ -14396,7 +14840,7 @@
       </c>
       <c r="N219" s="3"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>639</v>
       </c>
@@ -14426,7 +14870,7 @@
       <c r="M220" s="3"/>
       <c r="N220" s="3"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>641</v>
       </c>
@@ -14456,7 +14900,7 @@
       <c r="M221" s="3"/>
       <c r="N221" s="3"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>644</v>
       </c>
@@ -14486,7 +14930,7 @@
       <c r="M222" s="3"/>
       <c r="N222" s="3"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>647</v>
       </c>
@@ -14516,7 +14960,7 @@
       <c r="M223" s="3"/>
       <c r="N223" s="3"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>649</v>
       </c>
@@ -14546,7 +14990,7 @@
       <c r="M224" s="3"/>
       <c r="N224" s="3"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>651</v>
       </c>
@@ -14576,7 +15020,7 @@
       <c r="M225" s="3"/>
       <c r="N225" s="3"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>654</v>
       </c>
@@ -14606,7 +15050,7 @@
       <c r="M226" s="3"/>
       <c r="N226" s="3"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>657</v>
       </c>
@@ -14636,7 +15080,7 @@
       <c r="M227" s="3"/>
       <c r="N227" s="3"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>660</v>
       </c>
@@ -14672,7 +15116,7 @@
       </c>
       <c r="N228" s="3"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>663</v>
       </c>
@@ -14702,7 +15146,7 @@
       <c r="M229" s="3"/>
       <c r="N229" s="3"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>666</v>
       </c>
@@ -14732,7 +15176,7 @@
       <c r="M230" s="3"/>
       <c r="N230" s="3"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>669</v>
       </c>
@@ -14762,7 +15206,7 @@
       <c r="M231" s="3"/>
       <c r="N231" s="3"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>671</v>
       </c>
@@ -14792,7 +15236,7 @@
       <c r="M232" s="3"/>
       <c r="N232" s="3"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>673</v>
       </c>
@@ -14828,7 +15272,7 @@
       </c>
       <c r="N233" s="3"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>675</v>
       </c>
@@ -14858,7 +15302,7 @@
       <c r="M234" s="3"/>
       <c r="N234" s="3"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>677</v>
       </c>
@@ -14888,7 +15332,7 @@
       <c r="M235" s="3"/>
       <c r="N235" s="3"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>680</v>
       </c>
@@ -14924,7 +15368,7 @@
       </c>
       <c r="N236" s="3"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>684</v>
       </c>
@@ -14954,7 +15398,7 @@
       <c r="M237" s="3"/>
       <c r="N237" s="3"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>687</v>
       </c>
@@ -14984,7 +15428,7 @@
       <c r="M238" s="3"/>
       <c r="N238" s="3"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>690</v>
       </c>
@@ -15014,7 +15458,7 @@
       <c r="M239" s="3"/>
       <c r="N239" s="3"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>692</v>
       </c>
@@ -15044,7 +15488,7 @@
       <c r="M240" s="3"/>
       <c r="N240" s="3"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>695</v>
       </c>
@@ -15074,7 +15518,7 @@
       <c r="M241" s="3"/>
       <c r="N241" s="3"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>697</v>
       </c>
@@ -15104,7 +15548,7 @@
       <c r="M242" s="3"/>
       <c r="N242" s="3"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>699</v>
       </c>
@@ -15134,7 +15578,7 @@
       <c r="M243" s="3"/>
       <c r="N243" s="3"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>701</v>
       </c>
@@ -15172,7 +15616,7 @@
       </c>
       <c r="N244" s="3"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>703</v>
       </c>
@@ -15210,7 +15654,7 @@
       </c>
       <c r="N245" s="3"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>707</v>
       </c>
@@ -15240,7 +15684,7 @@
       <c r="M246" s="3"/>
       <c r="N246" s="3"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>710</v>
       </c>
@@ -15270,7 +15714,7 @@
       <c r="M247" s="3"/>
       <c r="N247" s="3"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>713</v>
       </c>
@@ -15308,7 +15752,7 @@
       </c>
       <c r="N248" s="3"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>717</v>
       </c>
@@ -15338,7 +15782,7 @@
       <c r="M249" s="3"/>
       <c r="N249" s="3"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>719</v>
       </c>
@@ -15368,7 +15812,7 @@
       <c r="M250" s="3"/>
       <c r="N250" s="3"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>722</v>
       </c>
@@ -15398,7 +15842,7 @@
       <c r="M251" s="3"/>
       <c r="N251" s="3"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
         <v>724</v>
       </c>
@@ -15428,7 +15872,7 @@
       <c r="M252" s="3"/>
       <c r="N252" s="3"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>726</v>
       </c>
@@ -15458,7 +15902,7 @@
       <c r="M253" s="3"/>
       <c r="N253" s="3"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>728</v>
       </c>
@@ -15488,7 +15932,7 @@
       <c r="M254" s="3"/>
       <c r="N254" s="3"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>730</v>
       </c>
@@ -15518,7 +15962,7 @@
       <c r="M255" s="3"/>
       <c r="N255" s="3"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>733</v>
       </c>
@@ -15548,7 +15992,7 @@
       <c r="M256" s="3"/>
       <c r="N256" s="3"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>735</v>
       </c>
@@ -15578,7 +16022,7 @@
       <c r="M257" s="3"/>
       <c r="N257" s="3"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>738</v>
       </c>
@@ -15608,7 +16052,7 @@
       <c r="M258" s="3"/>
       <c r="N258" s="3"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
         <v>740</v>
       </c>
@@ -15638,7 +16082,7 @@
       <c r="M259" s="3"/>
       <c r="N259" s="3"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
         <v>743</v>
       </c>
@@ -15676,7 +16120,7 @@
       </c>
       <c r="N260" s="3"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
         <v>747</v>
       </c>
@@ -15706,7 +16150,7 @@
       <c r="M261" s="3"/>
       <c r="N261" s="3"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>750</v>
       </c>
@@ -15736,7 +16180,7 @@
       <c r="M262" s="3"/>
       <c r="N262" s="3"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
         <v>753</v>
       </c>
@@ -15766,7 +16210,7 @@
       <c r="M263" s="3"/>
       <c r="N263" s="3"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>756</v>
       </c>
@@ -15804,7 +16248,7 @@
       </c>
       <c r="N264" s="3"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
         <v>758</v>
       </c>
@@ -15834,7 +16278,7 @@
       <c r="M265" s="3"/>
       <c r="N265" s="3"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>760</v>
       </c>
@@ -15864,7 +16308,7 @@
       <c r="M266" s="3"/>
       <c r="N266" s="3"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
         <v>763</v>
       </c>
@@ -15902,7 +16346,7 @@
       </c>
       <c r="N267" s="3"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
         <v>766</v>
       </c>
@@ -15940,7 +16384,7 @@
       </c>
       <c r="N268" s="3"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>769</v>
       </c>
@@ -15970,7 +16414,7 @@
       <c r="M269" s="3"/>
       <c r="N269" s="3"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
         <v>772</v>
       </c>
@@ -16000,7 +16444,7 @@
       <c r="M270" s="3"/>
       <c r="N270" s="3"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
         <v>775</v>
       </c>
@@ -16030,7 +16474,7 @@
       <c r="M271" s="3"/>
       <c r="N271" s="3"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>778</v>
       </c>
@@ -16068,7 +16512,7 @@
       </c>
       <c r="N272" s="3"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
         <v>782</v>
       </c>
@@ -16106,7 +16550,7 @@
       </c>
       <c r="N273" s="3"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>785</v>
       </c>
@@ -16136,7 +16580,7 @@
       <c r="M274" s="3"/>
       <c r="N274" s="3"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
         <v>787</v>
       </c>
@@ -16174,7 +16618,7 @@
       </c>
       <c r="N275" s="3"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
         <v>790</v>
       </c>
@@ -16204,7 +16648,7 @@
       <c r="M276" s="3"/>
       <c r="N276" s="3"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
         <v>793</v>
       </c>
@@ -16234,7 +16678,7 @@
       <c r="M277" s="3"/>
       <c r="N277" s="3"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
         <v>795</v>
       </c>
@@ -16264,7 +16708,7 @@
       <c r="M278" s="3"/>
       <c r="N278" s="3"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
         <v>797</v>
       </c>
@@ -16302,7 +16746,7 @@
       </c>
       <c r="N279" s="3"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
         <v>801</v>
       </c>
@@ -16340,7 +16784,7 @@
       </c>
       <c r="N280" s="3"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
         <v>803</v>
       </c>
@@ -16370,7 +16814,7 @@
       <c r="M281" s="3"/>
       <c r="N281" s="3"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
         <v>805</v>
       </c>
@@ -16400,7 +16844,7 @@
       <c r="M282" s="3"/>
       <c r="N282" s="3"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
         <v>807</v>
       </c>
@@ -16438,7 +16882,7 @@
       </c>
       <c r="N283" s="3"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
         <v>810</v>
       </c>
@@ -16468,7 +16912,7 @@
       <c r="M284" s="3"/>
       <c r="N284" s="3"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
         <v>813</v>
       </c>
@@ -16498,7 +16942,7 @@
       <c r="M285" s="3"/>
       <c r="N285" s="3"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
         <v>815</v>
       </c>
@@ -16528,7 +16972,7 @@
       <c r="M286" s="3"/>
       <c r="N286" s="3"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
         <v>818</v>
       </c>
@@ -16558,7 +17002,7 @@
       <c r="M287" s="3"/>
       <c r="N287" s="3"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
         <v>820</v>
       </c>
@@ -16596,7 +17040,7 @@
       </c>
       <c r="N288" s="3"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
         <v>823</v>
       </c>
@@ -16626,7 +17070,7 @@
       <c r="M289" s="3"/>
       <c r="N289" s="3"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
         <v>825</v>
       </c>
@@ -16656,7 +17100,7 @@
       <c r="M290" s="3"/>
       <c r="N290" s="3"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
         <v>828</v>
       </c>
@@ -16686,7 +17130,7 @@
       <c r="M291" s="3"/>
       <c r="N291" s="3"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
         <v>828</v>
       </c>
@@ -16716,7 +17160,7 @@
       <c r="M292" s="3"/>
       <c r="N292" s="3"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
         <v>833</v>
       </c>
@@ -16746,7 +17190,7 @@
       <c r="M293" s="3"/>
       <c r="N293" s="3"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
         <v>835</v>
       </c>
@@ -16776,7 +17220,7 @@
       <c r="M294" s="3"/>
       <c r="N294" s="3"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
         <v>838</v>
       </c>
@@ -16814,7 +17258,7 @@
       </c>
       <c r="N295" s="3"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
         <v>841</v>
       </c>
@@ -16852,7 +17296,7 @@
       </c>
       <c r="N296" s="3"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
         <v>843</v>
       </c>
@@ -16882,7 +17326,7 @@
       <c r="M297" s="3"/>
       <c r="N297" s="3"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
         <v>846</v>
       </c>
@@ -16912,7 +17356,7 @@
       <c r="M298" s="3"/>
       <c r="N298" s="3"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
         <v>849</v>
       </c>
@@ -16942,7 +17386,7 @@
       <c r="M299" s="3"/>
       <c r="N299" s="3"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
         <v>851</v>
       </c>
@@ -16972,7 +17416,7 @@
       <c r="M300" s="3"/>
       <c r="N300" s="3"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
         <v>854</v>
       </c>
@@ -17002,7 +17446,7 @@
       <c r="M301" s="3"/>
       <c r="N301" s="3"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
         <v>857</v>
       </c>
@@ -17032,7 +17476,7 @@
       <c r="M302" s="3"/>
       <c r="N302" s="3"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
         <v>860</v>
       </c>
@@ -17070,7 +17514,7 @@
       </c>
       <c r="N303" s="3"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
         <v>862</v>
       </c>
@@ -17100,7 +17544,7 @@
       <c r="M304" s="3"/>
       <c r="N304" s="3"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
         <v>864</v>
       </c>
@@ -17138,7 +17582,7 @@
       </c>
       <c r="N305" s="3"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
         <v>864</v>
       </c>
@@ -17176,7 +17620,7 @@
       </c>
       <c r="N306" s="3"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
         <v>868</v>
       </c>
@@ -17206,7 +17650,7 @@
       <c r="M307" s="3"/>
       <c r="N307" s="3"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
         <v>871</v>
       </c>
@@ -17236,7 +17680,7 @@
       <c r="M308" s="3"/>
       <c r="N308" s="3"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
         <v>874</v>
       </c>
@@ -17266,7 +17710,7 @@
       <c r="M309" s="3"/>
       <c r="N309" s="3"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
         <v>876</v>
       </c>
@@ -17296,7 +17740,7 @@
       <c r="M310" s="3"/>
       <c r="N310" s="3"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
         <v>878</v>
       </c>
@@ -17326,7 +17770,7 @@
       <c r="M311" s="3"/>
       <c r="N311" s="3"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
         <v>881</v>
       </c>
@@ -17356,7 +17800,7 @@
       <c r="M312" s="3"/>
       <c r="N312" s="3"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
         <v>884</v>
       </c>
@@ -17386,7 +17830,7 @@
       <c r="M313" s="3"/>
       <c r="N313" s="3"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
         <v>887</v>
       </c>
@@ -17424,7 +17868,7 @@
       </c>
       <c r="N314" s="3"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
         <v>891</v>
       </c>
@@ -17462,7 +17906,7 @@
       </c>
       <c r="N315" s="3"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
         <v>894</v>
       </c>
@@ -17500,7 +17944,7 @@
       </c>
       <c r="N316" s="3"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
         <v>897</v>
       </c>
@@ -17538,7 +17982,7 @@
       </c>
       <c r="N317" s="3"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
         <v>900</v>
       </c>
@@ -17568,7 +18012,7 @@
       <c r="M318" s="3"/>
       <c r="N318" s="3"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
         <v>903</v>
       </c>
@@ -17598,7 +18042,7 @@
       <c r="M319" s="3"/>
       <c r="N319" s="3"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
         <v>906</v>
       </c>
@@ -17636,7 +18080,7 @@
       </c>
       <c r="N320" s="3"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
         <v>909</v>
       </c>
@@ -17666,7 +18110,7 @@
       <c r="M321" s="3"/>
       <c r="N321" s="3"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>912</v>
       </c>
@@ -17696,7 +18140,7 @@
       <c r="M322" s="3"/>
       <c r="N322" s="3"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
         <v>915</v>
       </c>
@@ -17726,7 +18170,7 @@
       <c r="M323" s="3"/>
       <c r="N323" s="3"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
         <v>918</v>
       </c>
@@ -17756,7 +18200,7 @@
       <c r="M324" s="3"/>
       <c r="N324" s="3"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
         <v>921</v>
       </c>
@@ -17786,7 +18230,7 @@
       <c r="M325" s="3"/>
       <c r="N325" s="3"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
         <v>923</v>
       </c>
@@ -17816,7 +18260,7 @@
       <c r="M326" s="3"/>
       <c r="N326" s="3"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
         <v>925</v>
       </c>
@@ -17846,7 +18290,7 @@
       <c r="M327" s="3"/>
       <c r="N327" s="3"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
         <v>927</v>
       </c>
@@ -17876,7 +18320,7 @@
       <c r="M328" s="3"/>
       <c r="N328" s="3"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>930</v>
       </c>
@@ -17906,7 +18350,7 @@
       <c r="M329" s="3"/>
       <c r="N329" s="3"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
         <v>933</v>
       </c>
@@ -17936,7 +18380,7 @@
       <c r="M330" s="3"/>
       <c r="N330" s="3"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
         <v>935</v>
       </c>
@@ -17974,7 +18418,7 @@
       </c>
       <c r="N331" s="3"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
         <v>938</v>
       </c>
@@ -18004,7 +18448,7 @@
       <c r="M332" s="3"/>
       <c r="N332" s="3"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
         <v>941</v>
       </c>
@@ -18042,7 +18486,7 @@
       </c>
       <c r="N333" s="3"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
         <v>945</v>
       </c>
@@ -18072,7 +18516,7 @@
       <c r="M334" s="3"/>
       <c r="N334" s="3"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
         <v>947</v>
       </c>
@@ -18110,7 +18554,7 @@
       </c>
       <c r="N335" s="3"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>951</v>
       </c>
@@ -18148,7 +18592,7 @@
       </c>
       <c r="N336" s="3"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
         <v>953</v>
       </c>
@@ -18178,7 +18622,7 @@
       <c r="M337" s="3"/>
       <c r="N337" s="3"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>956</v>
       </c>
@@ -18208,7 +18652,7 @@
       <c r="M338" s="3"/>
       <c r="N338" s="3"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
         <v>959</v>
       </c>
@@ -18238,7 +18682,7 @@
       <c r="M339" s="3"/>
       <c r="N339" s="3"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>962</v>
       </c>
@@ -18268,7 +18712,7 @@
       <c r="M340" s="3"/>
       <c r="N340" s="3"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
         <v>965</v>
       </c>
@@ -18306,7 +18750,7 @@
       </c>
       <c r="N341" s="3"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
         <v>967</v>
       </c>
@@ -18342,7 +18786,7 @@
       </c>
       <c r="N342" s="3"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>970</v>
       </c>
@@ -18372,7 +18816,7 @@
       <c r="M343" s="3"/>
       <c r="N343" s="3"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
         <v>972</v>
       </c>
@@ -18410,7 +18854,7 @@
       </c>
       <c r="N344" s="3"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
         <v>975</v>
       </c>
@@ -18440,7 +18884,7 @@
       <c r="M345" s="3"/>
       <c r="N345" s="3"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
         <v>978</v>
       </c>
@@ -18470,7 +18914,7 @@
       <c r="M346" s="3"/>
       <c r="N346" s="3"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
         <v>981</v>
       </c>
@@ -18500,7 +18944,7 @@
       <c r="M347" s="3"/>
       <c r="N347" s="3"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>984</v>
       </c>
@@ -18530,7 +18974,7 @@
       <c r="M348" s="3"/>
       <c r="N348" s="3"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
         <v>987</v>
       </c>
@@ -18568,7 +19012,7 @@
       </c>
       <c r="N349" s="3"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
         <v>989</v>
       </c>
@@ -18606,7 +19050,7 @@
       </c>
       <c r="N350" s="3"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
         <v>993</v>
       </c>
@@ -18636,7 +19080,7 @@
       <c r="M351" s="3"/>
       <c r="N351" s="3"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
         <v>996</v>
       </c>
@@ -18674,7 +19118,7 @@
       </c>
       <c r="N352" s="3"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>1000</v>
       </c>
@@ -18704,7 +19148,7 @@
       <c r="M353" s="3"/>
       <c r="N353" s="3"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>1003</v>
       </c>
@@ -18734,7 +19178,7 @@
       <c r="M354" s="3"/>
       <c r="N354" s="3"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
         <v>1006</v>
       </c>
@@ -18772,7 +19216,7 @@
       </c>
       <c r="N355" s="3"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>1010</v>
       </c>
@@ -18802,7 +19246,7 @@
       <c r="M356" s="3"/>
       <c r="N356" s="3"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
         <v>1013</v>
       </c>
@@ -18832,7 +19276,7 @@
       <c r="M357" s="3"/>
       <c r="N357" s="3"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
         <v>1016</v>
       </c>
@@ -18870,7 +19314,7 @@
       </c>
       <c r="N358" s="3"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>1020</v>
       </c>
@@ -18900,7 +19344,7 @@
       <c r="M359" s="3"/>
       <c r="N359" s="3"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
         <v>1023</v>
       </c>
@@ -18930,7 +19374,7 @@
       <c r="M360" s="3"/>
       <c r="N360" s="3"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>1025</v>
       </c>
@@ -18960,7 +19404,7 @@
       <c r="M361" s="3"/>
       <c r="N361" s="3"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
         <v>1028</v>
       </c>
@@ -18998,7 +19442,7 @@
       </c>
       <c r="N362" s="3"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
         <v>1031</v>
       </c>
@@ -19028,7 +19472,7 @@
       <c r="M363" s="3"/>
       <c r="N363" s="3"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>1033</v>
       </c>
@@ -19058,7 +19502,7 @@
       <c r="M364" s="3"/>
       <c r="N364" s="3"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
         <v>1035</v>
       </c>
@@ -19088,7 +19532,7 @@
       <c r="M365" s="3"/>
       <c r="N365" s="3"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>1038</v>
       </c>
@@ -19118,7 +19562,7 @@
       <c r="M366" s="3"/>
       <c r="N366" s="3"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>1040</v>
       </c>
@@ -19148,7 +19592,7 @@
       <c r="M367" s="3"/>
       <c r="N367" s="3"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>1042</v>
       </c>
@@ -19178,7 +19622,7 @@
       <c r="M368" s="3"/>
       <c r="N368" s="3"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>1045</v>
       </c>
@@ -19208,7 +19652,7 @@
       <c r="M369" s="3"/>
       <c r="N369" s="3"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
         <v>1048</v>
       </c>
@@ -19246,7 +19690,7 @@
       </c>
       <c r="N370" s="3"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
         <v>1052</v>
       </c>
@@ -19276,7 +19720,7 @@
       <c r="M371" s="3"/>
       <c r="N371" s="3"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
         <v>1054</v>
       </c>
@@ -19306,7 +19750,7 @@
       <c r="M372" s="3"/>
       <c r="N372" s="3"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
         <v>1057</v>
       </c>
@@ -19344,7 +19788,7 @@
       </c>
       <c r="N373" s="3"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
         <v>1060</v>
       </c>
@@ -19374,7 +19818,7 @@
       <c r="M374" s="3"/>
       <c r="N374" s="3"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
         <v>1062</v>
       </c>
@@ -19410,7 +19854,7 @@
       </c>
       <c r="N375" s="3"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>1066</v>
       </c>
@@ -19448,7 +19892,7 @@
       </c>
       <c r="N376" s="3"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
         <v>1070</v>
       </c>
@@ -19484,7 +19928,7 @@
       </c>
       <c r="N377" s="3"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
         <v>1073</v>
       </c>
@@ -19514,7 +19958,7 @@
       <c r="M378" s="3"/>
       <c r="N378" s="3"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
         <v>1075</v>
       </c>
@@ -19544,7 +19988,7 @@
       <c r="M379" s="3"/>
       <c r="N379" s="3"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
         <v>1077</v>
       </c>
@@ -19574,7 +20018,7 @@
       <c r="M380" s="3"/>
       <c r="N380" s="3"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
         <v>1079</v>
       </c>
@@ -19604,7 +20048,7 @@
       <c r="M381" s="3"/>
       <c r="N381" s="3"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
         <v>1081</v>
       </c>
@@ -19640,7 +20084,7 @@
       </c>
       <c r="N382" s="3"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
         <v>1085</v>
       </c>
@@ -19670,7 +20114,7 @@
       <c r="M383" s="3"/>
       <c r="N383" s="3"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
         <v>1088</v>
       </c>
@@ -19700,7 +20144,7 @@
       <c r="M384" s="3"/>
       <c r="N384" s="3"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
         <v>1091</v>
       </c>
@@ -19736,7 +20180,7 @@
       </c>
       <c r="N385" s="3"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
         <v>1094</v>
       </c>
@@ -19774,7 +20218,7 @@
       </c>
       <c r="N386" s="3"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
         <v>1098</v>
       </c>
@@ -19804,7 +20248,7 @@
       <c r="M387" s="3"/>
       <c r="N387" s="3"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
         <v>1100</v>
       </c>
@@ -19834,7 +20278,7 @@
       <c r="M388" s="3"/>
       <c r="N388" s="3"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
         <v>1103</v>
       </c>
@@ -19870,7 +20314,7 @@
       </c>
       <c r="N389" s="3"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
         <v>1106</v>
       </c>
@@ -19908,7 +20352,7 @@
       </c>
       <c r="N390" s="3"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
         <v>1109</v>
       </c>
@@ -19938,7 +20382,7 @@
       <c r="M391" s="3"/>
       <c r="N391" s="3"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
         <v>1112</v>
       </c>
@@ -19968,7 +20412,7 @@
       <c r="M392" s="3"/>
       <c r="N392" s="3"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
         <v>1115</v>
       </c>
@@ -20004,7 +20448,7 @@
       </c>
       <c r="N393" s="3"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
         <v>1118</v>
       </c>
@@ -20034,7 +20478,7 @@
       <c r="M394" s="3"/>
       <c r="N394" s="3"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
         <v>1120</v>
       </c>
@@ -20064,7 +20508,7 @@
       <c r="M395" s="3"/>
       <c r="N395" s="3"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
         <v>1123</v>
       </c>
@@ -20100,7 +20544,7 @@
       </c>
       <c r="N396" s="3"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
         <v>1126</v>
       </c>
@@ -20130,7 +20574,7 @@
       <c r="M397" s="3"/>
       <c r="N397" s="3"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
         <v>1128</v>
       </c>
@@ -20168,7 +20612,7 @@
       </c>
       <c r="N398" s="3"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
         <v>1131</v>
       </c>
@@ -20204,7 +20648,7 @@
       </c>
       <c r="N399" s="3"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
         <v>1134</v>
       </c>
@@ -20234,7 +20678,7 @@
       <c r="M400" s="3"/>
       <c r="N400" s="3"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
         <v>1137</v>
       </c>
@@ -20270,7 +20714,7 @@
       </c>
       <c r="N401" s="3"/>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
         <v>1139</v>
       </c>
@@ -20300,7 +20744,7 @@
       <c r="M402" s="3"/>
       <c r="N402" s="3"/>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
         <v>1141</v>
       </c>
@@ -20330,7 +20774,7 @@
       <c r="M403" s="3"/>
       <c r="N403" s="3"/>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
         <v>1144</v>
       </c>
@@ -20368,7 +20812,7 @@
       </c>
       <c r="N404" s="3"/>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
         <v>1148</v>
       </c>
@@ -20398,7 +20842,7 @@
       <c r="M405" s="3"/>
       <c r="N405" s="3"/>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
         <v>1150</v>
       </c>
@@ -20428,7 +20872,7 @@
       <c r="M406" s="3"/>
       <c r="N406" s="3"/>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
         <v>1153</v>
       </c>
@@ -20458,7 +20902,7 @@
       <c r="M407" s="3"/>
       <c r="N407" s="3"/>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
         <v>1155</v>
       </c>
@@ -20488,7 +20932,7 @@
       <c r="M408" s="3"/>
       <c r="N408" s="3"/>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
         <v>1157</v>
       </c>
@@ -20524,7 +20968,7 @@
       </c>
       <c r="N409" s="3"/>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
         <v>1161</v>
       </c>
@@ -20562,7 +21006,7 @@
       </c>
       <c r="N410" s="3"/>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
         <v>1165</v>
       </c>
@@ -20598,7 +21042,7 @@
       </c>
       <c r="N411" s="3"/>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
         <v>1168</v>
       </c>
@@ -20628,7 +21072,7 @@
       <c r="M412" s="3"/>
       <c r="N412" s="3"/>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
         <v>1171</v>
       </c>
@@ -20664,7 +21108,7 @@
       </c>
       <c r="N413" s="3"/>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
         <v>1174</v>
       </c>
@@ -20694,7 +21138,7 @@
       <c r="M414" s="3"/>
       <c r="N414" s="3"/>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
         <v>1176</v>
       </c>
@@ -20730,7 +21174,7 @@
       </c>
       <c r="N415" s="3"/>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
         <v>1179</v>
       </c>
@@ -20760,7 +21204,7 @@
       <c r="M416" s="3"/>
       <c r="N416" s="3"/>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
         <v>1182</v>
       </c>
@@ -20790,7 +21234,7 @@
       <c r="M417" s="3"/>
       <c r="N417" s="3"/>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
         <v>1184</v>
       </c>
@@ -20826,7 +21270,7 @@
       </c>
       <c r="N418" s="3"/>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
         <v>1187</v>
       </c>
@@ -20856,7 +21300,7 @@
       <c r="M419" s="3"/>
       <c r="N419" s="3"/>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
         <v>1189</v>
       </c>
@@ -20886,7 +21330,7 @@
       <c r="M420" s="3"/>
       <c r="N420" s="3"/>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
         <v>1191</v>
       </c>
@@ -20922,7 +21366,7 @@
       </c>
       <c r="N421" s="3"/>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
         <v>1194</v>
       </c>
@@ -20962,7 +21406,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
         <v>1199</v>
       </c>
@@ -20992,7 +21436,7 @@
       <c r="M423" s="3"/>
       <c r="N423" s="3"/>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
         <v>1201</v>
       </c>
@@ -21022,7 +21466,7 @@
       <c r="M424" s="3"/>
       <c r="N424" s="3"/>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
         <v>1203</v>
       </c>
@@ -21052,7 +21496,7 @@
       <c r="M425" s="3"/>
       <c r="N425" s="3"/>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
         <v>1206</v>
       </c>
@@ -21088,7 +21532,7 @@
       </c>
       <c r="N426" s="3"/>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
         <v>1209</v>
       </c>
@@ -21118,7 +21562,7 @@
       <c r="M427" s="3"/>
       <c r="N427" s="3"/>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
         <v>1211</v>
       </c>
@@ -21148,7 +21592,7 @@
       <c r="M428" s="3"/>
       <c r="N428" s="3"/>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
         <v>1214</v>
       </c>
@@ -21184,7 +21628,7 @@
       </c>
       <c r="N429" s="3"/>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
         <v>1216</v>
       </c>
@@ -21214,7 +21658,7 @@
       <c r="M430" s="3"/>
       <c r="N430" s="3"/>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
         <v>1218</v>
       </c>
@@ -21244,7 +21688,7 @@
       <c r="M431" s="3"/>
       <c r="N431" s="3"/>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
         <v>1220</v>
       </c>
@@ -21274,7 +21718,7 @@
       <c r="M432" s="3"/>
       <c r="N432" s="3"/>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
         <v>1222</v>
       </c>
@@ -21304,7 +21748,7 @@
       <c r="M433" s="3"/>
       <c r="N433" s="3"/>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
         <v>1225</v>
       </c>
@@ -21334,7 +21778,7 @@
       <c r="M434" s="3"/>
       <c r="N434" s="3"/>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
         <v>1225</v>
       </c>
@@ -21364,7 +21808,7 @@
       <c r="M435" s="3"/>
       <c r="N435" s="3"/>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
         <v>1230</v>
       </c>
@@ -21404,7 +21848,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
         <v>1234</v>
       </c>
@@ -21434,7 +21878,7 @@
       <c r="M437" s="3"/>
       <c r="N437" s="3"/>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
         <v>1236</v>
       </c>
@@ -21464,7 +21908,7 @@
       <c r="M438" s="3"/>
       <c r="N438" s="3"/>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
         <v>1238</v>
       </c>
@@ -21494,7 +21938,7 @@
       <c r="M439" s="3"/>
       <c r="N439" s="3"/>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
         <v>1240</v>
       </c>
@@ -21532,7 +21976,7 @@
       </c>
       <c r="N440" s="3"/>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
         <v>1244</v>
       </c>
@@ -21562,7 +22006,7 @@
       <c r="M441" s="3"/>
       <c r="N441" s="3"/>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
         <v>1246</v>
       </c>
@@ -21592,7 +22036,7 @@
       <c r="M442" s="3"/>
       <c r="N442" s="3"/>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
         <v>1248</v>
       </c>
@@ -21622,7 +22066,7 @@
       <c r="M443" s="3"/>
       <c r="N443" s="3"/>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
         <v>1250</v>
       </c>
@@ -21652,7 +22096,7 @@
       <c r="M444" s="3"/>
       <c r="N444" s="3"/>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
         <v>1253</v>
       </c>
@@ -21688,7 +22132,7 @@
       </c>
       <c r="N445" s="3"/>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
         <v>1257</v>
       </c>
@@ -21724,7 +22168,7 @@
       </c>
       <c r="N446" s="3"/>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
         <v>1261</v>
       </c>
@@ -21754,7 +22198,7 @@
       <c r="M447" s="3"/>
       <c r="N447" s="3"/>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
         <v>1264</v>
       </c>
@@ -21784,7 +22228,7 @@
       <c r="M448" s="3"/>
       <c r="N448" s="3"/>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
         <v>1267</v>
       </c>
@@ -21814,7 +22258,7 @@
       <c r="M449" s="3"/>
       <c r="N449" s="3"/>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
         <v>1270</v>
       </c>
@@ -21852,7 +22296,7 @@
       </c>
       <c r="N450" s="3"/>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
         <v>1274</v>
       </c>
@@ -21882,7 +22326,7 @@
       <c r="M451" s="3"/>
       <c r="N451" s="3"/>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
         <v>1277</v>
       </c>
@@ -21918,7 +22362,7 @@
       </c>
       <c r="N452" s="3"/>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
         <v>1280</v>
       </c>
@@ -21948,7 +22392,7 @@
       <c r="M453" s="3"/>
       <c r="N453" s="3"/>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>1282</v>
       </c>
@@ -21984,7 +22428,7 @@
       </c>
       <c r="N454" s="3"/>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>1285</v>
       </c>
@@ -22024,7 +22468,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
         <v>1289</v>
       </c>
@@ -22054,7 +22498,7 @@
       <c r="M456" s="3"/>
       <c r="N456" s="3"/>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
         <v>1291</v>
       </c>
@@ -22084,7 +22528,7 @@
       <c r="M457" s="3"/>
       <c r="N457" s="3"/>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
         <v>1293</v>
       </c>
@@ -22120,7 +22564,7 @@
       </c>
       <c r="N458" s="3"/>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
         <v>1297</v>
       </c>
@@ -22156,7 +22600,7 @@
       </c>
       <c r="N459" s="3"/>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
         <v>1300</v>
       </c>
@@ -22186,7 +22630,7 @@
       <c r="M460" s="3"/>
       <c r="N460" s="3"/>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
         <v>1302</v>
       </c>
@@ -22216,7 +22660,7 @@
       <c r="M461" s="3"/>
       <c r="N461" s="3"/>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
         <v>1305</v>
       </c>
@@ -22252,7 +22696,7 @@
       </c>
       <c r="N462" s="3"/>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
         <v>1308</v>
       </c>
@@ -22292,7 +22736,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
         <v>1313</v>
       </c>
@@ -22328,7 +22772,7 @@
       </c>
       <c r="N464" s="3"/>
     </row>
-    <row r="465" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
         <v>1317</v>
       </c>
@@ -22358,7 +22802,7 @@
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
         <v>1319</v>
       </c>
@@ -22388,7 +22832,7 @@
       <c r="M466" s="3"/>
       <c r="N466" s="3"/>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
         <v>1321</v>
       </c>
@@ -22418,7 +22862,7 @@
       <c r="M467" s="3"/>
       <c r="N467" s="3"/>
     </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
         <v>1324</v>
       </c>
@@ -22448,7 +22892,7 @@
       <c r="M468" s="3"/>
       <c r="N468" s="3"/>
     </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
         <v>1326</v>
       </c>
@@ -22478,7 +22922,7 @@
       <c r="M469" s="3"/>
       <c r="N469" s="3"/>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
         <v>1329</v>
       </c>
@@ -22508,7 +22952,7 @@
       <c r="M470" s="3"/>
       <c r="N470" s="3"/>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
         <v>1332</v>
       </c>
@@ -22538,7 +22982,7 @@
       <c r="M471" s="3"/>
       <c r="N471" s="3"/>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
         <v>1335</v>
       </c>
@@ -22568,7 +23012,7 @@
       <c r="M472" s="3"/>
       <c r="N472" s="3"/>
     </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>1337</v>
       </c>
@@ -22598,7 +23042,7 @@
       <c r="M473" s="3"/>
       <c r="N473" s="3"/>
     </row>
-    <row r="474" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
         <v>1339</v>
       </c>
@@ -22628,7 +23072,7 @@
       <c r="M474" s="3"/>
       <c r="N474" s="3"/>
     </row>
-    <row r="475" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
         <v>1341</v>
       </c>
@@ -22658,7 +23102,7 @@
       <c r="M475" s="3"/>
       <c r="N475" s="3"/>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
         <v>1343</v>
       </c>
@@ -22688,7 +23132,7 @@
       <c r="M476" s="3"/>
       <c r="N476" s="3"/>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
         <v>1346</v>
       </c>
@@ -22718,7 +23162,7 @@
       <c r="M477" s="3"/>
       <c r="N477" s="3"/>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
         <v>1349</v>
       </c>
@@ -22748,7 +23192,7 @@
       <c r="M478" s="3"/>
       <c r="N478" s="3"/>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
         <v>1352</v>
       </c>
@@ -22784,7 +23228,7 @@
       </c>
       <c r="N479" s="3"/>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
         <v>1355</v>
       </c>
@@ -22814,7 +23258,7 @@
       <c r="M480" s="3"/>
       <c r="N480" s="3"/>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
         <v>1357</v>
       </c>
@@ -22844,7 +23288,7 @@
       <c r="M481" s="3"/>
       <c r="N481" s="3"/>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
         <v>1360</v>
       </c>
@@ -22874,7 +23318,7 @@
       <c r="M482" s="3"/>
       <c r="N482" s="3"/>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
         <v>1363</v>
       </c>
@@ -22904,7 +23348,7 @@
       <c r="M483" s="3"/>
       <c r="N483" s="3"/>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
         <v>1366</v>
       </c>
@@ -22934,7 +23378,7 @@
       <c r="M484" s="3"/>
       <c r="N484" s="3"/>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
         <v>1368</v>
       </c>
@@ -22974,7 +23418,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A486" s="3" t="s">
         <v>1373</v>
       </c>
@@ -23012,7 +23456,7 @@
       </c>
       <c r="N486" s="3"/>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
         <v>1377</v>
       </c>
@@ -23042,7 +23486,7 @@
       <c r="M487" s="3"/>
       <c r="N487" s="3"/>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A488" s="3" t="s">
         <v>1379</v>
       </c>
@@ -23072,7 +23516,7 @@
       <c r="M488" s="3"/>
       <c r="N488" s="3"/>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
         <v>1381</v>
       </c>
@@ -23102,7 +23546,7 @@
       <c r="M489" s="3"/>
       <c r="N489" s="3"/>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A490" s="3" t="s">
         <v>1384</v>
       </c>
@@ -23132,7 +23576,7 @@
       <c r="M490" s="3"/>
       <c r="N490" s="3"/>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
         <v>1387</v>
       </c>
@@ -23162,7 +23606,7 @@
       <c r="M491" s="3"/>
       <c r="N491" s="3"/>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A492" s="3" t="s">
         <v>1390</v>
       </c>
@@ -23198,7 +23642,7 @@
       </c>
       <c r="N492" s="3"/>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
         <v>1390</v>
       </c>
@@ -23234,7 +23678,7 @@
       </c>
       <c r="N493" s="3"/>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A494" s="3" t="s">
         <v>1390</v>
       </c>
@@ -23264,7 +23708,7 @@
       <c r="M494" s="3"/>
       <c r="N494" s="3"/>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
         <v>1398</v>
       </c>
@@ -23294,7 +23738,7 @@
       <c r="M495" s="3"/>
       <c r="N495" s="3"/>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A496" s="3" t="s">
         <v>1398</v>
       </c>
@@ -23324,7 +23768,7 @@
       <c r="M496" s="3"/>
       <c r="N496" s="3"/>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
         <v>1403</v>
       </c>
@@ -23354,7 +23798,7 @@
       <c r="M497" s="3"/>
       <c r="N497" s="3"/>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A498" s="3" t="s">
         <v>1406</v>
       </c>
@@ -23384,7 +23828,7 @@
       <c r="M498" s="3"/>
       <c r="N498" s="3"/>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
         <v>1409</v>
       </c>
@@ -23420,7 +23864,7 @@
       </c>
       <c r="N499" s="3"/>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A500" s="3" t="s">
         <v>1413</v>
       </c>
@@ -23450,7 +23894,7 @@
       <c r="M500" s="3"/>
       <c r="N500" s="3"/>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
         <v>1413</v>
       </c>
@@ -23480,7 +23924,7 @@
       <c r="M501" s="3"/>
       <c r="N501" s="3"/>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A502" s="3" t="s">
         <v>1417</v>
       </c>
@@ -23510,7 +23954,7 @@
       <c r="M502" s="3"/>
       <c r="N502" s="3"/>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
         <v>1420</v>
       </c>
@@ -23546,7 +23990,7 @@
       </c>
       <c r="N503" s="3"/>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A504" s="3" t="s">
         <v>1420</v>
       </c>
@@ -23576,7 +24020,7 @@
       <c r="M504" s="3"/>
       <c r="N504" s="3"/>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
         <v>1425</v>
       </c>
@@ -23606,7 +24050,7 @@
       <c r="M505" s="3"/>
       <c r="N505" s="3"/>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A506" s="3" t="s">
         <v>1425</v>
       </c>
@@ -23636,7 +24080,7 @@
       <c r="M506" s="3"/>
       <c r="N506" s="3"/>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
         <v>1428</v>
       </c>
@@ -23666,7 +24110,7 @@
       <c r="M507" s="3"/>
       <c r="N507" s="3"/>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A508" s="3" t="s">
         <v>1430</v>
       </c>
@@ -23696,7 +24140,7 @@
       <c r="M508" s="3"/>
       <c r="N508" s="3"/>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
         <v>1433</v>
       </c>
@@ -23726,7 +24170,7 @@
       <c r="M509" s="3"/>
       <c r="N509" s="3"/>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A510" s="3" t="s">
         <v>1435</v>
       </c>
@@ -23756,7 +24200,7 @@
       <c r="M510" s="3"/>
       <c r="N510" s="3"/>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
         <v>1437</v>
       </c>
@@ -23786,7 +24230,7 @@
       <c r="M511" s="3"/>
       <c r="N511" s="3"/>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A512" s="3" t="s">
         <v>1439</v>
       </c>
@@ -23816,7 +24260,7 @@
       <c r="M512" s="3"/>
       <c r="N512" s="3"/>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
         <v>1442</v>
       </c>
@@ -23854,7 +24298,7 @@
       </c>
       <c r="N513" s="3"/>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A514" s="3" t="s">
         <v>1445</v>
       </c>
@@ -23890,7 +24334,7 @@
       </c>
       <c r="N514" s="3"/>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
         <v>1449</v>
       </c>
@@ -23920,7 +24364,7 @@
       <c r="M515" s="3"/>
       <c r="N515" s="3"/>
     </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A516" s="3" t="s">
         <v>1452</v>
       </c>
@@ -23950,7 +24394,7 @@
       <c r="M516" s="3"/>
       <c r="N516" s="3"/>
     </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
         <v>1454</v>
       </c>
@@ -23986,7 +24430,7 @@
       </c>
       <c r="N517" s="3"/>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A518" s="3" t="s">
         <v>1456</v>
       </c>
@@ -24022,7 +24466,7 @@
       </c>
       <c r="N518" s="3"/>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
         <v>1459</v>
       </c>
@@ -24052,7 +24496,7 @@
       <c r="M519" s="3"/>
       <c r="N519" s="3"/>
     </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A520" s="3" t="s">
         <v>1462</v>
       </c>
@@ -24082,7 +24526,7 @@
       <c r="M520" s="3"/>
       <c r="N520" s="3"/>
     </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
         <v>1464</v>
       </c>
@@ -24112,7 +24556,7 @@
       <c r="M521" s="3"/>
       <c r="N521" s="3"/>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A522" s="3" t="s">
         <v>1466</v>
       </c>
@@ -24148,7 +24592,7 @@
       </c>
       <c r="N522" s="3"/>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
         <v>1469</v>
       </c>
@@ -24178,7 +24622,7 @@
       <c r="M523" s="3"/>
       <c r="N523" s="3"/>
     </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A524" s="3" t="s">
         <v>1472</v>
       </c>
@@ -24218,7 +24662,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
         <v>1476</v>
       </c>
@@ -24254,7 +24698,7 @@
       </c>
       <c r="N525" s="3"/>
     </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A526" s="3" t="s">
         <v>1479</v>
       </c>
@@ -24284,7 +24728,7 @@
       <c r="M526" s="3"/>
       <c r="N526" s="3"/>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
         <v>1482</v>
       </c>
@@ -24314,7 +24758,7 @@
       <c r="M527" s="3"/>
       <c r="N527" s="3"/>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A528" s="3" t="s">
         <v>1485</v>
       </c>
@@ -24344,7 +24788,7 @@
       <c r="M528" s="3"/>
       <c r="N528" s="3"/>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
         <v>1488</v>
       </c>
@@ -24374,7 +24818,7 @@
       <c r="M529" s="3"/>
       <c r="N529" s="3"/>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A530" s="3" t="s">
         <v>1491</v>
       </c>
@@ -24404,7 +24848,7 @@
       <c r="M530" s="3"/>
       <c r="N530" s="3"/>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
         <v>1493</v>
       </c>
@@ -24440,7 +24884,7 @@
       </c>
       <c r="N531" s="3"/>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A532" s="3" t="s">
         <v>1495</v>
       </c>
@@ -24470,7 +24914,7 @@
       <c r="M532" s="3"/>
       <c r="N532" s="3"/>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
         <v>1497</v>
       </c>
@@ -24500,7 +24944,7 @@
       <c r="M533" s="3"/>
       <c r="N533" s="3"/>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A534" s="3" t="s">
         <v>1500</v>
       </c>
@@ -24536,7 +24980,7 @@
       </c>
       <c r="N534" s="3"/>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
         <v>1503</v>
       </c>
@@ -24566,7 +25010,7 @@
       <c r="M535" s="3"/>
       <c r="N535" s="3"/>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A536" s="3" t="s">
         <v>1505</v>
       </c>
@@ -24596,7 +25040,7 @@
       <c r="M536" s="3"/>
       <c r="N536" s="3"/>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
         <v>1508</v>
       </c>
@@ -24626,7 +25070,7 @@
       <c r="M537" s="3"/>
       <c r="N537" s="3"/>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A538" s="3" t="s">
         <v>1511</v>
       </c>
@@ -24666,7 +25110,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
         <v>1515</v>
       </c>
@@ -24696,7 +25140,7 @@
       <c r="M539" s="3"/>
       <c r="N539" s="3"/>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A540" s="3" t="s">
         <v>1518</v>
       </c>
@@ -24726,7 +25170,7 @@
       <c r="M540" s="3"/>
       <c r="N540" s="3"/>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
         <v>1521</v>
       </c>
@@ -24756,7 +25200,7 @@
       <c r="M541" s="3"/>
       <c r="N541" s="3"/>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A542" s="3" t="s">
         <v>1524</v>
       </c>
@@ -24786,7 +25230,7 @@
       <c r="M542" s="3"/>
       <c r="N542" s="3"/>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
         <v>1526</v>
       </c>
@@ -24822,7 +25266,7 @@
       </c>
       <c r="N543" s="3"/>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A544" s="3" t="s">
         <v>1530</v>
       </c>
@@ -24858,7 +25302,7 @@
       </c>
       <c r="N544" s="3"/>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
         <v>1533</v>
       </c>
@@ -24888,7 +25332,7 @@
       <c r="M545" s="3"/>
       <c r="N545" s="3"/>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A546" s="3" t="s">
         <v>1536</v>
       </c>
@@ -24918,7 +25362,7 @@
       <c r="M546" s="3"/>
       <c r="N546" s="3"/>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
         <v>1539</v>
       </c>
@@ -24956,7 +25400,7 @@
       </c>
       <c r="N547" s="3"/>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A548" s="3" t="s">
         <v>1543</v>
       </c>
@@ -24986,7 +25430,7 @@
       <c r="M548" s="3"/>
       <c r="N548" s="3"/>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
         <v>1545</v>
       </c>
@@ -25022,7 +25466,7 @@
       </c>
       <c r="N549" s="3"/>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A550" s="3" t="s">
         <v>1549</v>
       </c>
@@ -25052,7 +25496,7 @@
       <c r="M550" s="3"/>
       <c r="N550" s="3"/>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
         <v>1552</v>
       </c>
@@ -25082,7 +25526,7 @@
       <c r="M551" s="3"/>
       <c r="N551" s="3"/>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A552" s="3" t="s">
         <v>1555</v>
       </c>
@@ -25112,7 +25556,7 @@
       <c r="M552" s="3"/>
       <c r="N552" s="3"/>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
         <v>1558</v>
       </c>
@@ -25142,7 +25586,7 @@
       <c r="M553" s="3"/>
       <c r="N553" s="3"/>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
         <v>1561</v>
       </c>
@@ -25172,7 +25616,7 @@
       <c r="M554" s="3"/>
       <c r="N554" s="3"/>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
         <v>1563</v>
       </c>
@@ -25202,7 +25646,7 @@
       <c r="M555" s="3"/>
       <c r="N555" s="3"/>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A556" s="3" t="s">
         <v>1565</v>
       </c>
@@ -25232,7 +25676,7 @@
       <c r="M556" s="3"/>
       <c r="N556" s="3"/>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
         <v>1567</v>
       </c>
@@ -25262,7 +25706,7 @@
       <c r="M557" s="3"/>
       <c r="N557" s="3"/>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A558" s="3" t="s">
         <v>1569</v>
       </c>
@@ -25292,7 +25736,7 @@
       <c r="M558" s="3"/>
       <c r="N558" s="3"/>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
         <v>1572</v>
       </c>
@@ -25322,7 +25766,7 @@
       <c r="M559" s="3"/>
       <c r="N559" s="3"/>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A560" s="3" t="s">
         <v>1575</v>
       </c>
@@ -25352,7 +25796,7 @@
       <c r="M560" s="3"/>
       <c r="N560" s="3"/>
     </row>
-    <row r="561" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
         <v>1578</v>
       </c>
@@ -25382,7 +25826,7 @@
       <c r="M561" s="3"/>
       <c r="N561" s="3"/>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A562" s="3" t="s">
         <v>1580</v>
       </c>
@@ -25412,7 +25856,7 @@
       <c r="M562" s="3"/>
       <c r="N562" s="3"/>
     </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
         <v>1582</v>
       </c>
@@ -25452,7 +25896,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A564" s="3" t="s">
         <v>1587</v>
       </c>
@@ -25482,7 +25926,7 @@
       <c r="M564" s="3"/>
       <c r="N564" s="3"/>
     </row>
-    <row r="565" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
         <v>1590</v>
       </c>
@@ -25512,7 +25956,7 @@
       <c r="M565" s="3"/>
       <c r="N565" s="3"/>
     </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A566" s="3" t="s">
         <v>1592</v>
       </c>
@@ -25542,7 +25986,7 @@
       <c r="M566" s="3"/>
       <c r="N566" s="3"/>
     </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
         <v>1595</v>
       </c>
@@ -25572,7 +26016,7 @@
       <c r="M567" s="3"/>
       <c r="N567" s="3"/>
     </row>
-    <row r="568" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A568" s="3" t="s">
         <v>1598</v>
       </c>
@@ -25608,7 +26052,7 @@
       </c>
       <c r="N568" s="3"/>
     </row>
-    <row r="569" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
         <v>1601</v>
       </c>
@@ -25638,7 +26082,7 @@
       <c r="M569" s="3"/>
       <c r="N569" s="3"/>
     </row>
-    <row r="570" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A570" s="3" t="s">
         <v>1604</v>
       </c>
@@ -25668,7 +26112,7 @@
       <c r="M570" s="3"/>
       <c r="N570" s="3"/>
     </row>
-    <row r="571" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
         <v>1606</v>
       </c>
@@ -25698,7 +26142,7 @@
       <c r="M571" s="3"/>
       <c r="N571" s="3"/>
     </row>
-    <row r="572" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A572" s="3" t="s">
         <v>1609</v>
       </c>
@@ -25728,7 +26172,7 @@
       <c r="M572" s="3"/>
       <c r="N572" s="3"/>
     </row>
-    <row r="573" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
         <v>1611</v>
       </c>
@@ -25764,7 +26208,7 @@
       </c>
       <c r="N573" s="3"/>
     </row>
-    <row r="574" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A574" s="3" t="s">
         <v>1615</v>
       </c>
@@ -25800,7 +26244,7 @@
       </c>
       <c r="N574" s="3"/>
     </row>
-    <row r="575" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
         <v>1617</v>
       </c>
@@ -25830,7 +26274,7 @@
       <c r="M575" s="3"/>
       <c r="N575" s="3"/>
     </row>
-    <row r="576" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
         <v>1620</v>
       </c>
@@ -25866,7 +26310,7 @@
       </c>
       <c r="N576" s="3"/>
     </row>
-    <row r="577" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
         <v>1622</v>
       </c>
@@ -25896,7 +26340,7 @@
       <c r="M577" s="3"/>
       <c r="N577" s="3"/>
     </row>
-    <row r="578" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A578" s="3" t="s">
         <v>1624</v>
       </c>
@@ -25926,7 +26370,7 @@
       <c r="M578" s="3"/>
       <c r="N578" s="3"/>
     </row>
-    <row r="579" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
         <v>1626</v>
       </c>
@@ -25956,7 +26400,7 @@
       <c r="M579" s="3"/>
       <c r="N579" s="3"/>
     </row>
-    <row r="580" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A580" s="3" t="s">
         <v>1628</v>
       </c>
@@ -25986,7 +26430,7 @@
       <c r="M580" s="3"/>
       <c r="N580" s="3"/>
     </row>
-    <row r="581" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
         <v>1631</v>
       </c>
@@ -26022,7 +26466,7 @@
       </c>
       <c r="N581" s="3"/>
     </row>
-    <row r="582" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A582" s="3" t="s">
         <v>1635</v>
       </c>
@@ -26058,7 +26502,7 @@
       </c>
       <c r="N582" s="3"/>
     </row>
-    <row r="583" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
         <v>1639</v>
       </c>
@@ -26094,7 +26538,7 @@
       </c>
       <c r="N583" s="3"/>
     </row>
-    <row r="584" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A584" s="3" t="s">
         <v>1641</v>
       </c>
@@ -26124,7 +26568,7 @@
       <c r="M584" s="3"/>
       <c r="N584" s="3"/>
     </row>
-    <row r="585" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
         <v>1643</v>
       </c>
@@ -26154,7 +26598,7 @@
       <c r="M585" s="3"/>
       <c r="N585" s="3"/>
     </row>
-    <row r="586" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A586" s="3" t="s">
         <v>1646</v>
       </c>
@@ -26184,7 +26628,7 @@
       <c r="M586" s="3"/>
       <c r="N586" s="3"/>
     </row>
-    <row r="587" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
         <v>1649</v>
       </c>
@@ -26220,7 +26664,7 @@
       </c>
       <c r="N587" s="3"/>
     </row>
-    <row r="588" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A588" s="3" t="s">
         <v>1651</v>
       </c>
@@ -26250,7 +26694,7 @@
       <c r="M588" s="3"/>
       <c r="N588" s="3"/>
     </row>
-    <row r="589" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
         <v>1653</v>
       </c>
@@ -26286,7 +26730,7 @@
       </c>
       <c r="N589" s="3"/>
     </row>
-    <row r="590" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A590" s="3" t="s">
         <v>1658</v>
       </c>
@@ -26316,7 +26760,7 @@
       <c r="M590" s="3"/>
       <c r="N590" s="3"/>
     </row>
-    <row r="591" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
         <v>1661</v>
       </c>
@@ -26346,7 +26790,7 @@
       <c r="M591" s="3"/>
       <c r="N591" s="3"/>
     </row>
-    <row r="592" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A592" s="3" t="s">
         <v>1664</v>
       </c>
@@ -26376,7 +26820,7 @@
       <c r="M592" s="3"/>
       <c r="N592" s="3"/>
     </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
         <v>1666</v>
       </c>
@@ -26406,7 +26850,7 @@
       <c r="M593" s="3"/>
       <c r="N593" s="3"/>
     </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A594" s="3" t="s">
         <v>1669</v>
       </c>
@@ -26446,7 +26890,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
         <v>1675</v>
       </c>
@@ -26484,7 +26928,7 @@
       </c>
       <c r="N595" s="3"/>
     </row>
-    <row r="596" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A596" s="3" t="s">
         <v>1680</v>
       </c>
@@ -26520,7 +26964,7 @@
       </c>
       <c r="N596" s="3"/>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
         <v>1684</v>
       </c>
@@ -26550,7 +26994,7 @@
       <c r="M597" s="3"/>
       <c r="N597" s="3"/>
     </row>
-    <row r="598" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A598" s="3" t="s">
         <v>1686</v>
       </c>
@@ -26586,7 +27030,7 @@
       </c>
       <c r="N598" s="3"/>
     </row>
-    <row r="599" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
         <v>1689</v>
       </c>
@@ -26616,7 +27060,7 @@
       <c r="M599" s="3"/>
       <c r="N599" s="3"/>
     </row>
-    <row r="600" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A600" s="3" t="s">
         <v>1692</v>
       </c>
@@ -26652,7 +27096,7 @@
       </c>
       <c r="N600" s="3"/>
     </row>
-    <row r="601" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
         <v>1694</v>
       </c>
@@ -26682,7 +27126,7 @@
       <c r="M601" s="3"/>
       <c r="N601" s="3"/>
     </row>
-    <row r="602" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A602" s="3" t="s">
         <v>1697</v>
       </c>
@@ -26720,7 +27164,7 @@
       </c>
       <c r="N602" s="3"/>
     </row>
-    <row r="603" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
         <v>1701</v>
       </c>
@@ -26758,7 +27202,7 @@
       </c>
       <c r="N603" s="3"/>
     </row>
-    <row r="604" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A604" s="3" t="s">
         <v>1704</v>
       </c>
@@ -26788,7 +27232,7 @@
       <c r="M604" s="3"/>
       <c r="N604" s="3"/>
     </row>
-    <row r="605" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
         <v>1707</v>
       </c>
@@ -26818,7 +27262,7 @@
       <c r="M605" s="3"/>
       <c r="N605" s="3"/>
     </row>
-    <row r="606" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A606" s="3" t="s">
         <v>1709</v>
       </c>
@@ -26848,7 +27292,7 @@
       <c r="M606" s="3"/>
       <c r="N606" s="3"/>
     </row>
-    <row r="607" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
         <v>1712</v>
       </c>
@@ -26878,7 +27322,7 @@
       <c r="M607" s="3"/>
       <c r="N607" s="3"/>
     </row>
-    <row r="608" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A608" s="3" t="s">
         <v>1715</v>
       </c>
@@ -26914,7 +27358,7 @@
       </c>
       <c r="N608" s="3"/>
     </row>
-    <row r="609" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
         <v>1718</v>
       </c>
@@ -26944,7 +27388,7 @@
       <c r="M609" s="3"/>
       <c r="N609" s="3"/>
     </row>
-    <row r="610" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A610" s="3" t="s">
         <v>1720</v>
       </c>
@@ -26984,7 +27428,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="611" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
         <v>1725</v>
       </c>
@@ -27020,7 +27464,7 @@
       </c>
       <c r="N611" s="3"/>
     </row>
-    <row r="612" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A612" s="3" t="s">
         <v>1728</v>
       </c>
@@ -27050,7 +27494,7 @@
       <c r="M612" s="3"/>
       <c r="N612" s="3"/>
     </row>
-    <row r="613" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
         <v>1731</v>
       </c>
@@ -27080,7 +27524,7 @@
       <c r="M613" s="3"/>
       <c r="N613" s="3"/>
     </row>
-    <row r="614" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A614" s="3" t="s">
         <v>1734</v>
       </c>
@@ -27110,7 +27554,7 @@
       <c r="M614" s="3"/>
       <c r="N614" s="3"/>
     </row>
-    <row r="615" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
         <v>1737</v>
       </c>
@@ -27140,7 +27584,7 @@
       <c r="M615" s="3"/>
       <c r="N615" s="3"/>
     </row>
-    <row r="616" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A616" s="3" t="s">
         <v>1739</v>
       </c>
@@ -27176,7 +27620,7 @@
       </c>
       <c r="N616" s="3"/>
     </row>
-    <row r="617" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A617" s="3" t="s">
         <v>1742</v>
       </c>
@@ -27206,7 +27650,7 @@
       <c r="M617" s="3"/>
       <c r="N617" s="3"/>
     </row>
-    <row r="618" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A618" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27236,7 +27680,7 @@
       <c r="M618" s="3"/>
       <c r="N618" s="3"/>
     </row>
-    <row r="619" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A619" s="3" t="s">
         <v>1747</v>
       </c>
@@ -27272,7 +27716,7 @@
       </c>
       <c r="N619" s="3"/>
     </row>
-    <row r="620" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A620" s="3" t="s">
         <v>1750</v>
       </c>
@@ -27302,7 +27746,7 @@
       <c r="M620" s="3"/>
       <c r="N620" s="3"/>
     </row>
-    <row r="621" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
         <v>1753</v>
       </c>
@@ -27338,7 +27782,7 @@
       </c>
       <c r="N621" s="3"/>
     </row>
-    <row r="622" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A622" s="3" t="s">
         <v>1756</v>
       </c>
@@ -27368,7 +27812,7 @@
       <c r="M622" s="3"/>
       <c r="N622" s="3"/>
     </row>
-    <row r="623" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
         <v>1759</v>
       </c>
@@ -27404,7 +27848,7 @@
       </c>
       <c r="N623" s="3"/>
     </row>
-    <row r="624" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A624" s="3" t="s">
         <v>1763</v>
       </c>
@@ -27434,7 +27878,7 @@
       <c r="M624" s="3"/>
       <c r="N624" s="3"/>
     </row>
-    <row r="625" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
         <v>1765</v>
       </c>
@@ -27464,7 +27908,7 @@
       <c r="M625" s="3"/>
       <c r="N625" s="3"/>
     </row>
-    <row r="626" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A626" s="3" t="s">
         <v>1767</v>
       </c>
@@ -27494,7 +27938,7 @@
       <c r="M626" s="3"/>
       <c r="N626" s="3"/>
     </row>
-    <row r="627" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
         <v>1769</v>
       </c>
@@ -27524,7 +27968,7 @@
       <c r="M627" s="3"/>
       <c r="N627" s="3"/>
     </row>
-    <row r="628" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A628" s="3" t="s">
         <v>1772</v>
       </c>
@@ -27554,7 +27998,7 @@
       <c r="M628" s="3"/>
       <c r="N628" s="3"/>
     </row>
-    <row r="629" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
         <v>1774</v>
       </c>
@@ -27584,7 +28028,7 @@
       <c r="M629" s="3"/>
       <c r="N629" s="3"/>
     </row>
-    <row r="630" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A630" s="3" t="s">
         <v>1776</v>
       </c>
@@ -27620,7 +28064,7 @@
       </c>
       <c r="N630" s="3"/>
     </row>
-    <row r="631" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
         <v>1779</v>
       </c>
@@ -27660,7 +28104,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="632" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A632" s="3" t="s">
         <v>1784</v>
       </c>
@@ -27690,7 +28134,7 @@
       <c r="M632" s="3"/>
       <c r="N632" s="3"/>
     </row>
-    <row r="633" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
         <v>1787</v>
       </c>
@@ -27720,7 +28164,7 @@
       <c r="M633" s="3"/>
       <c r="N633" s="3"/>
     </row>
-    <row r="634" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A634" s="3" t="s">
         <v>1789</v>
       </c>
@@ -27756,7 +28200,7 @@
       </c>
       <c r="N634" s="3"/>
     </row>
-    <row r="635" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A635" s="3" t="s">
         <v>1475</v>
       </c>
@@ -27788,7 +28232,7 @@
       <c r="M635" s="3"/>
       <c r="N635" s="3"/>
     </row>
-    <row r="636" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A636" s="3" t="s">
         <v>1794</v>
       </c>
@@ -27826,7 +28270,7 @@
       </c>
       <c r="N636" s="3"/>
     </row>
-    <row r="637" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A637" s="3" t="s">
         <v>1797</v>
       </c>
@@ -27862,7 +28306,7 @@
       </c>
       <c r="N637" s="3"/>
     </row>
-    <row r="638" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A638" s="3" t="s">
         <v>1799</v>
       </c>
@@ -27892,7 +28336,7 @@
       <c r="M638" s="3"/>
       <c r="N638" s="3"/>
     </row>
-    <row r="639" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
         <v>1802</v>
       </c>
@@ -27922,7 +28366,7 @@
       <c r="M639" s="3"/>
       <c r="N639" s="3"/>
     </row>
-    <row r="640" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A640" s="3" t="s">
         <v>1805</v>
       </c>
@@ -27952,7 +28396,7 @@
       <c r="M640" s="3"/>
       <c r="N640" s="3"/>
     </row>
-    <row r="641" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
         <v>1807</v>
       </c>
@@ -27988,7 +28432,7 @@
       </c>
       <c r="N641" s="3"/>
     </row>
-    <row r="642" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A642" s="3" t="s">
         <v>1809</v>
       </c>
@@ -28020,7 +28464,7 @@
       <c r="M642" s="3"/>
       <c r="N642" s="3"/>
     </row>
-    <row r="643" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
         <v>1811</v>
       </c>
@@ -28050,7 +28494,7 @@
       <c r="M643" s="3"/>
       <c r="N643" s="3"/>
     </row>
-    <row r="644" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A644" s="3" t="s">
         <v>1814</v>
       </c>
@@ -28080,7 +28524,7 @@
       <c r="M644" s="3"/>
       <c r="N644" s="3"/>
     </row>
-    <row r="645" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
         <v>1815</v>
       </c>
@@ -28116,7 +28560,7 @@
       </c>
       <c r="N645" s="3"/>
     </row>
-    <row r="646" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A646" s="3" t="s">
         <v>1819</v>
       </c>
@@ -28146,7 +28590,7 @@
       <c r="M646" s="3"/>
       <c r="N646" s="3"/>
     </row>
-    <row r="647" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
         <v>1822</v>
       </c>
@@ -28176,7 +28620,7 @@
       <c r="M647" s="3"/>
       <c r="N647" s="3"/>
     </row>
-    <row r="648" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A648" s="3" t="s">
         <v>1825</v>
       </c>
@@ -28206,7 +28650,7 @@
       <c r="M648" s="3"/>
       <c r="N648" s="3"/>
     </row>
-    <row r="649" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
         <v>1828</v>
       </c>
@@ -28244,7 +28688,7 @@
       </c>
       <c r="N649" s="3"/>
     </row>
-    <row r="650" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A650" s="3" t="s">
         <v>1831</v>
       </c>
@@ -28280,7 +28724,7 @@
       </c>
       <c r="N650" s="3"/>
     </row>
-    <row r="651" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
         <v>1835</v>
       </c>
@@ -28310,7 +28754,7 @@
       <c r="M651" s="3"/>
       <c r="N651" s="3"/>
     </row>
-    <row r="652" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A652" s="3" t="s">
         <v>1837</v>
       </c>
@@ -28346,7 +28790,7 @@
       </c>
       <c r="N652" s="3"/>
     </row>
-    <row r="653" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
         <v>1841</v>
       </c>
@@ -28376,7 +28820,7 @@
       <c r="M653" s="3"/>
       <c r="N653" s="3"/>
     </row>
-    <row r="654" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
         <v>1844</v>
       </c>
@@ -28406,7 +28850,7 @@
       <c r="M654" s="3"/>
       <c r="N654" s="3"/>
     </row>
-    <row r="655" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A655" s="3" t="s">
         <v>1846</v>
       </c>
@@ -28436,7 +28880,7 @@
       <c r="M655" s="3"/>
       <c r="N655" s="3"/>
     </row>
-    <row r="656" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A656" s="3" t="s">
         <v>1849</v>
       </c>
@@ -28466,7 +28910,7 @@
       <c r="M656" s="3"/>
       <c r="N656" s="3"/>
     </row>
-    <row r="657" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A657" s="3" t="s">
         <v>1852</v>
       </c>
@@ -28496,7 +28940,7 @@
       <c r="M657" s="3"/>
       <c r="N657" s="3"/>
     </row>
-    <row r="658" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A658" s="3" t="s">
         <v>1855</v>
       </c>
@@ -28532,7 +28976,7 @@
       </c>
       <c r="N658" s="3"/>
     </row>
-    <row r="659" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
         <v>1859</v>
       </c>
@@ -28568,7 +29012,7 @@
       </c>
       <c r="N659" s="3"/>
     </row>
-    <row r="660" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A660" s="3" t="s">
         <v>1862</v>
       </c>
@@ -28598,7 +29042,7 @@
       <c r="M660" s="3"/>
       <c r="N660" s="3"/>
     </row>
-    <row r="661" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A661" s="3" t="s">
         <v>1864</v>
       </c>
@@ -28628,7 +29072,7 @@
       <c r="M661" s="3"/>
       <c r="N661" s="3"/>
     </row>
-    <row r="662" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A662" s="3" t="s">
         <v>1867</v>
       </c>
@@ -28664,7 +29108,7 @@
       </c>
       <c r="N662" s="3"/>
     </row>
-    <row r="663" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A663" s="3" t="s">
         <v>1871</v>
       </c>
@@ -28704,7 +29148,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="664" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A664" s="3" t="s">
         <v>1876</v>
       </c>
@@ -28734,7 +29178,7 @@
       <c r="M664" s="3"/>
       <c r="N664" s="3"/>
     </row>
-    <row r="665" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A665" s="3" t="s">
         <v>1879</v>
       </c>
@@ -28774,7 +29218,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="666" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A666" s="3" t="s">
         <v>1883</v>
       </c>
@@ -28810,7 +29254,7 @@
       </c>
       <c r="N666" s="3"/>
     </row>
-    <row r="667" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A667" s="3" t="s">
         <v>1886</v>
       </c>
@@ -28840,7 +29284,7 @@
       <c r="M667" s="3"/>
       <c r="N667" s="3"/>
     </row>
-    <row r="668" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A668" s="3" t="s">
         <v>1888</v>
       </c>
@@ -28870,7 +29314,7 @@
       <c r="M668" s="3"/>
       <c r="N668" s="3"/>
     </row>
-    <row r="669" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A669" s="3" t="s">
         <v>1890</v>
       </c>
@@ -28900,7 +29344,7 @@
       <c r="M669" s="3"/>
       <c r="N669" s="3"/>
     </row>
-    <row r="670" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A670" s="3" t="s">
         <v>1892</v>
       </c>
@@ -28930,7 +29374,7 @@
       <c r="M670" s="3"/>
       <c r="N670" s="3"/>
     </row>
-    <row r="671" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A671" s="3" t="s">
         <v>1894</v>
       </c>
@@ -28960,7 +29404,7 @@
       <c r="M671" s="3"/>
       <c r="N671" s="3"/>
     </row>
-    <row r="672" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A672" s="3" t="s">
         <v>1896</v>
       </c>
@@ -28990,7 +29434,7 @@
       <c r="M672" s="3"/>
       <c r="N672" s="3"/>
     </row>
-    <row r="673" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A673" s="3" t="s">
         <v>1898</v>
       </c>
@@ -29020,7 +29464,7 @@
       <c r="M673" s="3"/>
       <c r="N673" s="3"/>
     </row>
-    <row r="674" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A674" s="3" t="s">
         <v>1901</v>
       </c>
@@ -29050,7 +29494,7 @@
       <c r="M674" s="3"/>
       <c r="N674" s="3"/>
     </row>
-    <row r="675" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A675" s="3" t="s">
         <v>1904</v>
       </c>
@@ -29080,7 +29524,7 @@
       <c r="M675" s="3"/>
       <c r="N675" s="3"/>
     </row>
-    <row r="676" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A676" s="3" t="s">
         <v>1907</v>
       </c>
@@ -29110,7 +29554,7 @@
       <c r="M676" s="3"/>
       <c r="N676" s="3"/>
     </row>
-    <row r="677" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A677" s="3" t="s">
         <v>1910</v>
       </c>
@@ -29140,7 +29584,7 @@
       <c r="M677" s="3"/>
       <c r="N677" s="3"/>
     </row>
-    <row r="678" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A678" s="3" t="s">
         <v>1913</v>
       </c>
@@ -29170,7 +29614,7 @@
       <c r="M678" s="3"/>
       <c r="N678" s="3"/>
     </row>
-    <row r="679" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A679" s="3" t="s">
         <v>1916</v>
       </c>
@@ -29200,7 +29644,7 @@
       <c r="M679" s="3"/>
       <c r="N679" s="3"/>
     </row>
-    <row r="680" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A680" s="3" t="s">
         <v>1919</v>
       </c>
@@ -29230,7 +29674,7 @@
       <c r="M680" s="3"/>
       <c r="N680" s="3"/>
     </row>
-    <row r="681" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A681" s="3" t="s">
         <v>1922</v>
       </c>
@@ -29260,7 +29704,7 @@
       <c r="M681" s="3"/>
       <c r="N681" s="3"/>
     </row>
-    <row r="682" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A682" s="3" t="s">
         <v>1925</v>
       </c>
@@ -29290,7 +29734,7 @@
       <c r="M682" s="3"/>
       <c r="N682" s="3"/>
     </row>
-    <row r="683" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A683" s="3" t="s">
         <v>1928</v>
       </c>
@@ -29320,7 +29764,7 @@
       <c r="M683" s="3"/>
       <c r="N683" s="3"/>
     </row>
-    <row r="684" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A684" s="3" t="s">
         <v>1931</v>
       </c>
@@ -29350,7 +29794,7 @@
       <c r="M684" s="3"/>
       <c r="N684" s="3"/>
     </row>
-    <row r="685" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A685" s="3" t="s">
         <v>1933</v>
       </c>
@@ -29386,7 +29830,7 @@
       </c>
       <c r="N685" s="3"/>
     </row>
-    <row r="686" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A686" s="3" t="s">
         <v>1937</v>
       </c>
@@ -29416,7 +29860,7 @@
       <c r="M686" s="3"/>
       <c r="N686" s="3"/>
     </row>
-    <row r="687" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A687" s="3" t="s">
         <v>1937</v>
       </c>
@@ -29446,7 +29890,7 @@
       <c r="M687" s="3"/>
       <c r="N687" s="3"/>
     </row>
-    <row r="688" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A688" s="3" t="s">
         <v>1940</v>
       </c>
@@ -29476,7 +29920,7 @@
       <c r="M688" s="3"/>
       <c r="N688" s="3"/>
     </row>
-    <row r="689" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A689" s="3" t="s">
         <v>1943</v>
       </c>
@@ -29506,7 +29950,7 @@
       <c r="M689" s="3"/>
       <c r="N689" s="3"/>
     </row>
-    <row r="690" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A690" s="3" t="s">
         <v>1945</v>
       </c>
@@ -29542,7 +29986,7 @@
       </c>
       <c r="N690" s="3"/>
     </row>
-    <row r="691" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A691" s="3" t="s">
         <v>1947</v>
       </c>
@@ -29578,7 +30022,7 @@
       </c>
       <c r="N691" s="3"/>
     </row>
-    <row r="692" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A692" s="3" t="s">
         <v>1949</v>
       </c>
@@ -29608,7 +30052,7 @@
       <c r="M692" s="3"/>
       <c r="N692" s="3"/>
     </row>
-    <row r="693" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A693" s="3" t="s">
         <v>1951</v>
       </c>
@@ -29646,7 +30090,7 @@
       </c>
       <c r="N693" s="3"/>
     </row>
-    <row r="694" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A694" s="3" t="s">
         <v>1954</v>
       </c>
@@ -29686,7 +30130,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="695" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A695" s="3" t="s">
         <v>1959</v>
       </c>
@@ -29716,7 +30160,7 @@
       <c r="M695" s="3"/>
       <c r="N695" s="3"/>
     </row>
-    <row r="696" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A696" s="3" t="s">
         <v>1959</v>
       </c>
@@ -29746,7 +30190,7 @@
       <c r="M696" s="3"/>
       <c r="N696" s="3"/>
     </row>
-    <row r="697" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A697" s="3" t="s">
         <v>1962</v>
       </c>
@@ -29776,7 +30220,7 @@
       <c r="M697" s="3"/>
       <c r="N697" s="3"/>
     </row>
-    <row r="698" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A698" s="3" t="s">
         <v>1964</v>
       </c>
@@ -29806,7 +30250,7 @@
       <c r="M698" s="3"/>
       <c r="N698" s="3"/>
     </row>
-    <row r="699" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A699" s="3" t="s">
         <v>1967</v>
       </c>
@@ -29836,7 +30280,7 @@
       <c r="M699" s="3"/>
       <c r="N699" s="3"/>
     </row>
-    <row r="700" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A700" s="3" t="s">
         <v>1969</v>
       </c>
@@ -29866,7 +30310,7 @@
       <c r="M700" s="3"/>
       <c r="N700" s="3"/>
     </row>
-    <row r="701" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A701" s="3" t="s">
         <v>1971</v>
       </c>
@@ -29896,7 +30340,7 @@
       <c r="M701" s="3"/>
       <c r="N701" s="3"/>
     </row>
-    <row r="702" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A702" s="3" t="s">
         <v>1974</v>
       </c>
@@ -29932,7 +30376,7 @@
       </c>
       <c r="N702" s="3"/>
     </row>
-    <row r="703" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A703" s="3" t="s">
         <v>1977</v>
       </c>
@@ -29968,7 +30412,7 @@
       </c>
       <c r="N703" s="3"/>
     </row>
-    <row r="704" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A704" s="3" t="s">
         <v>1981</v>
       </c>
@@ -29998,7 +30442,7 @@
       <c r="M704" s="3"/>
       <c r="N704" s="3"/>
     </row>
-    <row r="705" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A705" s="3" t="s">
         <v>1983</v>
       </c>
@@ -30028,7 +30472,7 @@
       <c r="M705" s="3"/>
       <c r="N705" s="3"/>
     </row>
-    <row r="706" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A706" s="3" t="s">
         <v>1986</v>
       </c>
@@ -30064,7 +30508,7 @@
       </c>
       <c r="N706" s="3"/>
     </row>
-    <row r="707" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A707" s="3" t="s">
         <v>1989</v>
       </c>
@@ -30100,7 +30544,7 @@
       </c>
       <c r="N707" s="3"/>
     </row>
-    <row r="708" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A708" s="3" t="s">
         <v>1992</v>
       </c>
@@ -30130,7 +30574,7 @@
       <c r="M708" s="3"/>
       <c r="N708" s="3"/>
     </row>
-    <row r="709" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A709" s="3" t="s">
         <v>1995</v>
       </c>
@@ -30166,7 +30610,7 @@
       </c>
       <c r="N709" s="3"/>
     </row>
-    <row r="710" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A710" s="3" t="s">
         <v>1997</v>
       </c>
@@ -30196,7 +30640,7 @@
       <c r="M710" s="3"/>
       <c r="N710" s="3"/>
     </row>
-    <row r="711" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A711" s="3" t="s">
         <v>1999</v>
       </c>
@@ -30226,7 +30670,7 @@
       <c r="M711" s="3"/>
       <c r="N711" s="3"/>
     </row>
-    <row r="712" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A712" s="3" t="s">
         <v>2001</v>
       </c>
@@ -30256,7 +30700,7 @@
       <c r="M712" s="3"/>
       <c r="N712" s="3"/>
     </row>
-    <row r="713" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A713" s="3" t="s">
         <v>2004</v>
       </c>
@@ -30286,7 +30730,7 @@
       <c r="M713" s="3"/>
       <c r="N713" s="3"/>
     </row>
-    <row r="714" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A714" s="3" t="s">
         <v>2007</v>
       </c>
@@ -30326,7 +30770,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="715" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A715" s="3" t="s">
         <v>2012</v>
       </c>
@@ -30356,7 +30800,7 @@
       <c r="M715" s="3"/>
       <c r="N715" s="3"/>
     </row>
-    <row r="716" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A716" s="3" t="s">
         <v>2014</v>
       </c>
@@ -30386,7 +30830,7 @@
       <c r="M716" s="3"/>
       <c r="N716" s="3"/>
     </row>
-    <row r="717" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A717" s="3" t="s">
         <v>2017</v>
       </c>
@@ -30422,7 +30866,7 @@
       </c>
       <c r="N717" s="3"/>
     </row>
-    <row r="718" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A718" s="3" t="s">
         <v>2020</v>
       </c>
@@ -30458,7 +30902,7 @@
       </c>
       <c r="N718" s="3"/>
     </row>
-    <row r="719" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A719" s="3" t="s">
         <v>2023</v>
       </c>
@@ -30494,7 +30938,7 @@
       </c>
       <c r="N719" s="3"/>
     </row>
-    <row r="720" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A720" s="3" t="s">
         <v>2025</v>
       </c>
@@ -30530,7 +30974,7 @@
       </c>
       <c r="N720" s="3"/>
     </row>
-    <row r="721" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A721" s="3" t="s">
         <v>2029</v>
       </c>
@@ -30560,7 +31004,7 @@
       <c r="M721" s="3"/>
       <c r="N721" s="3"/>
     </row>
-    <row r="722" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A722" s="3" t="s">
         <v>2031</v>
       </c>
@@ -30590,7 +31034,7 @@
       <c r="M722" s="3"/>
       <c r="N722" s="3"/>
     </row>
-    <row r="723" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A723" s="3" t="s">
         <v>2034</v>
       </c>
@@ -30620,7 +31064,7 @@
       <c r="M723" s="3"/>
       <c r="N723" s="3"/>
     </row>
-    <row r="724" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A724" s="3" t="s">
         <v>2037</v>
       </c>
@@ -30660,7 +31104,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="725" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A725" s="3" t="s">
         <v>2042</v>
       </c>
@@ -30698,7 +31142,7 @@
       </c>
       <c r="N725" s="3"/>
     </row>
-    <row r="726" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A726" s="3" t="s">
         <v>2046</v>
       </c>
@@ -30728,7 +31172,7 @@
       <c r="M726" s="3"/>
       <c r="N726" s="3"/>
     </row>
-    <row r="727" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A727" s="3" t="s">
         <v>2048</v>
       </c>
@@ -30758,7 +31202,7 @@
       <c r="M727" s="3"/>
       <c r="N727" s="3"/>
     </row>
-    <row r="728" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A728" s="3" t="s">
         <v>2051</v>
       </c>
@@ -30788,7 +31232,7 @@
       <c r="M728" s="3"/>
       <c r="N728" s="3"/>
     </row>
-    <row r="729" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A729" s="3" t="s">
         <v>2053</v>
       </c>
@@ -30818,7 +31262,7 @@
       <c r="M729" s="3"/>
       <c r="N729" s="3"/>
     </row>
-    <row r="730" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A730" s="3" t="s">
         <v>2055</v>
       </c>
@@ -30854,7 +31298,7 @@
       </c>
       <c r="N730" s="3"/>
     </row>
-    <row r="731" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A731" s="3" t="s">
         <v>2058</v>
       </c>
@@ -30890,7 +31334,7 @@
       </c>
       <c r="N731" s="3"/>
     </row>
-    <row r="732" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A732" s="3" t="s">
         <v>2061</v>
       </c>
@@ -30926,7 +31370,7 @@
       </c>
       <c r="N732" s="3"/>
     </row>
-    <row r="733" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A733" s="3" t="s">
         <v>2064</v>
       </c>
@@ -30956,7 +31400,7 @@
       <c r="M733" s="3"/>
       <c r="N733" s="3"/>
     </row>
-    <row r="734" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A734" s="3" t="s">
         <v>2067</v>
       </c>
@@ -30986,7 +31430,7 @@
       <c r="M734" s="3"/>
       <c r="N734" s="3"/>
     </row>
-    <row r="735" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A735" s="3" t="s">
         <v>2070</v>
       </c>
@@ -31016,7 +31460,7 @@
       <c r="M735" s="3"/>
       <c r="N735" s="3"/>
     </row>
-    <row r="736" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A736" s="3" t="s">
         <v>2073</v>
       </c>
@@ -31046,7 +31490,7 @@
       <c r="M736" s="3"/>
       <c r="N736" s="3"/>
     </row>
-    <row r="737" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A737" s="3" t="s">
         <v>2076</v>
       </c>
@@ -31076,7 +31520,7 @@
       <c r="M737" s="3"/>
       <c r="N737" s="3"/>
     </row>
-    <row r="738" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A738" s="3" t="s">
         <v>2078</v>
       </c>
@@ -31106,7 +31550,7 @@
       <c r="M738" s="3"/>
       <c r="N738" s="3"/>
     </row>
-    <row r="739" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A739" s="3" t="s">
         <v>2081</v>
       </c>
@@ -31142,7 +31586,7 @@
       </c>
       <c r="N739" s="3"/>
     </row>
-    <row r="740" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A740" s="3" t="s">
         <v>2085</v>
       </c>
@@ -31172,7 +31616,7 @@
       <c r="M740" s="3"/>
       <c r="N740" s="3"/>
     </row>
-    <row r="741" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A741" s="3" t="s">
         <v>2088</v>
       </c>
@@ -31202,7 +31646,7 @@
       <c r="M741" s="3"/>
       <c r="N741" s="3"/>
     </row>
-    <row r="742" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A742" s="3" t="s">
         <v>2091</v>
       </c>
@@ -31211,7 +31655,7 @@
         <v>112</v>
       </c>
       <c r="D742" s="3">
-        <v>5622271458</v>
+        <v>5622402770</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>53</v>
@@ -31232,7 +31676,7 @@
       <c r="M742" s="3"/>
       <c r="N742" s="3"/>
     </row>
-    <row r="743" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A743" s="3" t="s">
         <v>2091</v>
       </c>
@@ -31241,7 +31685,7 @@
         <v>112</v>
       </c>
       <c r="D743" s="3">
-        <v>5622402770</v>
+        <v>5622271458</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>53</v>
@@ -31262,7 +31706,7 @@
       <c r="M743" s="3"/>
       <c r="N743" s="3"/>
     </row>
-    <row r="744" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A744" s="3" t="s">
         <v>2094</v>
       </c>
@@ -31302,7 +31746,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="745" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A745" s="3" t="s">
         <v>2099</v>
       </c>
@@ -31342,7 +31786,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="746" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A746" s="3" t="s">
         <v>2104</v>
       </c>
@@ -31372,7 +31816,7 @@
       <c r="M746" s="3"/>
       <c r="N746" s="3"/>
     </row>
-    <row r="747" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A747" s="3" t="s">
         <v>2107</v>
       </c>
@@ -31402,7 +31846,7 @@
       <c r="M747" s="3"/>
       <c r="N747" s="3"/>
     </row>
-    <row r="748" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A748" s="3" t="s">
         <v>2110</v>
       </c>
@@ -31432,7 +31876,7 @@
       <c r="M748" s="3"/>
       <c r="N748" s="3"/>
     </row>
-    <row r="749" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A749" s="3" t="s">
         <v>2113</v>
       </c>
@@ -31468,7 +31912,7 @@
       </c>
       <c r="N749" s="3"/>
     </row>
-    <row r="750" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A750" s="3" t="s">
         <v>2116</v>
       </c>
@@ -31508,7 +31952,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="751" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A751" s="3" t="s">
         <v>2121</v>
       </c>
@@ -31544,7 +31988,7 @@
       </c>
       <c r="N751" s="3"/>
     </row>
-    <row r="752" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A752" s="3" t="s">
         <v>2123</v>
       </c>
@@ -31580,7 +32024,7 @@
       </c>
       <c r="N752" s="3"/>
     </row>
-    <row r="753" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A753" s="3" t="s">
         <v>2126</v>
       </c>
@@ -31616,7 +32060,7 @@
       </c>
       <c r="N753" s="3"/>
     </row>
-    <row r="754" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A754" s="3" t="s">
         <v>2130</v>
       </c>
@@ -31646,7 +32090,7 @@
       <c r="M754" s="3"/>
       <c r="N754" s="3"/>
     </row>
-    <row r="755" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A755" s="3" t="s">
         <v>2133</v>
       </c>
@@ -31676,7 +32120,7 @@
       <c r="M755" s="3"/>
       <c r="N755" s="3"/>
     </row>
-    <row r="756" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A756" s="3" t="s">
         <v>2136</v>
       </c>
@@ -31706,7 +32150,7 @@
       <c r="M756" s="3"/>
       <c r="N756" s="3"/>
     </row>
-    <row r="757" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A757" s="3" t="s">
         <v>2139</v>
       </c>
@@ -31736,7 +32180,7 @@
       <c r="M757" s="3"/>
       <c r="N757" s="3"/>
     </row>
-    <row r="758" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A758" s="3" t="s">
         <v>2142</v>
       </c>
@@ -31766,7 +32210,7 @@
       <c r="M758" s="3"/>
       <c r="N758" s="3"/>
     </row>
-    <row r="759" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A759" s="3" t="s">
         <v>2145</v>
       </c>
@@ -31802,7 +32246,7 @@
       </c>
       <c r="N759" s="3"/>
     </row>
-    <row r="760" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A760" s="3" t="s">
         <v>2148</v>
       </c>
@@ -31832,7 +32276,7 @@
       <c r="M760" s="3"/>
       <c r="N760" s="3"/>
     </row>
-    <row r="761" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A761" s="3" t="s">
         <v>2150</v>
       </c>
@@ -31862,7 +32306,7 @@
       <c r="M761" s="3"/>
       <c r="N761" s="3"/>
     </row>
-    <row r="762" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A762" s="3" t="s">
         <v>2153</v>
       </c>
@@ -31898,7 +32342,7 @@
       </c>
       <c r="N762" s="3"/>
     </row>
-    <row r="763" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A763" s="3" t="s">
         <v>2156</v>
       </c>
@@ -31934,7 +32378,7 @@
       </c>
       <c r="N763" s="3"/>
     </row>
-    <row r="764" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A764" s="3" t="s">
         <v>2159</v>
       </c>
@@ -31964,7 +32408,7 @@
       <c r="M764" s="3"/>
       <c r="N764" s="3"/>
     </row>
-    <row r="765" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A765" s="3" t="s">
         <v>2161</v>
       </c>
@@ -31994,7 +32438,7 @@
       <c r="M765" s="3"/>
       <c r="N765" s="3"/>
     </row>
-    <row r="766" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A766" s="3" t="s">
         <v>2164</v>
       </c>
@@ -32024,7 +32468,7 @@
       <c r="M766" s="3"/>
       <c r="N766" s="3"/>
     </row>
-    <row r="767" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A767" s="3" t="s">
         <v>2166</v>
       </c>
@@ -32054,7 +32498,7 @@
       <c r="M767" s="3"/>
       <c r="N767" s="3"/>
     </row>
-    <row r="768" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A768" s="3" t="s">
         <v>2169</v>
       </c>
@@ -32090,7 +32534,7 @@
       </c>
       <c r="N768" s="3"/>
     </row>
-    <row r="769" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A769" s="3" t="s">
         <v>2172</v>
       </c>
@@ -32130,7 +32574,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="770" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A770" s="3" t="s">
         <v>2177</v>
       </c>
@@ -32166,7 +32610,7 @@
       </c>
       <c r="N770" s="3"/>
     </row>
-    <row r="771" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A771" s="3" t="s">
         <v>2180</v>
       </c>
@@ -32202,7 +32646,7 @@
       </c>
       <c r="N771" s="3"/>
     </row>
-    <row r="772" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A772" s="3" t="s">
         <v>2182</v>
       </c>
@@ -32232,7 +32676,7 @@
       <c r="M772" s="3"/>
       <c r="N772" s="3"/>
     </row>
-    <row r="773" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
         <v>2185</v>
       </c>
@@ -32268,7 +32712,7 @@
       </c>
       <c r="N773" s="3"/>
     </row>
-    <row r="774" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
         <v>2187</v>
       </c>
@@ -32304,7 +32748,7 @@
       </c>
       <c r="N774" s="3"/>
     </row>
-    <row r="775" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A775" s="3" t="s">
         <v>2190</v>
       </c>
@@ -32334,7 +32778,7 @@
       <c r="M775" s="3"/>
       <c r="N775" s="3"/>
     </row>
-    <row r="776" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A776" s="3" t="s">
         <v>2192</v>
       </c>
@@ -32370,7 +32814,7 @@
       </c>
       <c r="N776" s="3"/>
     </row>
-    <row r="777" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A777" s="3" t="s">
         <v>2195</v>
       </c>
@@ -32400,7 +32844,7 @@
       <c r="M777" s="3"/>
       <c r="N777" s="3"/>
     </row>
-    <row r="778" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A778" s="3" t="s">
         <v>2197</v>
       </c>
@@ -32430,7 +32874,7 @@
       <c r="M778" s="3"/>
       <c r="N778" s="3"/>
     </row>
-    <row r="779" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A779" s="3" t="s">
         <v>2199</v>
       </c>
@@ -32466,7 +32910,7 @@
       </c>
       <c r="N779" s="3"/>
     </row>
-    <row r="780" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A780" s="3" t="s">
         <v>2201</v>
       </c>
@@ -32496,7 +32940,7 @@
       <c r="M780" s="3"/>
       <c r="N780" s="3"/>
     </row>
-    <row r="781" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A781" s="3" t="s">
         <v>2203</v>
       </c>
@@ -32530,7 +32974,7 @@
       <c r="M781" s="3"/>
       <c r="N781" s="3"/>
     </row>
-    <row r="782" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A782" s="3" t="s">
         <v>2207</v>
       </c>
@@ -32560,7 +33004,7 @@
       <c r="M782" s="3"/>
       <c r="N782" s="3"/>
     </row>
-    <row r="783" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A783" s="3" t="s">
         <v>2210</v>
       </c>
@@ -32590,7 +33034,7 @@
       <c r="M783" s="3"/>
       <c r="N783" s="3"/>
     </row>
-    <row r="784" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A784" s="3" t="s">
         <v>2212</v>
       </c>
@@ -32620,7 +33064,7 @@
       <c r="M784" s="3"/>
       <c r="N784" s="3"/>
     </row>
-    <row r="785" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A785" s="3" t="s">
         <v>2215</v>
       </c>
@@ -32654,7 +33098,7 @@
       <c r="M785" s="3"/>
       <c r="N785" s="3"/>
     </row>
-    <row r="786" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A786" s="3" t="s">
         <v>2218</v>
       </c>
@@ -32684,7 +33128,7 @@
       <c r="M786" s="3"/>
       <c r="N786" s="3"/>
     </row>
-    <row r="787" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A787" s="3" t="s">
         <v>2221</v>
       </c>
@@ -32720,7 +33164,7 @@
       </c>
       <c r="N787" s="3"/>
     </row>
-    <row r="788" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A788" s="3" t="s">
         <v>2225</v>
       </c>
@@ -32750,7 +33194,7 @@
       <c r="M788" s="3"/>
       <c r="N788" s="3"/>
     </row>
-    <row r="789" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A789" s="3" t="s">
         <v>2227</v>
       </c>
@@ -32780,7 +33224,7 @@
       <c r="M789" s="3"/>
       <c r="N789" s="3"/>
     </row>
-    <row r="790" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A790" s="3" t="s">
         <v>2229</v>
       </c>
@@ -32816,7 +33260,7 @@
       </c>
       <c r="N790" s="3"/>
     </row>
-    <row r="791" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A791" s="3" t="s">
         <v>2231</v>
       </c>
@@ -32846,7 +33290,7 @@
       <c r="M791" s="3"/>
       <c r="N791" s="3"/>
     </row>
-    <row r="792" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A792" s="3" t="s">
         <v>2233</v>
       </c>
@@ -32876,7 +33320,7 @@
       <c r="M792" s="3"/>
       <c r="N792" s="3"/>
     </row>
-    <row r="793" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A793" s="3" t="s">
         <v>2236</v>
       </c>
@@ -32906,7 +33350,7 @@
       <c r="M793" s="3"/>
       <c r="N793" s="3"/>
     </row>
-    <row r="794" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A794" s="3" t="s">
         <v>2238</v>
       </c>
@@ -32936,7 +33380,7 @@
       <c r="M794" s="3"/>
       <c r="N794" s="3"/>
     </row>
-    <row r="795" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A795" s="3" t="s">
         <v>2240</v>
       </c>
@@ -32966,7 +33410,7 @@
       <c r="M795" s="3"/>
       <c r="N795" s="3"/>
     </row>
-    <row r="796" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A796" s="3" t="s">
         <v>2242</v>
       </c>
@@ -33002,7 +33446,7 @@
       </c>
       <c r="N796" s="3"/>
     </row>
-    <row r="797" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A797" s="3" t="s">
         <v>2246</v>
       </c>
@@ -33038,7 +33482,7 @@
       </c>
       <c r="N797" s="3"/>
     </row>
-    <row r="798" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A798" s="3" t="s">
         <v>2250</v>
       </c>
@@ -33068,7 +33512,7 @@
       <c r="M798" s="3"/>
       <c r="N798" s="3"/>
     </row>
-    <row r="799" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A799" s="3" t="s">
         <v>2252</v>
       </c>
@@ -33098,7 +33542,7 @@
       <c r="M799" s="3"/>
       <c r="N799" s="3"/>
     </row>
-    <row r="800" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A800" s="3" t="s">
         <v>2255</v>
       </c>
@@ -33128,7 +33572,7 @@
       <c r="M800" s="3"/>
       <c r="N800" s="3"/>
     </row>
-    <row r="801" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A801" s="3" t="s">
         <v>2255</v>
       </c>
@@ -33164,7 +33608,7 @@
       </c>
       <c r="N801" s="3"/>
     </row>
-    <row r="802" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A802" s="3" t="s">
         <v>2260</v>
       </c>
@@ -33194,7 +33638,7 @@
       <c r="M802" s="3"/>
       <c r="N802" s="3"/>
     </row>
-    <row r="803" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A803" s="3" t="s">
         <v>2263</v>
       </c>
@@ -33224,7 +33668,7 @@
       <c r="M803" s="3"/>
       <c r="N803" s="3"/>
     </row>
-    <row r="804" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A804" s="3" t="s">
         <v>2266</v>
       </c>
@@ -33260,7 +33704,7 @@
       </c>
       <c r="N804" s="3"/>
     </row>
-    <row r="805" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A805" s="3" t="s">
         <v>2270</v>
       </c>
@@ -33290,7 +33734,7 @@
       <c r="M805" s="3"/>
       <c r="N805" s="3"/>
     </row>
-    <row r="806" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A806" s="3" t="s">
         <v>2273</v>
       </c>
@@ -33328,7 +33772,7 @@
       </c>
       <c r="N806" s="3"/>
     </row>
-    <row r="807" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A807" s="3" t="s">
         <v>2277</v>
       </c>
@@ -33358,7 +33802,7 @@
       <c r="M807" s="3"/>
       <c r="N807" s="3"/>
     </row>
-    <row r="808" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A808" s="3" t="s">
         <v>2279</v>
       </c>
@@ -33388,7 +33832,7 @@
       <c r="M808" s="3"/>
       <c r="N808" s="3"/>
     </row>
-    <row r="809" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A809" s="3" t="s">
         <v>2282</v>
       </c>
@@ -33418,7 +33862,7 @@
       <c r="M809" s="3"/>
       <c r="N809" s="3"/>
     </row>
-    <row r="810" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A810" s="3" t="s">
         <v>2285</v>
       </c>
@@ -33448,7 +33892,7 @@
       <c r="M810" s="3"/>
       <c r="N810" s="3"/>
     </row>
-    <row r="811" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A811" s="3" t="s">
         <v>2288</v>
       </c>
@@ -33478,7 +33922,7 @@
       <c r="M811" s="3"/>
       <c r="N811" s="3"/>
     </row>
-    <row r="812" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A812" s="3" t="s">
         <v>2290</v>
       </c>
@@ -33508,7 +33952,7 @@
       <c r="M812" s="3"/>
       <c r="N812" s="3"/>
     </row>
-    <row r="813" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A813" s="3" t="s">
         <v>2293</v>
       </c>
@@ -33538,7 +33982,7 @@
       <c r="M813" s="3"/>
       <c r="N813" s="3"/>
     </row>
-    <row r="814" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A814" s="3" t="s">
         <v>2296</v>
       </c>
@@ -33574,7 +34018,7 @@
       </c>
       <c r="N814" s="3"/>
     </row>
-    <row r="815" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A815" s="3" t="s">
         <v>2299</v>
       </c>
@@ -33604,7 +34048,7 @@
       <c r="M815" s="3"/>
       <c r="N815" s="3"/>
     </row>
-    <row r="816" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A816" s="3" t="s">
         <v>2302</v>
       </c>
@@ -33634,7 +34078,7 @@
       <c r="M816" s="3"/>
       <c r="N816" s="3"/>
     </row>
-    <row r="817" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A817" s="3" t="s">
         <v>2304</v>
       </c>
@@ -33674,7 +34118,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="818" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A818" s="3" t="s">
         <v>2308</v>
       </c>
@@ -33704,7 +34148,7 @@
       <c r="M818" s="3"/>
       <c r="N818" s="3"/>
     </row>
-    <row r="819" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A819" s="3" t="s">
         <v>2311</v>
       </c>
@@ -33734,7 +34178,7 @@
       <c r="M819" s="3"/>
       <c r="N819" s="3"/>
     </row>
-    <row r="820" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A820" s="3" t="s">
         <v>2314</v>
       </c>
@@ -33764,7 +34208,7 @@
       <c r="M820" s="3"/>
       <c r="N820" s="3"/>
     </row>
-    <row r="821" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A821" s="3" t="s">
         <v>2317</v>
       </c>
@@ -33794,7 +34238,7 @@
       <c r="M821" s="3"/>
       <c r="N821" s="3"/>
     </row>
-    <row r="822" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A822" s="3" t="s">
         <v>2320</v>
       </c>
@@ -33830,7 +34274,7 @@
       </c>
       <c r="N822" s="3"/>
     </row>
-    <row r="823" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A823" s="3" t="s">
         <v>2324</v>
       </c>
@@ -33860,7 +34304,7 @@
       <c r="M823" s="3"/>
       <c r="N823" s="3"/>
     </row>
-    <row r="824" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A824" s="3" t="s">
         <v>2327</v>
       </c>
@@ -33896,7 +34340,7 @@
       </c>
       <c r="N824" s="3"/>
     </row>
-    <row r="825" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A825" s="3" t="s">
         <v>2331</v>
       </c>
@@ -33926,7 +34370,7 @@
       <c r="M825" s="3"/>
       <c r="N825" s="3"/>
     </row>
-    <row r="826" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A826" s="3" t="s">
         <v>2334</v>
       </c>
@@ -33956,7 +34400,7 @@
       <c r="M826" s="3"/>
       <c r="N826" s="3"/>
     </row>
-    <row r="827" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A827" s="3" t="s">
         <v>2337</v>
       </c>
@@ -33992,7 +34436,7 @@
       </c>
       <c r="N827" s="3"/>
     </row>
-    <row r="828" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A828" s="3" t="s">
         <v>2341</v>
       </c>
@@ -34022,7 +34466,7 @@
       <c r="M828" s="3"/>
       <c r="N828" s="3"/>
     </row>
-    <row r="829" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A829" s="3" t="s">
         <v>2344</v>
       </c>
@@ -34052,7 +34496,7 @@
       <c r="M829" s="3"/>
       <c r="N829" s="3"/>
     </row>
-    <row r="830" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A830" s="3" t="s">
         <v>2346</v>
       </c>
@@ -34088,7 +34532,7 @@
       </c>
       <c r="N830" s="3"/>
     </row>
-    <row r="831" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A831" s="3" t="s">
         <v>2349</v>
       </c>
@@ -34124,7 +34568,7 @@
       </c>
       <c r="N831" s="3"/>
     </row>
-    <row r="832" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A832" s="3" t="s">
         <v>2352</v>
       </c>
@@ -34154,7 +34598,7 @@
       <c r="M832" s="3"/>
       <c r="N832" s="3"/>
     </row>
-    <row r="833" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A833" s="3" t="s">
         <v>2354</v>
       </c>
@@ -34174,19 +34618,25 @@
       <c r="G833" s="3" t="s">
         <v>2356</v>
       </c>
-      <c r="H833" s="3"/>
+      <c r="H833" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I833" s="3"/>
       <c r="J833" s="3"/>
       <c r="K833" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L833" s="3"/>
-      <c r="M833" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L833" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M833" s="3" t="s">
+        <v>2357</v>
+      </c>
       <c r="N833" s="3"/>
     </row>
-    <row r="834" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A834" s="3" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="B834" s="3"/>
       <c r="C834" s="3">
@@ -34202,7 +34652,7 @@
         <v>714</v>
       </c>
       <c r="G834" s="3" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="H834" s="3"/>
       <c r="I834" s="3"/>
@@ -34214,6 +34664,1728 @@
       <c r="M834" s="3"/>
       <c r="N834" s="3"/>
     </row>
+    <row r="835" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A835" s="3" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B835" s="3"/>
+      <c r="C835" s="3">
+        <v>112</v>
+      </c>
+      <c r="D835" s="3">
+        <v>5731159797</v>
+      </c>
+      <c r="E835" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F835" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G835" s="3" t="s">
+        <v>2361</v>
+      </c>
+      <c r="H835" s="3"/>
+      <c r="I835" s="3"/>
+      <c r="J835" s="3"/>
+      <c r="K835" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L835" s="3"/>
+      <c r="M835" s="3"/>
+      <c r="N835" s="3"/>
+    </row>
+    <row r="836" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A836" s="3" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B836" s="3"/>
+      <c r="C836" s="3">
+        <v>113</v>
+      </c>
+      <c r="D836" s="3">
+        <v>5735049101</v>
+      </c>
+      <c r="E836" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F836" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G836" s="3" t="s">
+        <v>2363</v>
+      </c>
+      <c r="H836" s="3"/>
+      <c r="I836" s="3"/>
+      <c r="J836" s="3"/>
+      <c r="K836" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L836" s="3"/>
+      <c r="M836" s="3"/>
+      <c r="N836" s="3"/>
+    </row>
+    <row r="837" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A837" s="3" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B837" s="3"/>
+      <c r="C837" s="3">
+        <v>113</v>
+      </c>
+      <c r="D837" s="3">
+        <v>5728891809</v>
+      </c>
+      <c r="E837" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F837" s="3" t="s">
+        <v>2365</v>
+      </c>
+      <c r="G837" s="3" t="s">
+        <v>2366</v>
+      </c>
+      <c r="H837" s="3"/>
+      <c r="I837" s="3"/>
+      <c r="J837" s="3"/>
+      <c r="K837" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L837" s="3"/>
+      <c r="M837" s="3"/>
+      <c r="N837" s="3"/>
+    </row>
+    <row r="838" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A838" s="3" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B838" s="3"/>
+      <c r="C838" s="3">
+        <v>113</v>
+      </c>
+      <c r="D838" s="3">
+        <v>5729517169</v>
+      </c>
+      <c r="E838" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F838" s="3" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G838" s="3" t="s">
+        <v>2369</v>
+      </c>
+      <c r="H838" s="3"/>
+      <c r="I838" s="3"/>
+      <c r="J838" s="3"/>
+      <c r="K838" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L838" s="3"/>
+      <c r="M838" s="3"/>
+      <c r="N838" s="3"/>
+    </row>
+    <row r="839" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A839" s="3" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B839" s="3"/>
+      <c r="C839" s="3">
+        <v>113</v>
+      </c>
+      <c r="D839" s="3">
+        <v>5730059592</v>
+      </c>
+      <c r="E839" s="3" t="s">
+        <v>2371</v>
+      </c>
+      <c r="F839" s="3" t="s">
+        <v>2372</v>
+      </c>
+      <c r="G839" s="3" t="s">
+        <v>2373</v>
+      </c>
+      <c r="H839" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I839" s="3"/>
+      <c r="J839" s="3"/>
+      <c r="K839" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L839" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M839" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="N839" s="3"/>
+    </row>
+    <row r="840" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A840" s="3" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B840" s="3"/>
+      <c r="C840" s="3">
+        <v>111</v>
+      </c>
+      <c r="D840" s="3">
+        <v>5736929717</v>
+      </c>
+      <c r="E840" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F840" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G840" s="3" t="s">
+        <v>2375</v>
+      </c>
+      <c r="H840" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I840" s="3"/>
+      <c r="J840" s="3"/>
+      <c r="K840" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L840" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M840" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="N840" s="3"/>
+    </row>
+    <row r="841" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A841" s="3" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B841" s="3"/>
+      <c r="C841" s="3">
+        <v>111</v>
+      </c>
+      <c r="D841" s="3">
+        <v>5737160564</v>
+      </c>
+      <c r="E841" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F841" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G841" s="3" t="s">
+        <v>2377</v>
+      </c>
+      <c r="H841" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I841" s="3"/>
+      <c r="J841" s="3"/>
+      <c r="K841" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L841" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M841" s="3" t="s">
+        <v>2378</v>
+      </c>
+      <c r="N841" s="3"/>
+    </row>
+    <row r="842" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A842" s="3" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B842" s="3"/>
+      <c r="C842" s="3">
+        <v>111</v>
+      </c>
+      <c r="D842" s="3">
+        <v>5737691736</v>
+      </c>
+      <c r="E842" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F842" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="G842" s="3" t="s">
+        <v>2380</v>
+      </c>
+      <c r="H842" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I842" s="3"/>
+      <c r="J842" s="3"/>
+      <c r="K842" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L842" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M842" s="3" t="s">
+        <v>2381</v>
+      </c>
+      <c r="N842" s="3"/>
+    </row>
+    <row r="843" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A843" s="3" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B843" s="3"/>
+      <c r="C843" s="3">
+        <v>111</v>
+      </c>
+      <c r="D843" s="3">
+        <v>5737924755</v>
+      </c>
+      <c r="E843" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F843" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G843" s="3" t="s">
+        <v>2383</v>
+      </c>
+      <c r="H843" s="3"/>
+      <c r="I843" s="3"/>
+      <c r="J843" s="3"/>
+      <c r="K843" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L843" s="3"/>
+      <c r="M843" s="3"/>
+      <c r="N843" s="3"/>
+    </row>
+    <row r="844" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A844" s="3" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B844" s="3"/>
+      <c r="C844" s="3">
+        <v>112</v>
+      </c>
+      <c r="D844" s="3">
+        <v>5738675701</v>
+      </c>
+      <c r="E844" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F844" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G844" s="3" t="s">
+        <v>2385</v>
+      </c>
+      <c r="H844" s="3"/>
+      <c r="I844" s="3"/>
+      <c r="J844" s="3"/>
+      <c r="K844" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L844" s="3"/>
+      <c r="M844" s="3"/>
+      <c r="N844" s="3"/>
+    </row>
+    <row r="845" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A845" s="3" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B845" s="3"/>
+      <c r="C845" s="3">
+        <v>113</v>
+      </c>
+      <c r="D845" s="3">
+        <v>5738885891</v>
+      </c>
+      <c r="E845" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F845" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G845" s="3" t="s">
+        <v>2387</v>
+      </c>
+      <c r="H845" s="3"/>
+      <c r="I845" s="3"/>
+      <c r="J845" s="3"/>
+      <c r="K845" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L845" s="3"/>
+      <c r="M845" s="3"/>
+      <c r="N845" s="3"/>
+    </row>
+    <row r="846" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A846" s="3" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B846" s="3"/>
+      <c r="C846" s="3">
+        <v>112</v>
+      </c>
+      <c r="D846" s="3">
+        <v>5738901718</v>
+      </c>
+      <c r="E846" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F846" s="3" t="s">
+        <v>2389</v>
+      </c>
+      <c r="G846" s="3" t="s">
+        <v>2390</v>
+      </c>
+      <c r="H846" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I846" s="3"/>
+      <c r="J846" s="3"/>
+      <c r="K846" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L846" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M846" s="3" t="s">
+        <v>2381</v>
+      </c>
+      <c r="N846" s="3"/>
+    </row>
+    <row r="847" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A847" s="3" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B847" s="3"/>
+      <c r="C847" s="3">
+        <v>111</v>
+      </c>
+      <c r="D847" s="3">
+        <v>5738926901</v>
+      </c>
+      <c r="E847" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F847" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G847" s="3" t="s">
+        <v>2392</v>
+      </c>
+      <c r="H847" s="3"/>
+      <c r="I847" s="3"/>
+      <c r="J847" s="3"/>
+      <c r="K847" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L847" s="3"/>
+      <c r="M847" s="3"/>
+      <c r="N847" s="3"/>
+    </row>
+    <row r="848" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A848" s="3" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B848" s="3"/>
+      <c r="C848" s="3">
+        <v>110</v>
+      </c>
+      <c r="D848" s="3">
+        <v>5738989826</v>
+      </c>
+      <c r="E848" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F848" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G848" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="H848" s="3"/>
+      <c r="I848" s="3"/>
+      <c r="J848" s="3"/>
+      <c r="K848" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L848" s="3"/>
+      <c r="M848" s="3"/>
+      <c r="N848" s="3"/>
+    </row>
+    <row r="849" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A849" s="3" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B849" s="3"/>
+      <c r="C849" s="3">
+        <v>112</v>
+      </c>
+      <c r="D849" s="3">
+        <v>5739051902</v>
+      </c>
+      <c r="E849" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F849" s="3" t="s">
+        <v>2396</v>
+      </c>
+      <c r="G849" s="3" t="s">
+        <v>2397</v>
+      </c>
+      <c r="H849" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I849" s="3"/>
+      <c r="J849" s="3"/>
+      <c r="K849" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L849" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M849" s="3" t="s">
+        <v>2381</v>
+      </c>
+      <c r="N849" s="3"/>
+    </row>
+    <row r="850" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A850" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B850" s="3"/>
+      <c r="C850" s="3">
+        <v>113</v>
+      </c>
+      <c r="D850" s="3">
+        <v>5745461605</v>
+      </c>
+      <c r="E850" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F850" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G850" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="H850" s="3"/>
+      <c r="I850" s="3"/>
+      <c r="J850" s="3"/>
+      <c r="K850" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L850" s="3"/>
+      <c r="M850" s="3"/>
+      <c r="N850" s="3"/>
+    </row>
+    <row r="851" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A851" s="3" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B851" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C851" s="3">
+        <v>301</v>
+      </c>
+      <c r="D851" s="3">
+        <v>5745562442</v>
+      </c>
+      <c r="E851" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F851" s="3" t="s">
+        <v>2401</v>
+      </c>
+      <c r="G851" s="3" t="s">
+        <v>2402</v>
+      </c>
+      <c r="H851" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I851" s="3"/>
+      <c r="J851" s="3"/>
+      <c r="K851" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L851" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M851" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="N851" s="3" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="852" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A852" s="3" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B852" s="3"/>
+      <c r="C852" s="3">
+        <v>301</v>
+      </c>
+      <c r="D852" s="3">
+        <v>5745571438</v>
+      </c>
+      <c r="E852" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F852" s="3" t="s">
+        <v>2406</v>
+      </c>
+      <c r="G852" s="3" t="s">
+        <v>2407</v>
+      </c>
+      <c r="H852" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I852" s="3"/>
+      <c r="J852" s="3"/>
+      <c r="K852" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L852" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M852" s="3" t="s">
+        <v>2408</v>
+      </c>
+      <c r="N852" s="3"/>
+    </row>
+    <row r="853" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A853" s="3" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B853" s="3"/>
+      <c r="C853" s="3">
+        <v>301</v>
+      </c>
+      <c r="D853" s="3">
+        <v>5746249689</v>
+      </c>
+      <c r="E853" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F853" s="3" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G853" s="3" t="s">
+        <v>2411</v>
+      </c>
+      <c r="H853" s="3"/>
+      <c r="I853" s="3"/>
+      <c r="J853" s="3"/>
+      <c r="K853" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L853" s="3"/>
+      <c r="M853" s="3"/>
+      <c r="N853" s="3"/>
+    </row>
+    <row r="854" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A854" s="3" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B854" s="3"/>
+      <c r="C854" s="3">
+        <v>301</v>
+      </c>
+      <c r="D854" s="3">
+        <v>5746268528</v>
+      </c>
+      <c r="E854" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F854" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G854" s="3" t="s">
+        <v>2413</v>
+      </c>
+      <c r="H854" s="3"/>
+      <c r="I854" s="3"/>
+      <c r="J854" s="3"/>
+      <c r="K854" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L854" s="3"/>
+      <c r="M854" s="3"/>
+      <c r="N854" s="3"/>
+    </row>
+    <row r="855" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A855" s="3" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B855" s="3"/>
+      <c r="C855" s="3">
+        <v>111</v>
+      </c>
+      <c r="D855" s="3">
+        <v>5746314728</v>
+      </c>
+      <c r="E855" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F855" s="3" t="s">
+        <v>2415</v>
+      </c>
+      <c r="G855" s="3" t="s">
+        <v>2416</v>
+      </c>
+      <c r="H855" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I855" s="3"/>
+      <c r="J855" s="3"/>
+      <c r="K855" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L855" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M855" s="3" t="s">
+        <v>2408</v>
+      </c>
+      <c r="N855" s="3"/>
+    </row>
+    <row r="856" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A856" s="3" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B856" s="3"/>
+      <c r="C856" s="3">
+        <v>111</v>
+      </c>
+      <c r="D856" s="3">
+        <v>5747015073</v>
+      </c>
+      <c r="E856" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F856" s="3" t="s">
+        <v>2418</v>
+      </c>
+      <c r="G856" s="3" t="s">
+        <v>2419</v>
+      </c>
+      <c r="H856" s="3"/>
+      <c r="I856" s="3"/>
+      <c r="J856" s="3"/>
+      <c r="K856" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L856" s="3"/>
+      <c r="M856" s="3"/>
+      <c r="N856" s="3"/>
+    </row>
+    <row r="857" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A857" s="3" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B857" s="3"/>
+      <c r="C857" s="3">
+        <v>112</v>
+      </c>
+      <c r="D857" s="3">
+        <v>5747346232</v>
+      </c>
+      <c r="E857" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F857" s="3" t="s">
+        <v>2421</v>
+      </c>
+      <c r="G857" s="3" t="s">
+        <v>2422</v>
+      </c>
+      <c r="H857" s="3"/>
+      <c r="I857" s="3"/>
+      <c r="J857" s="3"/>
+      <c r="K857" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L857" s="3"/>
+      <c r="M857" s="3"/>
+      <c r="N857" s="3"/>
+    </row>
+    <row r="858" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A858" s="3" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B858" s="3"/>
+      <c r="C858" s="3">
+        <v>113</v>
+      </c>
+      <c r="D858" s="3">
+        <v>5755668365</v>
+      </c>
+      <c r="E858" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F858" s="3" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G858" s="3" t="s">
+        <v>2425</v>
+      </c>
+      <c r="H858" s="3"/>
+      <c r="I858" s="3"/>
+      <c r="J858" s="3"/>
+      <c r="K858" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L858" s="3"/>
+      <c r="M858" s="3"/>
+      <c r="N858" s="3"/>
+    </row>
+    <row r="859" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A859" s="3" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B859" s="3"/>
+      <c r="C859" s="3">
+        <v>111</v>
+      </c>
+      <c r="D859" s="3">
+        <v>5750452367</v>
+      </c>
+      <c r="E859" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F859" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G859" s="3" t="s">
+        <v>2427</v>
+      </c>
+      <c r="H859" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I859" s="3"/>
+      <c r="J859" s="3"/>
+      <c r="K859" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L859" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M859" s="3" t="s">
+        <v>2428</v>
+      </c>
+      <c r="N859" s="3"/>
+    </row>
+    <row r="860" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A860" s="3" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B860" s="3"/>
+      <c r="C860" s="3">
+        <v>112</v>
+      </c>
+      <c r="D860" s="3">
+        <v>5762547207</v>
+      </c>
+      <c r="E860" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F860" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="G860" s="3" t="s">
+        <v>2430</v>
+      </c>
+      <c r="H860" s="3"/>
+      <c r="I860" s="3"/>
+      <c r="J860" s="3"/>
+      <c r="K860" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L860" s="3"/>
+      <c r="M860" s="3"/>
+      <c r="N860" s="3"/>
+    </row>
+    <row r="861" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A861" s="3" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B861" s="3"/>
+      <c r="C861" s="3">
+        <v>112</v>
+      </c>
+      <c r="D861" s="3">
+        <v>5752219381</v>
+      </c>
+      <c r="E861" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F861" s="3" t="s">
+        <v>2432</v>
+      </c>
+      <c r="G861" s="3" t="s">
+        <v>2433</v>
+      </c>
+      <c r="H861" s="3"/>
+      <c r="I861" s="3"/>
+      <c r="J861" s="3"/>
+      <c r="K861" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L861" s="3"/>
+      <c r="M861" s="3"/>
+      <c r="N861" s="3"/>
+    </row>
+    <row r="862" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A862" s="3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B862" s="3"/>
+      <c r="C862" s="3">
+        <v>112</v>
+      </c>
+      <c r="D862" s="3">
+        <v>5752237811</v>
+      </c>
+      <c r="E862" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F862" s="3" t="s">
+        <v>2435</v>
+      </c>
+      <c r="G862" s="3" t="s">
+        <v>2436</v>
+      </c>
+      <c r="H862" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I862" s="3"/>
+      <c r="J862" s="3"/>
+      <c r="K862" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L862" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M862" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="N862" s="3"/>
+    </row>
+    <row r="863" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A863" s="3" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B863" s="3"/>
+      <c r="C863" s="3">
+        <v>111</v>
+      </c>
+      <c r="D863" s="3">
+        <v>5752783172</v>
+      </c>
+      <c r="E863" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F863" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="G863" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="H863" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I863" s="3"/>
+      <c r="J863" s="3"/>
+      <c r="K863" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L863" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M863" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="N863" s="3"/>
+    </row>
+    <row r="864" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A864" s="3" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B864" s="3"/>
+      <c r="C864" s="3">
+        <v>111</v>
+      </c>
+      <c r="D864" s="3">
+        <v>5752848510</v>
+      </c>
+      <c r="E864" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F864" s="3" t="s">
+        <v>2442</v>
+      </c>
+      <c r="G864" s="3" t="s">
+        <v>2443</v>
+      </c>
+      <c r="H864" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I864" s="3"/>
+      <c r="J864" s="3"/>
+      <c r="K864" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L864" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M864" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="N864" s="3"/>
+    </row>
+    <row r="865" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A865" s="3" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B865" s="3"/>
+      <c r="C865" s="3">
+        <v>111</v>
+      </c>
+      <c r="D865" s="3">
+        <v>5752903552</v>
+      </c>
+      <c r="E865" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F865" s="3" t="s">
+        <v>2445</v>
+      </c>
+      <c r="G865" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="H865" s="3"/>
+      <c r="I865" s="3"/>
+      <c r="J865" s="3"/>
+      <c r="K865" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L865" s="3"/>
+      <c r="M865" s="3"/>
+      <c r="N865" s="3"/>
+    </row>
+    <row r="866" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A866" s="3" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B866" s="3"/>
+      <c r="C866" s="3">
+        <v>111</v>
+      </c>
+      <c r="D866" s="3">
+        <v>5753076792</v>
+      </c>
+      <c r="E866" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F866" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G866" s="3" t="s">
+        <v>2449</v>
+      </c>
+      <c r="H866" s="3"/>
+      <c r="I866" s="3"/>
+      <c r="J866" s="3"/>
+      <c r="K866" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L866" s="3"/>
+      <c r="M866" s="3"/>
+      <c r="N866" s="3"/>
+    </row>
+    <row r="867" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A867" s="3" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B867" s="3"/>
+      <c r="C867" s="3">
+        <v>111</v>
+      </c>
+      <c r="D867" s="3">
+        <v>5753507623</v>
+      </c>
+      <c r="E867" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F867" s="3" t="s">
+        <v>2451</v>
+      </c>
+      <c r="G867" s="3" t="s">
+        <v>2452</v>
+      </c>
+      <c r="H867" s="3"/>
+      <c r="I867" s="3"/>
+      <c r="J867" s="3"/>
+      <c r="K867" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L867" s="3"/>
+      <c r="M867" s="3"/>
+      <c r="N867" s="3"/>
+    </row>
+    <row r="868" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A868" s="3" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B868" s="3"/>
+      <c r="C868" s="3">
+        <v>112</v>
+      </c>
+      <c r="D868" s="3">
+        <v>5753587951</v>
+      </c>
+      <c r="E868" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F868" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="G868" s="3" t="s">
+        <v>2455</v>
+      </c>
+      <c r="H868" s="3"/>
+      <c r="I868" s="3"/>
+      <c r="J868" s="3"/>
+      <c r="K868" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L868" s="3"/>
+      <c r="M868" s="3"/>
+      <c r="N868" s="3"/>
+    </row>
+    <row r="869" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A869" s="3" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B869" s="3"/>
+      <c r="C869" s="3">
+        <v>110</v>
+      </c>
+      <c r="D869" s="3">
+        <v>5753675458</v>
+      </c>
+      <c r="E869" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F869" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="G869" s="3" t="s">
+        <v>2457</v>
+      </c>
+      <c r="H869" s="3"/>
+      <c r="I869" s="3"/>
+      <c r="J869" s="3"/>
+      <c r="K869" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L869" s="3"/>
+      <c r="M869" s="3"/>
+      <c r="N869" s="3"/>
+    </row>
+    <row r="870" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A870" s="3" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B870" s="3"/>
+      <c r="C870" s="3">
+        <v>110</v>
+      </c>
+      <c r="D870" s="3">
+        <v>5754327935</v>
+      </c>
+      <c r="E870" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F870" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="G870" s="3" t="s">
+        <v>2459</v>
+      </c>
+      <c r="H870" s="3"/>
+      <c r="I870" s="3"/>
+      <c r="J870" s="3"/>
+      <c r="K870" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L870" s="3"/>
+      <c r="M870" s="3"/>
+      <c r="N870" s="3"/>
+    </row>
+    <row r="871" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A871" s="3" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B871" s="3"/>
+      <c r="C871" s="3">
+        <v>110</v>
+      </c>
+      <c r="D871" s="3">
+        <v>5754383768</v>
+      </c>
+      <c r="E871" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F871" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G871" s="3" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H871" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I871" s="3"/>
+      <c r="J871" s="3"/>
+      <c r="K871" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L871" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M871" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="N871" s="3"/>
+    </row>
+    <row r="872" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A872" s="3" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B872" s="3"/>
+      <c r="C872" s="3">
+        <v>112</v>
+      </c>
+      <c r="D872" s="3">
+        <v>5769276112</v>
+      </c>
+      <c r="E872" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F872" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="G872" s="3" t="s">
+        <v>2463</v>
+      </c>
+      <c r="H872" s="3"/>
+      <c r="I872" s="3"/>
+      <c r="J872" s="3"/>
+      <c r="K872" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L872" s="3"/>
+      <c r="M872" s="3"/>
+      <c r="N872" s="3"/>
+    </row>
+    <row r="873" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A873" s="3" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B873" s="3"/>
+      <c r="C873" s="3">
+        <v>110</v>
+      </c>
+      <c r="D873" s="3">
+        <v>5759367745</v>
+      </c>
+      <c r="E873" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F873" s="3" t="s">
+        <v>2465</v>
+      </c>
+      <c r="G873" s="3" t="s">
+        <v>2466</v>
+      </c>
+      <c r="H873" s="3"/>
+      <c r="I873" s="3"/>
+      <c r="J873" s="3"/>
+      <c r="K873" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L873" s="3"/>
+      <c r="M873" s="3"/>
+      <c r="N873" s="3"/>
+    </row>
+    <row r="874" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A874" s="3" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B874" s="3"/>
+      <c r="C874" s="3">
+        <v>110</v>
+      </c>
+      <c r="D874" s="3">
+        <v>5769161645</v>
+      </c>
+      <c r="E874" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F874" s="3" t="s">
+        <v>2468</v>
+      </c>
+      <c r="G874" s="3" t="s">
+        <v>2469</v>
+      </c>
+      <c r="H874" s="3"/>
+      <c r="I874" s="3"/>
+      <c r="J874" s="3"/>
+      <c r="K874" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L874" s="3"/>
+      <c r="M874" s="3"/>
+      <c r="N874" s="3"/>
+    </row>
+    <row r="875" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A875" s="3" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B875" s="3"/>
+      <c r="C875" s="3">
+        <v>110</v>
+      </c>
+      <c r="D875" s="3">
+        <v>5759801149</v>
+      </c>
+      <c r="E875" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F875" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G875" s="3" t="s">
+        <v>2471</v>
+      </c>
+      <c r="H875" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I875" s="3"/>
+      <c r="J875" s="3"/>
+      <c r="K875" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L875" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M875" s="3" t="s">
+        <v>2472</v>
+      </c>
+      <c r="N875" s="3"/>
+    </row>
+    <row r="876" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A876" s="3" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B876" s="3" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C876" s="3">
+        <v>111</v>
+      </c>
+      <c r="D876" s="3">
+        <v>5760869439</v>
+      </c>
+      <c r="E876" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F876" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G876" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="H876" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I876" s="3"/>
+      <c r="J876" s="3"/>
+      <c r="K876" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L876" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M876" s="3" t="s">
+        <v>2472</v>
+      </c>
+      <c r="N876" s="3"/>
+    </row>
+    <row r="877" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A877" s="3" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B877" s="3"/>
+      <c r="C877" s="3">
+        <v>112</v>
+      </c>
+      <c r="D877" s="3">
+        <v>5763492134</v>
+      </c>
+      <c r="E877" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F877" s="3" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G877" s="3" t="s">
+        <v>2478</v>
+      </c>
+      <c r="H877" s="3"/>
+      <c r="I877" s="3"/>
+      <c r="J877" s="3"/>
+      <c r="K877" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L877" s="3"/>
+      <c r="M877" s="3"/>
+      <c r="N877" s="3"/>
+    </row>
+    <row r="878" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A878" s="3" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B878" s="3"/>
+      <c r="C878" s="3">
+        <v>111</v>
+      </c>
+      <c r="D878" s="3">
+        <v>5763565748</v>
+      </c>
+      <c r="E878" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F878" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G878" s="3" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H878" s="3"/>
+      <c r="I878" s="3"/>
+      <c r="J878" s="3"/>
+      <c r="K878" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L878" s="3"/>
+      <c r="M878" s="3"/>
+      <c r="N878" s="3"/>
+    </row>
+    <row r="879" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A879" s="3" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B879" s="3"/>
+      <c r="C879" s="3">
+        <v>111</v>
+      </c>
+      <c r="D879" s="3">
+        <v>5763603742</v>
+      </c>
+      <c r="E879" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F879" s="3" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G879" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="H879" s="3"/>
+      <c r="I879" s="3"/>
+      <c r="J879" s="3"/>
+      <c r="K879" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L879" s="3"/>
+      <c r="M879" s="3"/>
+      <c r="N879" s="3"/>
+    </row>
+    <row r="880" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A880" s="3" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B880" s="3"/>
+      <c r="C880" s="3">
+        <v>112</v>
+      </c>
+      <c r="D880" s="3">
+        <v>5764256562</v>
+      </c>
+      <c r="E880" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F880" s="3" t="s">
+        <v>2485</v>
+      </c>
+      <c r="G880" s="3" t="s">
+        <v>2486</v>
+      </c>
+      <c r="H880" s="3"/>
+      <c r="I880" s="3"/>
+      <c r="J880" s="3"/>
+      <c r="K880" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L880" s="3"/>
+      <c r="M880" s="3"/>
+      <c r="N880" s="3"/>
+    </row>
+    <row r="881" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A881" s="3" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B881" s="3"/>
+      <c r="C881" s="3">
+        <v>112</v>
+      </c>
+      <c r="D881" s="3">
+        <v>5764273459</v>
+      </c>
+      <c r="E881" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F881" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G881" s="3" t="s">
+        <v>2488</v>
+      </c>
+      <c r="H881" s="3"/>
+      <c r="I881" s="3"/>
+      <c r="J881" s="3"/>
+      <c r="K881" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L881" s="3"/>
+      <c r="M881" s="3"/>
+      <c r="N881" s="3"/>
+    </row>
+    <row r="882" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A882" s="3" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B882" s="3"/>
+      <c r="C882" s="3">
+        <v>112</v>
+      </c>
+      <c r="D882" s="3">
+        <v>5766211902</v>
+      </c>
+      <c r="E882" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F882" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G882" s="3" t="s">
+        <v>2490</v>
+      </c>
+      <c r="H882" s="3"/>
+      <c r="I882" s="3"/>
+      <c r="J882" s="3"/>
+      <c r="K882" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L882" s="3"/>
+      <c r="M882" s="3"/>
+      <c r="N882" s="3"/>
+    </row>
+    <row r="883" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A883" s="3" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B883" s="3"/>
+      <c r="C883" s="3">
+        <v>111</v>
+      </c>
+      <c r="D883" s="3">
+        <v>5766229405</v>
+      </c>
+      <c r="E883" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F883" s="3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="G883" s="3" t="s">
+        <v>2492</v>
+      </c>
+      <c r="H883" s="3"/>
+      <c r="I883" s="3"/>
+      <c r="J883" s="3"/>
+      <c r="K883" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L883" s="3"/>
+      <c r="M883" s="3"/>
+      <c r="N883" s="3"/>
+    </row>
+    <row r="884" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A884" s="3" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B884" s="3"/>
+      <c r="C884" s="3">
+        <v>111</v>
+      </c>
+      <c r="D884" s="3">
+        <v>5766740139</v>
+      </c>
+      <c r="E884" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F884" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G884" s="3" t="s">
+        <v>2494</v>
+      </c>
+      <c r="H884" s="3"/>
+      <c r="I884" s="3"/>
+      <c r="J884" s="3"/>
+      <c r="K884" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L884" s="3"/>
+      <c r="M884" s="3"/>
+      <c r="N884" s="3"/>
+    </row>
+    <row r="885" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A885" s="3" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B885" s="3"/>
+      <c r="C885" s="3">
+        <v>111</v>
+      </c>
+      <c r="D885" s="3">
+        <v>5767477214</v>
+      </c>
+      <c r="E885" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F885" s="3" t="s">
+        <v>2496</v>
+      </c>
+      <c r="G885" s="3" t="s">
+        <v>2497</v>
+      </c>
+      <c r="H885" s="3"/>
+      <c r="I885" s="3"/>
+      <c r="J885" s="3"/>
+      <c r="K885" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L885" s="3"/>
+      <c r="M885" s="3"/>
+      <c r="N885" s="3"/>
+    </row>
+    <row r="886" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A886" s="3" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B886" s="3"/>
+      <c r="C886" s="3">
+        <v>111</v>
+      </c>
+      <c r="D886" s="3">
+        <v>5767660049</v>
+      </c>
+      <c r="E886" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F886" s="3" t="s">
+        <v>2499</v>
+      </c>
+      <c r="G886" s="3" t="s">
+        <v>2500</v>
+      </c>
+      <c r="H886" s="3"/>
+      <c r="I886" s="3"/>
+      <c r="J886" s="3"/>
+      <c r="K886" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L886" s="3"/>
+      <c r="M886" s="3"/>
+      <c r="N886" s="3"/>
+    </row>
+    <row r="887" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A887" s="3" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B887" s="3"/>
+      <c r="C887" s="3">
+        <v>112</v>
+      </c>
+      <c r="D887" s="3">
+        <v>5768550840</v>
+      </c>
+      <c r="E887" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F887" s="3" t="s">
+        <v>2502</v>
+      </c>
+      <c r="G887" s="3" t="s">
+        <v>2503</v>
+      </c>
+      <c r="H887" s="3"/>
+      <c r="I887" s="3"/>
+      <c r="J887" s="3"/>
+      <c r="K887" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L887" s="3"/>
+      <c r="M887" s="3"/>
+      <c r="N887" s="3"/>
+    </row>
+    <row r="888" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A888" s="3" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B888" s="3"/>
+      <c r="C888" s="3">
+        <v>301</v>
+      </c>
+      <c r="D888" s="3">
+        <v>5772303179</v>
+      </c>
+      <c r="E888" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F888" s="3" t="s">
+        <v>2505</v>
+      </c>
+      <c r="G888" s="3" t="s">
+        <v>2506</v>
+      </c>
+      <c r="H888" s="3"/>
+      <c r="I888" s="3"/>
+      <c r="J888" s="3"/>
+      <c r="K888" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L888" s="3"/>
+      <c r="M888" s="3"/>
+      <c r="N888" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CFCEE20-B3E6-4805-8A93-4D38117A3F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B339CDB-8C11-4F31-AAF9-13CD85D3BCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5374" uniqueCount="2507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5756" uniqueCount="2678">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -7459,6 +7459,9 @@
     <t>29.641094, -97.711280</t>
   </si>
   <si>
+    <t>05/18/26 09:49 EDT</t>
+  </si>
+  <si>
     <t>05/15/26 07:52 EDT</t>
   </si>
   <si>
@@ -7507,6 +7510,12 @@
     <t>29.468270, -98.282640</t>
   </si>
   <si>
+    <t>05/15/26 15:54 EDT</t>
+  </si>
+  <si>
+    <t>29.506400, -98.132100</t>
+  </si>
+  <si>
     <t>05/15/26 16:52 EDT</t>
   </si>
   <si>
@@ -7541,6 +7550,510 @@
   </si>
   <si>
     <t>29.471079, -98.217660</t>
+  </si>
+  <si>
+    <t>05/18/26 08:36 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.480642, -98.245470</t>
+  </si>
+  <si>
+    <t>05/18/26 09:16 EDT</t>
+  </si>
+  <si>
+    <t>29.424778, -98.420720</t>
+  </si>
+  <si>
+    <t>05/18/26 12:03 EDT</t>
+  </si>
+  <si>
+    <t>29.440718, -98.375110</t>
+  </si>
+  <si>
+    <t>05/18/26 12:14 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi N of Terrell Hills TX</t>
+  </si>
+  <si>
+    <t>29.516148, -98.430405</t>
+  </si>
+  <si>
+    <t>05/18/26 14:25 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi S of Schertz TX</t>
+  </si>
+  <si>
+    <t>29.515050, -98.241554</t>
+  </si>
+  <si>
+    <t>05/19/26 08:50 EDT</t>
+  </si>
+  <si>
+    <t>05/18/26 14:36 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi NW of Schertz TX</t>
+  </si>
+  <si>
+    <t>29.573992, -98.259690</t>
+  </si>
+  <si>
+    <t>05/18/26 16:28 EDT</t>
+  </si>
+  <si>
+    <t>29.541061, -98.072510</t>
+  </si>
+  <si>
+    <t>05/18/26 16:52 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.568438, -98.156370</t>
+  </si>
+  <si>
+    <t>05/18/26 17:34 EDT</t>
+  </si>
+  <si>
+    <t>29.519749, -98.138010</t>
+  </si>
+  <si>
+    <t>05/18/26 18:20 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi NE of Kyle TX</t>
+  </si>
+  <si>
+    <t>30.026453, -97.851364</t>
+  </si>
+  <si>
+    <t>05/18/26 19:23 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi SW of Hondo TX</t>
+  </si>
+  <si>
+    <t>29.345781, -99.174380</t>
+  </si>
+  <si>
+    <t>05/18/26 19:40 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi E of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.591389, -97.952170</t>
+  </si>
+  <si>
+    <t>05/19/26 07:31 EDT</t>
+  </si>
+  <si>
+    <t>29.525276, -98.122730</t>
+  </si>
+  <si>
+    <t>05/20/26 08:59 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 10:20 EDT</t>
+  </si>
+  <si>
+    <t>21.4mi E of Del Rio TX</t>
+  </si>
+  <si>
+    <t>29.333630, -100.527650</t>
+  </si>
+  <si>
+    <t>05/19/26 13:50 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 10:48 EDT</t>
+  </si>
+  <si>
+    <t>29.441113, -98.373800</t>
+  </si>
+  <si>
+    <t>05/19/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>29.412117, -98.515045</t>
+  </si>
+  <si>
+    <t>05/19/26 11:13 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi E of Del Rio TX</t>
+  </si>
+  <si>
+    <t>29.369259, -100.850730</t>
+  </si>
+  <si>
+    <t>05/19/26 11:41 EDT</t>
+  </si>
+  <si>
+    <t>29.507076, -98.131170</t>
+  </si>
+  <si>
+    <t>05/19/26 12:14 EDT</t>
+  </si>
+  <si>
+    <t>6.1mi W of Uvalde TX</t>
+  </si>
+  <si>
+    <t>29.202387, -99.878975</t>
+  </si>
+  <si>
+    <t>05/19/26 12:26 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi NE of Uvalde TX</t>
+  </si>
+  <si>
+    <t>29.223760, -99.762020</t>
+  </si>
+  <si>
+    <t>05/19/26 12:49 EDT</t>
+  </si>
+  <si>
+    <t>16.6mi W of Hondo TX</t>
+  </si>
+  <si>
+    <t>29.313305, -99.433840</t>
+  </si>
+  <si>
+    <t>05/19/26 13:02 EDT</t>
+  </si>
+  <si>
+    <t>8.1mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.348959, -98.425896</t>
+  </si>
+  <si>
+    <t>3.7mi S of Converse TX</t>
+  </si>
+  <si>
+    <t>29.456762, -98.322910</t>
+  </si>
+  <si>
+    <t>05/19/26 14:32 EDT</t>
+  </si>
+  <si>
+    <t>0.8mi S of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.688578, -98.118060</t>
+  </si>
+  <si>
+    <t>05/19/26 16:22 EDT</t>
+  </si>
+  <si>
+    <t>6.4mi NE of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.648060, -97.886185</t>
+  </si>
+  <si>
+    <t>05/20/26 09:00 EDT</t>
+  </si>
+  <si>
+    <t>05/20/26 12:20 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 16:42 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi S of Helotes TX</t>
+  </si>
+  <si>
+    <t>29.533695, -98.682960</t>
+  </si>
+  <si>
+    <t>05/19/26 16:56 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi NW of San Antonio TX</t>
+  </si>
+  <si>
+    <t>29.495039, -98.547700</t>
+  </si>
+  <si>
+    <t>05/19/26 16:59 EDT</t>
+  </si>
+  <si>
+    <t>29.421144, -98.259680</t>
+  </si>
+  <si>
+    <t>05/19/26 17:13 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi SW of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.430063, -98.411290</t>
+  </si>
+  <si>
+    <t>05/19/26 17:53 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.473913, -98.265190</t>
+  </si>
+  <si>
+    <t>05/19/26 17:58 EDT</t>
+  </si>
+  <si>
+    <t>29.498594, -98.192825</t>
+  </si>
+  <si>
+    <t>05/20/26 09:01 EDT</t>
+  </si>
+  <si>
+    <t>05/19/26 22:02 EDT</t>
+  </si>
+  <si>
+    <t>0.8mi NW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.594288, -97.978780</t>
+  </si>
+  <si>
+    <t>05/19/26 22:19 EDT</t>
+  </si>
+  <si>
+    <t>29.497395, -98.195244</t>
+  </si>
+  <si>
+    <t>05/20/26 09:17 EDT</t>
+  </si>
+  <si>
+    <t>29.578580, -98.262620</t>
+  </si>
+  <si>
+    <t>05/20/26 09:50 EDT</t>
+  </si>
+  <si>
+    <t>29.612865, -98.284775</t>
+  </si>
+  <si>
+    <t>05/20/26 10:20 EDT</t>
+  </si>
+  <si>
+    <t>4.4mi SE of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.330881, -98.582344</t>
+  </si>
+  <si>
+    <t>05/21/26 10:15 EDT</t>
+  </si>
+  <si>
+    <t>05/21/26 10:17 EDT</t>
+  </si>
+  <si>
+    <t>05/20/26 11:01 EDT</t>
+  </si>
+  <si>
+    <t>4.4mi S of Austin TX</t>
+  </si>
+  <si>
+    <t>30.238663, -97.738270</t>
+  </si>
+  <si>
+    <t>05/20/26 13:41 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi NW of Pearsall TX</t>
+  </si>
+  <si>
+    <t>28.913874, -99.108520</t>
+  </si>
+  <si>
+    <t>05/21/26 10:16 EDT</t>
+  </si>
+  <si>
+    <t>05/20/26 15:54 EDT</t>
+  </si>
+  <si>
+    <t>12.8mi SW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.246980, -98.757890</t>
+  </si>
+  <si>
+    <t>05/20/26 16:02 EDT</t>
+  </si>
+  <si>
+    <t>29.474058, -98.264730</t>
+  </si>
+  <si>
+    <t>05/20/26 16:05 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi E of Converse TX</t>
+  </si>
+  <si>
+    <t>29.485403, -98.231180</t>
+  </si>
+  <si>
+    <t>05/20/26 17:48 EDT</t>
+  </si>
+  <si>
+    <t>21.8mi E of Crystal City TX</t>
+  </si>
+  <si>
+    <t>28.592453, -99.484580</t>
+  </si>
+  <si>
+    <t>05/20/26 17:50 EDT</t>
+  </si>
+  <si>
+    <t>23.3mi E of Crystal City TX</t>
+  </si>
+  <si>
+    <t>28.608192, -99.452930</t>
+  </si>
+  <si>
+    <t>05/21/26 10:36 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi W of Windcrest TX</t>
+  </si>
+  <si>
+    <t>29.518850, -98.398964</t>
+  </si>
+  <si>
+    <t>05/21/26 12:13 EDT</t>
+  </si>
+  <si>
+    <t>13.8mi NE of Floresville TX</t>
+  </si>
+  <si>
+    <t>29.225712, -97.955000</t>
+  </si>
+  <si>
+    <t>05/21/26 13:21 EDT</t>
+  </si>
+  <si>
+    <t>29.580760, -97.991780</t>
+  </si>
+  <si>
+    <t>05/21/26 15:54 EDT</t>
+  </si>
+  <si>
+    <t>29.538626, -98.072190</t>
+  </si>
+  <si>
+    <t>05/22/26 08:58 EDT</t>
+  </si>
+  <si>
+    <t>05/21/26 19:01 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi SE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.676737, -98.059975</t>
+  </si>
+  <si>
+    <t>05/21/26 19:09 EDT</t>
+  </si>
+  <si>
+    <t>7.2mi E of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.701488, -97.995710</t>
+  </si>
+  <si>
+    <t>05/23/26 08:57 EDT</t>
+  </si>
+  <si>
+    <t>5.7mi E of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.612877, -97.877020</t>
+  </si>
+  <si>
+    <t>05/23/26 09:36 EDT</t>
+  </si>
+  <si>
+    <t>29.612724, -97.877045</t>
+  </si>
+  <si>
+    <t>05/23/26 12:29 EDT</t>
+  </si>
+  <si>
+    <t>29.609758, -97.878390</t>
+  </si>
+  <si>
+    <t>05/23/26 12:31 EDT</t>
+  </si>
+  <si>
+    <t>29.606514, -97.886620</t>
+  </si>
+  <si>
+    <t>29.606514, -97.886660</t>
+  </si>
+  <si>
+    <t>29.606298, -97.887560</t>
+  </si>
+  <si>
+    <t>05/23/26 12:56 EDT</t>
+  </si>
+  <si>
+    <t>29.603748, -97.898415</t>
+  </si>
+  <si>
+    <t>05/23/26 13:01 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi NE of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.599522, -97.943510</t>
+  </si>
+  <si>
+    <t>05/23/26 13:26 EDT</t>
+  </si>
+  <si>
+    <t>29.534218, -98.093410</t>
+  </si>
+  <si>
+    <t>05/23/26 13:32 EDT</t>
+  </si>
+  <si>
+    <t>29.513964, -98.152770</t>
+  </si>
+  <si>
+    <t>05/23/26 13:35 EDT</t>
+  </si>
+  <si>
+    <t>29.503471, -98.181110</t>
+  </si>
+  <si>
+    <t>05/23/26 13:38 EDT</t>
+  </si>
+  <si>
+    <t>29.498144, -98.195730</t>
+  </si>
+  <si>
+    <t>05/23/26 14:22 EDT</t>
+  </si>
+  <si>
+    <t>29.491549, -98.154470</t>
+  </si>
+  <si>
+    <t>05/23/26 14:24 EDT</t>
+  </si>
+  <si>
+    <t>29.496386, -98.145310</t>
   </si>
 </sst>
 </file>
@@ -7902,7 +8415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N888"/>
+  <dimension ref="A1:N952"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -31655,7 +32168,7 @@
         <v>112</v>
       </c>
       <c r="D742" s="3">
-        <v>5622402770</v>
+        <v>5622271458</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>53</v>
@@ -31685,7 +32198,7 @@
         <v>112</v>
       </c>
       <c r="D743" s="3">
-        <v>5622271458</v>
+        <v>5622402770</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>53</v>
@@ -36046,19 +36559,25 @@
       <c r="G877" s="3" t="s">
         <v>2478</v>
       </c>
-      <c r="H877" s="3"/>
+      <c r="H877" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I877" s="3"/>
       <c r="J877" s="3"/>
       <c r="K877" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L877" s="3"/>
-      <c r="M877" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L877" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M877" s="3" t="s">
+        <v>2479</v>
+      </c>
       <c r="N877" s="3"/>
     </row>
     <row r="878" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A878" s="3" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="B878" s="3"/>
       <c r="C878" s="3">
@@ -36074,7 +36593,7 @@
         <v>158</v>
       </c>
       <c r="G878" s="3" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="H878" s="3"/>
       <c r="I878" s="3"/>
@@ -36088,7 +36607,7 @@
     </row>
     <row r="879" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A879" s="3" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="B879" s="3"/>
       <c r="C879" s="3">
@@ -36101,24 +36620,30 @@
         <v>34</v>
       </c>
       <c r="F879" s="3" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="G879" s="3" t="s">
-        <v>2483</v>
-      </c>
-      <c r="H879" s="3"/>
+        <v>2484</v>
+      </c>
+      <c r="H879" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I879" s="3"/>
       <c r="J879" s="3"/>
       <c r="K879" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L879" s="3"/>
-      <c r="M879" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L879" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M879" s="3" t="s">
+        <v>2479</v>
+      </c>
       <c r="N879" s="3"/>
     </row>
     <row r="880" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A880" s="3" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="B880" s="3"/>
       <c r="C880" s="3">
@@ -36131,10 +36656,10 @@
         <v>71</v>
       </c>
       <c r="F880" s="3" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="G880" s="3" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="H880" s="3"/>
       <c r="I880" s="3"/>
@@ -36148,7 +36673,7 @@
     </row>
     <row r="881" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A881" s="3" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="B881" s="3"/>
       <c r="C881" s="3">
@@ -36164,7 +36689,7 @@
         <v>65</v>
       </c>
       <c r="G881" s="3" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="H881" s="3"/>
       <c r="I881" s="3"/>
@@ -36178,7 +36703,7 @@
     </row>
     <row r="882" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A882" s="3" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="B882" s="3"/>
       <c r="C882" s="3">
@@ -36194,7 +36719,7 @@
         <v>205</v>
       </c>
       <c r="G882" s="3" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="H882" s="3"/>
       <c r="I882" s="3"/>
@@ -36208,7 +36733,7 @@
     </row>
     <row r="883" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A883" s="3" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="B883" s="3"/>
       <c r="C883" s="3">
@@ -36224,21 +36749,27 @@
         <v>2018</v>
       </c>
       <c r="G883" s="3" t="s">
-        <v>2492</v>
-      </c>
-      <c r="H883" s="3"/>
+        <v>2493</v>
+      </c>
+      <c r="H883" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I883" s="3"/>
       <c r="J883" s="3"/>
       <c r="K883" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L883" s="3"/>
-      <c r="M883" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L883" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M883" s="3" t="s">
+        <v>2479</v>
+      </c>
       <c r="N883" s="3"/>
     </row>
     <row r="884" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A884" s="3" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="B884" s="3"/>
       <c r="C884" s="3">
@@ -36254,7 +36785,7 @@
         <v>1095</v>
       </c>
       <c r="G884" s="3" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="H884" s="3"/>
       <c r="I884" s="3"/>
@@ -36268,20 +36799,20 @@
     </row>
     <row r="885" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A885" s="3" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="B885" s="3"/>
       <c r="C885" s="3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D885" s="3">
-        <v>5767477214</v>
+        <v>5774053833</v>
       </c>
       <c r="E885" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F885" s="3" t="s">
-        <v>2496</v>
+        <v>230</v>
       </c>
       <c r="G885" s="3" t="s">
         <v>2497</v>
@@ -36305,10 +36836,10 @@
         <v>111</v>
       </c>
       <c r="D886" s="3">
-        <v>5767660049</v>
+        <v>5767477214</v>
       </c>
       <c r="E886" s="3" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F886" s="3" t="s">
         <v>2499</v>
@@ -36332,13 +36863,13 @@
       </c>
       <c r="B887" s="3"/>
       <c r="C887" s="3">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D887" s="3">
-        <v>5768550840</v>
+        <v>5767660049</v>
       </c>
       <c r="E887" s="3" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="F887" s="3" t="s">
         <v>2502</v>
@@ -36346,14 +36877,20 @@
       <c r="G887" s="3" t="s">
         <v>2503</v>
       </c>
-      <c r="H887" s="3"/>
+      <c r="H887" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I887" s="3"/>
       <c r="J887" s="3"/>
       <c r="K887" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L887" s="3"/>
-      <c r="M887" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L887" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M887" s="3" t="s">
+        <v>2479</v>
+      </c>
       <c r="N887" s="3"/>
     </row>
     <row r="888" spans="1:14" x14ac:dyDescent="0.3">
@@ -36362,13 +36899,13 @@
       </c>
       <c r="B888" s="3"/>
       <c r="C888" s="3">
-        <v>301</v>
+        <v>112</v>
       </c>
       <c r="D888" s="3">
-        <v>5772303179</v>
+        <v>5768550840</v>
       </c>
       <c r="E888" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F888" s="3" t="s">
         <v>2505</v>
@@ -36386,6 +36923,2026 @@
       <c r="M888" s="3"/>
       <c r="N888" s="3"/>
     </row>
+    <row r="889" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A889" s="3" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B889" s="3"/>
+      <c r="C889" s="3">
+        <v>301</v>
+      </c>
+      <c r="D889" s="3">
+        <v>5772303179</v>
+      </c>
+      <c r="E889" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F889" s="3" t="s">
+        <v>2508</v>
+      </c>
+      <c r="G889" s="3" t="s">
+        <v>2509</v>
+      </c>
+      <c r="H889" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I889" s="3"/>
+      <c r="J889" s="3"/>
+      <c r="K889" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L889" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M889" s="3" t="s">
+        <v>2479</v>
+      </c>
+      <c r="N889" s="3"/>
+    </row>
+    <row r="890" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A890" s="3" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B890" s="3"/>
+      <c r="C890" s="3">
+        <v>112</v>
+      </c>
+      <c r="D890" s="3">
+        <v>5779034957</v>
+      </c>
+      <c r="E890" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F890" s="3" t="s">
+        <v>2511</v>
+      </c>
+      <c r="G890" s="3" t="s">
+        <v>2512</v>
+      </c>
+      <c r="H890" s="3"/>
+      <c r="I890" s="3"/>
+      <c r="J890" s="3"/>
+      <c r="K890" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L890" s="3"/>
+      <c r="M890" s="3"/>
+      <c r="N890" s="3"/>
+    </row>
+    <row r="891" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A891" s="3" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B891" s="3"/>
+      <c r="C891" s="3">
+        <v>110</v>
+      </c>
+      <c r="D891" s="3">
+        <v>5779236456</v>
+      </c>
+      <c r="E891" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F891" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G891" s="3" t="s">
+        <v>2514</v>
+      </c>
+      <c r="H891" s="3"/>
+      <c r="I891" s="3"/>
+      <c r="J891" s="3"/>
+      <c r="K891" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L891" s="3"/>
+      <c r="M891" s="3"/>
+      <c r="N891" s="3"/>
+    </row>
+    <row r="892" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A892" s="3" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B892" s="3"/>
+      <c r="C892" s="3">
+        <v>113</v>
+      </c>
+      <c r="D892" s="3">
+        <v>5780318896</v>
+      </c>
+      <c r="E892" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F892" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G892" s="3" t="s">
+        <v>2516</v>
+      </c>
+      <c r="H892" s="3"/>
+      <c r="I892" s="3"/>
+      <c r="J892" s="3"/>
+      <c r="K892" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L892" s="3"/>
+      <c r="M892" s="3"/>
+      <c r="N892" s="3"/>
+    </row>
+    <row r="893" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A893" s="3" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B893" s="3"/>
+      <c r="C893" s="3">
+        <v>113</v>
+      </c>
+      <c r="D893" s="3">
+        <v>5780409131</v>
+      </c>
+      <c r="E893" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F893" s="3" t="s">
+        <v>2518</v>
+      </c>
+      <c r="G893" s="3" t="s">
+        <v>2519</v>
+      </c>
+      <c r="H893" s="3"/>
+      <c r="I893" s="3"/>
+      <c r="J893" s="3"/>
+      <c r="K893" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L893" s="3"/>
+      <c r="M893" s="3"/>
+      <c r="N893" s="3"/>
+    </row>
+    <row r="894" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A894" s="3" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B894" s="3"/>
+      <c r="C894" s="3">
+        <v>112</v>
+      </c>
+      <c r="D894" s="3">
+        <v>5781537742</v>
+      </c>
+      <c r="E894" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F894" s="3" t="s">
+        <v>2521</v>
+      </c>
+      <c r="G894" s="3" t="s">
+        <v>2522</v>
+      </c>
+      <c r="H894" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I894" s="3"/>
+      <c r="J894" s="3"/>
+      <c r="K894" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L894" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M894" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="N894" s="3"/>
+    </row>
+    <row r="895" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A895" s="3" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B895" s="3"/>
+      <c r="C895" s="3">
+        <v>112</v>
+      </c>
+      <c r="D895" s="3">
+        <v>5781636912</v>
+      </c>
+      <c r="E895" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F895" s="3" t="s">
+        <v>2525</v>
+      </c>
+      <c r="G895" s="3" t="s">
+        <v>2526</v>
+      </c>
+      <c r="H895" s="3"/>
+      <c r="I895" s="3"/>
+      <c r="J895" s="3"/>
+      <c r="K895" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L895" s="3"/>
+      <c r="M895" s="3"/>
+      <c r="N895" s="3"/>
+    </row>
+    <row r="896" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A896" s="3" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B896" s="3"/>
+      <c r="C896" s="3">
+        <v>111</v>
+      </c>
+      <c r="D896" s="3">
+        <v>5782606164</v>
+      </c>
+      <c r="E896" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F896" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G896" s="3" t="s">
+        <v>2528</v>
+      </c>
+      <c r="H896" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I896" s="3"/>
+      <c r="J896" s="3"/>
+      <c r="K896" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L896" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M896" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="N896" s="3"/>
+    </row>
+    <row r="897" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A897" s="3" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B897" s="3"/>
+      <c r="C897" s="3">
+        <v>113</v>
+      </c>
+      <c r="D897" s="3">
+        <v>5782791658</v>
+      </c>
+      <c r="E897" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F897" s="3" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G897" s="3" t="s">
+        <v>2531</v>
+      </c>
+      <c r="H897" s="3"/>
+      <c r="I897" s="3"/>
+      <c r="J897" s="3"/>
+      <c r="K897" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L897" s="3"/>
+      <c r="M897" s="3"/>
+      <c r="N897" s="3"/>
+    </row>
+    <row r="898" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A898" s="3" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B898" s="3"/>
+      <c r="C898" s="3">
+        <v>111</v>
+      </c>
+      <c r="D898" s="3">
+        <v>5783119515</v>
+      </c>
+      <c r="E898" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F898" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G898" s="3" t="s">
+        <v>2533</v>
+      </c>
+      <c r="H898" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I898" s="3"/>
+      <c r="J898" s="3"/>
+      <c r="K898" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L898" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M898" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="N898" s="3"/>
+    </row>
+    <row r="899" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A899" s="3" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B899" s="3"/>
+      <c r="C899" s="3">
+        <v>112</v>
+      </c>
+      <c r="D899" s="3">
+        <v>5783446603</v>
+      </c>
+      <c r="E899" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F899" s="3" t="s">
+        <v>2535</v>
+      </c>
+      <c r="G899" s="3" t="s">
+        <v>2536</v>
+      </c>
+      <c r="H899" s="3"/>
+      <c r="I899" s="3"/>
+      <c r="J899" s="3"/>
+      <c r="K899" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L899" s="3"/>
+      <c r="M899" s="3"/>
+      <c r="N899" s="3"/>
+    </row>
+    <row r="900" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A900" s="3" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B900" s="3"/>
+      <c r="C900" s="3">
+        <v>111</v>
+      </c>
+      <c r="D900" s="3">
+        <v>5783850023</v>
+      </c>
+      <c r="E900" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F900" s="3" t="s">
+        <v>2538</v>
+      </c>
+      <c r="G900" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="H900" s="3"/>
+      <c r="I900" s="3"/>
+      <c r="J900" s="3"/>
+      <c r="K900" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L900" s="3"/>
+      <c r="M900" s="3"/>
+      <c r="N900" s="3"/>
+    </row>
+    <row r="901" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A901" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B901" s="3"/>
+      <c r="C901" s="3">
+        <v>113</v>
+      </c>
+      <c r="D901" s="3">
+        <v>5783950890</v>
+      </c>
+      <c r="E901" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F901" s="3" t="s">
+        <v>2541</v>
+      </c>
+      <c r="G901" s="3" t="s">
+        <v>2542</v>
+      </c>
+      <c r="H901" s="3"/>
+      <c r="I901" s="3"/>
+      <c r="J901" s="3"/>
+      <c r="K901" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L901" s="3"/>
+      <c r="M901" s="3"/>
+      <c r="N901" s="3"/>
+    </row>
+    <row r="902" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A902" s="3" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B902" s="3" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C902" s="3">
+        <v>111</v>
+      </c>
+      <c r="D902" s="3">
+        <v>5785592859</v>
+      </c>
+      <c r="E902" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F902" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G902" s="3" t="s">
+        <v>2544</v>
+      </c>
+      <c r="H902" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I902" s="3"/>
+      <c r="J902" s="3"/>
+      <c r="K902" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L902" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M902" s="3" t="s">
+        <v>2545</v>
+      </c>
+      <c r="N902" s="3"/>
+    </row>
+    <row r="903" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A903" s="3" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B903" s="3"/>
+      <c r="C903" s="3">
+        <v>111</v>
+      </c>
+      <c r="D903" s="3">
+        <v>5786490221</v>
+      </c>
+      <c r="E903" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F903" s="3" t="s">
+        <v>2547</v>
+      </c>
+      <c r="G903" s="3" t="s">
+        <v>2548</v>
+      </c>
+      <c r="H903" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I903" s="3"/>
+      <c r="J903" s="3"/>
+      <c r="K903" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L903" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M903" s="3" t="s">
+        <v>2549</v>
+      </c>
+      <c r="N903" s="3"/>
+    </row>
+    <row r="904" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A904" s="3" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B904" s="3"/>
+      <c r="C904" s="3">
+        <v>113</v>
+      </c>
+      <c r="D904" s="3">
+        <v>5786674019</v>
+      </c>
+      <c r="E904" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F904" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G904" s="3" t="s">
+        <v>2551</v>
+      </c>
+      <c r="H904" s="3"/>
+      <c r="I904" s="3"/>
+      <c r="J904" s="3"/>
+      <c r="K904" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L904" s="3"/>
+      <c r="M904" s="3"/>
+      <c r="N904" s="3"/>
+    </row>
+    <row r="905" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A905" s="3" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B905" s="3"/>
+      <c r="C905" s="3">
+        <v>113</v>
+      </c>
+      <c r="D905" s="3">
+        <v>5786754862</v>
+      </c>
+      <c r="E905" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F905" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="G905" s="3" t="s">
+        <v>2553</v>
+      </c>
+      <c r="H905" s="3"/>
+      <c r="I905" s="3"/>
+      <c r="J905" s="3"/>
+      <c r="K905" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L905" s="3"/>
+      <c r="M905" s="3"/>
+      <c r="N905" s="3"/>
+    </row>
+    <row r="906" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A906" s="3" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B906" s="3"/>
+      <c r="C906" s="3">
+        <v>111</v>
+      </c>
+      <c r="D906" s="3">
+        <v>5786849918</v>
+      </c>
+      <c r="E906" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F906" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G906" s="3" t="s">
+        <v>2556</v>
+      </c>
+      <c r="H906" s="3"/>
+      <c r="I906" s="3"/>
+      <c r="J906" s="3"/>
+      <c r="K906" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L906" s="3"/>
+      <c r="M906" s="3"/>
+      <c r="N906" s="3"/>
+    </row>
+    <row r="907" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A907" s="3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B907" s="3"/>
+      <c r="C907" s="3">
+        <v>110</v>
+      </c>
+      <c r="D907" s="3">
+        <v>5787065042</v>
+      </c>
+      <c r="E907" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F907" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G907" s="3" t="s">
+        <v>2558</v>
+      </c>
+      <c r="H907" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I907" s="3"/>
+      <c r="J907" s="3"/>
+      <c r="K907" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L907" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M907" s="3" t="s">
+        <v>2549</v>
+      </c>
+      <c r="N907" s="3"/>
+    </row>
+    <row r="908" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A908" s="3" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B908" s="3"/>
+      <c r="C908" s="3">
+        <v>111</v>
+      </c>
+      <c r="D908" s="3">
+        <v>5787336827</v>
+      </c>
+      <c r="E908" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F908" s="3" t="s">
+        <v>2560</v>
+      </c>
+      <c r="G908" s="3" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H908" s="3"/>
+      <c r="I908" s="3"/>
+      <c r="J908" s="3"/>
+      <c r="K908" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L908" s="3"/>
+      <c r="M908" s="3"/>
+      <c r="N908" s="3"/>
+    </row>
+    <row r="909" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A909" s="3" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B909" s="3"/>
+      <c r="C909" s="3">
+        <v>111</v>
+      </c>
+      <c r="D909" s="3">
+        <v>5787438174</v>
+      </c>
+      <c r="E909" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F909" s="3" t="s">
+        <v>2563</v>
+      </c>
+      <c r="G909" s="3" t="s">
+        <v>2564</v>
+      </c>
+      <c r="H909" s="3"/>
+      <c r="I909" s="3"/>
+      <c r="J909" s="3"/>
+      <c r="K909" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L909" s="3"/>
+      <c r="M909" s="3"/>
+      <c r="N909" s="3"/>
+    </row>
+    <row r="910" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A910" s="3" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B910" s="3"/>
+      <c r="C910" s="3">
+        <v>111</v>
+      </c>
+      <c r="D910" s="3">
+        <v>5787634805</v>
+      </c>
+      <c r="E910" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F910" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="G910" s="3" t="s">
+        <v>2567</v>
+      </c>
+      <c r="H910" s="3"/>
+      <c r="I910" s="3"/>
+      <c r="J910" s="3"/>
+      <c r="K910" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L910" s="3"/>
+      <c r="M910" s="3"/>
+      <c r="N910" s="3"/>
+    </row>
+    <row r="911" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A911" s="3" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B911" s="3"/>
+      <c r="C911" s="3">
+        <v>112</v>
+      </c>
+      <c r="D911" s="3">
+        <v>5787740498</v>
+      </c>
+      <c r="E911" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F911" s="3" t="s">
+        <v>2569</v>
+      </c>
+      <c r="G911" s="3" t="s">
+        <v>2570</v>
+      </c>
+      <c r="H911" s="3"/>
+      <c r="I911" s="3"/>
+      <c r="J911" s="3"/>
+      <c r="K911" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L911" s="3"/>
+      <c r="M911" s="3"/>
+      <c r="N911" s="3"/>
+    </row>
+    <row r="912" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A912" s="3" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B912" s="3"/>
+      <c r="C912" s="3">
+        <v>112</v>
+      </c>
+      <c r="D912" s="3">
+        <v>5788169841</v>
+      </c>
+      <c r="E912" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F912" s="3" t="s">
+        <v>2571</v>
+      </c>
+      <c r="G912" s="3" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H912" s="3"/>
+      <c r="I912" s="3"/>
+      <c r="J912" s="3"/>
+      <c r="K912" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L912" s="3"/>
+      <c r="M912" s="3"/>
+      <c r="N912" s="3"/>
+    </row>
+    <row r="913" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A913" s="3" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B913" s="3"/>
+      <c r="C913" s="3">
+        <v>112</v>
+      </c>
+      <c r="D913" s="3">
+        <v>5788554457</v>
+      </c>
+      <c r="E913" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F913" s="3" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G913" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="H913" s="3"/>
+      <c r="I913" s="3"/>
+      <c r="J913" s="3"/>
+      <c r="K913" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L913" s="3"/>
+      <c r="M913" s="3"/>
+      <c r="N913" s="3"/>
+    </row>
+    <row r="914" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A914" s="3" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B914" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C914" s="3">
+        <v>110</v>
+      </c>
+      <c r="D914" s="3">
+        <v>5789530991</v>
+      </c>
+      <c r="E914" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F914" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="G914" s="3" t="s">
+        <v>2578</v>
+      </c>
+      <c r="H914" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I914" s="3"/>
+      <c r="J914" s="3"/>
+      <c r="K914" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L914" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M914" s="3" t="s">
+        <v>2579</v>
+      </c>
+      <c r="N914" s="3" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="915" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A915" s="3" t="s">
+        <v>2581</v>
+      </c>
+      <c r="B915" s="3"/>
+      <c r="C915" s="3">
+        <v>111</v>
+      </c>
+      <c r="D915" s="3">
+        <v>5789700530</v>
+      </c>
+      <c r="E915" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F915" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="G915" s="3" t="s">
+        <v>2583</v>
+      </c>
+      <c r="H915" s="3"/>
+      <c r="I915" s="3"/>
+      <c r="J915" s="3"/>
+      <c r="K915" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L915" s="3"/>
+      <c r="M915" s="3"/>
+      <c r="N915" s="3"/>
+    </row>
+    <row r="916" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A916" s="3" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B916" s="3"/>
+      <c r="C916" s="3">
+        <v>111</v>
+      </c>
+      <c r="D916" s="3">
+        <v>5789817712</v>
+      </c>
+      <c r="E916" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F916" s="3" t="s">
+        <v>2585</v>
+      </c>
+      <c r="G916" s="3" t="s">
+        <v>2586</v>
+      </c>
+      <c r="H916" s="3"/>
+      <c r="I916" s="3"/>
+      <c r="J916" s="3"/>
+      <c r="K916" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L916" s="3"/>
+      <c r="M916" s="3"/>
+      <c r="N916" s="3"/>
+    </row>
+    <row r="917" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A917" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B917" s="3"/>
+      <c r="C917" s="3">
+        <v>113</v>
+      </c>
+      <c r="D917" s="3">
+        <v>5789842632</v>
+      </c>
+      <c r="E917" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F917" s="3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="G917" s="3" t="s">
+        <v>2588</v>
+      </c>
+      <c r="H917" s="3"/>
+      <c r="I917" s="3"/>
+      <c r="J917" s="3"/>
+      <c r="K917" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L917" s="3"/>
+      <c r="M917" s="3"/>
+      <c r="N917" s="3"/>
+    </row>
+    <row r="918" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A918" s="3" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B918" s="3"/>
+      <c r="C918" s="3">
+        <v>111</v>
+      </c>
+      <c r="D918" s="3">
+        <v>5789949991</v>
+      </c>
+      <c r="E918" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F918" s="3" t="s">
+        <v>2590</v>
+      </c>
+      <c r="G918" s="3" t="s">
+        <v>2591</v>
+      </c>
+      <c r="H918" s="3"/>
+      <c r="I918" s="3"/>
+      <c r="J918" s="3"/>
+      <c r="K918" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L918" s="3"/>
+      <c r="M918" s="3"/>
+      <c r="N918" s="3"/>
+    </row>
+    <row r="919" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A919" s="3" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B919" s="3"/>
+      <c r="C919" s="3">
+        <v>111</v>
+      </c>
+      <c r="D919" s="3">
+        <v>5790255050</v>
+      </c>
+      <c r="E919" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F919" s="3" t="s">
+        <v>2593</v>
+      </c>
+      <c r="G919" s="3" t="s">
+        <v>2594</v>
+      </c>
+      <c r="H919" s="3"/>
+      <c r="I919" s="3"/>
+      <c r="J919" s="3"/>
+      <c r="K919" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L919" s="3"/>
+      <c r="M919" s="3"/>
+      <c r="N919" s="3"/>
+    </row>
+    <row r="920" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A920" s="3" t="s">
+        <v>2595</v>
+      </c>
+      <c r="B920" s="3" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C920" s="3">
+        <v>111</v>
+      </c>
+      <c r="D920" s="3">
+        <v>5790291671</v>
+      </c>
+      <c r="E920" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F920" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G920" s="3" t="s">
+        <v>2596</v>
+      </c>
+      <c r="H920" s="3"/>
+      <c r="I920" s="3"/>
+      <c r="J920" s="3"/>
+      <c r="K920" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L920" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M920" s="3" t="s">
+        <v>2597</v>
+      </c>
+      <c r="N920" s="3"/>
+    </row>
+    <row r="921" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A921" s="3" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B921" s="3"/>
+      <c r="C921" s="3">
+        <v>110</v>
+      </c>
+      <c r="D921" s="3">
+        <v>5791486517</v>
+      </c>
+      <c r="E921" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F921" s="3" t="s">
+        <v>2599</v>
+      </c>
+      <c r="G921" s="3" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H921" s="3"/>
+      <c r="I921" s="3"/>
+      <c r="J921" s="3"/>
+      <c r="K921" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L921" s="3"/>
+      <c r="M921" s="3"/>
+      <c r="N921" s="3"/>
+    </row>
+    <row r="922" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A922" s="3" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B922" s="3"/>
+      <c r="C922" s="3">
+        <v>110</v>
+      </c>
+      <c r="D922" s="3">
+        <v>5791521861</v>
+      </c>
+      <c r="E922" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F922" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G922" s="3" t="s">
+        <v>2602</v>
+      </c>
+      <c r="H922" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I922" s="3"/>
+      <c r="J922" s="3"/>
+      <c r="K922" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L922" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M922" s="3" t="s">
+        <v>2597</v>
+      </c>
+      <c r="N922" s="3"/>
+    </row>
+    <row r="923" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A923" s="3" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B923" s="3"/>
+      <c r="C923" s="3">
+        <v>111</v>
+      </c>
+      <c r="D923" s="3">
+        <v>5793202378</v>
+      </c>
+      <c r="E923" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F923" s="3" t="s">
+        <v>2243</v>
+      </c>
+      <c r="G923" s="3" t="s">
+        <v>2604</v>
+      </c>
+      <c r="H923" s="3"/>
+      <c r="I923" s="3"/>
+      <c r="J923" s="3"/>
+      <c r="K923" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L923" s="3"/>
+      <c r="M923" s="3"/>
+      <c r="N923" s="3"/>
+    </row>
+    <row r="924" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A924" s="3" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B924" s="3"/>
+      <c r="C924" s="3">
+        <v>111</v>
+      </c>
+      <c r="D924" s="3">
+        <v>5793380879</v>
+      </c>
+      <c r="E924" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F924" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="G924" s="3" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H924" s="3"/>
+      <c r="I924" s="3"/>
+      <c r="J924" s="3"/>
+      <c r="K924" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L924" s="3"/>
+      <c r="M924" s="3"/>
+      <c r="N924" s="3"/>
+    </row>
+    <row r="925" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A925" s="3" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B925" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C925" s="3">
+        <v>110</v>
+      </c>
+      <c r="D925" s="3">
+        <v>5793554614</v>
+      </c>
+      <c r="E925" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F925" s="3" t="s">
+        <v>2608</v>
+      </c>
+      <c r="G925" s="3" t="s">
+        <v>2609</v>
+      </c>
+      <c r="H925" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I925" s="3"/>
+      <c r="J925" s="3"/>
+      <c r="K925" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L925" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M925" s="3" t="s">
+        <v>2610</v>
+      </c>
+      <c r="N925" s="3" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="926" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A926" s="3" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B926" s="3"/>
+      <c r="C926" s="3">
+        <v>111</v>
+      </c>
+      <c r="D926" s="3">
+        <v>5793831196</v>
+      </c>
+      <c r="E926" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F926" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="G926" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="H926" s="3"/>
+      <c r="I926" s="3"/>
+      <c r="J926" s="3"/>
+      <c r="K926" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L926" s="3"/>
+      <c r="M926" s="3"/>
+      <c r="N926" s="3"/>
+    </row>
+    <row r="927" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A927" s="3" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B927" s="3"/>
+      <c r="C927" s="3">
+        <v>110</v>
+      </c>
+      <c r="D927" s="3">
+        <v>5795175909</v>
+      </c>
+      <c r="E927" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F927" s="3" t="s">
+        <v>2616</v>
+      </c>
+      <c r="G927" s="3" t="s">
+        <v>2617</v>
+      </c>
+      <c r="H927" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I927" s="3"/>
+      <c r="J927" s="3"/>
+      <c r="K927" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L927" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M927" s="3" t="s">
+        <v>2618</v>
+      </c>
+      <c r="N927" s="3"/>
+    </row>
+    <row r="928" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A928" s="3" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B928" s="3"/>
+      <c r="C928" s="3">
+        <v>112</v>
+      </c>
+      <c r="D928" s="3">
+        <v>5796402216</v>
+      </c>
+      <c r="E928" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F928" s="3" t="s">
+        <v>2620</v>
+      </c>
+      <c r="G928" s="3" t="s">
+        <v>2621</v>
+      </c>
+      <c r="H928" s="3"/>
+      <c r="I928" s="3"/>
+      <c r="J928" s="3"/>
+      <c r="K928" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L928" s="3"/>
+      <c r="M928" s="3"/>
+      <c r="N928" s="3"/>
+    </row>
+    <row r="929" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A929" s="3" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B929" s="3"/>
+      <c r="C929" s="3">
+        <v>110</v>
+      </c>
+      <c r="D929" s="3">
+        <v>5796476541</v>
+      </c>
+      <c r="E929" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F929" s="3" t="s">
+        <v>2593</v>
+      </c>
+      <c r="G929" s="3" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H929" s="3"/>
+      <c r="I929" s="3"/>
+      <c r="J929" s="3"/>
+      <c r="K929" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L929" s="3"/>
+      <c r="M929" s="3"/>
+      <c r="N929" s="3"/>
+    </row>
+    <row r="930" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A930" s="3" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B930" s="3"/>
+      <c r="C930" s="3">
+        <v>110</v>
+      </c>
+      <c r="D930" s="3">
+        <v>5796501083</v>
+      </c>
+      <c r="E930" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F930" s="3" t="s">
+        <v>2625</v>
+      </c>
+      <c r="G930" s="3" t="s">
+        <v>2626</v>
+      </c>
+      <c r="H930" s="3"/>
+      <c r="I930" s="3"/>
+      <c r="J930" s="3"/>
+      <c r="K930" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L930" s="3"/>
+      <c r="M930" s="3"/>
+      <c r="N930" s="3"/>
+    </row>
+    <row r="931" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A931" s="3" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B931" s="3"/>
+      <c r="C931" s="3">
+        <v>112</v>
+      </c>
+      <c r="D931" s="3">
+        <v>5797322190</v>
+      </c>
+      <c r="E931" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F931" s="3" t="s">
+        <v>2628</v>
+      </c>
+      <c r="G931" s="3" t="s">
+        <v>2629</v>
+      </c>
+      <c r="H931" s="3"/>
+      <c r="I931" s="3"/>
+      <c r="J931" s="3"/>
+      <c r="K931" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L931" s="3"/>
+      <c r="M931" s="3"/>
+      <c r="N931" s="3"/>
+    </row>
+    <row r="932" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A932" s="3" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B932" s="3"/>
+      <c r="C932" s="3">
+        <v>112</v>
+      </c>
+      <c r="D932" s="3">
+        <v>5797336730</v>
+      </c>
+      <c r="E932" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F932" s="3" t="s">
+        <v>2631</v>
+      </c>
+      <c r="G932" s="3" t="s">
+        <v>2632</v>
+      </c>
+      <c r="H932" s="3"/>
+      <c r="I932" s="3"/>
+      <c r="J932" s="3"/>
+      <c r="K932" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L932" s="3"/>
+      <c r="M932" s="3"/>
+      <c r="N932" s="3"/>
+    </row>
+    <row r="933" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A933" s="3" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B933" s="3"/>
+      <c r="C933" s="3">
+        <v>112</v>
+      </c>
+      <c r="D933" s="3">
+        <v>5800730514</v>
+      </c>
+      <c r="E933" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F933" s="3" t="s">
+        <v>2634</v>
+      </c>
+      <c r="G933" s="3" t="s">
+        <v>2635</v>
+      </c>
+      <c r="H933" s="3"/>
+      <c r="I933" s="3"/>
+      <c r="J933" s="3"/>
+      <c r="K933" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L933" s="3"/>
+      <c r="M933" s="3"/>
+      <c r="N933" s="3"/>
+    </row>
+    <row r="934" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A934" s="3" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B934" s="3"/>
+      <c r="C934" s="3">
+        <v>111</v>
+      </c>
+      <c r="D934" s="3">
+        <v>5801463373</v>
+      </c>
+      <c r="E934" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F934" s="3" t="s">
+        <v>2637</v>
+      </c>
+      <c r="G934" s="3" t="s">
+        <v>2638</v>
+      </c>
+      <c r="H934" s="3"/>
+      <c r="I934" s="3"/>
+      <c r="J934" s="3"/>
+      <c r="K934" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L934" s="3"/>
+      <c r="M934" s="3"/>
+      <c r="N934" s="3"/>
+    </row>
+    <row r="935" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A935" s="3" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B935" s="3"/>
+      <c r="C935" s="3">
+        <v>111</v>
+      </c>
+      <c r="D935" s="3">
+        <v>5802055196</v>
+      </c>
+      <c r="E935" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F935" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G935" s="3" t="s">
+        <v>2640</v>
+      </c>
+      <c r="H935" s="3"/>
+      <c r="I935" s="3"/>
+      <c r="J935" s="3"/>
+      <c r="K935" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L935" s="3"/>
+      <c r="M935" s="3"/>
+      <c r="N935" s="3"/>
+    </row>
+    <row r="936" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A936" s="3" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B936" s="3"/>
+      <c r="C936" s="3">
+        <v>301</v>
+      </c>
+      <c r="D936" s="3">
+        <v>5803419842</v>
+      </c>
+      <c r="E936" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F936" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="G936" s="3" t="s">
+        <v>2642</v>
+      </c>
+      <c r="H936" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I936" s="3"/>
+      <c r="J936" s="3"/>
+      <c r="K936" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L936" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M936" s="3" t="s">
+        <v>2643</v>
+      </c>
+      <c r="N936" s="3"/>
+    </row>
+    <row r="937" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A937" s="3" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B937" s="3"/>
+      <c r="C937" s="3">
+        <v>111</v>
+      </c>
+      <c r="D937" s="3">
+        <v>5804826271</v>
+      </c>
+      <c r="E937" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F937" s="3" t="s">
+        <v>2645</v>
+      </c>
+      <c r="G937" s="3" t="s">
+        <v>2646</v>
+      </c>
+      <c r="H937" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I937" s="3"/>
+      <c r="J937" s="3"/>
+      <c r="K937" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L937" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M937" s="3" t="s">
+        <v>2643</v>
+      </c>
+      <c r="N937" s="3"/>
+    </row>
+    <row r="938" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A938" s="3" t="s">
+        <v>2647</v>
+      </c>
+      <c r="B938" s="3"/>
+      <c r="C938" s="3">
+        <v>111</v>
+      </c>
+      <c r="D938" s="3">
+        <v>5804874879</v>
+      </c>
+      <c r="E938" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F938" s="3" t="s">
+        <v>2648</v>
+      </c>
+      <c r="G938" s="3" t="s">
+        <v>2649</v>
+      </c>
+      <c r="H938" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I938" s="3"/>
+      <c r="J938" s="3"/>
+      <c r="K938" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L938" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M938" s="3" t="s">
+        <v>2643</v>
+      </c>
+      <c r="N938" s="3"/>
+    </row>
+    <row r="939" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A939" s="3" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B939" s="3"/>
+      <c r="C939" s="3">
+        <v>110</v>
+      </c>
+      <c r="D939" s="3">
+        <v>5813184365</v>
+      </c>
+      <c r="E939" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F939" s="3" t="s">
+        <v>2651</v>
+      </c>
+      <c r="G939" s="3" t="s">
+        <v>2652</v>
+      </c>
+      <c r="H939" s="3"/>
+      <c r="I939" s="3"/>
+      <c r="J939" s="3"/>
+      <c r="K939" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L939" s="3"/>
+      <c r="M939" s="3"/>
+      <c r="N939" s="3"/>
+    </row>
+    <row r="940" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A940" s="3" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B940" s="3"/>
+      <c r="C940" s="3">
+        <v>112</v>
+      </c>
+      <c r="D940" s="3">
+        <v>5813283063</v>
+      </c>
+      <c r="E940" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F940" s="3" t="s">
+        <v>2651</v>
+      </c>
+      <c r="G940" s="3" t="s">
+        <v>2654</v>
+      </c>
+      <c r="H940" s="3"/>
+      <c r="I940" s="3"/>
+      <c r="J940" s="3"/>
+      <c r="K940" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L940" s="3"/>
+      <c r="M940" s="3"/>
+      <c r="N940" s="3"/>
+    </row>
+    <row r="941" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A941" s="3" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B941" s="3"/>
+      <c r="C941" s="3">
+        <v>110</v>
+      </c>
+      <c r="D941" s="3">
+        <v>5813977351</v>
+      </c>
+      <c r="E941" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F941" s="3" t="s">
+        <v>2401</v>
+      </c>
+      <c r="G941" s="3" t="s">
+        <v>2656</v>
+      </c>
+      <c r="H941" s="3"/>
+      <c r="I941" s="3"/>
+      <c r="J941" s="3"/>
+      <c r="K941" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L941" s="3"/>
+      <c r="M941" s="3"/>
+      <c r="N941" s="3"/>
+    </row>
+    <row r="942" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A942" s="3" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B942" s="3"/>
+      <c r="C942" s="3">
+        <v>112</v>
+      </c>
+      <c r="D942" s="3">
+        <v>5813988083</v>
+      </c>
+      <c r="E942" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F942" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G942" s="3" t="s">
+        <v>2658</v>
+      </c>
+      <c r="H942" s="3"/>
+      <c r="I942" s="3"/>
+      <c r="J942" s="3"/>
+      <c r="K942" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L942" s="3"/>
+      <c r="M942" s="3"/>
+      <c r="N942" s="3"/>
+    </row>
+    <row r="943" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A943" s="3" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B943" s="3"/>
+      <c r="C943" s="3">
+        <v>110</v>
+      </c>
+      <c r="D943" s="3">
+        <v>5813989068</v>
+      </c>
+      <c r="E943" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F943" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G943" s="3" t="s">
+        <v>2659</v>
+      </c>
+      <c r="H943" s="3"/>
+      <c r="I943" s="3"/>
+      <c r="J943" s="3"/>
+      <c r="K943" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L943" s="3"/>
+      <c r="M943" s="3"/>
+      <c r="N943" s="3"/>
+    </row>
+    <row r="944" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A944" s="3" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B944" s="3"/>
+      <c r="C944" s="3">
+        <v>110</v>
+      </c>
+      <c r="D944" s="3">
+        <v>5813989072</v>
+      </c>
+      <c r="E944" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F944" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G944" s="3" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H944" s="3"/>
+      <c r="I944" s="3"/>
+      <c r="J944" s="3"/>
+      <c r="K944" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L944" s="3"/>
+      <c r="M944" s="3"/>
+      <c r="N944" s="3"/>
+    </row>
+    <row r="945" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A945" s="3" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B945" s="3"/>
+      <c r="C945" s="3">
+        <v>110</v>
+      </c>
+      <c r="D945" s="3">
+        <v>5814127654</v>
+      </c>
+      <c r="E945" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F945" s="3" t="s">
+        <v>2406</v>
+      </c>
+      <c r="G945" s="3" t="s">
+        <v>2662</v>
+      </c>
+      <c r="H945" s="3"/>
+      <c r="I945" s="3"/>
+      <c r="J945" s="3"/>
+      <c r="K945" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L945" s="3"/>
+      <c r="M945" s="3"/>
+      <c r="N945" s="3"/>
+    </row>
+    <row r="946" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A946" s="3" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B946" s="3"/>
+      <c r="C946" s="3">
+        <v>110</v>
+      </c>
+      <c r="D946" s="3">
+        <v>5814161186</v>
+      </c>
+      <c r="E946" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F946" s="3" t="s">
+        <v>2664</v>
+      </c>
+      <c r="G946" s="3" t="s">
+        <v>2665</v>
+      </c>
+      <c r="H946" s="3"/>
+      <c r="I946" s="3"/>
+      <c r="J946" s="3"/>
+      <c r="K946" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L946" s="3"/>
+      <c r="M946" s="3"/>
+      <c r="N946" s="3"/>
+    </row>
+    <row r="947" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A947" s="3" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B947" s="3"/>
+      <c r="C947" s="3">
+        <v>110</v>
+      </c>
+      <c r="D947" s="3">
+        <v>5814297610</v>
+      </c>
+      <c r="E947" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F947" s="3" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G947" s="3" t="s">
+        <v>2667</v>
+      </c>
+      <c r="H947" s="3"/>
+      <c r="I947" s="3"/>
+      <c r="J947" s="3"/>
+      <c r="K947" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L947" s="3"/>
+      <c r="M947" s="3"/>
+      <c r="N947" s="3"/>
+    </row>
+    <row r="948" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A948" s="3" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B948" s="3"/>
+      <c r="C948" s="3">
+        <v>110</v>
+      </c>
+      <c r="D948" s="3">
+        <v>5814331648</v>
+      </c>
+      <c r="E948" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F948" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G948" s="3" t="s">
+        <v>2669</v>
+      </c>
+      <c r="H948" s="3"/>
+      <c r="I948" s="3"/>
+      <c r="J948" s="3"/>
+      <c r="K948" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L948" s="3"/>
+      <c r="M948" s="3"/>
+      <c r="N948" s="3"/>
+    </row>
+    <row r="949" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A949" s="3" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B949" s="3"/>
+      <c r="C949" s="3">
+        <v>110</v>
+      </c>
+      <c r="D949" s="3">
+        <v>5814348995</v>
+      </c>
+      <c r="E949" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F949" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="G949" s="3" t="s">
+        <v>2671</v>
+      </c>
+      <c r="H949" s="3"/>
+      <c r="I949" s="3"/>
+      <c r="J949" s="3"/>
+      <c r="K949" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L949" s="3"/>
+      <c r="M949" s="3"/>
+      <c r="N949" s="3"/>
+    </row>
+    <row r="950" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A950" s="3" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B950" s="3"/>
+      <c r="C950" s="3">
+        <v>110</v>
+      </c>
+      <c r="D950" s="3">
+        <v>5814365802</v>
+      </c>
+      <c r="E950" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F950" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G950" s="3" t="s">
+        <v>2673</v>
+      </c>
+      <c r="H950" s="3"/>
+      <c r="I950" s="3"/>
+      <c r="J950" s="3"/>
+      <c r="K950" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L950" s="3"/>
+      <c r="M950" s="3"/>
+      <c r="N950" s="3"/>
+    </row>
+    <row r="951" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A951" s="3" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B951" s="3"/>
+      <c r="C951" s="3">
+        <v>110</v>
+      </c>
+      <c r="D951" s="3">
+        <v>5814622384</v>
+      </c>
+      <c r="E951" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F951" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G951" s="3" t="s">
+        <v>2675</v>
+      </c>
+      <c r="H951" s="3"/>
+      <c r="I951" s="3"/>
+      <c r="J951" s="3"/>
+      <c r="K951" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L951" s="3"/>
+      <c r="M951" s="3"/>
+      <c r="N951" s="3"/>
+    </row>
+    <row r="952" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A952" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B952" s="3"/>
+      <c r="C952" s="3">
+        <v>110</v>
+      </c>
+      <c r="D952" s="3">
+        <v>5814633936</v>
+      </c>
+      <c r="E952" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F952" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G952" s="3" t="s">
+        <v>2677</v>
+      </c>
+      <c r="H952" s="3"/>
+      <c r="I952" s="3"/>
+      <c r="J952" s="3"/>
+      <c r="K952" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L952" s="3"/>
+      <c r="M952" s="3"/>
+      <c r="N952" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mott's Wrecker Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B339CDB-8C11-4F31-AAF9-13CD85D3BCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F555A42-0A1C-4F12-942A-6947C7EE5E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5756" uniqueCount="2678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="2728">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -7981,6 +7981,18 @@
     <t>29.612877, -97.877020</t>
   </si>
   <si>
+    <t>05/26/26 11:16 EDT</t>
+  </si>
+  <si>
+    <t>05/23/26 09:29 EDT</t>
+  </si>
+  <si>
+    <t>6.5mi NE of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.651915, -97.886826</t>
+  </si>
+  <si>
     <t>05/23/26 09:36 EDT</t>
   </si>
   <si>
@@ -7993,6 +8005,9 @@
     <t>29.609758, -97.878390</t>
   </si>
   <si>
+    <t>05/26/26 11:18 EDT</t>
+  </si>
+  <si>
     <t>05/23/26 12:31 EDT</t>
   </si>
   <si>
@@ -8005,6 +8020,9 @@
     <t>29.606298, -97.887560</t>
   </si>
   <si>
+    <t>05/26/26 11:17 EDT</t>
+  </si>
+  <si>
     <t>05/23/26 12:56 EDT</t>
   </si>
   <si>
@@ -8054,6 +8072,138 @@
   </si>
   <si>
     <t>29.496386, -98.145310</t>
+  </si>
+  <si>
+    <t>05/23/26 14:59 EDT</t>
+  </si>
+  <si>
+    <t>29.506435, -98.132130</t>
+  </si>
+  <si>
+    <t>05/26/26 08:31 EDT</t>
+  </si>
+  <si>
+    <t>0.3mi N of Converse TX</t>
+  </si>
+  <si>
+    <t>29.512733, -98.308266</t>
+  </si>
+  <si>
+    <t>05/26/26 13:03 EDT</t>
+  </si>
+  <si>
+    <t>29.541035, -98.072520</t>
+  </si>
+  <si>
+    <t>05/26/26 15:59 EDT</t>
+  </si>
+  <si>
+    <t>5.9mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.547040, -98.052734</t>
+  </si>
+  <si>
+    <t>05/27/26 10:33 EDT</t>
+  </si>
+  <si>
+    <t>05/26/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi E of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.690088, -98.044070</t>
+  </si>
+  <si>
+    <t>05/26/26 18:06 EDT</t>
+  </si>
+  <si>
+    <t>29.534788, -98.090450</t>
+  </si>
+  <si>
+    <t>05/27/26 10:35 EDT</t>
+  </si>
+  <si>
+    <t>05/26/26 18:18 EDT</t>
+  </si>
+  <si>
+    <t>29.451363, -98.298160</t>
+  </si>
+  <si>
+    <t>05/26/26 18:34 EDT</t>
+  </si>
+  <si>
+    <t>3mi SW of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.428104, -98.417130</t>
+  </si>
+  <si>
+    <t>05/26/26 19:17 EDT</t>
+  </si>
+  <si>
+    <t>6.3mi SE of San Antonio TX</t>
+  </si>
+  <si>
+    <t>29.384167, -98.470406</t>
+  </si>
+  <si>
+    <t>05/26/26 19:21 EDT</t>
+  </si>
+  <si>
+    <t>3.3mi S of Alamo Heights TX</t>
+  </si>
+  <si>
+    <t>29.435944, -98.477220</t>
+  </si>
+  <si>
+    <t>05/26/26 19:51 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi W of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.462700, -98.404270</t>
+  </si>
+  <si>
+    <t>05/26/26 22:24 EDT</t>
+  </si>
+  <si>
+    <t>29.612875, -98.284830</t>
+  </si>
+  <si>
+    <t>05/27/26 08:24 EDT</t>
+  </si>
+  <si>
+    <t>29.460096, -98.312500</t>
+  </si>
+  <si>
+    <t>05/27/26 08:35 EDT</t>
+  </si>
+  <si>
+    <t>14.6mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.250565, -98.395280</t>
+  </si>
+  <si>
+    <t>05/27/26 08:42 EDT</t>
+  </si>
+  <si>
+    <t>15mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.243908, -98.398130</t>
+  </si>
+  <si>
+    <t>05/27/26 09:18 EDT</t>
+  </si>
+  <si>
+    <t>11.7mi N of Pleasanton TX</t>
+  </si>
+  <si>
+    <t>29.123327, -98.431180</t>
   </si>
 </sst>
 </file>
@@ -8415,7 +8565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N952"/>
+  <dimension ref="A1:N969"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -38543,35 +38693,41 @@
       <c r="G939" s="3" t="s">
         <v>2652</v>
       </c>
-      <c r="H939" s="3"/>
+      <c r="H939" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I939" s="3"/>
       <c r="J939" s="3"/>
       <c r="K939" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L939" s="3"/>
-      <c r="M939" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L939" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M939" s="3" t="s">
+        <v>2653</v>
+      </c>
       <c r="N939" s="3"/>
     </row>
     <row r="940" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A940" s="3" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="B940" s="3"/>
       <c r="C940" s="3">
         <v>112</v>
       </c>
       <c r="D940" s="3">
-        <v>5813283063</v>
+        <v>5820596139</v>
       </c>
       <c r="E940" s="3" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="F940" s="3" t="s">
-        <v>2651</v>
+        <v>2655</v>
       </c>
       <c r="G940" s="3" t="s">
-        <v>2654</v>
+        <v>2656</v>
       </c>
       <c r="H940" s="3"/>
       <c r="I940" s="3"/>
@@ -38585,74 +38741,88 @@
     </row>
     <row r="941" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A941" s="3" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
       <c r="B941" s="3"/>
       <c r="C941" s="3">
+        <v>112</v>
+      </c>
+      <c r="D941" s="3">
+        <v>5813283063</v>
+      </c>
+      <c r="E941" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F941" s="3" t="s">
+        <v>2651</v>
+      </c>
+      <c r="G941" s="3" t="s">
+        <v>2658</v>
+      </c>
+      <c r="H941" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D941" s="3">
-        <v>5813977351</v>
-      </c>
-      <c r="E941" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F941" s="3" t="s">
-        <v>2401</v>
-      </c>
-      <c r="G941" s="3" t="s">
-        <v>2656</v>
-      </c>
-      <c r="H941" s="3"/>
       <c r="I941" s="3"/>
       <c r="J941" s="3"/>
       <c r="K941" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L941" s="3"/>
-      <c r="M941" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L941" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M941" s="3" t="s">
+        <v>2653</v>
+      </c>
       <c r="N941" s="3"/>
     </row>
     <row r="942" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A942" s="3" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B942" s="3"/>
+        <v>2659</v>
+      </c>
+      <c r="B942" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="C942" s="3">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D942" s="3">
-        <v>5813988083</v>
+        <v>5813977351</v>
       </c>
       <c r="E942" s="3" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="F942" s="3" t="s">
-        <v>1394</v>
+        <v>2401</v>
       </c>
       <c r="G942" s="3" t="s">
-        <v>2658</v>
-      </c>
-      <c r="H942" s="3"/>
+        <v>2660</v>
+      </c>
+      <c r="H942" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I942" s="3"/>
       <c r="J942" s="3"/>
       <c r="K942" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L942" s="3"/>
-      <c r="M942" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L942" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M942" s="3" t="s">
+        <v>2661</v>
+      </c>
       <c r="N942" s="3"/>
     </row>
     <row r="943" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A943" s="3" t="s">
-        <v>2657</v>
+        <v>2662</v>
       </c>
       <c r="B943" s="3"/>
       <c r="C943" s="3">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D943" s="3">
-        <v>5813989068</v>
+        <v>5813988083</v>
       </c>
       <c r="E943" s="3" t="s">
         <v>17</v>
@@ -38661,7 +38831,7 @@
         <v>1394</v>
       </c>
       <c r="G943" s="3" t="s">
-        <v>2659</v>
+        <v>2663</v>
       </c>
       <c r="H943" s="3"/>
       <c r="I943" s="3"/>
@@ -38675,83 +38845,97 @@
     </row>
     <row r="944" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A944" s="3" t="s">
-        <v>2657</v>
+        <v>2662</v>
       </c>
       <c r="B944" s="3"/>
       <c r="C944" s="3">
         <v>110</v>
       </c>
       <c r="D944" s="3">
-        <v>5813989072</v>
+        <v>5813989068</v>
       </c>
       <c r="E944" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F944" s="3" t="s">
         <v>1394</v>
       </c>
       <c r="G944" s="3" t="s">
-        <v>2660</v>
-      </c>
-      <c r="H944" s="3"/>
+        <v>2664</v>
+      </c>
+      <c r="H944" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I944" s="3"/>
       <c r="J944" s="3"/>
       <c r="K944" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L944" s="3"/>
-      <c r="M944" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L944" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M944" s="3" t="s">
+        <v>2653</v>
+      </c>
       <c r="N944" s="3"/>
     </row>
     <row r="945" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A945" s="3" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B945" s="3"/>
+        <v>2662</v>
+      </c>
+      <c r="B945" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="C945" s="3">
         <v>110</v>
       </c>
       <c r="D945" s="3">
-        <v>5814127654</v>
+        <v>5813989072</v>
       </c>
       <c r="E945" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F945" s="3" t="s">
-        <v>2406</v>
+        <v>1394</v>
       </c>
       <c r="G945" s="3" t="s">
-        <v>2662</v>
-      </c>
-      <c r="H945" s="3"/>
+        <v>2665</v>
+      </c>
+      <c r="H945" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I945" s="3"/>
       <c r="J945" s="3"/>
       <c r="K945" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L945" s="3"/>
-      <c r="M945" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L945" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M945" s="3" t="s">
+        <v>2666</v>
+      </c>
       <c r="N945" s="3"/>
     </row>
     <row r="946" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A946" s="3" t="s">
-        <v>2663</v>
+        <v>2667</v>
       </c>
       <c r="B946" s="3"/>
       <c r="C946" s="3">
         <v>110</v>
       </c>
       <c r="D946" s="3">
-        <v>5814161186</v>
+        <v>5814127654</v>
       </c>
       <c r="E946" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F946" s="3" t="s">
-        <v>2664</v>
+        <v>2406</v>
       </c>
       <c r="G946" s="3" t="s">
-        <v>2665</v>
+        <v>2668</v>
       </c>
       <c r="H946" s="3"/>
       <c r="I946" s="3"/>
@@ -38765,23 +38949,23 @@
     </row>
     <row r="947" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A947" s="3" t="s">
-        <v>2666</v>
+        <v>2669</v>
       </c>
       <c r="B947" s="3"/>
       <c r="C947" s="3">
         <v>110</v>
       </c>
       <c r="D947" s="3">
-        <v>5814297610</v>
+        <v>5814161186</v>
       </c>
       <c r="E947" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F947" s="3" t="s">
-        <v>2410</v>
+        <v>2670</v>
       </c>
       <c r="G947" s="3" t="s">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="H947" s="3"/>
       <c r="I947" s="3"/>
@@ -38795,23 +38979,23 @@
     </row>
     <row r="948" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A948" s="3" t="s">
-        <v>2668</v>
+        <v>2672</v>
       </c>
       <c r="B948" s="3"/>
       <c r="C948" s="3">
         <v>110</v>
       </c>
       <c r="D948" s="3">
-        <v>5814331648</v>
+        <v>5814297610</v>
       </c>
       <c r="E948" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F948" s="3" t="s">
-        <v>552</v>
+        <v>2410</v>
       </c>
       <c r="G948" s="3" t="s">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="H948" s="3"/>
       <c r="I948" s="3"/>
@@ -38825,23 +39009,23 @@
     </row>
     <row r="949" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A949" s="3" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
       <c r="B949" s="3"/>
       <c r="C949" s="3">
         <v>110</v>
       </c>
       <c r="D949" s="3">
-        <v>5814348995</v>
+        <v>5814331648</v>
       </c>
       <c r="E949" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F949" s="3" t="s">
-        <v>798</v>
+        <v>552</v>
       </c>
       <c r="G949" s="3" t="s">
-        <v>2671</v>
+        <v>2675</v>
       </c>
       <c r="H949" s="3"/>
       <c r="I949" s="3"/>
@@ -38855,23 +39039,23 @@
     </row>
     <row r="950" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A950" s="3" t="s">
-        <v>2672</v>
+        <v>2676</v>
       </c>
       <c r="B950" s="3"/>
       <c r="C950" s="3">
         <v>110</v>
       </c>
       <c r="D950" s="3">
-        <v>5814365802</v>
+        <v>5814348995</v>
       </c>
       <c r="E950" s="3" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="F950" s="3" t="s">
-        <v>158</v>
+        <v>798</v>
       </c>
       <c r="G950" s="3" t="s">
-        <v>2673</v>
+        <v>2677</v>
       </c>
       <c r="H950" s="3"/>
       <c r="I950" s="3"/>
@@ -38885,23 +39069,23 @@
     </row>
     <row r="951" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A951" s="3" t="s">
-        <v>2674</v>
+        <v>2678</v>
       </c>
       <c r="B951" s="3"/>
       <c r="C951" s="3">
         <v>110</v>
       </c>
       <c r="D951" s="3">
-        <v>5814622384</v>
+        <v>5814365802</v>
       </c>
       <c r="E951" s="3" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="F951" s="3" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="G951" s="3" t="s">
-        <v>2675</v>
+        <v>2679</v>
       </c>
       <c r="H951" s="3"/>
       <c r="I951" s="3"/>
@@ -38915,23 +39099,23 @@
     </row>
     <row r="952" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A952" s="3" t="s">
-        <v>2676</v>
+        <v>2680</v>
       </c>
       <c r="B952" s="3"/>
       <c r="C952" s="3">
         <v>110</v>
       </c>
       <c r="D952" s="3">
-        <v>5814633936</v>
+        <v>5814622384</v>
       </c>
       <c r="E952" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F952" s="3" t="s">
-        <v>301</v>
+        <v>60</v>
       </c>
       <c r="G952" s="3" t="s">
-        <v>2677</v>
+        <v>2681</v>
       </c>
       <c r="H952" s="3"/>
       <c r="I952" s="3"/>
@@ -38943,6 +39127,542 @@
       <c r="M952" s="3"/>
       <c r="N952" s="3"/>
     </row>
+    <row r="953" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A953" s="3" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B953" s="3"/>
+      <c r="C953" s="3">
+        <v>110</v>
+      </c>
+      <c r="D953" s="3">
+        <v>5814633936</v>
+      </c>
+      <c r="E953" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F953" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G953" s="3" t="s">
+        <v>2683</v>
+      </c>
+      <c r="H953" s="3"/>
+      <c r="I953" s="3"/>
+      <c r="J953" s="3"/>
+      <c r="K953" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L953" s="3"/>
+      <c r="M953" s="3"/>
+      <c r="N953" s="3"/>
+    </row>
+    <row r="954" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A954" s="3" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B954" s="3"/>
+      <c r="C954" s="3">
+        <v>112</v>
+      </c>
+      <c r="D954" s="3">
+        <v>5820634380</v>
+      </c>
+      <c r="E954" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F954" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G954" s="3" t="s">
+        <v>2685</v>
+      </c>
+      <c r="H954" s="3"/>
+      <c r="I954" s="3"/>
+      <c r="J954" s="3"/>
+      <c r="K954" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L954" s="3"/>
+      <c r="M954" s="3"/>
+      <c r="N954" s="3"/>
+    </row>
+    <row r="955" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A955" s="3" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B955" s="3"/>
+      <c r="C955" s="3">
+        <v>301</v>
+      </c>
+      <c r="D955" s="3">
+        <v>5826303168</v>
+      </c>
+      <c r="E955" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F955" s="3" t="s">
+        <v>2687</v>
+      </c>
+      <c r="G955" s="3" t="s">
+        <v>2688</v>
+      </c>
+      <c r="H955" s="3"/>
+      <c r="I955" s="3"/>
+      <c r="J955" s="3"/>
+      <c r="K955" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L955" s="3"/>
+      <c r="M955" s="3"/>
+      <c r="N955" s="3"/>
+    </row>
+    <row r="956" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A956" s="3" t="s">
+        <v>2689</v>
+      </c>
+      <c r="B956" s="3"/>
+      <c r="C956" s="3">
+        <v>110</v>
+      </c>
+      <c r="D956" s="3">
+        <v>5828163298</v>
+      </c>
+      <c r="E956" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F956" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G956" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="H956" s="3"/>
+      <c r="I956" s="3"/>
+      <c r="J956" s="3"/>
+      <c r="K956" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L956" s="3"/>
+      <c r="M956" s="3"/>
+      <c r="N956" s="3"/>
+    </row>
+    <row r="957" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A957" s="3" t="s">
+        <v>2691</v>
+      </c>
+      <c r="B957" s="3"/>
+      <c r="C957" s="3">
+        <v>111</v>
+      </c>
+      <c r="D957" s="3">
+        <v>5829775217</v>
+      </c>
+      <c r="E957" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F957" s="3" t="s">
+        <v>2692</v>
+      </c>
+      <c r="G957" s="3" t="s">
+        <v>2693</v>
+      </c>
+      <c r="H957" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I957" s="3"/>
+      <c r="J957" s="3"/>
+      <c r="K957" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L957" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M957" s="3" t="s">
+        <v>2694</v>
+      </c>
+      <c r="N957" s="3"/>
+    </row>
+    <row r="958" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A958" s="3" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B958" s="3"/>
+      <c r="C958" s="3">
+        <v>112</v>
+      </c>
+      <c r="D958" s="3">
+        <v>5830347852</v>
+      </c>
+      <c r="E958" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F958" s="3" t="s">
+        <v>2696</v>
+      </c>
+      <c r="G958" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="H958" s="3"/>
+      <c r="I958" s="3"/>
+      <c r="J958" s="3"/>
+      <c r="K958" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L958" s="3"/>
+      <c r="M958" s="3"/>
+      <c r="N958" s="3"/>
+    </row>
+    <row r="959" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A959" s="3" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B959" s="3" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C959" s="3">
+        <v>111</v>
+      </c>
+      <c r="D959" s="3">
+        <v>5830790655</v>
+      </c>
+      <c r="E959" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F959" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="G959" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="H959" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I959" s="3"/>
+      <c r="J959" s="3"/>
+      <c r="K959" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L959" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M959" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="N959" s="3"/>
+    </row>
+    <row r="960" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A960" s="3" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B960" s="3"/>
+      <c r="C960" s="3">
+        <v>112</v>
+      </c>
+      <c r="D960" s="3">
+        <v>5830882825</v>
+      </c>
+      <c r="E960" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F960" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G960" s="3" t="s">
+        <v>2702</v>
+      </c>
+      <c r="H960" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I960" s="3"/>
+      <c r="J960" s="3"/>
+      <c r="K960" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L960" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M960" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="N960" s="3"/>
+    </row>
+    <row r="961" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A961" s="3" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B961" s="3"/>
+      <c r="C961" s="3">
+        <v>112</v>
+      </c>
+      <c r="D961" s="3">
+        <v>5830991098</v>
+      </c>
+      <c r="E961" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F961" s="3" t="s">
+        <v>2704</v>
+      </c>
+      <c r="G961" s="3" t="s">
+        <v>2705</v>
+      </c>
+      <c r="H961" s="3"/>
+      <c r="I961" s="3"/>
+      <c r="J961" s="3"/>
+      <c r="K961" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L961" s="3"/>
+      <c r="M961" s="3"/>
+      <c r="N961" s="3"/>
+    </row>
+    <row r="962" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A962" s="3" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B962" s="3"/>
+      <c r="C962" s="3">
+        <v>112</v>
+      </c>
+      <c r="D962" s="3">
+        <v>5831281360</v>
+      </c>
+      <c r="E962" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F962" s="3" t="s">
+        <v>2707</v>
+      </c>
+      <c r="G962" s="3" t="s">
+        <v>2708</v>
+      </c>
+      <c r="H962" s="3"/>
+      <c r="I962" s="3"/>
+      <c r="J962" s="3"/>
+      <c r="K962" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L962" s="3"/>
+      <c r="M962" s="3"/>
+      <c r="N962" s="3"/>
+    </row>
+    <row r="963" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A963" s="3" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B963" s="3"/>
+      <c r="C963" s="3">
+        <v>112</v>
+      </c>
+      <c r="D963" s="3">
+        <v>5831314336</v>
+      </c>
+      <c r="E963" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F963" s="3" t="s">
+        <v>2710</v>
+      </c>
+      <c r="G963" s="3" t="s">
+        <v>2711</v>
+      </c>
+      <c r="H963" s="3"/>
+      <c r="I963" s="3"/>
+      <c r="J963" s="3"/>
+      <c r="K963" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L963" s="3"/>
+      <c r="M963" s="3"/>
+      <c r="N963" s="3"/>
+    </row>
+    <row r="964" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A964" s="3" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B964" s="3"/>
+      <c r="C964" s="3">
+        <v>112</v>
+      </c>
+      <c r="D964" s="3">
+        <v>5831486636</v>
+      </c>
+      <c r="E964" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F964" s="3" t="s">
+        <v>2713</v>
+      </c>
+      <c r="G964" s="3" t="s">
+        <v>2714</v>
+      </c>
+      <c r="H964" s="3"/>
+      <c r="I964" s="3"/>
+      <c r="J964" s="3"/>
+      <c r="K964" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L964" s="3"/>
+      <c r="M964" s="3"/>
+      <c r="N964" s="3"/>
+    </row>
+    <row r="965" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A965" s="3" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B965" s="3"/>
+      <c r="C965" s="3">
+        <v>111</v>
+      </c>
+      <c r="D965" s="3">
+        <v>5831994373</v>
+      </c>
+      <c r="E965" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F965" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="G965" s="3" t="s">
+        <v>2716</v>
+      </c>
+      <c r="H965" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I965" s="3"/>
+      <c r="J965" s="3"/>
+      <c r="K965" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L965" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M965" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="N965" s="3"/>
+    </row>
+    <row r="966" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A966" s="3" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B966" s="3"/>
+      <c r="C966" s="3">
+        <v>112</v>
+      </c>
+      <c r="D966" s="3">
+        <v>5833329274</v>
+      </c>
+      <c r="E966" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F966" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G966" s="3" t="s">
+        <v>2718</v>
+      </c>
+      <c r="H966" s="3"/>
+      <c r="I966" s="3"/>
+      <c r="J966" s="3"/>
+      <c r="K966" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L966" s="3"/>
+      <c r="M966" s="3"/>
+      <c r="N966" s="3"/>
+    </row>
+    <row r="967" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A967" s="3" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B967" s="3"/>
+      <c r="C967" s="3">
+        <v>110</v>
+      </c>
+      <c r="D967" s="3">
+        <v>5833381937</v>
+      </c>
+      <c r="E967" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F967" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G967" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="H967" s="3"/>
+      <c r="I967" s="3"/>
+      <c r="J967" s="3"/>
+      <c r="K967" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L967" s="3"/>
+      <c r="M967" s="3"/>
+      <c r="N967" s="3"/>
+    </row>
+    <row r="968" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A968" s="3" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B968" s="3"/>
+      <c r="C968" s="3">
+        <v>112</v>
+      </c>
+      <c r="D968" s="3">
+        <v>5833419556</v>
+      </c>
+      <c r="E968" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F968" s="3" t="s">
+        <v>2723</v>
+      </c>
+      <c r="G968" s="3" t="s">
+        <v>2724</v>
+      </c>
+      <c r="H968" s="3"/>
+      <c r="I968" s="3"/>
+      <c r="J968" s="3"/>
+      <c r="K968" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L968" s="3"/>
+      <c r="M968" s="3"/>
+      <c r="N968" s="3"/>
+    </row>
+    <row r="969" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A969" s="3" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B969" s="3"/>
+      <c r="C969" s="3">
+        <v>110</v>
+      </c>
+      <c r="D969" s="3">
+        <v>5833604662</v>
+      </c>
+      <c r="E969" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F969" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="G969" s="3" t="s">
+        <v>2727</v>
+      </c>
+      <c r="H969" s="3"/>
+      <c r="I969" s="3"/>
+      <c r="J969" s="3"/>
+      <c r="K969" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L969" s="3"/>
+      <c r="M969" s="3"/>
+      <c r="N969" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott's Wrecker Service- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E8C357C-4BF1-41D9-88ED-8CA3D47BC3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90AA7E4C-EB15-4CFE-B962-A82B75842BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6546" uniqueCount="3020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6711" uniqueCount="3098">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -9073,6 +9073,9 @@
     <t>29.448645, -98.349380</t>
   </si>
   <si>
+    <t>06/15/26 09:32 EDT</t>
+  </si>
+  <si>
     <t>06/13/26 18:05 EDT</t>
   </si>
   <si>
@@ -9080,6 +9083,237 @@
   </si>
   <si>
     <t>30.009205, -97.687860</t>
+  </si>
+  <si>
+    <t>06/15/26 14:45 EDT</t>
+  </si>
+  <si>
+    <t>6.2mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.579042, -98.110550</t>
+  </si>
+  <si>
+    <t>06/15/26 15:06 EDT</t>
+  </si>
+  <si>
+    <t>29.498163, -98.195720</t>
+  </si>
+  <si>
+    <t>06/15/26 15:56 EDT</t>
+  </si>
+  <si>
+    <t>29.511707, -98.159300</t>
+  </si>
+  <si>
+    <t>06/16/26 09:14 EDT</t>
+  </si>
+  <si>
+    <t>06/15/26 20:29 EDT</t>
+  </si>
+  <si>
+    <t>29.424334, -98.429634</t>
+  </si>
+  <si>
+    <t>06/15/26 20:30 EDT</t>
+  </si>
+  <si>
+    <t>29.424374, -98.422550</t>
+  </si>
+  <si>
+    <t>06/16/26 09:58 EDT</t>
+  </si>
+  <si>
+    <t>29.541033, -98.072530</t>
+  </si>
+  <si>
+    <t>06/16/26 11:56 EDT</t>
+  </si>
+  <si>
+    <t>29.092806, -97.287450</t>
+  </si>
+  <si>
+    <t>06/17/26 09:47 EDT</t>
+  </si>
+  <si>
+    <t>06/16/26 12:25 EDT</t>
+  </si>
+  <si>
+    <t>2mi SW of Victoria TX</t>
+  </si>
+  <si>
+    <t>28.805674, -97.003600</t>
+  </si>
+  <si>
+    <t>06/17/26 07:45 EDT</t>
+  </si>
+  <si>
+    <t>5mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.515053, -98.150276</t>
+  </si>
+  <si>
+    <t>06/17/26 09:59 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi NE of Pleasanton TX</t>
+  </si>
+  <si>
+    <t>29.000110, -98.431340</t>
+  </si>
+  <si>
+    <t>06/17/26 12:06 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi S of Houston TX</t>
+  </si>
+  <si>
+    <t>29.737053, -95.368900</t>
+  </si>
+  <si>
+    <t>06/17/26 15:17 EDT</t>
+  </si>
+  <si>
+    <t>27mi N of Rockport TX</t>
+  </si>
+  <si>
+    <t>28.411135, -97.164950</t>
+  </si>
+  <si>
+    <t>06/17/26 15:37 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 16:42 EDT</t>
+  </si>
+  <si>
+    <t>29.406410, -98.439500</t>
+  </si>
+  <si>
+    <t>06/17/26 16:55 EDT</t>
+  </si>
+  <si>
+    <t>7.1mi NW of Corpus Christi TX</t>
+  </si>
+  <si>
+    <t>27.803238, -97.453285</t>
+  </si>
+  <si>
+    <t>06/18/26 16:49 EDT</t>
+  </si>
+  <si>
+    <t>10.9mi W of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.367743, -98.797740</t>
+  </si>
+  <si>
+    <t>06/19/26 15:33 EDT</t>
+  </si>
+  <si>
+    <t>29.492100, -98.212555</t>
+  </si>
+  <si>
+    <t>29.491184, -98.215250</t>
+  </si>
+  <si>
+    <t>06/19/26 15:36 EDT</t>
+  </si>
+  <si>
+    <t>11.3mi S of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.226328, -98.583984</t>
+  </si>
+  <si>
+    <t>06/19/26 16:32 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.433548, -98.390060</t>
+  </si>
+  <si>
+    <t>COLLISION-WARNING</t>
+  </si>
+  <si>
+    <t>06/19/26 16:36 EDT</t>
+  </si>
+  <si>
+    <t>5.6mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.380670, -98.392265</t>
+  </si>
+  <si>
+    <t>06/19/26 16:42 EDT</t>
+  </si>
+  <si>
+    <t>7.7mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.371685, -98.309390</t>
+  </si>
+  <si>
+    <t>06/19/26 16:55 EDT</t>
+  </si>
+  <si>
+    <t>9mi NE of Pleasanton TX</t>
+  </si>
+  <si>
+    <t>29.081774, -98.433105</t>
+  </si>
+  <si>
+    <t>06/19/26 17:11 EDT</t>
+  </si>
+  <si>
+    <t>11.4mi SE of Pleasanton TX</t>
+  </si>
+  <si>
+    <t>28.838848, -98.374275</t>
+  </si>
+  <si>
+    <t>06/19/26 17:16 EDT</t>
+  </si>
+  <si>
+    <t>29.504192, -98.177925</t>
+  </si>
+  <si>
+    <t>06/19/26 17:58 EDT</t>
+  </si>
+  <si>
+    <t>15.9mi SW of Beeville TX</t>
+  </si>
+  <si>
+    <t>28.217615, -97.899280</t>
+  </si>
+  <si>
+    <t>06/19/26 20:59 EDT</t>
+  </si>
+  <si>
+    <t>12.3mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.283424, -98.395480</t>
+  </si>
+  <si>
+    <t>06/20/26 09:49 EDT</t>
+  </si>
+  <si>
+    <t>3mi NW of Windcrest TX</t>
+  </si>
+  <si>
+    <t>29.541565, -98.420360</t>
+  </si>
+  <si>
+    <t>06/20/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>5.2mi NW of Bulverde TX</t>
+  </si>
+  <si>
+    <t>29.806564, -98.515270</t>
   </si>
 </sst>
 </file>
@@ -9441,7 +9675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1076"/>
+  <dimension ref="A1:N1105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -44001,15 +44235,19 @@
       <c r="I1075" s="3"/>
       <c r="J1075" s="3"/>
       <c r="K1075" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1075" s="3"/>
-      <c r="M1075" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1075" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1075" s="3" t="s">
+        <v>3017</v>
+      </c>
       <c r="N1075" s="3"/>
     </row>
     <row r="1076" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1076" s="3" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="B1076" s="3"/>
       <c r="C1076" s="3">
@@ -44022,20 +44260,926 @@
         <v>80</v>
       </c>
       <c r="F1076" s="3" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="G1076" s="3" t="s">
-        <v>3019</v>
-      </c>
-      <c r="H1076" s="3"/>
+        <v>3020</v>
+      </c>
+      <c r="H1076" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1076" s="3"/>
       <c r="J1076" s="3"/>
       <c r="K1076" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1076" s="3"/>
-      <c r="M1076" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1076" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1076" s="3" t="s">
+        <v>3017</v>
+      </c>
       <c r="N1076" s="3"/>
+    </row>
+    <row r="1077" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1077" s="3" t="s">
+        <v>3021</v>
+      </c>
+      <c r="B1077" s="3"/>
+      <c r="C1077" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1077" s="3">
+        <v>5953051979</v>
+      </c>
+      <c r="E1077" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1077" s="3" t="s">
+        <v>3022</v>
+      </c>
+      <c r="G1077" s="3" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H1077" s="3"/>
+      <c r="I1077" s="3"/>
+      <c r="J1077" s="3"/>
+      <c r="K1077" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1077" s="3"/>
+      <c r="M1077" s="3"/>
+      <c r="N1077" s="3"/>
+    </row>
+    <row r="1078" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1078" s="3" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B1078" s="3"/>
+      <c r="C1078" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1078" s="3">
+        <v>5953249916</v>
+      </c>
+      <c r="E1078" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1078" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1078" s="3" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H1078" s="3"/>
+      <c r="I1078" s="3"/>
+      <c r="J1078" s="3"/>
+      <c r="K1078" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1078" s="3"/>
+      <c r="M1078" s="3"/>
+      <c r="N1078" s="3"/>
+    </row>
+    <row r="1079" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1079" s="3" t="s">
+        <v>3026</v>
+      </c>
+      <c r="B1079" s="3"/>
+      <c r="C1079" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1079" s="3">
+        <v>5953689624</v>
+      </c>
+      <c r="E1079" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1079" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1079" s="3" t="s">
+        <v>3027</v>
+      </c>
+      <c r="H1079" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1079" s="3"/>
+      <c r="J1079" s="3"/>
+      <c r="K1079" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1079" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1079" s="3" t="s">
+        <v>3028</v>
+      </c>
+      <c r="N1079" s="3"/>
+    </row>
+    <row r="1080" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1080" s="3" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B1080" s="3"/>
+      <c r="C1080" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1080" s="3">
+        <v>5955522837</v>
+      </c>
+      <c r="E1080" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1080" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1080" s="3" t="s">
+        <v>3030</v>
+      </c>
+      <c r="H1080" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1080" s="3"/>
+      <c r="J1080" s="3"/>
+      <c r="K1080" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1080" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1080" s="3" t="s">
+        <v>3028</v>
+      </c>
+      <c r="N1080" s="3"/>
+    </row>
+    <row r="1081" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1081" s="3" t="s">
+        <v>3031</v>
+      </c>
+      <c r="B1081" s="3"/>
+      <c r="C1081" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1081" s="3">
+        <v>5955526693</v>
+      </c>
+      <c r="E1081" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1081" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G1081" s="3" t="s">
+        <v>3032</v>
+      </c>
+      <c r="H1081" s="3"/>
+      <c r="I1081" s="3"/>
+      <c r="J1081" s="3"/>
+      <c r="K1081" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1081" s="3"/>
+      <c r="M1081" s="3"/>
+      <c r="N1081" s="3"/>
+    </row>
+    <row r="1082" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1082" s="3" t="s">
+        <v>3033</v>
+      </c>
+      <c r="B1082" s="3"/>
+      <c r="C1082" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1082" s="3">
+        <v>5957797388</v>
+      </c>
+      <c r="E1082" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1082" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1082" s="3" t="s">
+        <v>3034</v>
+      </c>
+      <c r="H1082" s="3"/>
+      <c r="I1082" s="3"/>
+      <c r="J1082" s="3"/>
+      <c r="K1082" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1082" s="3"/>
+      <c r="M1082" s="3"/>
+      <c r="N1082" s="3"/>
+    </row>
+    <row r="1083" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1083" s="3" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B1083" s="3"/>
+      <c r="C1083" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1083" s="3">
+        <v>5958641827</v>
+      </c>
+      <c r="E1083" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1083" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1083" s="3" t="s">
+        <v>3036</v>
+      </c>
+      <c r="H1083" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1083" s="3"/>
+      <c r="J1083" s="3"/>
+      <c r="K1083" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1083" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1083" s="3" t="s">
+        <v>3037</v>
+      </c>
+      <c r="N1083" s="3"/>
+    </row>
+    <row r="1084" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1084" s="3" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B1084" s="3"/>
+      <c r="C1084" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1084" s="3">
+        <v>5958889971</v>
+      </c>
+      <c r="E1084" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1084" s="3" t="s">
+        <v>3039</v>
+      </c>
+      <c r="G1084" s="3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="H1084" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1084" s="3"/>
+      <c r="J1084" s="3"/>
+      <c r="K1084" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1084" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1084" s="3" t="s">
+        <v>3037</v>
+      </c>
+      <c r="N1084" s="3"/>
+    </row>
+    <row r="1085" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1085" s="3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B1085" s="3"/>
+      <c r="C1085" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1085" s="3">
+        <v>5964301227</v>
+      </c>
+      <c r="E1085" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1085" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="G1085" s="3" t="s">
+        <v>3043</v>
+      </c>
+      <c r="H1085" s="3"/>
+      <c r="I1085" s="3"/>
+      <c r="J1085" s="3"/>
+      <c r="K1085" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1085" s="3"/>
+      <c r="M1085" s="3"/>
+      <c r="N1085" s="3"/>
+    </row>
+    <row r="1086" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1086" s="3" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B1086" s="3"/>
+      <c r="C1086" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1086" s="3">
+        <v>5977859520</v>
+      </c>
+      <c r="E1086" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1086" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="G1086" s="3" t="s">
+        <v>3046</v>
+      </c>
+      <c r="H1086" s="3"/>
+      <c r="I1086" s="3"/>
+      <c r="J1086" s="3"/>
+      <c r="K1086" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1086" s="3"/>
+      <c r="M1086" s="3"/>
+      <c r="N1086" s="3"/>
+    </row>
+    <row r="1087" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1087" s="3" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B1087" s="3"/>
+      <c r="C1087" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1087" s="3">
+        <v>5965938775</v>
+      </c>
+      <c r="E1087" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1087" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="G1087" s="3" t="s">
+        <v>3049</v>
+      </c>
+      <c r="H1087" s="3"/>
+      <c r="I1087" s="3"/>
+      <c r="J1087" s="3"/>
+      <c r="K1087" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1087" s="3"/>
+      <c r="M1087" s="3"/>
+      <c r="N1087" s="3"/>
+    </row>
+    <row r="1088" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1088" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="B1088" s="3"/>
+      <c r="C1088" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1088" s="3">
+        <v>5967690500</v>
+      </c>
+      <c r="E1088" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1088" s="3" t="s">
+        <v>3051</v>
+      </c>
+      <c r="G1088" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="H1088" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1088" s="3"/>
+      <c r="J1088" s="3"/>
+      <c r="K1088" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1088" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1088" s="3" t="s">
+        <v>3053</v>
+      </c>
+      <c r="N1088" s="3"/>
+    </row>
+    <row r="1089" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1089" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B1089" s="3"/>
+      <c r="C1089" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1089" s="3">
+        <v>5968423462</v>
+      </c>
+      <c r="E1089" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1089" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G1089" s="3" t="s">
+        <v>3055</v>
+      </c>
+      <c r="H1089" s="3"/>
+      <c r="I1089" s="3"/>
+      <c r="J1089" s="3"/>
+      <c r="K1089" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1089" s="3"/>
+      <c r="M1089" s="3"/>
+      <c r="N1089" s="3"/>
+    </row>
+    <row r="1090" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1090" s="3" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B1090" s="3"/>
+      <c r="C1090" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1090" s="3">
+        <v>5968530950</v>
+      </c>
+      <c r="E1090" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1090" s="3" t="s">
+        <v>3057</v>
+      </c>
+      <c r="G1090" s="3" t="s">
+        <v>3058</v>
+      </c>
+      <c r="H1090" s="3"/>
+      <c r="I1090" s="3"/>
+      <c r="J1090" s="3"/>
+      <c r="K1090" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1090" s="3"/>
+      <c r="M1090" s="3"/>
+      <c r="N1090" s="3"/>
+    </row>
+    <row r="1091" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1091" s="3" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B1091" s="3"/>
+      <c r="C1091" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1091" s="3">
+        <v>5975689676</v>
+      </c>
+      <c r="E1091" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1091" s="3" t="s">
+        <v>3060</v>
+      </c>
+      <c r="G1091" s="3" t="s">
+        <v>3061</v>
+      </c>
+      <c r="H1091" s="3"/>
+      <c r="I1091" s="3"/>
+      <c r="J1091" s="3"/>
+      <c r="K1091" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1091" s="3"/>
+      <c r="M1091" s="3"/>
+      <c r="N1091" s="3"/>
+    </row>
+    <row r="1092" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1092" s="3" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B1092" s="3"/>
+      <c r="C1092" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1092" s="3">
+        <v>5981837722</v>
+      </c>
+      <c r="E1092" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1092" s="3" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G1092" s="3" t="s">
+        <v>3063</v>
+      </c>
+      <c r="H1092" s="3"/>
+      <c r="I1092" s="3"/>
+      <c r="J1092" s="3"/>
+      <c r="K1092" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1092" s="3"/>
+      <c r="M1092" s="3"/>
+      <c r="N1092" s="3"/>
+    </row>
+    <row r="1093" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1093" s="3" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B1093" s="3"/>
+      <c r="C1093" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1093" s="3">
+        <v>5981845362</v>
+      </c>
+      <c r="E1093" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1093" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="G1093" s="3" t="s">
+        <v>3064</v>
+      </c>
+      <c r="H1093" s="3"/>
+      <c r="I1093" s="3"/>
+      <c r="J1093" s="3"/>
+      <c r="K1093" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1093" s="3"/>
+      <c r="M1093" s="3"/>
+      <c r="N1093" s="3"/>
+    </row>
+    <row r="1094" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1094" s="3" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B1094" s="3"/>
+      <c r="C1094" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1094" s="3">
+        <v>5981868624</v>
+      </c>
+      <c r="E1094" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1094" s="3" t="s">
+        <v>3066</v>
+      </c>
+      <c r="G1094" s="3" t="s">
+        <v>3067</v>
+      </c>
+      <c r="H1094" s="3"/>
+      <c r="I1094" s="3"/>
+      <c r="J1094" s="3"/>
+      <c r="K1094" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1094" s="3"/>
+      <c r="M1094" s="3"/>
+      <c r="N1094" s="3"/>
+    </row>
+    <row r="1095" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1095" s="3" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B1095" s="3"/>
+      <c r="C1095" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1095" s="3">
+        <v>5982274614</v>
+      </c>
+      <c r="E1095" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1095" s="3" t="s">
+        <v>3069</v>
+      </c>
+      <c r="G1095" s="3" t="s">
+        <v>3070</v>
+      </c>
+      <c r="H1095" s="3"/>
+      <c r="I1095" s="3"/>
+      <c r="J1095" s="3"/>
+      <c r="K1095" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1095" s="3"/>
+      <c r="M1095" s="3"/>
+      <c r="N1095" s="3"/>
+    </row>
+    <row r="1096" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1096" s="3" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B1096" s="3"/>
+      <c r="C1096" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1096" s="3">
+        <v>5982274613</v>
+      </c>
+      <c r="E1096" s="3" t="s">
+        <v>3071</v>
+      </c>
+      <c r="F1096" s="3" t="s">
+        <v>3069</v>
+      </c>
+      <c r="G1096" s="3" t="s">
+        <v>3070</v>
+      </c>
+      <c r="H1096" s="3"/>
+      <c r="I1096" s="3"/>
+      <c r="J1096" s="3"/>
+      <c r="K1096" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1096" s="3"/>
+      <c r="M1096" s="3"/>
+      <c r="N1096" s="3"/>
+    </row>
+    <row r="1097" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1097" s="3" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B1097" s="3"/>
+      <c r="C1097" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1097" s="3">
+        <v>5982303503</v>
+      </c>
+      <c r="E1097" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1097" s="3" t="s">
+        <v>3073</v>
+      </c>
+      <c r="G1097" s="3" t="s">
+        <v>3074</v>
+      </c>
+      <c r="H1097" s="3"/>
+      <c r="I1097" s="3"/>
+      <c r="J1097" s="3"/>
+      <c r="K1097" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1097" s="3"/>
+      <c r="M1097" s="3"/>
+      <c r="N1097" s="3"/>
+    </row>
+    <row r="1098" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1098" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="B1098" s="3"/>
+      <c r="C1098" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1098" s="3">
+        <v>5982344394</v>
+      </c>
+      <c r="E1098" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1098" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="G1098" s="3" t="s">
+        <v>3077</v>
+      </c>
+      <c r="H1098" s="3"/>
+      <c r="I1098" s="3"/>
+      <c r="J1098" s="3"/>
+      <c r="K1098" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1098" s="3"/>
+      <c r="M1098" s="3"/>
+      <c r="N1098" s="3"/>
+    </row>
+    <row r="1099" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1099" s="3" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B1099" s="3"/>
+      <c r="C1099" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1099" s="3">
+        <v>5982441806</v>
+      </c>
+      <c r="E1099" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1099" s="3" t="s">
+        <v>3079</v>
+      </c>
+      <c r="G1099" s="3" t="s">
+        <v>3080</v>
+      </c>
+      <c r="H1099" s="3"/>
+      <c r="I1099" s="3"/>
+      <c r="J1099" s="3"/>
+      <c r="K1099" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1099" s="3"/>
+      <c r="M1099" s="3"/>
+      <c r="N1099" s="3"/>
+    </row>
+    <row r="1100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1100" s="3" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B1100" s="3"/>
+      <c r="C1100" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1100" s="3">
+        <v>5982551951</v>
+      </c>
+      <c r="E1100" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1100" s="3" t="s">
+        <v>3082</v>
+      </c>
+      <c r="G1100" s="3" t="s">
+        <v>3083</v>
+      </c>
+      <c r="H1100" s="3"/>
+      <c r="I1100" s="3"/>
+      <c r="J1100" s="3"/>
+      <c r="K1100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1100" s="3"/>
+      <c r="M1100" s="3"/>
+      <c r="N1100" s="3"/>
+    </row>
+    <row r="1101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1101" s="3" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B1101" s="3"/>
+      <c r="C1101" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1101" s="3">
+        <v>5982588070</v>
+      </c>
+      <c r="E1101" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1101" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1101" s="3" t="s">
+        <v>3085</v>
+      </c>
+      <c r="H1101" s="3"/>
+      <c r="I1101" s="3"/>
+      <c r="J1101" s="3"/>
+      <c r="K1101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1101" s="3"/>
+      <c r="M1101" s="3"/>
+      <c r="N1101" s="3"/>
+    </row>
+    <row r="1102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1102" s="3" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B1102" s="3"/>
+      <c r="C1102" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1102" s="3">
+        <v>5982862612</v>
+      </c>
+      <c r="E1102" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1102" s="3" t="s">
+        <v>3087</v>
+      </c>
+      <c r="G1102" s="3" t="s">
+        <v>3088</v>
+      </c>
+      <c r="H1102" s="3"/>
+      <c r="I1102" s="3"/>
+      <c r="J1102" s="3"/>
+      <c r="K1102" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1102" s="3"/>
+      <c r="M1102" s="3"/>
+      <c r="N1102" s="3"/>
+    </row>
+    <row r="1103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1103" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="B1103" s="3"/>
+      <c r="C1103" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1103" s="3">
+        <v>5983758162</v>
+      </c>
+      <c r="E1103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1103" s="3" t="s">
+        <v>3090</v>
+      </c>
+      <c r="G1103" s="3" t="s">
+        <v>3091</v>
+      </c>
+      <c r="H1103" s="3"/>
+      <c r="I1103" s="3"/>
+      <c r="J1103" s="3"/>
+      <c r="K1103" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1103" s="3"/>
+      <c r="M1103" s="3"/>
+      <c r="N1103" s="3"/>
+    </row>
+    <row r="1104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1104" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B1104" s="3"/>
+      <c r="C1104" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1104" s="3">
+        <v>5985190490</v>
+      </c>
+      <c r="E1104" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1104" s="3" t="s">
+        <v>3093</v>
+      </c>
+      <c r="G1104" s="3" t="s">
+        <v>3094</v>
+      </c>
+      <c r="H1104" s="3"/>
+      <c r="I1104" s="3"/>
+      <c r="J1104" s="3"/>
+      <c r="K1104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1104" s="3"/>
+      <c r="M1104" s="3"/>
+      <c r="N1104" s="3"/>
+    </row>
+    <row r="1105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1105" s="3" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B1105" s="3"/>
+      <c r="C1105" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1105" s="3">
+        <v>5985506923</v>
+      </c>
+      <c r="E1105" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1105" s="3" t="s">
+        <v>3096</v>
+      </c>
+      <c r="G1105" s="3" t="s">
+        <v>3097</v>
+      </c>
+      <c r="H1105" s="3"/>
+      <c r="I1105" s="3"/>
+      <c r="J1105" s="3"/>
+      <c r="K1105" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1105" s="3"/>
+      <c r="M1105" s="3"/>
+      <c r="N1105" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90AA7E4C-EB15-4CFE-B962-A82B75842BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74B3D852-677E-4667-B716-31568BDD8EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6711" uniqueCount="3098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6868" uniqueCount="3170">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -9145,6 +9145,9 @@
     <t>28.805674, -97.003600</t>
   </si>
   <si>
+    <t>06/21/26 22:18 EDT</t>
+  </si>
+  <si>
     <t>06/17/26 07:45 EDT</t>
   </si>
   <si>
@@ -9214,9 +9217,18 @@
     <t>29.492100, -98.212555</t>
   </si>
   <si>
+    <t>06/22/26 12:47 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 12:59 EDT</t>
+  </si>
+  <si>
     <t>29.491184, -98.215250</t>
   </si>
   <si>
+    <t>06/21/26 20:59 EDT</t>
+  </si>
+  <si>
     <t>06/19/26 15:36 EDT</t>
   </si>
   <si>
@@ -9226,16 +9238,28 @@
     <t>29.226328, -98.583984</t>
   </si>
   <si>
+    <t>06/22/26 13:00 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 13:13 EDT</t>
+  </si>
+  <si>
     <t>06/19/26 16:32 EDT</t>
   </si>
   <si>
+    <t>COLLISION-WARNING</t>
+  </si>
+  <si>
     <t>1.9mi S of Kirby TX</t>
   </si>
   <si>
     <t>29.433548, -98.390060</t>
   </si>
   <si>
-    <t>COLLISION-WARNING</t>
+    <t>06/22/26 13:05 EDT</t>
+  </si>
+  <si>
+    <t>06/21/26 21:00 EDT</t>
   </si>
   <si>
     <t>06/19/26 16:36 EDT</t>
@@ -9280,6 +9304,9 @@
     <t>29.504192, -98.177925</t>
   </si>
   <si>
+    <t>06/22/26 13:06 EDT</t>
+  </si>
+  <si>
     <t>06/19/26 17:58 EDT</t>
   </si>
   <si>
@@ -9314,6 +9341,195 @@
   </si>
   <si>
     <t>29.806564, -98.515270</t>
+  </si>
+  <si>
+    <t>06/22/26 10:01 EDT</t>
+  </si>
+  <si>
+    <t>29.507328, -98.170260</t>
+  </si>
+  <si>
+    <t>06/22/26 15:59 EDT</t>
+  </si>
+  <si>
+    <t>6.9mi N of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.688313, -97.964140</t>
+  </si>
+  <si>
+    <t>06/22/26 16:03 EDT</t>
+  </si>
+  <si>
+    <t>9.3mi S of San Marcos TX</t>
+  </si>
+  <si>
+    <t>29.739632, -97.951100</t>
+  </si>
+  <si>
+    <t>06/22/26 17:59 EDT</t>
+  </si>
+  <si>
+    <t>29.586456, -97.994080</t>
+  </si>
+  <si>
+    <t>06/22/26 18:46 EDT</t>
+  </si>
+  <si>
+    <t>7.4mi S of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.483875, -97.949150</t>
+  </si>
+  <si>
+    <t>06/23/26 02:32 EDT</t>
+  </si>
+  <si>
+    <t>2.3mi S of Luling TX</t>
+  </si>
+  <si>
+    <t>29.649494, -97.638690</t>
+  </si>
+  <si>
+    <t>06/23/26 08:36 EDT</t>
+  </si>
+  <si>
+    <t>06/23/26 04:08 EDT</t>
+  </si>
+  <si>
+    <t>29.497390, -98.195200</t>
+  </si>
+  <si>
+    <t>06/23/26 05:29 EDT</t>
+  </si>
+  <si>
+    <t>29.506426, -98.132110</t>
+  </si>
+  <si>
+    <t>06/23/26 11:23 EDT</t>
+  </si>
+  <si>
+    <t>29.437927, -98.383120</t>
+  </si>
+  <si>
+    <t>06/23/26 23:29 EDT</t>
+  </si>
+  <si>
+    <t>29.559006, -98.343410</t>
+  </si>
+  <si>
+    <t>06/24/26 11:49 EDT</t>
+  </si>
+  <si>
+    <t>5.7mi SW of Luling TX</t>
+  </si>
+  <si>
+    <t>29.636750, -97.727455</t>
+  </si>
+  <si>
+    <t>06/24/26 15:55 EDT</t>
+  </si>
+  <si>
+    <t>1.2mi E of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.700788, -98.094574</t>
+  </si>
+  <si>
+    <t>06/25/26 07:38 EDT</t>
+  </si>
+  <si>
+    <t>06/24/26 16:15 EDT</t>
+  </si>
+  <si>
+    <t>29.396173, -98.499940</t>
+  </si>
+  <si>
+    <t>06/25/26 10:22 EDT</t>
+  </si>
+  <si>
+    <t>29.674465, -98.153510</t>
+  </si>
+  <si>
+    <t>06/25/26 11:16 EDT</t>
+  </si>
+  <si>
+    <t>29.529177, -98.113490</t>
+  </si>
+  <si>
+    <t>06/25/26 14:00 EDT</t>
+  </si>
+  <si>
+    <t>29.459583, -98.315900</t>
+  </si>
+  <si>
+    <t>06/25/26 14:53 EDT</t>
+  </si>
+  <si>
+    <t>2mi E of Selma TX</t>
+  </si>
+  <si>
+    <t>29.594463, -98.281525</t>
+  </si>
+  <si>
+    <t>06/25/26 23:29 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 16:30 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi S of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.689774, -98.114900</t>
+  </si>
+  <si>
+    <t>06/25/26 19:22 EDT</t>
+  </si>
+  <si>
+    <t>29.510834, -98.159900</t>
+  </si>
+  <si>
+    <t>06/26/26 12:09 EDT</t>
+  </si>
+  <si>
+    <t>18.6mi S of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.328980, -97.886280</t>
+  </si>
+  <si>
+    <t>06/26/26 12:16 EDT</t>
+  </si>
+  <si>
+    <t>23.8mi SE of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.281810, -97.789230</t>
+  </si>
+  <si>
+    <t>06/26/26 13:55 EDT</t>
+  </si>
+  <si>
+    <t>22.9mi E of Floresville TX</t>
+  </si>
+  <si>
+    <t>29.257717, -97.807304</t>
+  </si>
+  <si>
+    <t>06/26/26 13:57 EDT</t>
+  </si>
+  <si>
+    <t>20.7mi E of Floresville TX</t>
+  </si>
+  <si>
+    <t>29.249165, -97.843230</t>
+  </si>
+  <si>
+    <t>06/27/26 20:21 EDT</t>
+  </si>
+  <si>
+    <t>29.457270, -98.216060</t>
   </si>
 </sst>
 </file>
@@ -9675,7 +9891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1105"/>
+  <dimension ref="A1:N1129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -44530,7 +44746,7 @@
         <v>3040</v>
       </c>
       <c r="H1084" s="3" t="s">
-        <v>110</v>
+        <v>1678</v>
       </c>
       <c r="I1084" s="3"/>
       <c r="J1084" s="3"/>
@@ -44541,13 +44757,13 @@
         <v>39</v>
       </c>
       <c r="M1084" s="3" t="s">
-        <v>3037</v>
+        <v>3041</v>
       </c>
       <c r="N1084" s="3"/>
     </row>
     <row r="1085" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1085" s="3" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="B1085" s="3"/>
       <c r="C1085" s="3">
@@ -44560,10 +44776,10 @@
         <v>71</v>
       </c>
       <c r="F1085" s="3" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="G1085" s="3" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="H1085" s="3"/>
       <c r="I1085" s="3"/>
@@ -44577,7 +44793,7 @@
     </row>
     <row r="1086" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1086" s="3" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="B1086" s="3"/>
       <c r="C1086" s="3">
@@ -44590,10 +44806,10 @@
         <v>53</v>
       </c>
       <c r="F1086" s="3" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="G1086" s="3" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="H1086" s="3"/>
       <c r="I1086" s="3"/>
@@ -44607,7 +44823,7 @@
     </row>
     <row r="1087" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1087" s="3" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="B1087" s="3"/>
       <c r="C1087" s="3">
@@ -44620,10 +44836,10 @@
         <v>53</v>
       </c>
       <c r="F1087" s="3" t="s">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="G1087" s="3" t="s">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="H1087" s="3"/>
       <c r="I1087" s="3"/>
@@ -44637,7 +44853,7 @@
     </row>
     <row r="1088" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1088" s="3" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="B1088" s="3"/>
       <c r="C1088" s="3">
@@ -44650,10 +44866,10 @@
         <v>80</v>
       </c>
       <c r="F1088" s="3" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="G1088" s="3" t="s">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="H1088" s="3" t="s">
         <v>110</v>
@@ -44667,13 +44883,13 @@
         <v>39</v>
       </c>
       <c r="M1088" s="3" t="s">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="N1088" s="3"/>
     </row>
     <row r="1089" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1089" s="3" t="s">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="B1089" s="3"/>
       <c r="C1089" s="3">
@@ -44689,7 +44905,7 @@
         <v>1618</v>
       </c>
       <c r="G1089" s="3" t="s">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="H1089" s="3"/>
       <c r="I1089" s="3"/>
@@ -44703,7 +44919,7 @@
     </row>
     <row r="1090" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1090" s="3" t="s">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="B1090" s="3"/>
       <c r="C1090" s="3">
@@ -44716,10 +44932,10 @@
         <v>34</v>
       </c>
       <c r="F1090" s="3" t="s">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="G1090" s="3" t="s">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="H1090" s="3"/>
       <c r="I1090" s="3"/>
@@ -44733,7 +44949,7 @@
     </row>
     <row r="1091" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1091" s="3" t="s">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="B1091" s="3"/>
       <c r="C1091" s="3">
@@ -44746,10 +44962,10 @@
         <v>34</v>
       </c>
       <c r="F1091" s="3" t="s">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="G1091" s="3" t="s">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="H1091" s="3"/>
       <c r="I1091" s="3"/>
@@ -44763,9 +44979,11 @@
     </row>
     <row r="1092" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1092" s="3" t="s">
-        <v>3062</v>
-      </c>
-      <c r="B1092" s="3"/>
+        <v>3063</v>
+      </c>
+      <c r="B1092" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="C1092" s="3">
         <v>112</v>
       </c>
@@ -44779,21 +44997,29 @@
         <v>1826</v>
       </c>
       <c r="G1092" s="3" t="s">
-        <v>3063</v>
-      </c>
-      <c r="H1092" s="3"/>
+        <v>3064</v>
+      </c>
+      <c r="H1092" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I1092" s="3"/>
       <c r="J1092" s="3"/>
       <c r="K1092" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1092" s="3"/>
-      <c r="M1092" s="3"/>
-      <c r="N1092" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1092" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1092" s="3" t="s">
+        <v>3065</v>
+      </c>
+      <c r="N1092" s="3" t="s">
+        <v>3066</v>
+      </c>
     </row>
     <row r="1093" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1093" s="3" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="B1093" s="3"/>
       <c r="C1093" s="3">
@@ -44809,23 +45035,31 @@
         <v>1698</v>
       </c>
       <c r="G1093" s="3" t="s">
-        <v>3064</v>
-      </c>
-      <c r="H1093" s="3"/>
+        <v>3067</v>
+      </c>
+      <c r="H1093" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1093" s="3"/>
       <c r="J1093" s="3"/>
       <c r="K1093" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1093" s="3"/>
-      <c r="M1093" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1093" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1093" s="3" t="s">
+        <v>3068</v>
+      </c>
       <c r="N1093" s="3"/>
     </row>
     <row r="1094" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1094" s="3" t="s">
-        <v>3065</v>
-      </c>
-      <c r="B1094" s="3"/>
+        <v>3069</v>
+      </c>
+      <c r="B1094" s="3" t="s">
+        <v>2474</v>
+      </c>
       <c r="C1094" s="3">
         <v>301</v>
       </c>
@@ -44836,84 +45070,104 @@
         <v>80</v>
       </c>
       <c r="F1094" s="3" t="s">
-        <v>3066</v>
+        <v>3070</v>
       </c>
       <c r="G1094" s="3" t="s">
-        <v>3067</v>
-      </c>
-      <c r="H1094" s="3"/>
+        <v>3071</v>
+      </c>
+      <c r="H1094" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I1094" s="3"/>
       <c r="J1094" s="3"/>
       <c r="K1094" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1094" s="3"/>
-      <c r="M1094" s="3"/>
-      <c r="N1094" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1094" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1094" s="3" t="s">
+        <v>3072</v>
+      </c>
+      <c r="N1094" s="3" t="s">
+        <v>3073</v>
+      </c>
     </row>
     <row r="1095" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1095" s="3" t="s">
-        <v>3068</v>
+        <v>3074</v>
       </c>
       <c r="B1095" s="3"/>
       <c r="C1095" s="3">
         <v>112</v>
       </c>
       <c r="D1095" s="3">
-        <v>5982274614</v>
+        <v>5982274613</v>
       </c>
       <c r="E1095" s="3" t="s">
-        <v>428</v>
+        <v>3075</v>
       </c>
       <c r="F1095" s="3" t="s">
-        <v>3069</v>
+        <v>3076</v>
       </c>
       <c r="G1095" s="3" t="s">
-        <v>3070</v>
-      </c>
-      <c r="H1095" s="3"/>
+        <v>3077</v>
+      </c>
+      <c r="H1095" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1095" s="3"/>
       <c r="J1095" s="3"/>
       <c r="K1095" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1095" s="3"/>
-      <c r="M1095" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1095" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1095" s="3" t="s">
+        <v>3078</v>
+      </c>
       <c r="N1095" s="3"/>
     </row>
     <row r="1096" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1096" s="3" t="s">
-        <v>3068</v>
+        <v>3074</v>
       </c>
       <c r="B1096" s="3"/>
       <c r="C1096" s="3">
         <v>112</v>
       </c>
       <c r="D1096" s="3">
-        <v>5982274613</v>
+        <v>5982274614</v>
       </c>
       <c r="E1096" s="3" t="s">
-        <v>3071</v>
+        <v>428</v>
       </c>
       <c r="F1096" s="3" t="s">
-        <v>3069</v>
+        <v>3076</v>
       </c>
       <c r="G1096" s="3" t="s">
-        <v>3070</v>
-      </c>
-      <c r="H1096" s="3"/>
+        <v>3077</v>
+      </c>
+      <c r="H1096" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1096" s="3"/>
       <c r="J1096" s="3"/>
       <c r="K1096" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1096" s="3"/>
-      <c r="M1096" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1096" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1096" s="3" t="s">
+        <v>3079</v>
+      </c>
       <c r="N1096" s="3"/>
     </row>
     <row r="1097" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1097" s="3" t="s">
-        <v>3072</v>
+        <v>3080</v>
       </c>
       <c r="B1097" s="3"/>
       <c r="C1097" s="3">
@@ -44926,10 +45180,10 @@
         <v>80</v>
       </c>
       <c r="F1097" s="3" t="s">
-        <v>3073</v>
+        <v>3081</v>
       </c>
       <c r="G1097" s="3" t="s">
-        <v>3074</v>
+        <v>3082</v>
       </c>
       <c r="H1097" s="3"/>
       <c r="I1097" s="3"/>
@@ -44943,7 +45197,7 @@
     </row>
     <row r="1098" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1098" s="3" t="s">
-        <v>3075</v>
+        <v>3083</v>
       </c>
       <c r="B1098" s="3"/>
       <c r="C1098" s="3">
@@ -44956,10 +45210,10 @@
         <v>46</v>
       </c>
       <c r="F1098" s="3" t="s">
-        <v>3076</v>
+        <v>3084</v>
       </c>
       <c r="G1098" s="3" t="s">
-        <v>3077</v>
+        <v>3085</v>
       </c>
       <c r="H1098" s="3"/>
       <c r="I1098" s="3"/>
@@ -44973,7 +45227,7 @@
     </row>
     <row r="1099" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1099" s="3" t="s">
-        <v>3078</v>
+        <v>3086</v>
       </c>
       <c r="B1099" s="3"/>
       <c r="C1099" s="3">
@@ -44986,10 +45240,10 @@
         <v>71</v>
       </c>
       <c r="F1099" s="3" t="s">
-        <v>3079</v>
+        <v>3087</v>
       </c>
       <c r="G1099" s="3" t="s">
-        <v>3080</v>
+        <v>3088</v>
       </c>
       <c r="H1099" s="3"/>
       <c r="I1099" s="3"/>
@@ -45003,7 +45257,7 @@
     </row>
     <row r="1100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1100" s="3" t="s">
-        <v>3081</v>
+        <v>3089</v>
       </c>
       <c r="B1100" s="3"/>
       <c r="C1100" s="3">
@@ -45016,10 +45270,10 @@
         <v>80</v>
       </c>
       <c r="F1100" s="3" t="s">
-        <v>3082</v>
+        <v>3090</v>
       </c>
       <c r="G1100" s="3" t="s">
-        <v>3083</v>
+        <v>3091</v>
       </c>
       <c r="H1100" s="3"/>
       <c r="I1100" s="3"/>
@@ -45033,7 +45287,7 @@
     </row>
     <row r="1101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1101" s="3" t="s">
-        <v>3084</v>
+        <v>3092</v>
       </c>
       <c r="B1101" s="3"/>
       <c r="C1101" s="3">
@@ -45049,21 +45303,27 @@
         <v>218</v>
       </c>
       <c r="G1101" s="3" t="s">
-        <v>3085</v>
-      </c>
-      <c r="H1101" s="3"/>
+        <v>3093</v>
+      </c>
+      <c r="H1101" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1101" s="3"/>
       <c r="J1101" s="3"/>
       <c r="K1101" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1101" s="3"/>
-      <c r="M1101" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1101" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1101" s="3" t="s">
+        <v>3094</v>
+      </c>
       <c r="N1101" s="3"/>
     </row>
     <row r="1102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1102" s="3" t="s">
-        <v>3086</v>
+        <v>3095</v>
       </c>
       <c r="B1102" s="3"/>
       <c r="C1102" s="3">
@@ -45076,10 +45336,10 @@
         <v>71</v>
       </c>
       <c r="F1102" s="3" t="s">
-        <v>3087</v>
+        <v>3096</v>
       </c>
       <c r="G1102" s="3" t="s">
-        <v>3088</v>
+        <v>3097</v>
       </c>
       <c r="H1102" s="3"/>
       <c r="I1102" s="3"/>
@@ -45093,7 +45353,7 @@
     </row>
     <row r="1103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1103" s="3" t="s">
-        <v>3089</v>
+        <v>3098</v>
       </c>
       <c r="B1103" s="3"/>
       <c r="C1103" s="3">
@@ -45106,10 +45366,10 @@
         <v>53</v>
       </c>
       <c r="F1103" s="3" t="s">
-        <v>3090</v>
+        <v>3099</v>
       </c>
       <c r="G1103" s="3" t="s">
-        <v>3091</v>
+        <v>3100</v>
       </c>
       <c r="H1103" s="3"/>
       <c r="I1103" s="3"/>
@@ -45123,7 +45383,7 @@
     </row>
     <row r="1104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1104" s="3" t="s">
-        <v>3092</v>
+        <v>3101</v>
       </c>
       <c r="B1104" s="3"/>
       <c r="C1104" s="3">
@@ -45136,10 +45396,10 @@
         <v>34</v>
       </c>
       <c r="F1104" s="3" t="s">
-        <v>3093</v>
+        <v>3102</v>
       </c>
       <c r="G1104" s="3" t="s">
-        <v>3094</v>
+        <v>3103</v>
       </c>
       <c r="H1104" s="3"/>
       <c r="I1104" s="3"/>
@@ -45153,7 +45413,7 @@
     </row>
     <row r="1105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1105" s="3" t="s">
-        <v>3095</v>
+        <v>3104</v>
       </c>
       <c r="B1105" s="3"/>
       <c r="C1105" s="3">
@@ -45166,10 +45426,10 @@
         <v>34</v>
       </c>
       <c r="F1105" s="3" t="s">
-        <v>3096</v>
+        <v>3105</v>
       </c>
       <c r="G1105" s="3" t="s">
-        <v>3097</v>
+        <v>3106</v>
       </c>
       <c r="H1105" s="3"/>
       <c r="I1105" s="3"/>
@@ -45181,6 +45441,764 @@
       <c r="M1105" s="3"/>
       <c r="N1105" s="3"/>
     </row>
+    <row r="1106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1106" s="3" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B1106" s="3"/>
+      <c r="C1106" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1106" s="3">
+        <v>5994500938</v>
+      </c>
+      <c r="E1106" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1106" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1106" s="3" t="s">
+        <v>3108</v>
+      </c>
+      <c r="H1106" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1106" s="3"/>
+      <c r="J1106" s="3"/>
+      <c r="K1106" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1106" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1106" s="3" t="s">
+        <v>3094</v>
+      </c>
+      <c r="N1106" s="3"/>
+    </row>
+    <row r="1107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1107" s="3" t="s">
+        <v>3109</v>
+      </c>
+      <c r="B1107" s="3"/>
+      <c r="C1107" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1107" s="3">
+        <v>6006845849</v>
+      </c>
+      <c r="E1107" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1107" s="3" t="s">
+        <v>3110</v>
+      </c>
+      <c r="G1107" s="3" t="s">
+        <v>3111</v>
+      </c>
+      <c r="H1107" s="3"/>
+      <c r="I1107" s="3"/>
+      <c r="J1107" s="3"/>
+      <c r="K1107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1107" s="3"/>
+      <c r="M1107" s="3"/>
+      <c r="N1107" s="3"/>
+    </row>
+    <row r="1108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1108" s="3" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B1108" s="3"/>
+      <c r="C1108" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1108" s="3">
+        <v>5997449978</v>
+      </c>
+      <c r="E1108" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1108" s="3" t="s">
+        <v>3113</v>
+      </c>
+      <c r="G1108" s="3" t="s">
+        <v>3114</v>
+      </c>
+      <c r="H1108" s="3"/>
+      <c r="I1108" s="3"/>
+      <c r="J1108" s="3"/>
+      <c r="K1108" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1108" s="3"/>
+      <c r="M1108" s="3"/>
+      <c r="N1108" s="3"/>
+    </row>
+    <row r="1109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1109" s="3" t="s">
+        <v>3115</v>
+      </c>
+      <c r="B1109" s="3"/>
+      <c r="C1109" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1109" s="3">
+        <v>6007269556</v>
+      </c>
+      <c r="E1109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1109" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G1109" s="3" t="s">
+        <v>3116</v>
+      </c>
+      <c r="H1109" s="3"/>
+      <c r="I1109" s="3"/>
+      <c r="J1109" s="3"/>
+      <c r="K1109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1109" s="3"/>
+      <c r="M1109" s="3"/>
+      <c r="N1109" s="3"/>
+    </row>
+    <row r="1110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1110" s="3" t="s">
+        <v>3117</v>
+      </c>
+      <c r="B1110" s="3"/>
+      <c r="C1110" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1110" s="3">
+        <v>5998653362</v>
+      </c>
+      <c r="E1110" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1110" s="3" t="s">
+        <v>3118</v>
+      </c>
+      <c r="G1110" s="3" t="s">
+        <v>3119</v>
+      </c>
+      <c r="H1110" s="3"/>
+      <c r="I1110" s="3"/>
+      <c r="J1110" s="3"/>
+      <c r="K1110" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1110" s="3"/>
+      <c r="M1110" s="3"/>
+      <c r="N1110" s="3"/>
+    </row>
+    <row r="1111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1111" s="3" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B1111" s="3"/>
+      <c r="C1111" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1111" s="3">
+        <v>5999968378</v>
+      </c>
+      <c r="E1111" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1111" s="3" t="s">
+        <v>3121</v>
+      </c>
+      <c r="G1111" s="3" t="s">
+        <v>3122</v>
+      </c>
+      <c r="H1111" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1111" s="3"/>
+      <c r="J1111" s="3"/>
+      <c r="K1111" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1111" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1111" s="3" t="s">
+        <v>3123</v>
+      </c>
+      <c r="N1111" s="3"/>
+    </row>
+    <row r="1112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1112" s="3" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B1112" s="3"/>
+      <c r="C1112" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1112" s="3">
+        <v>6000118673</v>
+      </c>
+      <c r="E1112" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1112" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1112" s="3" t="s">
+        <v>3125</v>
+      </c>
+      <c r="H1112" s="3"/>
+      <c r="I1112" s="3"/>
+      <c r="J1112" s="3"/>
+      <c r="K1112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1112" s="3"/>
+      <c r="M1112" s="3"/>
+      <c r="N1112" s="3"/>
+    </row>
+    <row r="1113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1113" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1113" s="3"/>
+      <c r="C1113" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1113" s="3">
+        <v>6014068496</v>
+      </c>
+      <c r="E1113" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1113" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1113" s="3" t="s">
+        <v>3127</v>
+      </c>
+      <c r="H1113" s="3"/>
+      <c r="I1113" s="3"/>
+      <c r="J1113" s="3"/>
+      <c r="K1113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1113" s="3"/>
+      <c r="M1113" s="3"/>
+      <c r="N1113" s="3"/>
+    </row>
+    <row r="1114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1114" s="3" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B1114" s="3"/>
+      <c r="C1114" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1114" s="3">
+        <v>6002014852</v>
+      </c>
+      <c r="E1114" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1114" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G1114" s="3" t="s">
+        <v>3129</v>
+      </c>
+      <c r="H1114" s="3"/>
+      <c r="I1114" s="3"/>
+      <c r="J1114" s="3"/>
+      <c r="K1114" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1114" s="3"/>
+      <c r="M1114" s="3"/>
+      <c r="N1114" s="3"/>
+    </row>
+    <row r="1115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1115" s="3" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B1115" s="3"/>
+      <c r="C1115" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1115" s="3">
+        <v>6021380848</v>
+      </c>
+      <c r="E1115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1115" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G1115" s="3" t="s">
+        <v>3131</v>
+      </c>
+      <c r="H1115" s="3"/>
+      <c r="I1115" s="3"/>
+      <c r="J1115" s="3"/>
+      <c r="K1115" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1115" s="3"/>
+      <c r="M1115" s="3"/>
+      <c r="N1115" s="3"/>
+    </row>
+    <row r="1116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1116" s="3" t="s">
+        <v>3132</v>
+      </c>
+      <c r="B1116" s="3"/>
+      <c r="C1116" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1116" s="3">
+        <v>6009358015</v>
+      </c>
+      <c r="E1116" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1116" s="3" t="s">
+        <v>3133</v>
+      </c>
+      <c r="G1116" s="3" t="s">
+        <v>3134</v>
+      </c>
+      <c r="H1116" s="3"/>
+      <c r="I1116" s="3"/>
+      <c r="J1116" s="3"/>
+      <c r="K1116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1116" s="3"/>
+      <c r="M1116" s="3"/>
+      <c r="N1116" s="3"/>
+    </row>
+    <row r="1117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1117" s="3" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B1117" s="3"/>
+      <c r="C1117" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1117" s="3">
+        <v>6011628247</v>
+      </c>
+      <c r="E1117" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1117" s="3" t="s">
+        <v>3136</v>
+      </c>
+      <c r="G1117" s="3" t="s">
+        <v>3137</v>
+      </c>
+      <c r="H1117" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1117" s="3"/>
+      <c r="J1117" s="3"/>
+      <c r="K1117" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1117" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1117" s="3" t="s">
+        <v>3138</v>
+      </c>
+      <c r="N1117" s="3"/>
+    </row>
+    <row r="1118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1118" s="3" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B1118" s="3"/>
+      <c r="C1118" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1118" s="3">
+        <v>6011807044</v>
+      </c>
+      <c r="E1118" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1118" s="3" t="s">
+        <v>2074</v>
+      </c>
+      <c r="G1118" s="3" t="s">
+        <v>3140</v>
+      </c>
+      <c r="H1118" s="3"/>
+      <c r="I1118" s="3"/>
+      <c r="J1118" s="3"/>
+      <c r="K1118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1118" s="3"/>
+      <c r="M1118" s="3"/>
+      <c r="N1118" s="3"/>
+    </row>
+    <row r="1119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1119" s="3" t="s">
+        <v>3141</v>
+      </c>
+      <c r="B1119" s="3"/>
+      <c r="C1119" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1119" s="3">
+        <v>6016064064</v>
+      </c>
+      <c r="E1119" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1119" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G1119" s="3" t="s">
+        <v>3142</v>
+      </c>
+      <c r="H1119" s="3"/>
+      <c r="I1119" s="3"/>
+      <c r="J1119" s="3"/>
+      <c r="K1119" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1119" s="3"/>
+      <c r="M1119" s="3"/>
+      <c r="N1119" s="3"/>
+    </row>
+    <row r="1120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1120" s="3" t="s">
+        <v>3143</v>
+      </c>
+      <c r="B1120" s="3"/>
+      <c r="C1120" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1120" s="3">
+        <v>6016435040</v>
+      </c>
+      <c r="E1120" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1120" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G1120" s="3" t="s">
+        <v>3144</v>
+      </c>
+      <c r="H1120" s="3"/>
+      <c r="I1120" s="3"/>
+      <c r="J1120" s="3"/>
+      <c r="K1120" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1120" s="3"/>
+      <c r="M1120" s="3"/>
+      <c r="N1120" s="3"/>
+    </row>
+    <row r="1121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1121" s="3" t="s">
+        <v>3145</v>
+      </c>
+      <c r="B1121" s="3"/>
+      <c r="C1121" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1121" s="3">
+        <v>6017890364</v>
+      </c>
+      <c r="E1121" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1121" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1121" s="3" t="s">
+        <v>3146</v>
+      </c>
+      <c r="H1121" s="3"/>
+      <c r="I1121" s="3"/>
+      <c r="J1121" s="3"/>
+      <c r="K1121" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1121" s="3"/>
+      <c r="M1121" s="3"/>
+      <c r="N1121" s="3"/>
+    </row>
+    <row r="1122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1122" s="3" t="s">
+        <v>3147</v>
+      </c>
+      <c r="B1122" s="3"/>
+      <c r="C1122" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1122" s="3">
+        <v>6018379809</v>
+      </c>
+      <c r="E1122" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1122" s="3" t="s">
+        <v>3148</v>
+      </c>
+      <c r="G1122" s="3" t="s">
+        <v>3149</v>
+      </c>
+      <c r="H1122" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1122" s="3"/>
+      <c r="J1122" s="3"/>
+      <c r="K1122" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1122" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1122" s="3" t="s">
+        <v>3150</v>
+      </c>
+      <c r="N1122" s="3"/>
+    </row>
+    <row r="1123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1123" s="3" t="s">
+        <v>3151</v>
+      </c>
+      <c r="B1123" s="3"/>
+      <c r="C1123" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1123" s="3">
+        <v>6019258918</v>
+      </c>
+      <c r="E1123" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1123" s="3" t="s">
+        <v>3152</v>
+      </c>
+      <c r="G1123" s="3" t="s">
+        <v>3153</v>
+      </c>
+      <c r="H1123" s="3"/>
+      <c r="I1123" s="3"/>
+      <c r="J1123" s="3"/>
+      <c r="K1123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1123" s="3"/>
+      <c r="M1123" s="3"/>
+      <c r="N1123" s="3"/>
+    </row>
+    <row r="1124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1124" s="3" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B1124" s="3"/>
+      <c r="C1124" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1124" s="3">
+        <v>6020547799</v>
+      </c>
+      <c r="E1124" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1124" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1124" s="3" t="s">
+        <v>3155</v>
+      </c>
+      <c r="H1124" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1124" s="3"/>
+      <c r="J1124" s="3"/>
+      <c r="K1124" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1124" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1124" s="3" t="s">
+        <v>3150</v>
+      </c>
+      <c r="N1124" s="3"/>
+    </row>
+    <row r="1125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1125" s="3" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B1125" s="3"/>
+      <c r="C1125" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1125" s="3">
+        <v>6024086634</v>
+      </c>
+      <c r="E1125" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F1125" s="3" t="s">
+        <v>3157</v>
+      </c>
+      <c r="G1125" s="3" t="s">
+        <v>3158</v>
+      </c>
+      <c r="H1125" s="3"/>
+      <c r="I1125" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1125" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1125" s="3"/>
+      <c r="M1125" s="3"/>
+      <c r="N1125" s="3"/>
+    </row>
+    <row r="1126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1126" s="3" t="s">
+        <v>3159</v>
+      </c>
+      <c r="B1126" s="3"/>
+      <c r="C1126" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1126" s="3">
+        <v>6024145327</v>
+      </c>
+      <c r="E1126" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F1126" s="3" t="s">
+        <v>3160</v>
+      </c>
+      <c r="G1126" s="3" t="s">
+        <v>3161</v>
+      </c>
+      <c r="H1126" s="3"/>
+      <c r="I1126" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1126" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1126" s="3"/>
+      <c r="M1126" s="3"/>
+      <c r="N1126" s="3"/>
+    </row>
+    <row r="1127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1127" s="3" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B1127" s="3"/>
+      <c r="C1127" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1127" s="3">
+        <v>6025018198</v>
+      </c>
+      <c r="E1127" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1127" s="3" t="s">
+        <v>3163</v>
+      </c>
+      <c r="G1127" s="3" t="s">
+        <v>3164</v>
+      </c>
+      <c r="H1127" s="3"/>
+      <c r="I1127" s="3"/>
+      <c r="J1127" s="3"/>
+      <c r="K1127" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1127" s="3"/>
+      <c r="M1127" s="3"/>
+      <c r="N1127" s="3"/>
+    </row>
+    <row r="1128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1128" s="3" t="s">
+        <v>3165</v>
+      </c>
+      <c r="B1128" s="3"/>
+      <c r="C1128" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1128" s="3">
+        <v>6025036377</v>
+      </c>
+      <c r="E1128" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1128" s="3" t="s">
+        <v>3166</v>
+      </c>
+      <c r="G1128" s="3" t="s">
+        <v>3167</v>
+      </c>
+      <c r="H1128" s="3"/>
+      <c r="I1128" s="3"/>
+      <c r="J1128" s="3"/>
+      <c r="K1128" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1128" s="3"/>
+      <c r="M1128" s="3"/>
+      <c r="N1128" s="3"/>
+    </row>
+    <row r="1129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1129" s="3" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B1129" s="3"/>
+      <c r="C1129" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1129" s="3">
+        <v>6032937596</v>
+      </c>
+      <c r="E1129" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1129" s="3" t="s">
+        <v>2108</v>
+      </c>
+      <c r="G1129" s="3" t="s">
+        <v>3169</v>
+      </c>
+      <c r="H1129" s="3"/>
+      <c r="I1129" s="3"/>
+      <c r="J1129" s="3"/>
+      <c r="K1129" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1129" s="3"/>
+      <c r="M1129" s="3"/>
+      <c r="N1129" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FECE593-A986-4AD3-8D5E-F65130F5BC25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE411CFA-3917-496D-8EAB-ADE58C525663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7100" uniqueCount="3282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7319" uniqueCount="3382">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -9757,6 +9757,9 @@
     <t>28.326450, -98.114240</t>
   </si>
   <si>
+    <t>07/06/26 09:58 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 10:26 EDT</t>
   </si>
   <si>
@@ -9799,6 +9802,9 @@
     <t>29.517353, -98.136215</t>
   </si>
   <si>
+    <t>07/06/26 09:59 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 14:44 EDT</t>
   </si>
   <si>
@@ -9826,6 +9832,9 @@
     <t>29.444250, -98.433800</t>
   </si>
   <si>
+    <t>07/06/26 10:05 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 09:45 EDT</t>
   </si>
   <si>
@@ -9835,6 +9844,9 @@
     <t>29.604618, -97.965340</t>
   </si>
   <si>
+    <t>07/06/26 10:06 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 11:29 EDT</t>
   </si>
   <si>
@@ -9866,6 +9878,294 @@
   </si>
   <si>
     <t>29.274410, -98.364720</t>
+  </si>
+  <si>
+    <t>07/06/26 10:51 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi E of Buda TX</t>
+  </si>
+  <si>
+    <t>30.071505, -97.827830</t>
+  </si>
+  <si>
+    <t>07/06/26 11:28 EDT</t>
+  </si>
+  <si>
+    <t>29.517933, -98.136566</t>
+  </si>
+  <si>
+    <t>07/07/26 08:09 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 11:47 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi N of Windcrest TX</t>
+  </si>
+  <si>
+    <t>29.535902, -98.386380</t>
+  </si>
+  <si>
+    <t>07/06/26 12:06 EDT</t>
+  </si>
+  <si>
+    <t>2mi SE of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.572153, -97.940250</t>
+  </si>
+  <si>
+    <t>07/06/26 13:55 EDT</t>
+  </si>
+  <si>
+    <t>29.514244, -98.104004</t>
+  </si>
+  <si>
+    <t>07/06/26 16:40 EDT</t>
+  </si>
+  <si>
+    <t>6.7mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.542994, -98.065140</t>
+  </si>
+  <si>
+    <t>07/07/26 12:10 EDT</t>
+  </si>
+  <si>
+    <t>29.458170, -98.317795</t>
+  </si>
+  <si>
+    <t>07/08/26 07:50 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 12:59 EDT</t>
+  </si>
+  <si>
+    <t>29.458231, -98.307880</t>
+  </si>
+  <si>
+    <t>07/07/26 13:51 EDT</t>
+  </si>
+  <si>
+    <t>29.559391, -98.343090</t>
+  </si>
+  <si>
+    <t>07/07/26 14:15 EDT</t>
+  </si>
+  <si>
+    <t>0.4mi SE of Selma TX</t>
+  </si>
+  <si>
+    <t>29.582289, -98.308620</t>
+  </si>
+  <si>
+    <t>07/07/26 14:20 EDT</t>
+  </si>
+  <si>
+    <t>29.613245, -98.284070</t>
+  </si>
+  <si>
+    <t>07/07/26 16:41 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi SW of Luling TX</t>
+  </si>
+  <si>
+    <t>29.651470, -97.672520</t>
+  </si>
+  <si>
+    <t>07/07/26 17:37 EDT</t>
+  </si>
+  <si>
+    <t>4mi SE of Luling TX</t>
+  </si>
+  <si>
+    <t>29.653221, -97.588770</t>
+  </si>
+  <si>
+    <t>07/07/26 19:03 EDT</t>
+  </si>
+  <si>
+    <t>5.6mi W of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.719900, -98.205000</t>
+  </si>
+  <si>
+    <t>07/07/26 19:59 EDT</t>
+  </si>
+  <si>
+    <t>4.1mi W of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.721249, -98.177960</t>
+  </si>
+  <si>
+    <t>07/07/26 20:30 EDT</t>
+  </si>
+  <si>
+    <t>29.582256, -97.999535</t>
+  </si>
+  <si>
+    <t>07/07/26 20:58 EDT</t>
+  </si>
+  <si>
+    <t>29.529652, -98.109790</t>
+  </si>
+  <si>
+    <t>07/08/26 07:51 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 10:45 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi E of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.599274, -97.925410</t>
+  </si>
+  <si>
+    <t>07/08/26 16:31 EDT</t>
+  </si>
+  <si>
+    <t>29.399700, -98.532880</t>
+  </si>
+  <si>
+    <t>07/08/26 18:24 EDT</t>
+  </si>
+  <si>
+    <t>5.1mi S of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.490103, -98.217180</t>
+  </si>
+  <si>
+    <t>07/08/26 20:34 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.495640, -98.289375</t>
+  </si>
+  <si>
+    <t>07/08/26 21:37 EDT</t>
+  </si>
+  <si>
+    <t>5mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.552443, -98.040230</t>
+  </si>
+  <si>
+    <t>07/09/26 07:57 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 23:31 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi SE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.667198, -98.053380</t>
+  </si>
+  <si>
+    <t>07/09/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>29.434938, -98.393180</t>
+  </si>
+  <si>
+    <t>07/10/26 08:15 EDT</t>
+  </si>
+  <si>
+    <t>07/09/26 15:58 EDT</t>
+  </si>
+  <si>
+    <t>7.7mi S of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.275335, -98.621670</t>
+  </si>
+  <si>
+    <t>07/09/26 20:59 EDT</t>
+  </si>
+  <si>
+    <t>20.8mi SE of Uvalde TX</t>
+  </si>
+  <si>
+    <t>28.960972, -99.593710</t>
+  </si>
+  <si>
+    <t>07/09/26 21:40 EDT</t>
+  </si>
+  <si>
+    <t>17mi NE of Eagle Pass TX</t>
+  </si>
+  <si>
+    <t>28.869959, -100.269350</t>
+  </si>
+  <si>
+    <t>07/09/26 21:56 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi NE of Eagle Pass TX</t>
+  </si>
+  <si>
+    <t>28.720001, -100.467980</t>
+  </si>
+  <si>
+    <t>07/10/26 14:04 EDT</t>
+  </si>
+  <si>
+    <t>29.345547, -98.403534</t>
+  </si>
+  <si>
+    <t>07/10/26 14:29 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi W of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.585173, -98.042170</t>
+  </si>
+  <si>
+    <t>07/10/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.434332, -98.360730</t>
+  </si>
+  <si>
+    <t>07/10/26 16:08 EDT</t>
+  </si>
+  <si>
+    <t>29.505682, -98.133980</t>
+  </si>
+  <si>
+    <t>07/10/26 18:48 EDT</t>
+  </si>
+  <si>
+    <t>29.537252, -98.081950</t>
+  </si>
+  <si>
+    <t>07/11/26 11:54 EDT</t>
+  </si>
+  <si>
+    <t>29.401710, -98.468000</t>
+  </si>
+  <si>
+    <t>07/11/26 12:27 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi SE of Scenic Oaks TX</t>
+  </si>
+  <si>
+    <t>29.655361, -98.639150</t>
   </si>
 </sst>
 </file>
@@ -10227,7 +10527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1170"/>
+  <dimension ref="A1:N1205"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -33980,7 +34280,7 @@
         <v>112</v>
       </c>
       <c r="D742" s="3">
-        <v>5622402770</v>
+        <v>5622271458</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>53</v>
@@ -34010,7 +34310,7 @@
         <v>112</v>
       </c>
       <c r="D743" s="3">
-        <v>5622271458</v>
+        <v>5622402770</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>53</v>
@@ -47389,19 +47689,25 @@
       <c r="G1156" s="3" t="s">
         <v>3244</v>
       </c>
-      <c r="H1156" s="3"/>
+      <c r="H1156" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1156" s="3"/>
       <c r="J1156" s="3"/>
       <c r="K1156" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1156" s="3"/>
-      <c r="M1156" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1156" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1156" s="3" t="s">
+        <v>3245</v>
+      </c>
       <c r="N1156" s="3"/>
     </row>
     <row r="1157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1157" s="3" t="s">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="B1157" s="3"/>
       <c r="C1157" s="3">
@@ -47414,10 +47720,10 @@
         <v>71</v>
       </c>
       <c r="F1157" s="3" t="s">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="G1157" s="3" t="s">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="H1157" s="3"/>
       <c r="I1157" s="3"/>
@@ -47431,7 +47737,7 @@
     </row>
     <row r="1158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1158" s="3" t="s">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="B1158" s="3"/>
       <c r="C1158" s="3">
@@ -47444,10 +47750,10 @@
         <v>71</v>
       </c>
       <c r="F1158" s="3" t="s">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="G1158" s="3" t="s">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="H1158" s="3"/>
       <c r="I1158" s="3"/>
@@ -47461,7 +47767,7 @@
     </row>
     <row r="1159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1159" s="3" t="s">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="B1159" s="3"/>
       <c r="C1159" s="3">
@@ -47474,10 +47780,10 @@
         <v>71</v>
       </c>
       <c r="F1159" s="3" t="s">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="G1159" s="3" t="s">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="H1159" s="3"/>
       <c r="I1159" s="3"/>
@@ -47491,7 +47797,7 @@
     </row>
     <row r="1160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1160" s="3" t="s">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="B1160" s="3"/>
       <c r="C1160" s="3">
@@ -47504,10 +47810,10 @@
         <v>71</v>
       </c>
       <c r="F1160" s="3" t="s">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="G1160" s="3" t="s">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="H1160" s="3"/>
       <c r="I1160" s="3"/>
@@ -47521,7 +47827,7 @@
     </row>
     <row r="1161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1161" s="3" t="s">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="B1161" s="3"/>
       <c r="C1161" s="3">
@@ -47537,23 +47843,31 @@
         <v>211</v>
       </c>
       <c r="G1161" s="3" t="s">
-        <v>3258</v>
-      </c>
-      <c r="H1161" s="3"/>
+        <v>3259</v>
+      </c>
+      <c r="H1161" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1161" s="3"/>
       <c r="J1161" s="3"/>
       <c r="K1161" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1161" s="3"/>
-      <c r="M1161" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1161" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1161" s="3" t="s">
+        <v>3260</v>
+      </c>
       <c r="N1161" s="3"/>
     </row>
     <row r="1162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1162" s="3" t="s">
-        <v>3259</v>
-      </c>
-      <c r="B1162" s="3"/>
+        <v>3261</v>
+      </c>
+      <c r="B1162" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="C1162" s="3">
         <v>110</v>
       </c>
@@ -47567,21 +47881,27 @@
         <v>298</v>
       </c>
       <c r="G1162" s="3" t="s">
-        <v>3260</v>
-      </c>
-      <c r="H1162" s="3"/>
+        <v>3262</v>
+      </c>
+      <c r="H1162" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I1162" s="3"/>
       <c r="J1162" s="3"/>
       <c r="K1162" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1162" s="3"/>
-      <c r="M1162" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1162" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1162" s="3" t="s">
+        <v>3260</v>
+      </c>
       <c r="N1162" s="3"/>
     </row>
     <row r="1163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1163" s="3" t="s">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="B1163" s="3"/>
       <c r="C1163" s="3">
@@ -47597,7 +47917,7 @@
         <v>3099</v>
       </c>
       <c r="G1163" s="3" t="s">
-        <v>3262</v>
+        <v>3264</v>
       </c>
       <c r="H1163" s="3"/>
       <c r="I1163" s="3"/>
@@ -47611,7 +47931,7 @@
     </row>
     <row r="1164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1164" s="3" t="s">
-        <v>3263</v>
+        <v>3265</v>
       </c>
       <c r="B1164" s="3"/>
       <c r="C1164" s="3">
@@ -47627,7 +47947,7 @@
         <v>779</v>
       </c>
       <c r="G1164" s="3" t="s">
-        <v>3264</v>
+        <v>3266</v>
       </c>
       <c r="H1164" s="3"/>
       <c r="I1164" s="3"/>
@@ -47641,7 +47961,7 @@
     </row>
     <row r="1165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1165" s="3" t="s">
-        <v>3265</v>
+        <v>3267</v>
       </c>
       <c r="B1165" s="3"/>
       <c r="C1165" s="3">
@@ -47654,24 +47974,30 @@
         <v>80</v>
       </c>
       <c r="F1165" s="3" t="s">
-        <v>3266</v>
+        <v>3268</v>
       </c>
       <c r="G1165" s="3" t="s">
-        <v>3267</v>
-      </c>
-      <c r="H1165" s="3"/>
+        <v>3269</v>
+      </c>
+      <c r="H1165" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1165" s="3"/>
       <c r="J1165" s="3"/>
       <c r="K1165" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1165" s="3"/>
-      <c r="M1165" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1165" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1165" s="3" t="s">
+        <v>3270</v>
+      </c>
       <c r="N1165" s="3"/>
     </row>
     <row r="1166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1166" s="3" t="s">
-        <v>3268</v>
+        <v>3271</v>
       </c>
       <c r="B1166" s="3"/>
       <c r="C1166" s="3">
@@ -47684,24 +48010,30 @@
         <v>80</v>
       </c>
       <c r="F1166" s="3" t="s">
-        <v>3269</v>
+        <v>3272</v>
       </c>
       <c r="G1166" s="3" t="s">
-        <v>3270</v>
-      </c>
-      <c r="H1166" s="3"/>
+        <v>3273</v>
+      </c>
+      <c r="H1166" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1166" s="3"/>
       <c r="J1166" s="3"/>
       <c r="K1166" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1166" s="3"/>
-      <c r="M1166" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1166" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1166" s="3" t="s">
+        <v>3274</v>
+      </c>
       <c r="N1166" s="3"/>
     </row>
     <row r="1167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1167" s="3" t="s">
-        <v>3271</v>
+        <v>3275</v>
       </c>
       <c r="B1167" s="3"/>
       <c r="C1167" s="3">
@@ -47717,7 +48049,7 @@
         <v>158</v>
       </c>
       <c r="G1167" s="3" t="s">
-        <v>3272</v>
+        <v>3276</v>
       </c>
       <c r="H1167" s="3"/>
       <c r="I1167" s="3"/>
@@ -47731,7 +48063,7 @@
     </row>
     <row r="1168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1168" s="3" t="s">
-        <v>3273</v>
+        <v>3277</v>
       </c>
       <c r="B1168" s="3"/>
       <c r="C1168" s="3">
@@ -47744,24 +48076,30 @@
         <v>164</v>
       </c>
       <c r="F1168" s="3" t="s">
-        <v>3274</v>
+        <v>3278</v>
       </c>
       <c r="G1168" s="3" t="s">
-        <v>3275</v>
-      </c>
-      <c r="H1168" s="3"/>
+        <v>3279</v>
+      </c>
+      <c r="H1168" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1168" s="3"/>
       <c r="J1168" s="3"/>
       <c r="K1168" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1168" s="3"/>
-      <c r="M1168" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1168" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1168" s="3" t="s">
+        <v>3274</v>
+      </c>
       <c r="N1168" s="3"/>
     </row>
     <row r="1169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1169" s="3" t="s">
-        <v>3276</v>
+        <v>3280</v>
       </c>
       <c r="B1169" s="3"/>
       <c r="C1169" s="3">
@@ -47774,10 +48112,10 @@
         <v>53</v>
       </c>
       <c r="F1169" s="3" t="s">
-        <v>3277</v>
+        <v>3281</v>
       </c>
       <c r="G1169" s="3" t="s">
-        <v>3278</v>
+        <v>3282</v>
       </c>
       <c r="H1169" s="3"/>
       <c r="I1169" s="3"/>
@@ -47791,7 +48129,7 @@
     </row>
     <row r="1170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1170" s="3" t="s">
-        <v>3279</v>
+        <v>3283</v>
       </c>
       <c r="B1170" s="3"/>
       <c r="C1170" s="3">
@@ -47804,10 +48142,10 @@
         <v>2204</v>
       </c>
       <c r="F1170" s="3" t="s">
-        <v>3280</v>
+        <v>3284</v>
       </c>
       <c r="G1170" s="3" t="s">
-        <v>3281</v>
+        <v>3285</v>
       </c>
       <c r="H1170" s="3"/>
       <c r="I1170" s="3">
@@ -47822,6 +48160,1110 @@
       <c r="L1170" s="3"/>
       <c r="M1170" s="3"/>
       <c r="N1170" s="3"/>
+    </row>
+    <row r="1171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1171" s="3" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B1171" s="3"/>
+      <c r="C1171" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1171" s="3">
+        <v>6079325549</v>
+      </c>
+      <c r="E1171" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1171" s="3" t="s">
+        <v>3287</v>
+      </c>
+      <c r="G1171" s="3" t="s">
+        <v>3288</v>
+      </c>
+      <c r="H1171" s="3"/>
+      <c r="I1171" s="3"/>
+      <c r="J1171" s="3"/>
+      <c r="K1171" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1171" s="3"/>
+      <c r="M1171" s="3"/>
+      <c r="N1171" s="3"/>
+    </row>
+    <row r="1172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1172" s="3" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B1172" s="3"/>
+      <c r="C1172" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1172" s="3">
+        <v>6079576967</v>
+      </c>
+      <c r="E1172" s="3" t="s">
+        <v>2257</v>
+      </c>
+      <c r="F1172" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1172" s="3" t="s">
+        <v>3290</v>
+      </c>
+      <c r="H1172" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1172" s="3"/>
+      <c r="J1172" s="3"/>
+      <c r="K1172" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1172" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1172" s="3" t="s">
+        <v>3291</v>
+      </c>
+      <c r="N1172" s="3"/>
+    </row>
+    <row r="1173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1173" s="3" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B1173" s="3"/>
+      <c r="C1173" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1173" s="3">
+        <v>6079710425</v>
+      </c>
+      <c r="E1173" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1173" s="3" t="s">
+        <v>3293</v>
+      </c>
+      <c r="G1173" s="3" t="s">
+        <v>3294</v>
+      </c>
+      <c r="H1173" s="3"/>
+      <c r="I1173" s="3"/>
+      <c r="J1173" s="3"/>
+      <c r="K1173" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1173" s="3"/>
+      <c r="M1173" s="3"/>
+      <c r="N1173" s="3"/>
+    </row>
+    <row r="1174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1174" s="3" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B1174" s="3"/>
+      <c r="C1174" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1174" s="3">
+        <v>6079855095</v>
+      </c>
+      <c r="E1174" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1174" s="3" t="s">
+        <v>3296</v>
+      </c>
+      <c r="G1174" s="3" t="s">
+        <v>3297</v>
+      </c>
+      <c r="H1174" s="3"/>
+      <c r="I1174" s="3"/>
+      <c r="J1174" s="3"/>
+      <c r="K1174" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1174" s="3"/>
+      <c r="M1174" s="3"/>
+      <c r="N1174" s="3"/>
+    </row>
+    <row r="1175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1175" s="3" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B1175" s="3"/>
+      <c r="C1175" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1175" s="3">
+        <v>6080766051</v>
+      </c>
+      <c r="E1175" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1175" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G1175" s="3" t="s">
+        <v>3299</v>
+      </c>
+      <c r="H1175" s="3"/>
+      <c r="I1175" s="3"/>
+      <c r="J1175" s="3"/>
+      <c r="K1175" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1175" s="3"/>
+      <c r="M1175" s="3"/>
+      <c r="N1175" s="3"/>
+    </row>
+    <row r="1176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1176" s="3" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B1176" s="3"/>
+      <c r="C1176" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1176" s="3">
+        <v>6082159773</v>
+      </c>
+      <c r="E1176" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1176" s="3" t="s">
+        <v>3301</v>
+      </c>
+      <c r="G1176" s="3" t="s">
+        <v>3302</v>
+      </c>
+      <c r="H1176" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1176" s="3"/>
+      <c r="J1176" s="3"/>
+      <c r="K1176" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1176" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1176" s="3" t="s">
+        <v>3291</v>
+      </c>
+      <c r="N1176" s="3"/>
+    </row>
+    <row r="1177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1177" s="3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B1177" s="3"/>
+      <c r="C1177" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1177" s="3">
+        <v>6086775848</v>
+      </c>
+      <c r="E1177" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1177" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1177" s="3" t="s">
+        <v>3304</v>
+      </c>
+      <c r="H1177" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1177" s="3"/>
+      <c r="J1177" s="3"/>
+      <c r="K1177" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1177" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1177" s="3" t="s">
+        <v>3305</v>
+      </c>
+      <c r="N1177" s="3"/>
+    </row>
+    <row r="1178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1178" s="3" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B1178" s="3"/>
+      <c r="C1178" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1178" s="3">
+        <v>6098524372</v>
+      </c>
+      <c r="E1178" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1178" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1178" s="3" t="s">
+        <v>3307</v>
+      </c>
+      <c r="H1178" s="3"/>
+      <c r="I1178" s="3"/>
+      <c r="J1178" s="3"/>
+      <c r="K1178" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1178" s="3"/>
+      <c r="M1178" s="3"/>
+      <c r="N1178" s="3"/>
+    </row>
+    <row r="1179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1179" s="3" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B1179" s="3"/>
+      <c r="C1179" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1179" s="3">
+        <v>6087671276</v>
+      </c>
+      <c r="E1179" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1179" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G1179" s="3" t="s">
+        <v>3309</v>
+      </c>
+      <c r="H1179" s="3"/>
+      <c r="I1179" s="3"/>
+      <c r="J1179" s="3"/>
+      <c r="K1179" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1179" s="3"/>
+      <c r="M1179" s="3"/>
+      <c r="N1179" s="3"/>
+    </row>
+    <row r="1180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1180" s="3" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B1180" s="3"/>
+      <c r="C1180" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1180" s="3">
+        <v>6087894970</v>
+      </c>
+      <c r="E1180" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1180" s="3" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G1180" s="3" t="s">
+        <v>3312</v>
+      </c>
+      <c r="H1180" s="3"/>
+      <c r="I1180" s="3"/>
+      <c r="J1180" s="3"/>
+      <c r="K1180" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1180" s="3"/>
+      <c r="M1180" s="3"/>
+      <c r="N1180" s="3"/>
+    </row>
+    <row r="1181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1181" s="3" t="s">
+        <v>3313</v>
+      </c>
+      <c r="B1181" s="3"/>
+      <c r="C1181" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1181" s="3">
+        <v>6087935913</v>
+      </c>
+      <c r="E1181" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1181" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="G1181" s="3" t="s">
+        <v>3314</v>
+      </c>
+      <c r="H1181" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1181" s="3"/>
+      <c r="J1181" s="3"/>
+      <c r="K1181" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1181" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1181" s="3" t="s">
+        <v>3305</v>
+      </c>
+      <c r="N1181" s="3"/>
+    </row>
+    <row r="1182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1182" s="3" t="s">
+        <v>3315</v>
+      </c>
+      <c r="B1182" s="3"/>
+      <c r="C1182" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1182" s="3">
+        <v>6089157460</v>
+      </c>
+      <c r="E1182" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1182" s="3" t="s">
+        <v>3316</v>
+      </c>
+      <c r="G1182" s="3" t="s">
+        <v>3317</v>
+      </c>
+      <c r="H1182" s="3"/>
+      <c r="I1182" s="3"/>
+      <c r="J1182" s="3"/>
+      <c r="K1182" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1182" s="3"/>
+      <c r="M1182" s="3"/>
+      <c r="N1182" s="3"/>
+    </row>
+    <row r="1183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1183" s="3" t="s">
+        <v>3318</v>
+      </c>
+      <c r="B1183" s="3"/>
+      <c r="C1183" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1183" s="3">
+        <v>6089588735</v>
+      </c>
+      <c r="E1183" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1183" s="3" t="s">
+        <v>3319</v>
+      </c>
+      <c r="G1183" s="3" t="s">
+        <v>3320</v>
+      </c>
+      <c r="H1183" s="3"/>
+      <c r="I1183" s="3"/>
+      <c r="J1183" s="3"/>
+      <c r="K1183" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1183" s="3"/>
+      <c r="M1183" s="3"/>
+      <c r="N1183" s="3"/>
+    </row>
+    <row r="1184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1184" s="3" t="s">
+        <v>3321</v>
+      </c>
+      <c r="B1184" s="3"/>
+      <c r="C1184" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1184" s="3">
+        <v>6090186896</v>
+      </c>
+      <c r="E1184" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F1184" s="3" t="s">
+        <v>3322</v>
+      </c>
+      <c r="G1184" s="3" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H1184" s="3"/>
+      <c r="I1184" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1184" s="3">
+        <v>40</v>
+      </c>
+      <c r="K1184" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1184" s="3"/>
+      <c r="M1184" s="3"/>
+      <c r="N1184" s="3"/>
+    </row>
+    <row r="1185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1185" s="3" t="s">
+        <v>3324</v>
+      </c>
+      <c r="B1185" s="3"/>
+      <c r="C1185" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1185" s="3">
+        <v>6098292919</v>
+      </c>
+      <c r="E1185" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1185" s="3" t="s">
+        <v>3325</v>
+      </c>
+      <c r="G1185" s="3" t="s">
+        <v>3326</v>
+      </c>
+      <c r="H1185" s="3"/>
+      <c r="I1185" s="3"/>
+      <c r="J1185" s="3"/>
+      <c r="K1185" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1185" s="3"/>
+      <c r="M1185" s="3"/>
+      <c r="N1185" s="3"/>
+    </row>
+    <row r="1186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1186" s="3" t="s">
+        <v>3327</v>
+      </c>
+      <c r="B1186" s="3"/>
+      <c r="C1186" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1186" s="3">
+        <v>6090658459</v>
+      </c>
+      <c r="E1186" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1186" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1186" s="3" t="s">
+        <v>3328</v>
+      </c>
+      <c r="H1186" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1186" s="3"/>
+      <c r="J1186" s="3"/>
+      <c r="K1186" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1186" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1186" s="3" t="s">
+        <v>3305</v>
+      </c>
+      <c r="N1186" s="3"/>
+    </row>
+    <row r="1187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1187" s="3" t="s">
+        <v>3329</v>
+      </c>
+      <c r="B1187" s="3"/>
+      <c r="C1187" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1187" s="3">
+        <v>6090763562</v>
+      </c>
+      <c r="E1187" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1187" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G1187" s="3" t="s">
+        <v>3330</v>
+      </c>
+      <c r="H1187" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1187" s="3"/>
+      <c r="J1187" s="3"/>
+      <c r="K1187" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1187" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1187" s="3" t="s">
+        <v>3331</v>
+      </c>
+      <c r="N1187" s="3"/>
+    </row>
+    <row r="1188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1188" s="3" t="s">
+        <v>3332</v>
+      </c>
+      <c r="B1188" s="3"/>
+      <c r="C1188" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1188" s="3">
+        <v>6093193778</v>
+      </c>
+      <c r="E1188" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1188" s="3" t="s">
+        <v>3333</v>
+      </c>
+      <c r="G1188" s="3" t="s">
+        <v>3334</v>
+      </c>
+      <c r="H1188" s="3"/>
+      <c r="I1188" s="3"/>
+      <c r="J1188" s="3"/>
+      <c r="K1188" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1188" s="3"/>
+      <c r="M1188" s="3"/>
+      <c r="N1188" s="3"/>
+    </row>
+    <row r="1189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1189" s="3" t="s">
+        <v>3335</v>
+      </c>
+      <c r="B1189" s="3"/>
+      <c r="C1189" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1189" s="3">
+        <v>6096122208</v>
+      </c>
+      <c r="E1189" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1189" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G1189" s="3" t="s">
+        <v>3336</v>
+      </c>
+      <c r="H1189" s="3"/>
+      <c r="I1189" s="3"/>
+      <c r="J1189" s="3"/>
+      <c r="K1189" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1189" s="3"/>
+      <c r="M1189" s="3"/>
+      <c r="N1189" s="3"/>
+    </row>
+    <row r="1190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1190" s="3" t="s">
+        <v>3337</v>
+      </c>
+      <c r="B1190" s="3"/>
+      <c r="C1190" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1190" s="3">
+        <v>6096953313</v>
+      </c>
+      <c r="E1190" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1190" s="3" t="s">
+        <v>3338</v>
+      </c>
+      <c r="G1190" s="3" t="s">
+        <v>3339</v>
+      </c>
+      <c r="H1190" s="3"/>
+      <c r="I1190" s="3"/>
+      <c r="J1190" s="3"/>
+      <c r="K1190" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1190" s="3"/>
+      <c r="M1190" s="3"/>
+      <c r="N1190" s="3"/>
+    </row>
+    <row r="1191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1191" s="3" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B1191" s="3"/>
+      <c r="C1191" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1191" s="3">
+        <v>6097668515</v>
+      </c>
+      <c r="E1191" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1191" s="3" t="s">
+        <v>3341</v>
+      </c>
+      <c r="G1191" s="3" t="s">
+        <v>3342</v>
+      </c>
+      <c r="H1191" s="3"/>
+      <c r="I1191" s="3"/>
+      <c r="J1191" s="3"/>
+      <c r="K1191" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1191" s="3"/>
+      <c r="M1191" s="3"/>
+      <c r="N1191" s="3"/>
+    </row>
+    <row r="1192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1192" s="3" t="s">
+        <v>3343</v>
+      </c>
+      <c r="B1192" s="3"/>
+      <c r="C1192" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1192" s="3">
+        <v>6097869271</v>
+      </c>
+      <c r="E1192" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1192" s="3" t="s">
+        <v>3344</v>
+      </c>
+      <c r="G1192" s="3" t="s">
+        <v>3345</v>
+      </c>
+      <c r="H1192" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1192" s="3"/>
+      <c r="J1192" s="3"/>
+      <c r="K1192" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1192" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1192" s="3" t="s">
+        <v>3346</v>
+      </c>
+      <c r="N1192" s="3"/>
+    </row>
+    <row r="1193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1193" s="3" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B1193" s="3"/>
+      <c r="C1193" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1193" s="3">
+        <v>6098121422</v>
+      </c>
+      <c r="E1193" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1193" s="3" t="s">
+        <v>3348</v>
+      </c>
+      <c r="G1193" s="3" t="s">
+        <v>3349</v>
+      </c>
+      <c r="H1193" s="3"/>
+      <c r="I1193" s="3"/>
+      <c r="J1193" s="3"/>
+      <c r="K1193" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1193" s="3"/>
+      <c r="M1193" s="3"/>
+      <c r="N1193" s="3"/>
+    </row>
+    <row r="1194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1194" s="3" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B1194" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1194" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1194" s="3">
+        <v>6102315890</v>
+      </c>
+      <c r="E1194" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1194" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="G1194" s="3" t="s">
+        <v>3351</v>
+      </c>
+      <c r="H1194" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1194" s="3"/>
+      <c r="J1194" s="3"/>
+      <c r="K1194" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1194" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1194" s="3" t="s">
+        <v>3352</v>
+      </c>
+      <c r="N1194" s="3"/>
+    </row>
+    <row r="1195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1195" s="3" t="s">
+        <v>3353</v>
+      </c>
+      <c r="B1195" s="3"/>
+      <c r="C1195" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1195" s="3">
+        <v>6102848629</v>
+      </c>
+      <c r="E1195" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1195" s="3" t="s">
+        <v>3354</v>
+      </c>
+      <c r="G1195" s="3" t="s">
+        <v>3355</v>
+      </c>
+      <c r="H1195" s="3"/>
+      <c r="I1195" s="3"/>
+      <c r="J1195" s="3"/>
+      <c r="K1195" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1195" s="3"/>
+      <c r="M1195" s="3"/>
+      <c r="N1195" s="3"/>
+    </row>
+    <row r="1196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1196" s="3" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B1196" s="3"/>
+      <c r="C1196" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1196" s="3">
+        <v>6111748834</v>
+      </c>
+      <c r="E1196" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1196" s="3" t="s">
+        <v>3357</v>
+      </c>
+      <c r="G1196" s="3" t="s">
+        <v>3358</v>
+      </c>
+      <c r="H1196" s="3"/>
+      <c r="I1196" s="3"/>
+      <c r="J1196" s="3"/>
+      <c r="K1196" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1196" s="3"/>
+      <c r="M1196" s="3"/>
+      <c r="N1196" s="3"/>
+    </row>
+    <row r="1197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1197" s="3" t="s">
+        <v>3359</v>
+      </c>
+      <c r="B1197" s="3"/>
+      <c r="C1197" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1197" s="3">
+        <v>6104852410</v>
+      </c>
+      <c r="E1197" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1197" s="3" t="s">
+        <v>3360</v>
+      </c>
+      <c r="G1197" s="3" t="s">
+        <v>3361</v>
+      </c>
+      <c r="H1197" s="3"/>
+      <c r="I1197" s="3"/>
+      <c r="J1197" s="3"/>
+      <c r="K1197" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1197" s="3"/>
+      <c r="M1197" s="3"/>
+      <c r="N1197" s="3"/>
+    </row>
+    <row r="1198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1198" s="3" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B1198" s="3"/>
+      <c r="C1198" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1198" s="3">
+        <v>6104891572</v>
+      </c>
+      <c r="E1198" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1198" s="3" t="s">
+        <v>3363</v>
+      </c>
+      <c r="G1198" s="3" t="s">
+        <v>3364</v>
+      </c>
+      <c r="H1198" s="3"/>
+      <c r="I1198" s="3"/>
+      <c r="J1198" s="3"/>
+      <c r="K1198" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1198" s="3"/>
+      <c r="M1198" s="3"/>
+      <c r="N1198" s="3"/>
+    </row>
+    <row r="1199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1199" s="3" t="s">
+        <v>3365</v>
+      </c>
+      <c r="B1199" s="3"/>
+      <c r="C1199" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1199" s="3">
+        <v>6108735990</v>
+      </c>
+      <c r="E1199" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1199" s="3" t="s">
+        <v>2570</v>
+      </c>
+      <c r="G1199" s="3" t="s">
+        <v>3366</v>
+      </c>
+      <c r="H1199" s="3"/>
+      <c r="I1199" s="3"/>
+      <c r="J1199" s="3"/>
+      <c r="K1199" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1199" s="3"/>
+      <c r="M1199" s="3"/>
+      <c r="N1199" s="3"/>
+    </row>
+    <row r="1200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1200" s="3" t="s">
+        <v>3367</v>
+      </c>
+      <c r="B1200" s="3"/>
+      <c r="C1200" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1200" s="3">
+        <v>6116338590</v>
+      </c>
+      <c r="E1200" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1200" s="3" t="s">
+        <v>3368</v>
+      </c>
+      <c r="G1200" s="3" t="s">
+        <v>3369</v>
+      </c>
+      <c r="H1200" s="3"/>
+      <c r="I1200" s="3"/>
+      <c r="J1200" s="3"/>
+      <c r="K1200" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1200" s="3"/>
+      <c r="M1200" s="3"/>
+      <c r="N1200" s="3"/>
+    </row>
+    <row r="1201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1201" s="3" t="s">
+        <v>3370</v>
+      </c>
+      <c r="B1201" s="3"/>
+      <c r="C1201" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1201" s="3">
+        <v>6109187551</v>
+      </c>
+      <c r="E1201" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1201" s="3" t="s">
+        <v>3371</v>
+      </c>
+      <c r="G1201" s="3" t="s">
+        <v>3372</v>
+      </c>
+      <c r="H1201" s="3"/>
+      <c r="I1201" s="3"/>
+      <c r="J1201" s="3"/>
+      <c r="K1201" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1201" s="3"/>
+      <c r="M1201" s="3"/>
+      <c r="N1201" s="3"/>
+    </row>
+    <row r="1202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1202" s="3" t="s">
+        <v>3373</v>
+      </c>
+      <c r="B1202" s="3"/>
+      <c r="C1202" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1202" s="3">
+        <v>6109776148</v>
+      </c>
+      <c r="E1202" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1202" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G1202" s="3" t="s">
+        <v>3374</v>
+      </c>
+      <c r="H1202" s="3"/>
+      <c r="I1202" s="3"/>
+      <c r="J1202" s="3"/>
+      <c r="K1202" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1202" s="3"/>
+      <c r="M1202" s="3"/>
+      <c r="N1202" s="3"/>
+    </row>
+    <row r="1203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1203" s="3" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B1203" s="3"/>
+      <c r="C1203" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1203" s="3">
+        <v>6110877589</v>
+      </c>
+      <c r="E1203" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1203" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G1203" s="3" t="s">
+        <v>3376</v>
+      </c>
+      <c r="H1203" s="3"/>
+      <c r="I1203" s="3"/>
+      <c r="J1203" s="3"/>
+      <c r="K1203" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1203" s="3"/>
+      <c r="M1203" s="3"/>
+      <c r="N1203" s="3"/>
+    </row>
+    <row r="1204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1204" s="3" t="s">
+        <v>3377</v>
+      </c>
+      <c r="B1204" s="3"/>
+      <c r="C1204" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1204" s="3">
+        <v>6113331560</v>
+      </c>
+      <c r="E1204" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1204" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="G1204" s="3" t="s">
+        <v>3378</v>
+      </c>
+      <c r="H1204" s="3"/>
+      <c r="I1204" s="3"/>
+      <c r="J1204" s="3"/>
+      <c r="K1204" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1204" s="3"/>
+      <c r="M1204" s="3"/>
+      <c r="N1204" s="3"/>
+    </row>
+    <row r="1205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1205" s="3" t="s">
+        <v>3379</v>
+      </c>
+      <c r="B1205" s="3"/>
+      <c r="C1205" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1205" s="3">
+        <v>6113512601</v>
+      </c>
+      <c r="E1205" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1205" s="3" t="s">
+        <v>3380</v>
+      </c>
+      <c r="G1205" s="3" t="s">
+        <v>3381</v>
+      </c>
+      <c r="H1205" s="3"/>
+      <c r="I1205" s="3"/>
+      <c r="J1205" s="3"/>
+      <c r="K1205" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1205" s="3"/>
+      <c r="M1205" s="3"/>
+      <c r="N1205" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE411CFA-3917-496D-8EAB-ADE58C525663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5C56423-2AEE-42E4-BAE8-448DF1F105DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7319" uniqueCount="3382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7490" uniqueCount="3466">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -10123,6 +10123,9 @@
     <t>29.345547, -98.403534</t>
   </si>
   <si>
+    <t>07/13/26 08:52 EDT</t>
+  </si>
+  <si>
     <t>07/10/26 14:29 EDT</t>
   </si>
   <si>
@@ -10141,12 +10144,21 @@
     <t>29.434332, -98.360730</t>
   </si>
   <si>
+    <t>07/13/26 08:55 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 19:36 EDT</t>
+  </si>
+  <si>
     <t>07/10/26 16:08 EDT</t>
   </si>
   <si>
     <t>29.505682, -98.133980</t>
   </si>
   <si>
+    <t>07/13/26 08:57 EDT</t>
+  </si>
+  <si>
     <t>07/10/26 18:48 EDT</t>
   </si>
   <si>
@@ -10166,6 +10178,246 @@
   </si>
   <si>
     <t>29.655361, -98.639150</t>
+  </si>
+  <si>
+    <t>07/13/26 08:58 EDT</t>
+  </si>
+  <si>
+    <t>07/11/26 13:29 EDT</t>
+  </si>
+  <si>
+    <t>5.8mi E of Helotes TX</t>
+  </si>
+  <si>
+    <t>29.589802, -98.603060</t>
+  </si>
+  <si>
+    <t>07/13/26 10:46 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi NE of Buda TX</t>
+  </si>
+  <si>
+    <t>30.129433, -97.799934</t>
+  </si>
+  <si>
+    <t>07/14/26 10:36 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 12:02 EDT</t>
+  </si>
+  <si>
+    <t>4mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.543758, -98.148155</t>
+  </si>
+  <si>
+    <t>07/13/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi SW of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.671825, -98.158226</t>
+  </si>
+  <si>
+    <t>07/13/26 15:59 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi SE of Bulverde TX</t>
+  </si>
+  <si>
+    <t>29.745283, -98.384540</t>
+  </si>
+  <si>
+    <t>07/13/26 16:26 EDT</t>
+  </si>
+  <si>
+    <t>1.6mi NE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.720280, -98.104180</t>
+  </si>
+  <si>
+    <t>07/14/26 10:40 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 17:44 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi SW of San Marcos TX</t>
+  </si>
+  <si>
+    <t>29.842371, -97.969250</t>
+  </si>
+  <si>
+    <t>2.7mi SW of San Marcos TX</t>
+  </si>
+  <si>
+    <t>29.845259, -97.966030</t>
+  </si>
+  <si>
+    <t>07/13/26 19:48 EDT</t>
+  </si>
+  <si>
+    <t>3.7mi E of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.456604, -98.324200</t>
+  </si>
+  <si>
+    <t>07/14/26 11:57 EDT</t>
+  </si>
+  <si>
+    <t>29.458174, -98.317660</t>
+  </si>
+  <si>
+    <t>07/14/26 16:55 EDT</t>
+  </si>
+  <si>
+    <t>1.4mi E of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.698391, -98.091270</t>
+  </si>
+  <si>
+    <t>07/15/26 10:05 EDT</t>
+  </si>
+  <si>
+    <t>07/14/26 18:29 EDT</t>
+  </si>
+  <si>
+    <t>29.625610, -97.869340</t>
+  </si>
+  <si>
+    <t>07/14/26 21:10 EDT</t>
+  </si>
+  <si>
+    <t>29.437853, -98.383410</t>
+  </si>
+  <si>
+    <t>07/15/26 16:55 EDT</t>
+  </si>
+  <si>
+    <t>7mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.540930, -98.069620</t>
+  </si>
+  <si>
+    <t>07/16/26 07:46 EDT</t>
+  </si>
+  <si>
+    <t>07/16/26 10:29 EDT</t>
+  </si>
+  <si>
+    <t>7.9mi NE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.785393, -98.027010</t>
+  </si>
+  <si>
+    <t>07/16/26 10:52 EDT</t>
+  </si>
+  <si>
+    <t>7.7mi NE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.783480, -98.030014</t>
+  </si>
+  <si>
+    <t>07/16/26 11:20 EDT</t>
+  </si>
+  <si>
+    <t>29.537794, -98.080240</t>
+  </si>
+  <si>
+    <t>07/16/26 20:31 EDT</t>
+  </si>
+  <si>
+    <t>07/16/26 12:41 EDT</t>
+  </si>
+  <si>
+    <t>29.585058, -97.993420</t>
+  </si>
+  <si>
+    <t>07/16/26 14:51 EDT</t>
+  </si>
+  <si>
+    <t>29.778774, -98.736930</t>
+  </si>
+  <si>
+    <t>07/16/26 15:05 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi NW of Boerne TX</t>
+  </si>
+  <si>
+    <t>29.839184, -98.774900</t>
+  </si>
+  <si>
+    <t>07/16/26 20:32 EDT</t>
+  </si>
+  <si>
+    <t>07/16/26 15:25 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.444548, -98.376290</t>
+  </si>
+  <si>
+    <t>07/16/26 19:20 EDT</t>
+  </si>
+  <si>
+    <t>29.445189, -98.360370</t>
+  </si>
+  <si>
+    <t>07/17/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>28.2mi N of Laredo TX</t>
+  </si>
+  <si>
+    <t>27.958963, -99.379770</t>
+  </si>
+  <si>
+    <t>07/17/26 12:39 EDT</t>
+  </si>
+  <si>
+    <t>27.8mi N of Laredo TX</t>
+  </si>
+  <si>
+    <t>27.953892, -99.381744</t>
+  </si>
+  <si>
+    <t>07/17/26 14:11 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi S of Alamo Heights TX</t>
+  </si>
+  <si>
+    <t>29.439032, -98.479170</t>
+  </si>
+  <si>
+    <t>07/17/26 17:46 EDT</t>
+  </si>
+  <si>
+    <t>5.6mi N of Leon Valley TX</t>
+  </si>
+  <si>
+    <t>29.574814, -98.594300</t>
+  </si>
+  <si>
+    <t>07/17/26 17:51 EDT</t>
+  </si>
+  <si>
+    <t>0.7mi E of Selma TX</t>
+  </si>
+  <si>
+    <t>29.586838, -98.301930</t>
   </si>
 </sst>
 </file>
@@ -10527,7 +10779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1205"/>
+  <dimension ref="A1:N1232"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -34280,7 +34532,7 @@
         <v>112</v>
       </c>
       <c r="D742" s="3">
-        <v>5622271458</v>
+        <v>5622402770</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>53</v>
@@ -34310,7 +34562,7 @@
         <v>112</v>
       </c>
       <c r="D743" s="3">
-        <v>5622402770</v>
+        <v>5622271458</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>53</v>
@@ -49075,19 +49327,25 @@
       <c r="G1199" s="3" t="s">
         <v>3366</v>
       </c>
-      <c r="H1199" s="3"/>
+      <c r="H1199" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1199" s="3"/>
       <c r="J1199" s="3"/>
       <c r="K1199" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1199" s="3"/>
-      <c r="M1199" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1199" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1199" s="3" t="s">
+        <v>3367</v>
+      </c>
       <c r="N1199" s="3"/>
     </row>
     <row r="1200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1200" s="3" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="B1200" s="3"/>
       <c r="C1200" s="3">
@@ -49100,10 +49358,10 @@
         <v>53</v>
       </c>
       <c r="F1200" s="3" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="G1200" s="3" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="H1200" s="3"/>
       <c r="I1200" s="3"/>
@@ -49117,9 +49375,11 @@
     </row>
     <row r="1201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1201" s="3" t="s">
-        <v>3370</v>
-      </c>
-      <c r="B1201" s="3"/>
+        <v>3371</v>
+      </c>
+      <c r="B1201" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="C1201" s="3">
         <v>112</v>
       </c>
@@ -49130,24 +49390,32 @@
         <v>34</v>
       </c>
       <c r="F1201" s="3" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="G1201" s="3" t="s">
-        <v>3372</v>
-      </c>
-      <c r="H1201" s="3"/>
+        <v>3373</v>
+      </c>
+      <c r="H1201" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I1201" s="3"/>
       <c r="J1201" s="3"/>
       <c r="K1201" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1201" s="3"/>
-      <c r="M1201" s="3"/>
-      <c r="N1201" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1201" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1201" s="3" t="s">
+        <v>3374</v>
+      </c>
+      <c r="N1201" s="3" t="s">
+        <v>3375</v>
+      </c>
     </row>
     <row r="1202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1202" s="3" t="s">
-        <v>3373</v>
+        <v>3376</v>
       </c>
       <c r="B1202" s="3"/>
       <c r="C1202" s="3">
@@ -49163,21 +49431,27 @@
         <v>301</v>
       </c>
       <c r="G1202" s="3" t="s">
-        <v>3374</v>
-      </c>
-      <c r="H1202" s="3"/>
+        <v>3377</v>
+      </c>
+      <c r="H1202" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1202" s="3"/>
       <c r="J1202" s="3"/>
       <c r="K1202" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1202" s="3"/>
-      <c r="M1202" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1202" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1202" s="3" t="s">
+        <v>3378</v>
+      </c>
       <c r="N1202" s="3"/>
     </row>
     <row r="1203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1203" s="3" t="s">
-        <v>3375</v>
+        <v>3379</v>
       </c>
       <c r="B1203" s="3"/>
       <c r="C1203" s="3">
@@ -49193,7 +49467,7 @@
         <v>1180</v>
       </c>
       <c r="G1203" s="3" t="s">
-        <v>3376</v>
+        <v>3380</v>
       </c>
       <c r="H1203" s="3"/>
       <c r="I1203" s="3"/>
@@ -49207,7 +49481,7 @@
     </row>
     <row r="1204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1204" s="3" t="s">
-        <v>3377</v>
+        <v>3381</v>
       </c>
       <c r="B1204" s="3"/>
       <c r="C1204" s="3">
@@ -49223,7 +49497,7 @@
         <v>2071</v>
       </c>
       <c r="G1204" s="3" t="s">
-        <v>3378</v>
+        <v>3382</v>
       </c>
       <c r="H1204" s="3"/>
       <c r="I1204" s="3"/>
@@ -49237,7 +49511,7 @@
     </row>
     <row r="1205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1205" s="3" t="s">
-        <v>3379</v>
+        <v>3383</v>
       </c>
       <c r="B1205" s="3"/>
       <c r="C1205" s="3">
@@ -49250,20 +49524,880 @@
         <v>80</v>
       </c>
       <c r="F1205" s="3" t="s">
-        <v>3380</v>
+        <v>3384</v>
       </c>
       <c r="G1205" s="3" t="s">
-        <v>3381</v>
-      </c>
-      <c r="H1205" s="3"/>
+        <v>3385</v>
+      </c>
+      <c r="H1205" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1205" s="3"/>
       <c r="J1205" s="3"/>
       <c r="K1205" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1205" s="3"/>
-      <c r="M1205" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1205" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1205" s="3" t="s">
+        <v>3386</v>
+      </c>
       <c r="N1205" s="3"/>
+    </row>
+    <row r="1206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1206" s="3" t="s">
+        <v>3387</v>
+      </c>
+      <c r="B1206" s="3"/>
+      <c r="C1206" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1206" s="3">
+        <v>6120291170</v>
+      </c>
+      <c r="E1206" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1206" s="3" t="s">
+        <v>3388</v>
+      </c>
+      <c r="G1206" s="3" t="s">
+        <v>3389</v>
+      </c>
+      <c r="H1206" s="3"/>
+      <c r="I1206" s="3"/>
+      <c r="J1206" s="3"/>
+      <c r="K1206" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1206" s="3"/>
+      <c r="M1206" s="3"/>
+      <c r="N1206" s="3"/>
+    </row>
+    <row r="1207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1207" s="3" t="s">
+        <v>3390</v>
+      </c>
+      <c r="B1207" s="3"/>
+      <c r="C1207" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1207" s="3">
+        <v>6122155771</v>
+      </c>
+      <c r="E1207" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1207" s="3" t="s">
+        <v>3391</v>
+      </c>
+      <c r="G1207" s="3" t="s">
+        <v>3392</v>
+      </c>
+      <c r="H1207" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1207" s="3"/>
+      <c r="J1207" s="3"/>
+      <c r="K1207" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1207" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1207" s="3" t="s">
+        <v>3393</v>
+      </c>
+      <c r="N1207" s="3"/>
+    </row>
+    <row r="1208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1208" s="3" t="s">
+        <v>3394</v>
+      </c>
+      <c r="B1208" s="3"/>
+      <c r="C1208" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1208" s="3">
+        <v>6122709686</v>
+      </c>
+      <c r="E1208" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1208" s="3" t="s">
+        <v>3395</v>
+      </c>
+      <c r="G1208" s="3" t="s">
+        <v>3396</v>
+      </c>
+      <c r="H1208" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1208" s="3"/>
+      <c r="J1208" s="3"/>
+      <c r="K1208" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1208" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1208" s="3" t="s">
+        <v>3393</v>
+      </c>
+      <c r="N1208" s="3"/>
+    </row>
+    <row r="1209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1209" s="3" t="s">
+        <v>3397</v>
+      </c>
+      <c r="B1209" s="3"/>
+      <c r="C1209" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1209" s="3">
+        <v>6122757785</v>
+      </c>
+      <c r="E1209" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1209" s="3" t="s">
+        <v>3398</v>
+      </c>
+      <c r="G1209" s="3" t="s">
+        <v>3399</v>
+      </c>
+      <c r="H1209" s="3"/>
+      <c r="I1209" s="3"/>
+      <c r="J1209" s="3"/>
+      <c r="K1209" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1209" s="3"/>
+      <c r="M1209" s="3"/>
+      <c r="N1209" s="3"/>
+    </row>
+    <row r="1210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1210" s="3" t="s">
+        <v>3400</v>
+      </c>
+      <c r="B1210" s="3"/>
+      <c r="C1210" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1210" s="3">
+        <v>6124711146</v>
+      </c>
+      <c r="E1210" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1210" s="3" t="s">
+        <v>3401</v>
+      </c>
+      <c r="G1210" s="3" t="s">
+        <v>3402</v>
+      </c>
+      <c r="H1210" s="3"/>
+      <c r="I1210" s="3"/>
+      <c r="J1210" s="3"/>
+      <c r="K1210" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1210" s="3"/>
+      <c r="M1210" s="3"/>
+      <c r="N1210" s="3"/>
+    </row>
+    <row r="1211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1211" s="3" t="s">
+        <v>3403</v>
+      </c>
+      <c r="B1211" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1211" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1211" s="3">
+        <v>6124928204</v>
+      </c>
+      <c r="E1211" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1211" s="3" t="s">
+        <v>3404</v>
+      </c>
+      <c r="G1211" s="3" t="s">
+        <v>3405</v>
+      </c>
+      <c r="H1211" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1211" s="3"/>
+      <c r="J1211" s="3"/>
+      <c r="K1211" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1211" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1211" s="3" t="s">
+        <v>3406</v>
+      </c>
+      <c r="N1211" s="3"/>
+    </row>
+    <row r="1212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1212" s="3" t="s">
+        <v>3407</v>
+      </c>
+      <c r="B1212" s="3"/>
+      <c r="C1212" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1212" s="3">
+        <v>6125502770</v>
+      </c>
+      <c r="E1212" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1212" s="3" t="s">
+        <v>3408</v>
+      </c>
+      <c r="G1212" s="3" t="s">
+        <v>3409</v>
+      </c>
+      <c r="H1212" s="3"/>
+      <c r="I1212" s="3"/>
+      <c r="J1212" s="3"/>
+      <c r="K1212" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1212" s="3"/>
+      <c r="M1212" s="3"/>
+      <c r="N1212" s="3"/>
+    </row>
+    <row r="1213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1213" s="3" t="s">
+        <v>3407</v>
+      </c>
+      <c r="B1213" s="3"/>
+      <c r="C1213" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1213" s="3">
+        <v>6125502781</v>
+      </c>
+      <c r="E1213" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1213" s="3" t="s">
+        <v>3410</v>
+      </c>
+      <c r="G1213" s="3" t="s">
+        <v>3411</v>
+      </c>
+      <c r="H1213" s="3"/>
+      <c r="I1213" s="3"/>
+      <c r="J1213" s="3"/>
+      <c r="K1213" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1213" s="3"/>
+      <c r="M1213" s="3"/>
+      <c r="N1213" s="3"/>
+    </row>
+    <row r="1214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1214" s="3" t="s">
+        <v>3412</v>
+      </c>
+      <c r="B1214" s="3"/>
+      <c r="C1214" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1214" s="3">
+        <v>6126263578</v>
+      </c>
+      <c r="E1214" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1214" s="3" t="s">
+        <v>3413</v>
+      </c>
+      <c r="G1214" s="3" t="s">
+        <v>3414</v>
+      </c>
+      <c r="H1214" s="3"/>
+      <c r="I1214" s="3"/>
+      <c r="J1214" s="3"/>
+      <c r="K1214" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1214" s="3"/>
+      <c r="M1214" s="3"/>
+      <c r="N1214" s="3"/>
+    </row>
+    <row r="1215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1215" s="3" t="s">
+        <v>3415</v>
+      </c>
+      <c r="B1215" s="3"/>
+      <c r="C1215" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1215" s="3">
+        <v>6129460286</v>
+      </c>
+      <c r="E1215" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1215" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1215" s="3" t="s">
+        <v>3416</v>
+      </c>
+      <c r="H1215" s="3"/>
+      <c r="I1215" s="3"/>
+      <c r="J1215" s="3"/>
+      <c r="K1215" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1215" s="3"/>
+      <c r="M1215" s="3"/>
+      <c r="N1215" s="3"/>
+    </row>
+    <row r="1216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1216" s="3" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B1216" s="3"/>
+      <c r="C1216" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1216" s="3">
+        <v>6132009289</v>
+      </c>
+      <c r="E1216" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1216" s="3" t="s">
+        <v>3418</v>
+      </c>
+      <c r="G1216" s="3" t="s">
+        <v>3419</v>
+      </c>
+      <c r="H1216" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1216" s="3"/>
+      <c r="J1216" s="3"/>
+      <c r="K1216" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1216" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1216" s="3" t="s">
+        <v>3420</v>
+      </c>
+      <c r="N1216" s="3"/>
+    </row>
+    <row r="1217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1217" s="3" t="s">
+        <v>3421</v>
+      </c>
+      <c r="B1217" s="3"/>
+      <c r="C1217" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1217" s="3">
+        <v>6132667806</v>
+      </c>
+      <c r="E1217" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1217" s="3" t="s">
+        <v>2578</v>
+      </c>
+      <c r="G1217" s="3" t="s">
+        <v>3422</v>
+      </c>
+      <c r="H1217" s="3"/>
+      <c r="I1217" s="3"/>
+      <c r="J1217" s="3"/>
+      <c r="K1217" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1217" s="3"/>
+      <c r="M1217" s="3"/>
+      <c r="N1217" s="3"/>
+    </row>
+    <row r="1218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1218" s="3" t="s">
+        <v>3423</v>
+      </c>
+      <c r="B1218" s="3"/>
+      <c r="C1218" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1218" s="3">
+        <v>6133449098</v>
+      </c>
+      <c r="E1218" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1218" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G1218" s="3" t="s">
+        <v>3424</v>
+      </c>
+      <c r="H1218" s="3"/>
+      <c r="I1218" s="3"/>
+      <c r="J1218" s="3"/>
+      <c r="K1218" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1218" s="3"/>
+      <c r="M1218" s="3"/>
+      <c r="N1218" s="3"/>
+    </row>
+    <row r="1219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1219" s="3" t="s">
+        <v>3425</v>
+      </c>
+      <c r="B1219" s="3"/>
+      <c r="C1219" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1219" s="3">
+        <v>6138954451</v>
+      </c>
+      <c r="E1219" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1219" s="3" t="s">
+        <v>3426</v>
+      </c>
+      <c r="G1219" s="3" t="s">
+        <v>3427</v>
+      </c>
+      <c r="H1219" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1219" s="3"/>
+      <c r="J1219" s="3"/>
+      <c r="K1219" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1219" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1219" s="3" t="s">
+        <v>3428</v>
+      </c>
+      <c r="N1219" s="3"/>
+    </row>
+    <row r="1220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1220" s="3" t="s">
+        <v>3429</v>
+      </c>
+      <c r="B1220" s="3"/>
+      <c r="C1220" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1220" s="3">
+        <v>6154148246</v>
+      </c>
+      <c r="E1220" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1220" s="3" t="s">
+        <v>3430</v>
+      </c>
+      <c r="G1220" s="3" t="s">
+        <v>3431</v>
+      </c>
+      <c r="H1220" s="3"/>
+      <c r="I1220" s="3"/>
+      <c r="J1220" s="3"/>
+      <c r="K1220" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1220" s="3"/>
+      <c r="M1220" s="3"/>
+      <c r="N1220" s="3"/>
+    </row>
+    <row r="1221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1221" s="3" t="s">
+        <v>3432</v>
+      </c>
+      <c r="B1221" s="3"/>
+      <c r="C1221" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1221" s="3">
+        <v>6142866773</v>
+      </c>
+      <c r="E1221" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1221" s="3" t="s">
+        <v>3433</v>
+      </c>
+      <c r="G1221" s="3" t="s">
+        <v>3434</v>
+      </c>
+      <c r="H1221" s="3"/>
+      <c r="I1221" s="3"/>
+      <c r="J1221" s="3"/>
+      <c r="K1221" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1221" s="3"/>
+      <c r="M1221" s="3"/>
+      <c r="N1221" s="3"/>
+    </row>
+    <row r="1222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1222" s="3" t="s">
+        <v>3435</v>
+      </c>
+      <c r="B1222" s="3"/>
+      <c r="C1222" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1222" s="3">
+        <v>6143062284</v>
+      </c>
+      <c r="E1222" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1222" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="G1222" s="3" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H1222" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1222" s="3"/>
+      <c r="J1222" s="3"/>
+      <c r="K1222" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1222" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1222" s="3" t="s">
+        <v>3437</v>
+      </c>
+      <c r="N1222" s="3"/>
+    </row>
+    <row r="1223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1223" s="3" t="s">
+        <v>3438</v>
+      </c>
+      <c r="B1223" s="3"/>
+      <c r="C1223" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1223" s="3">
+        <v>6143713568</v>
+      </c>
+      <c r="E1223" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1223" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G1223" s="3" t="s">
+        <v>3439</v>
+      </c>
+      <c r="H1223" s="3"/>
+      <c r="I1223" s="3"/>
+      <c r="J1223" s="3"/>
+      <c r="K1223" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1223" s="3"/>
+      <c r="M1223" s="3"/>
+      <c r="N1223" s="3"/>
+    </row>
+    <row r="1224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1224" s="3" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B1224" s="3"/>
+      <c r="C1224" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1224" s="3">
+        <v>6144836487</v>
+      </c>
+      <c r="E1224" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1224" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="G1224" s="3" t="s">
+        <v>3441</v>
+      </c>
+      <c r="H1224" s="3"/>
+      <c r="I1224" s="3"/>
+      <c r="J1224" s="3"/>
+      <c r="K1224" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1224" s="3"/>
+      <c r="M1224" s="3"/>
+      <c r="N1224" s="3"/>
+    </row>
+    <row r="1225" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1225" s="3" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B1225" s="3"/>
+      <c r="C1225" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1225" s="3">
+        <v>6144956222</v>
+      </c>
+      <c r="E1225" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1225" s="3" t="s">
+        <v>3443</v>
+      </c>
+      <c r="G1225" s="3" t="s">
+        <v>3444</v>
+      </c>
+      <c r="H1225" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1225" s="3"/>
+      <c r="J1225" s="3"/>
+      <c r="K1225" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1225" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1225" s="3" t="s">
+        <v>3445</v>
+      </c>
+      <c r="N1225" s="3"/>
+    </row>
+    <row r="1226" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1226" s="3" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B1226" s="3"/>
+      <c r="C1226" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1226" s="3">
+        <v>6145133648</v>
+      </c>
+      <c r="E1226" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1226" s="3" t="s">
+        <v>3447</v>
+      </c>
+      <c r="G1226" s="3" t="s">
+        <v>3448</v>
+      </c>
+      <c r="H1226" s="3"/>
+      <c r="I1226" s="3"/>
+      <c r="J1226" s="3"/>
+      <c r="K1226" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1226" s="3"/>
+      <c r="M1226" s="3"/>
+      <c r="N1226" s="3"/>
+    </row>
+    <row r="1227" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1227" s="3" t="s">
+        <v>3449</v>
+      </c>
+      <c r="B1227" s="3"/>
+      <c r="C1227" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1227" s="3">
+        <v>6146784260</v>
+      </c>
+      <c r="E1227" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1227" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G1227" s="3" t="s">
+        <v>3450</v>
+      </c>
+      <c r="H1227" s="3"/>
+      <c r="I1227" s="3"/>
+      <c r="J1227" s="3"/>
+      <c r="K1227" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1227" s="3"/>
+      <c r="M1227" s="3"/>
+      <c r="N1227" s="3"/>
+    </row>
+    <row r="1228" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1228" s="3" t="s">
+        <v>3451</v>
+      </c>
+      <c r="B1228" s="3"/>
+      <c r="C1228" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1228" s="3">
+        <v>6149397997</v>
+      </c>
+      <c r="E1228" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1228" s="3" t="s">
+        <v>3452</v>
+      </c>
+      <c r="G1228" s="3" t="s">
+        <v>3453</v>
+      </c>
+      <c r="H1228" s="3"/>
+      <c r="I1228" s="3"/>
+      <c r="J1228" s="3"/>
+      <c r="K1228" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1228" s="3"/>
+      <c r="M1228" s="3"/>
+      <c r="N1228" s="3"/>
+    </row>
+    <row r="1229" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1229" s="3" t="s">
+        <v>3454</v>
+      </c>
+      <c r="B1229" s="3"/>
+      <c r="C1229" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1229" s="3">
+        <v>6150486591</v>
+      </c>
+      <c r="E1229" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1229" s="3" t="s">
+        <v>3455</v>
+      </c>
+      <c r="G1229" s="3" t="s">
+        <v>3456</v>
+      </c>
+      <c r="H1229" s="3"/>
+      <c r="I1229" s="3"/>
+      <c r="J1229" s="3"/>
+      <c r="K1229" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1229" s="3"/>
+      <c r="M1229" s="3"/>
+      <c r="N1229" s="3"/>
+    </row>
+    <row r="1230" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1230" s="3" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B1230" s="3"/>
+      <c r="C1230" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1230" s="3">
+        <v>6151273246</v>
+      </c>
+      <c r="E1230" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1230" s="3" t="s">
+        <v>3458</v>
+      </c>
+      <c r="G1230" s="3" t="s">
+        <v>3459</v>
+      </c>
+      <c r="H1230" s="3"/>
+      <c r="I1230" s="3"/>
+      <c r="J1230" s="3"/>
+      <c r="K1230" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1230" s="3"/>
+      <c r="M1230" s="3"/>
+      <c r="N1230" s="3"/>
+    </row>
+    <row r="1231" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1231" s="3" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B1231" s="3"/>
+      <c r="C1231" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1231" s="3">
+        <v>6152912421</v>
+      </c>
+      <c r="E1231" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1231" s="3" t="s">
+        <v>3461</v>
+      </c>
+      <c r="G1231" s="3" t="s">
+        <v>3462</v>
+      </c>
+      <c r="H1231" s="3"/>
+      <c r="I1231" s="3"/>
+      <c r="J1231" s="3"/>
+      <c r="K1231" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1231" s="3"/>
+      <c r="M1231" s="3"/>
+      <c r="N1231" s="3"/>
+    </row>
+    <row r="1232" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1232" s="3" t="s">
+        <v>3463</v>
+      </c>
+      <c r="B1232" s="3"/>
+      <c r="C1232" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1232" s="3">
+        <v>6152947599</v>
+      </c>
+      <c r="E1232" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1232" s="3" t="s">
+        <v>3464</v>
+      </c>
+      <c r="G1232" s="3" t="s">
+        <v>3465</v>
+      </c>
+      <c r="H1232" s="3"/>
+      <c r="I1232" s="3"/>
+      <c r="J1232" s="3"/>
+      <c r="K1232" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1232" s="3"/>
+      <c r="M1232" s="3"/>
+      <c r="N1232" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BCC0058-3386-48F2-8655-1702054B2A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D9AC9E2-5C37-4103-BEF1-694CCA01BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7767" uniqueCount="3599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8019" uniqueCount="3712">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -9247,21 +9247,21 @@
     <t>06/19/26 16:32 EDT</t>
   </si>
   <si>
+    <t>COLLISION-WARNING</t>
+  </si>
+  <si>
     <t>1.9mi S of Kirby TX</t>
   </si>
   <si>
     <t>29.433548, -98.390060</t>
   </si>
   <si>
+    <t>06/22/26 13:05 EDT</t>
+  </si>
+  <si>
     <t>06/21/26 21:00 EDT</t>
   </si>
   <si>
-    <t>COLLISION-WARNING</t>
-  </si>
-  <si>
-    <t>06/22/26 13:05 EDT</t>
-  </si>
-  <si>
     <t>06/19/26 16:36 EDT</t>
   </si>
   <si>
@@ -10780,6 +10780,9 @@
     <t>27.530613, -99.484190</t>
   </si>
   <si>
+    <t>07/27/26 10:14 EDT</t>
+  </si>
+  <si>
     <t>07/24/26 10:29 EDT</t>
   </si>
   <si>
@@ -10795,6 +10798,9 @@
     <t>29.491302, -98.214860</t>
   </si>
   <si>
+    <t>07/27/26 10:20 EDT</t>
+  </si>
+  <si>
     <t>07/24/26 15:29 EDT</t>
   </si>
   <si>
@@ -10804,6 +10810,12 @@
     <t>29.564795, -98.237236</t>
   </si>
   <si>
+    <t>07/27/26 10:17 EDT</t>
+  </si>
+  <si>
+    <t>07/27/26 10:29 EDT</t>
+  </si>
+  <si>
     <t>07/24/26 16:50 EDT</t>
   </si>
   <si>
@@ -10817,6 +10829,333 @@
   </si>
   <si>
     <t>29.574736, -97.417244</t>
+  </si>
+  <si>
+    <t>07/27/26 10:15 EDT</t>
+  </si>
+  <si>
+    <t>07/26/26 14:29 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi S of Kyle TX</t>
+  </si>
+  <si>
+    <t>29.968212, -97.875230</t>
+  </si>
+  <si>
+    <t>07/27/26 11:14 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi W of Live Oak TX</t>
+  </si>
+  <si>
+    <t>29.545805, -98.368904</t>
+  </si>
+  <si>
+    <t>07/27/26 11:27 EDT</t>
+  </si>
+  <si>
+    <t>29mi N of Beeville TX</t>
+  </si>
+  <si>
+    <t>28.814098, -97.858080</t>
+  </si>
+  <si>
+    <t>07/27/26 12:59 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi S of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.544916, -97.953020</t>
+  </si>
+  <si>
+    <t>29.457611, -98.321754</t>
+  </si>
+  <si>
+    <t>07/27/26 13:19 EDT</t>
+  </si>
+  <si>
+    <t>2.4mi NW of San Antonio TX</t>
+  </si>
+  <si>
+    <t>29.491096, -98.546360</t>
+  </si>
+  <si>
+    <t>07/27/26 14:25 EDT</t>
+  </si>
+  <si>
+    <t>4.2mi S of San Antonio TX</t>
+  </si>
+  <si>
+    <t>29.403173, -98.511734</t>
+  </si>
+  <si>
+    <t>07/27/26 15:35 EDT</t>
+  </si>
+  <si>
+    <t>29.481438, -98.242690</t>
+  </si>
+  <si>
+    <t>29.482458, -98.239700</t>
+  </si>
+  <si>
+    <t>07/28/26 07:26 EDT</t>
+  </si>
+  <si>
+    <t>07/27/26 15:38 EDT</t>
+  </si>
+  <si>
+    <t>29.494760, -98.203570</t>
+  </si>
+  <si>
+    <t>07/27/26 15:39 EDT</t>
+  </si>
+  <si>
+    <t>29.403727, -98.545530</t>
+  </si>
+  <si>
+    <t>07/27/26 15:40 EDT</t>
+  </si>
+  <si>
+    <t>4mi E of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.404630, -98.554600</t>
+  </si>
+  <si>
+    <t>07/27/26 16:20 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi E of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.599295, -97.932980</t>
+  </si>
+  <si>
+    <t>07/27/26 17:56 EDT</t>
+  </si>
+  <si>
+    <t>13.3mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.394829, -98.103630</t>
+  </si>
+  <si>
+    <t>07/29/26 07:54 EDT</t>
+  </si>
+  <si>
+    <t>07/27/26 18:43 EDT</t>
+  </si>
+  <si>
+    <t>29.561470, -98.031530</t>
+  </si>
+  <si>
+    <t>07/28/26 09:29 EDT</t>
+  </si>
+  <si>
+    <t>29.438307, -98.382840</t>
+  </si>
+  <si>
+    <t>07/28/26 10:13 EDT</t>
+  </si>
+  <si>
+    <t>29.445760, -98.360520</t>
+  </si>
+  <si>
+    <t>07/28/26 11:36 EDT</t>
+  </si>
+  <si>
+    <t>5.9mi SW of Luling TX</t>
+  </si>
+  <si>
+    <t>29.636524, -97.729690</t>
+  </si>
+  <si>
+    <t>07/28/26 20:56 EDT</t>
+  </si>
+  <si>
+    <t>07/28/26 13:59 EDT</t>
+  </si>
+  <si>
+    <t>29.464064, -98.297750</t>
+  </si>
+  <si>
+    <t>07/28/26 16:35 EDT</t>
+  </si>
+  <si>
+    <t>29.510181, -98.209510</t>
+  </si>
+  <si>
+    <t>07/29/26 09:11 EDT</t>
+  </si>
+  <si>
+    <t>29.510033, -98.163315</t>
+  </si>
+  <si>
+    <t>07/29/26 12:01 EDT</t>
+  </si>
+  <si>
+    <t>29.582280, -97.999500</t>
+  </si>
+  <si>
+    <t>07/30/26 08:15 EDT</t>
+  </si>
+  <si>
+    <t>07/29/26 14:48 EDT</t>
+  </si>
+  <si>
+    <t>29.582253, -97.999535</t>
+  </si>
+  <si>
+    <t>07/30/26 10:02 EDT</t>
+  </si>
+  <si>
+    <t>29.530250, -98.109080</t>
+  </si>
+  <si>
+    <t>07/30/26 10:03 EDT</t>
+  </si>
+  <si>
+    <t>29.527584, -98.117170</t>
+  </si>
+  <si>
+    <t>07/30/26 10:20 EDT</t>
+  </si>
+  <si>
+    <t>1mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.499190, -98.296910</t>
+  </si>
+  <si>
+    <t>07/30/26 21:12 EDT</t>
+  </si>
+  <si>
+    <t>07/30/26 15:32 EDT</t>
+  </si>
+  <si>
+    <t>29.550620, -98.407646</t>
+  </si>
+  <si>
+    <t>07/30/26 19:03 EDT</t>
+  </si>
+  <si>
+    <t>29.507483, -98.130325</t>
+  </si>
+  <si>
+    <t>07/30/26 21:13 EDT</t>
+  </si>
+  <si>
+    <t>07/31/26 09:52 EDT</t>
+  </si>
+  <si>
+    <t>1mi W of Universal City TX</t>
+  </si>
+  <si>
+    <t>29.554440, -98.323030</t>
+  </si>
+  <si>
+    <t>07/31/26 13:40 EDT</t>
+  </si>
+  <si>
+    <t>29.446875, -98.356520</t>
+  </si>
+  <si>
+    <t>08/03/26 07:15 EDT</t>
+  </si>
+  <si>
+    <t>29.446749, -98.359000</t>
+  </si>
+  <si>
+    <t>07/31/26 16:59 EDT</t>
+  </si>
+  <si>
+    <t>29.506481, -98.132110</t>
+  </si>
+  <si>
+    <t>07/31/26 18:30 EDT</t>
+  </si>
+  <si>
+    <t>9.3mi SW of Hornsby Bend TX</t>
+  </si>
+  <si>
+    <t>30.140340, -97.696480</t>
+  </si>
+  <si>
+    <t>08/03/26 07:16 EDT</t>
+  </si>
+  <si>
+    <t>08/03/26 07:20 EDT</t>
+  </si>
+  <si>
+    <t>08/02/26 18:29 EDT</t>
+  </si>
+  <si>
+    <t>5.7mi S of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.304441, -98.622826</t>
+  </si>
+  <si>
+    <t>08/03/26 07:14 EDT</t>
+  </si>
+  <si>
+    <t>08/02/26 18:40 EDT</t>
+  </si>
+  <si>
+    <t>16.2mi SW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.215775, -98.802870</t>
+  </si>
+  <si>
+    <t>08/03/26 07:13 EDT</t>
+  </si>
+  <si>
+    <t>08/02/26 22:03 EDT</t>
+  </si>
+  <si>
+    <t>24.1mi SE of Uvalde TX</t>
+  </si>
+  <si>
+    <t>28.951864, -99.516210</t>
+  </si>
+  <si>
+    <t>08/02/26 22:19 EDT</t>
+  </si>
+  <si>
+    <t>10.5mi NW of Pearsall TX</t>
+  </si>
+  <si>
+    <t>28.969446, -99.246190</t>
+  </si>
+  <si>
+    <t>08/02/26 22:27 EDT</t>
+  </si>
+  <si>
+    <t>8.5mi N of Pearsall TX</t>
+  </si>
+  <si>
+    <t>29.014189, -99.112830</t>
+  </si>
+  <si>
+    <t>08/02/26 22:38 EDT</t>
+  </si>
+  <si>
+    <t>15.1mi NE of Pearsall TX</t>
+  </si>
+  <si>
+    <t>29.079834, -98.969430</t>
+  </si>
+  <si>
+    <t>08/02/26 22:44 EDT</t>
+  </si>
+  <si>
+    <t>20.7mi NE of Pearsall TX</t>
+  </si>
+  <si>
+    <t>29.132158, -98.893130</t>
   </si>
 </sst>
 </file>
@@ -11178,7 +11517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1277"/>
+  <dimension ref="A1:N1317"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -46389,16 +46728,16 @@
         <v>112</v>
       </c>
       <c r="D1095" s="3">
-        <v>5982274614</v>
+        <v>5982274613</v>
       </c>
       <c r="E1095" s="3" t="s">
-        <v>428</v>
+        <v>3075</v>
       </c>
       <c r="F1095" s="3" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="G1095" s="3" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="H1095" s="3" t="s">
         <v>110</v>
@@ -46412,7 +46751,7 @@
         <v>39</v>
       </c>
       <c r="M1095" s="3" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="N1095" s="3"/>
     </row>
@@ -46425,16 +46764,16 @@
         <v>112</v>
       </c>
       <c r="D1096" s="3">
-        <v>5982274613</v>
+        <v>5982274614</v>
       </c>
       <c r="E1096" s="3" t="s">
-        <v>3078</v>
+        <v>428</v>
       </c>
       <c r="F1096" s="3" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="G1096" s="3" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="H1096" s="3" t="s">
         <v>110</v>
@@ -49565,7 +49904,7 @@
         <v>71</v>
       </c>
       <c r="F1194" s="3" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="G1194" s="3" t="s">
         <v>3351</v>
@@ -52092,19 +52431,25 @@
       <c r="G1272" s="3" t="s">
         <v>3585</v>
       </c>
-      <c r="H1272" s="3"/>
+      <c r="H1272" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1272" s="3"/>
       <c r="J1272" s="3"/>
       <c r="K1272" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1272" s="3"/>
-      <c r="M1272" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1272" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1272" s="3" t="s">
+        <v>3586</v>
+      </c>
       <c r="N1272" s="3"/>
     </row>
     <row r="1273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1273" s="3" t="s">
-        <v>3586</v>
+        <v>3587</v>
       </c>
       <c r="B1273" s="3"/>
       <c r="C1273" s="3">
@@ -52117,10 +52462,10 @@
         <v>53</v>
       </c>
       <c r="F1273" s="3" t="s">
-        <v>3587</v>
+        <v>3588</v>
       </c>
       <c r="G1273" s="3" t="s">
-        <v>3588</v>
+        <v>3589</v>
       </c>
       <c r="H1273" s="3"/>
       <c r="I1273" s="3"/>
@@ -52134,9 +52479,11 @@
     </row>
     <row r="1274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1274" s="3" t="s">
-        <v>3589</v>
-      </c>
-      <c r="B1274" s="3"/>
+        <v>3590</v>
+      </c>
+      <c r="B1274" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="C1274" s="3">
         <v>110</v>
       </c>
@@ -52150,23 +52497,31 @@
         <v>1698</v>
       </c>
       <c r="G1274" s="3" t="s">
-        <v>3590</v>
-      </c>
-      <c r="H1274" s="3"/>
+        <v>3591</v>
+      </c>
+      <c r="H1274" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1274" s="3"/>
       <c r="J1274" s="3"/>
       <c r="K1274" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1274" s="3"/>
-      <c r="M1274" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1274" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1274" s="3" t="s">
+        <v>3592</v>
+      </c>
       <c r="N1274" s="3"/>
     </row>
     <row r="1275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1275" s="3" t="s">
-        <v>3591</v>
-      </c>
-      <c r="B1275" s="3"/>
+        <v>3593</v>
+      </c>
+      <c r="B1275" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="C1275" s="3">
         <v>110</v>
       </c>
@@ -52177,24 +52532,32 @@
         <v>80</v>
       </c>
       <c r="F1275" s="3" t="s">
-        <v>3592</v>
+        <v>3594</v>
       </c>
       <c r="G1275" s="3" t="s">
-        <v>3593</v>
-      </c>
-      <c r="H1275" s="3"/>
+        <v>3595</v>
+      </c>
+      <c r="H1275" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I1275" s="3"/>
       <c r="J1275" s="3"/>
       <c r="K1275" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1275" s="3"/>
-      <c r="M1275" s="3"/>
-      <c r="N1275" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1275" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1275" s="3" t="s">
+        <v>3596</v>
+      </c>
+      <c r="N1275" s="3" t="s">
+        <v>3597</v>
+      </c>
     </row>
     <row r="1276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1276" s="3" t="s">
-        <v>3594</v>
+        <v>3598</v>
       </c>
       <c r="B1276" s="3"/>
       <c r="C1276" s="3">
@@ -52210,7 +52573,7 @@
         <v>1169</v>
       </c>
       <c r="G1276" s="3" t="s">
-        <v>3595</v>
+        <v>3599</v>
       </c>
       <c r="H1276" s="3"/>
       <c r="I1276" s="3"/>
@@ -52224,7 +52587,7 @@
     </row>
     <row r="1277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1277" s="3" t="s">
-        <v>3596</v>
+        <v>3600</v>
       </c>
       <c r="B1277" s="3"/>
       <c r="C1277" s="3">
@@ -52237,20 +52600,1300 @@
         <v>17</v>
       </c>
       <c r="F1277" s="3" t="s">
-        <v>3597</v>
+        <v>3601</v>
       </c>
       <c r="G1277" s="3" t="s">
-        <v>3598</v>
-      </c>
-      <c r="H1277" s="3"/>
+        <v>3602</v>
+      </c>
+      <c r="H1277" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="I1277" s="3"/>
       <c r="J1277" s="3"/>
       <c r="K1277" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1277" s="3"/>
-      <c r="M1277" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="L1277" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1277" s="3" t="s">
+        <v>3603</v>
+      </c>
       <c r="N1277" s="3"/>
+    </row>
+    <row r="1278" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1278" s="3" t="s">
+        <v>3604</v>
+      </c>
+      <c r="B1278" s="3"/>
+      <c r="C1278" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1278" s="3">
+        <v>6212512059</v>
+      </c>
+      <c r="E1278" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1278" s="3" t="s">
+        <v>3605</v>
+      </c>
+      <c r="G1278" s="3" t="s">
+        <v>3606</v>
+      </c>
+      <c r="H1278" s="3"/>
+      <c r="I1278" s="3"/>
+      <c r="J1278" s="3"/>
+      <c r="K1278" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1278" s="3"/>
+      <c r="M1278" s="3"/>
+      <c r="N1278" s="3"/>
+    </row>
+    <row r="1279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1279" s="3" t="s">
+        <v>3607</v>
+      </c>
+      <c r="B1279" s="3"/>
+      <c r="C1279" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1279" s="3">
+        <v>6208027606</v>
+      </c>
+      <c r="E1279" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1279" s="3" t="s">
+        <v>3608</v>
+      </c>
+      <c r="G1279" s="3" t="s">
+        <v>3609</v>
+      </c>
+      <c r="H1279" s="3"/>
+      <c r="I1279" s="3"/>
+      <c r="J1279" s="3"/>
+      <c r="K1279" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1279" s="3"/>
+      <c r="M1279" s="3"/>
+      <c r="N1279" s="3"/>
+    </row>
+    <row r="1280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1280" s="3" t="s">
+        <v>3610</v>
+      </c>
+      <c r="B1280" s="3"/>
+      <c r="C1280" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1280" s="3">
+        <v>6208125186</v>
+      </c>
+      <c r="E1280" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1280" s="3" t="s">
+        <v>3611</v>
+      </c>
+      <c r="G1280" s="3" t="s">
+        <v>3612</v>
+      </c>
+      <c r="H1280" s="3"/>
+      <c r="I1280" s="3"/>
+      <c r="J1280" s="3"/>
+      <c r="K1280" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1280" s="3"/>
+      <c r="M1280" s="3"/>
+      <c r="N1280" s="3"/>
+    </row>
+    <row r="1281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1281" s="3" t="s">
+        <v>3613</v>
+      </c>
+      <c r="B1281" s="3"/>
+      <c r="C1281" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1281" s="3">
+        <v>6220045473</v>
+      </c>
+      <c r="E1281" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1281" s="3" t="s">
+        <v>3614</v>
+      </c>
+      <c r="G1281" s="3" t="s">
+        <v>3615</v>
+      </c>
+      <c r="H1281" s="3"/>
+      <c r="I1281" s="3"/>
+      <c r="J1281" s="3"/>
+      <c r="K1281" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1281" s="3"/>
+      <c r="M1281" s="3"/>
+      <c r="N1281" s="3"/>
+    </row>
+    <row r="1282" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1282" s="3" t="s">
+        <v>3613</v>
+      </c>
+      <c r="B1282" s="3"/>
+      <c r="C1282" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1282" s="3">
+        <v>6219712374</v>
+      </c>
+      <c r="E1282" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1282" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G1282" s="3" t="s">
+        <v>3616</v>
+      </c>
+      <c r="H1282" s="3"/>
+      <c r="I1282" s="3"/>
+      <c r="J1282" s="3"/>
+      <c r="K1282" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1282" s="3"/>
+      <c r="M1282" s="3"/>
+      <c r="N1282" s="3"/>
+    </row>
+    <row r="1283" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1283" s="3" t="s">
+        <v>3617</v>
+      </c>
+      <c r="B1283" s="3"/>
+      <c r="C1283" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1283" s="3">
+        <v>6209044451</v>
+      </c>
+      <c r="E1283" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1283" s="3" t="s">
+        <v>3618</v>
+      </c>
+      <c r="G1283" s="3" t="s">
+        <v>3619</v>
+      </c>
+      <c r="H1283" s="3"/>
+      <c r="I1283" s="3"/>
+      <c r="J1283" s="3"/>
+      <c r="K1283" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1283" s="3"/>
+      <c r="M1283" s="3"/>
+      <c r="N1283" s="3"/>
+    </row>
+    <row r="1284" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1284" s="3" t="s">
+        <v>3620</v>
+      </c>
+      <c r="B1284" s="3"/>
+      <c r="C1284" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1284" s="3">
+        <v>6209622088</v>
+      </c>
+      <c r="E1284" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1284" s="3" t="s">
+        <v>3621</v>
+      </c>
+      <c r="G1284" s="3" t="s">
+        <v>3622</v>
+      </c>
+      <c r="H1284" s="3"/>
+      <c r="I1284" s="3"/>
+      <c r="J1284" s="3"/>
+      <c r="K1284" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1284" s="3"/>
+      <c r="M1284" s="3"/>
+      <c r="N1284" s="3"/>
+    </row>
+    <row r="1285" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1285" s="3" t="s">
+        <v>3623</v>
+      </c>
+      <c r="B1285" s="3"/>
+      <c r="C1285" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1285" s="3">
+        <v>6210230494</v>
+      </c>
+      <c r="E1285" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1285" s="3" t="s">
+        <v>3559</v>
+      </c>
+      <c r="G1285" s="3" t="s">
+        <v>3624</v>
+      </c>
+      <c r="H1285" s="3"/>
+      <c r="I1285" s="3"/>
+      <c r="J1285" s="3"/>
+      <c r="K1285" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1285" s="3"/>
+      <c r="M1285" s="3"/>
+      <c r="N1285" s="3"/>
+    </row>
+    <row r="1286" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1286" s="3" t="s">
+        <v>3623</v>
+      </c>
+      <c r="B1286" s="3"/>
+      <c r="C1286" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1286" s="3">
+        <v>6210238509</v>
+      </c>
+      <c r="E1286" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1286" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="G1286" s="3" t="s">
+        <v>3625</v>
+      </c>
+      <c r="H1286" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1286" s="3"/>
+      <c r="J1286" s="3"/>
+      <c r="K1286" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1286" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1286" s="3" t="s">
+        <v>3626</v>
+      </c>
+      <c r="N1286" s="3"/>
+    </row>
+    <row r="1287" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1287" s="3" t="s">
+        <v>3627</v>
+      </c>
+      <c r="B1287" s="3"/>
+      <c r="C1287" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1287" s="3">
+        <v>6210255016</v>
+      </c>
+      <c r="E1287" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1287" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G1287" s="3" t="s">
+        <v>3628</v>
+      </c>
+      <c r="H1287" s="3"/>
+      <c r="I1287" s="3"/>
+      <c r="J1287" s="3"/>
+      <c r="K1287" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1287" s="3"/>
+      <c r="M1287" s="3"/>
+      <c r="N1287" s="3"/>
+    </row>
+    <row r="1288" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1288" s="3" t="s">
+        <v>3629</v>
+      </c>
+      <c r="B1288" s="3"/>
+      <c r="C1288" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1288" s="3">
+        <v>6210270149</v>
+      </c>
+      <c r="E1288" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1288" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G1288" s="3" t="s">
+        <v>3630</v>
+      </c>
+      <c r="H1288" s="3"/>
+      <c r="I1288" s="3"/>
+      <c r="J1288" s="3"/>
+      <c r="K1288" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1288" s="3"/>
+      <c r="M1288" s="3"/>
+      <c r="N1288" s="3"/>
+    </row>
+    <row r="1289" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1289" s="3" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B1289" s="3"/>
+      <c r="C1289" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1289" s="3">
+        <v>6210270151</v>
+      </c>
+      <c r="E1289" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1289" s="3" t="s">
+        <v>3632</v>
+      </c>
+      <c r="G1289" s="3" t="s">
+        <v>3633</v>
+      </c>
+      <c r="H1289" s="3"/>
+      <c r="I1289" s="3"/>
+      <c r="J1289" s="3"/>
+      <c r="K1289" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1289" s="3"/>
+      <c r="M1289" s="3"/>
+      <c r="N1289" s="3"/>
+    </row>
+    <row r="1290" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1290" s="3" t="s">
+        <v>3634</v>
+      </c>
+      <c r="B1290" s="3"/>
+      <c r="C1290" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1290" s="3">
+        <v>6210600739</v>
+      </c>
+      <c r="E1290" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1290" s="3" t="s">
+        <v>3635</v>
+      </c>
+      <c r="G1290" s="3" t="s">
+        <v>3636</v>
+      </c>
+      <c r="H1290" s="3"/>
+      <c r="I1290" s="3"/>
+      <c r="J1290" s="3"/>
+      <c r="K1290" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1290" s="3"/>
+      <c r="M1290" s="3"/>
+      <c r="N1290" s="3"/>
+    </row>
+    <row r="1291" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1291" s="3" t="s">
+        <v>3637</v>
+      </c>
+      <c r="B1291" s="3"/>
+      <c r="C1291" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1291" s="3">
+        <v>6213777916</v>
+      </c>
+      <c r="E1291" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1291" s="3" t="s">
+        <v>3638</v>
+      </c>
+      <c r="G1291" s="3" t="s">
+        <v>3639</v>
+      </c>
+      <c r="H1291" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1291" s="3"/>
+      <c r="J1291" s="3"/>
+      <c r="K1291" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1291" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1291" s="3" t="s">
+        <v>3640</v>
+      </c>
+      <c r="N1291" s="3"/>
+    </row>
+    <row r="1292" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1292" s="3" t="s">
+        <v>3641</v>
+      </c>
+      <c r="B1292" s="3"/>
+      <c r="C1292" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1292" s="3">
+        <v>6213778895</v>
+      </c>
+      <c r="E1292" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1292" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1292" s="3" t="s">
+        <v>3642</v>
+      </c>
+      <c r="H1292" s="3"/>
+      <c r="I1292" s="3"/>
+      <c r="J1292" s="3"/>
+      <c r="K1292" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1292" s="3"/>
+      <c r="M1292" s="3"/>
+      <c r="N1292" s="3"/>
+    </row>
+    <row r="1293" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1293" s="3" t="s">
+        <v>3643</v>
+      </c>
+      <c r="B1293" s="3"/>
+      <c r="C1293" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1293" s="3">
+        <v>6227316173</v>
+      </c>
+      <c r="E1293" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1293" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G1293" s="3" t="s">
+        <v>3644</v>
+      </c>
+      <c r="H1293" s="3"/>
+      <c r="I1293" s="3"/>
+      <c r="J1293" s="3"/>
+      <c r="K1293" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1293" s="3"/>
+      <c r="M1293" s="3"/>
+      <c r="N1293" s="3"/>
+    </row>
+    <row r="1294" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1294" s="3" t="s">
+        <v>3645</v>
+      </c>
+      <c r="B1294" s="3"/>
+      <c r="C1294" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1294" s="3">
+        <v>6214496168</v>
+      </c>
+      <c r="E1294" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1294" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G1294" s="3" t="s">
+        <v>3646</v>
+      </c>
+      <c r="H1294" s="3"/>
+      <c r="I1294" s="3"/>
+      <c r="J1294" s="3"/>
+      <c r="K1294" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1294" s="3"/>
+      <c r="M1294" s="3"/>
+      <c r="N1294" s="3"/>
+    </row>
+    <row r="1295" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1295" s="3" t="s">
+        <v>3647</v>
+      </c>
+      <c r="B1295" s="3"/>
+      <c r="C1295" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1295" s="3">
+        <v>6215112258</v>
+      </c>
+      <c r="E1295" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1295" s="3" t="s">
+        <v>3648</v>
+      </c>
+      <c r="G1295" s="3" t="s">
+        <v>3649</v>
+      </c>
+      <c r="H1295" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1295" s="3"/>
+      <c r="J1295" s="3"/>
+      <c r="K1295" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1295" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1295" s="3" t="s">
+        <v>3650</v>
+      </c>
+      <c r="N1295" s="3"/>
+    </row>
+    <row r="1296" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1296" s="3" t="s">
+        <v>3651</v>
+      </c>
+      <c r="B1296" s="3"/>
+      <c r="C1296" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1296" s="3">
+        <v>6227170199</v>
+      </c>
+      <c r="E1296" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1296" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1296" s="3" t="s">
+        <v>3652</v>
+      </c>
+      <c r="H1296" s="3"/>
+      <c r="I1296" s="3"/>
+      <c r="J1296" s="3"/>
+      <c r="K1296" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1296" s="3"/>
+      <c r="M1296" s="3"/>
+      <c r="N1296" s="3"/>
+    </row>
+    <row r="1297" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1297" s="3" t="s">
+        <v>3653</v>
+      </c>
+      <c r="B1297" s="3"/>
+      <c r="C1297" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1297" s="3">
+        <v>6217772138</v>
+      </c>
+      <c r="E1297" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1297" s="3" t="s">
+        <v>2253</v>
+      </c>
+      <c r="G1297" s="3" t="s">
+        <v>3654</v>
+      </c>
+      <c r="H1297" s="3"/>
+      <c r="I1297" s="3"/>
+      <c r="J1297" s="3"/>
+      <c r="K1297" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1297" s="3"/>
+      <c r="M1297" s="3"/>
+      <c r="N1297" s="3"/>
+    </row>
+    <row r="1298" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1298" s="3" t="s">
+        <v>3655</v>
+      </c>
+      <c r="B1298" s="3"/>
+      <c r="C1298" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1298" s="3">
+        <v>6221289710</v>
+      </c>
+      <c r="E1298" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1298" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G1298" s="3" t="s">
+        <v>3656</v>
+      </c>
+      <c r="H1298" s="3"/>
+      <c r="I1298" s="3"/>
+      <c r="J1298" s="3"/>
+      <c r="K1298" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1298" s="3"/>
+      <c r="M1298" s="3"/>
+      <c r="N1298" s="3"/>
+    </row>
+    <row r="1299" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1299" s="3" t="s">
+        <v>3657</v>
+      </c>
+      <c r="B1299" s="3"/>
+      <c r="C1299" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1299" s="3">
+        <v>6222426842</v>
+      </c>
+      <c r="E1299" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1299" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1299" s="3" t="s">
+        <v>3658</v>
+      </c>
+      <c r="H1299" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1299" s="3"/>
+      <c r="J1299" s="3"/>
+      <c r="K1299" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1299" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1299" s="3" t="s">
+        <v>3659</v>
+      </c>
+      <c r="N1299" s="3"/>
+    </row>
+    <row r="1300" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1300" s="3" t="s">
+        <v>3660</v>
+      </c>
+      <c r="B1300" s="3"/>
+      <c r="C1300" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1300" s="3">
+        <v>6223924906</v>
+      </c>
+      <c r="E1300" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1300" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1300" s="3" t="s">
+        <v>3661</v>
+      </c>
+      <c r="H1300" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1300" s="3"/>
+      <c r="J1300" s="3"/>
+      <c r="K1300" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1300" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1300" s="3" t="s">
+        <v>3659</v>
+      </c>
+      <c r="N1300" s="3"/>
+    </row>
+    <row r="1301" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1301" s="3" t="s">
+        <v>3662</v>
+      </c>
+      <c r="B1301" s="3"/>
+      <c r="C1301" s="3">
+        <v>202</v>
+      </c>
+      <c r="D1301" s="3">
+        <v>6228740695</v>
+      </c>
+      <c r="E1301" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1301" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="G1301" s="3" t="s">
+        <v>3663</v>
+      </c>
+      <c r="H1301" s="3"/>
+      <c r="I1301" s="3"/>
+      <c r="J1301" s="3"/>
+      <c r="K1301" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1301" s="3"/>
+      <c r="M1301" s="3"/>
+      <c r="N1301" s="3"/>
+    </row>
+    <row r="1302" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1302" s="3" t="s">
+        <v>3664</v>
+      </c>
+      <c r="B1302" s="3"/>
+      <c r="C1302" s="3">
+        <v>202</v>
+      </c>
+      <c r="D1302" s="3">
+        <v>6228740703</v>
+      </c>
+      <c r="E1302" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1302" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1302" s="3" t="s">
+        <v>3665</v>
+      </c>
+      <c r="H1302" s="3"/>
+      <c r="I1302" s="3"/>
+      <c r="J1302" s="3"/>
+      <c r="K1302" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1302" s="3"/>
+      <c r="M1302" s="3"/>
+      <c r="N1302" s="3"/>
+    </row>
+    <row r="1303" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1303" s="3" t="s">
+        <v>3666</v>
+      </c>
+      <c r="B1303" s="3"/>
+      <c r="C1303" s="3">
+        <v>202</v>
+      </c>
+      <c r="D1303" s="3">
+        <v>6228801836</v>
+      </c>
+      <c r="E1303" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1303" s="3" t="s">
+        <v>3667</v>
+      </c>
+      <c r="G1303" s="3" t="s">
+        <v>3668</v>
+      </c>
+      <c r="H1303" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1303" s="3"/>
+      <c r="J1303" s="3"/>
+      <c r="K1303" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1303" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1303" s="3" t="s">
+        <v>3669</v>
+      </c>
+      <c r="N1303" s="3"/>
+    </row>
+    <row r="1304" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1304" s="3" t="s">
+        <v>3670</v>
+      </c>
+      <c r="B1304" s="3"/>
+      <c r="C1304" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1304" s="3">
+        <v>6231397537</v>
+      </c>
+      <c r="E1304" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1304" s="3" t="s">
+        <v>1832</v>
+      </c>
+      <c r="G1304" s="3" t="s">
+        <v>3671</v>
+      </c>
+      <c r="H1304" s="3"/>
+      <c r="I1304" s="3"/>
+      <c r="J1304" s="3"/>
+      <c r="K1304" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1304" s="3"/>
+      <c r="M1304" s="3"/>
+      <c r="N1304" s="3"/>
+    </row>
+    <row r="1305" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1305" s="3" t="s">
+        <v>3672</v>
+      </c>
+      <c r="B1305" s="3"/>
+      <c r="C1305" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1305" s="3">
+        <v>6232960968</v>
+      </c>
+      <c r="E1305" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1305" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1305" s="3" t="s">
+        <v>3673</v>
+      </c>
+      <c r="H1305" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1305" s="3"/>
+      <c r="J1305" s="3"/>
+      <c r="K1305" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1305" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1305" s="3" t="s">
+        <v>3674</v>
+      </c>
+      <c r="N1305" s="3"/>
+    </row>
+    <row r="1306" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1306" s="3" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B1306" s="3"/>
+      <c r="C1306" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1306" s="3">
+        <v>6235641961</v>
+      </c>
+      <c r="E1306" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1306" s="3" t="s">
+        <v>3676</v>
+      </c>
+      <c r="G1306" s="3" t="s">
+        <v>3677</v>
+      </c>
+      <c r="H1306" s="3"/>
+      <c r="I1306" s="3"/>
+      <c r="J1306" s="3"/>
+      <c r="K1306" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1306" s="3"/>
+      <c r="M1306" s="3"/>
+      <c r="N1306" s="3"/>
+    </row>
+    <row r="1307" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1307" s="3" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B1307" s="3"/>
+      <c r="C1307" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1307" s="3">
+        <v>6237337203</v>
+      </c>
+      <c r="E1307" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1307" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="G1307" s="3" t="s">
+        <v>3679</v>
+      </c>
+      <c r="H1307" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1307" s="3"/>
+      <c r="J1307" s="3"/>
+      <c r="K1307" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1307" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1307" s="3" t="s">
+        <v>3680</v>
+      </c>
+      <c r="N1307" s="3"/>
+    </row>
+    <row r="1308" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1308" s="3" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B1308" s="3"/>
+      <c r="C1308" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1308" s="3">
+        <v>6237337204</v>
+      </c>
+      <c r="E1308" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1308" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G1308" s="3" t="s">
+        <v>3681</v>
+      </c>
+      <c r="H1308" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1308" s="3"/>
+      <c r="J1308" s="3"/>
+      <c r="K1308" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1308" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1308" s="3" t="s">
+        <v>3680</v>
+      </c>
+      <c r="N1308" s="3"/>
+    </row>
+    <row r="1309" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1309" s="3" t="s">
+        <v>3682</v>
+      </c>
+      <c r="B1309" s="3"/>
+      <c r="C1309" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1309" s="3">
+        <v>6245349380</v>
+      </c>
+      <c r="E1309" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1309" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1309" s="3" t="s">
+        <v>3683</v>
+      </c>
+      <c r="H1309" s="3"/>
+      <c r="I1309" s="3"/>
+      <c r="J1309" s="3"/>
+      <c r="K1309" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1309" s="3"/>
+      <c r="M1309" s="3"/>
+      <c r="N1309" s="3"/>
+    </row>
+    <row r="1310" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1310" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B1310" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1310" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1310" s="3">
+        <v>6239568017</v>
+      </c>
+      <c r="E1310" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1310" s="3" t="s">
+        <v>3685</v>
+      </c>
+      <c r="G1310" s="3" t="s">
+        <v>3686</v>
+      </c>
+      <c r="H1310" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1310" s="3"/>
+      <c r="J1310" s="3"/>
+      <c r="K1310" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1310" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1310" s="3" t="s">
+        <v>3687</v>
+      </c>
+      <c r="N1310" s="3" t="s">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1311" s="3" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1311" s="3"/>
+      <c r="C1311" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1311" s="3">
+        <v>6248510844</v>
+      </c>
+      <c r="E1311" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1311" s="3" t="s">
+        <v>3690</v>
+      </c>
+      <c r="G1311" s="3" t="s">
+        <v>3691</v>
+      </c>
+      <c r="H1311" s="3"/>
+      <c r="I1311" s="3"/>
+      <c r="J1311" s="3"/>
+      <c r="K1311" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1311" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1311" s="3" t="s">
+        <v>3692</v>
+      </c>
+      <c r="N1311" s="3"/>
+    </row>
+    <row r="1312" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1312" s="3" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B1312" s="3"/>
+      <c r="C1312" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1312" s="3">
+        <v>6248562809</v>
+      </c>
+      <c r="E1312" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1312" s="3" t="s">
+        <v>3694</v>
+      </c>
+      <c r="G1312" s="3" t="s">
+        <v>3695</v>
+      </c>
+      <c r="H1312" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="I1312" s="3"/>
+      <c r="J1312" s="3"/>
+      <c r="K1312" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1312" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1312" s="3" t="s">
+        <v>3696</v>
+      </c>
+      <c r="N1312" s="3"/>
+    </row>
+    <row r="1313" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1313" s="3" t="s">
+        <v>3697</v>
+      </c>
+      <c r="B1313" s="3"/>
+      <c r="C1313" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1313" s="3">
+        <v>6249222101</v>
+      </c>
+      <c r="E1313" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1313" s="3" t="s">
+        <v>3698</v>
+      </c>
+      <c r="G1313" s="3" t="s">
+        <v>3699</v>
+      </c>
+      <c r="H1313" s="3"/>
+      <c r="I1313" s="3"/>
+      <c r="J1313" s="3"/>
+      <c r="K1313" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1313" s="3"/>
+      <c r="M1313" s="3"/>
+      <c r="N1313" s="3"/>
+    </row>
+    <row r="1314" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1314" s="3" t="s">
+        <v>3700</v>
+      </c>
+      <c r="B1314" s="3"/>
+      <c r="C1314" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1314" s="3">
+        <v>6249253766</v>
+      </c>
+      <c r="E1314" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1314" s="3" t="s">
+        <v>3701</v>
+      </c>
+      <c r="G1314" s="3" t="s">
+        <v>3702</v>
+      </c>
+      <c r="H1314" s="3"/>
+      <c r="I1314" s="3"/>
+      <c r="J1314" s="3"/>
+      <c r="K1314" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1314" s="3"/>
+      <c r="M1314" s="3"/>
+      <c r="N1314" s="3"/>
+    </row>
+    <row r="1315" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1315" s="3" t="s">
+        <v>3703</v>
+      </c>
+      <c r="B1315" s="3"/>
+      <c r="C1315" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1315" s="3">
+        <v>6249270653</v>
+      </c>
+      <c r="E1315" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1315" s="3" t="s">
+        <v>3704</v>
+      </c>
+      <c r="G1315" s="3" t="s">
+        <v>3705</v>
+      </c>
+      <c r="H1315" s="3"/>
+      <c r="I1315" s="3"/>
+      <c r="J1315" s="3"/>
+      <c r="K1315" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1315" s="3"/>
+      <c r="M1315" s="3"/>
+      <c r="N1315" s="3"/>
+    </row>
+    <row r="1316" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1316" s="3" t="s">
+        <v>3706</v>
+      </c>
+      <c r="B1316" s="3"/>
+      <c r="C1316" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1316" s="3">
+        <v>6249290274</v>
+      </c>
+      <c r="E1316" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1316" s="3" t="s">
+        <v>3707</v>
+      </c>
+      <c r="G1316" s="3" t="s">
+        <v>3708</v>
+      </c>
+      <c r="H1316" s="3"/>
+      <c r="I1316" s="3"/>
+      <c r="J1316" s="3"/>
+      <c r="K1316" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1316" s="3"/>
+      <c r="M1316" s="3"/>
+      <c r="N1316" s="3"/>
+    </row>
+    <row r="1317" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1317" s="3" t="s">
+        <v>3709</v>
+      </c>
+      <c r="B1317" s="3"/>
+      <c r="C1317" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1317" s="3">
+        <v>6249299121</v>
+      </c>
+      <c r="E1317" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1317" s="3" t="s">
+        <v>3710</v>
+      </c>
+      <c r="G1317" s="3" t="s">
+        <v>3711</v>
+      </c>
+      <c r="H1317" s="3"/>
+      <c r="I1317" s="3"/>
+      <c r="J1317" s="3"/>
+      <c r="K1317" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1317" s="3"/>
+      <c r="M1317" s="3"/>
+      <c r="N1317" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D9AC9E2-5C37-4103-BEF1-694CCA01BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{498B8D85-4B41-4B6C-B9E6-7FC3132D6164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="2895" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8019" uniqueCount="3712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8187" uniqueCount="3799">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -9247,21 +9247,21 @@
     <t>06/19/26 16:32 EDT</t>
   </si>
   <si>
+    <t>1.9mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.433548, -98.390060</t>
+  </si>
+  <si>
+    <t>06/21/26 21:00 EDT</t>
+  </si>
+  <si>
     <t>COLLISION-WARNING</t>
   </si>
   <si>
-    <t>1.9mi S of Kirby TX</t>
-  </si>
-  <si>
-    <t>29.433548, -98.390060</t>
-  </si>
-  <si>
     <t>06/22/26 13:05 EDT</t>
   </si>
   <si>
-    <t>06/21/26 21:00 EDT</t>
-  </si>
-  <si>
     <t>06/19/26 16:36 EDT</t>
   </si>
   <si>
@@ -10972,7 +10972,7 @@
     <t>29.636524, -97.729690</t>
   </si>
   <si>
-    <t>07/28/26 20:56 EDT</t>
+    <t>08/04/26 20:55 EDT</t>
   </si>
   <si>
     <t>07/28/26 13:59 EDT</t>
@@ -10999,9 +10999,6 @@
     <t>29.582280, -97.999500</t>
   </si>
   <si>
-    <t>07/30/26 08:15 EDT</t>
-  </si>
-  <si>
     <t>07/29/26 14:48 EDT</t>
   </si>
   <si>
@@ -11110,7 +11107,10 @@
     <t>29.215775, -98.802870</t>
   </si>
   <si>
-    <t>08/03/26 07:13 EDT</t>
+    <t>08/03/26 17:55 EDT</t>
+  </si>
+  <si>
+    <t>08/03/26 18:38 EDT</t>
   </si>
   <si>
     <t>08/02/26 22:03 EDT</t>
@@ -11156,6 +11156,267 @@
   </si>
   <si>
     <t>29.132158, -98.893130</t>
+  </si>
+  <si>
+    <t>08/03/26 13:03 EDT</t>
+  </si>
+  <si>
+    <t>8.5mi E of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.614721, -97.829750</t>
+  </si>
+  <si>
+    <t>08/03/26 13:59 EDT</t>
+  </si>
+  <si>
+    <t>29.503805, -98.288460</t>
+  </si>
+  <si>
+    <t>08/03/26 18:00 EDT</t>
+  </si>
+  <si>
+    <t>08/03/26 14:59 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.571743, -98.010666</t>
+  </si>
+  <si>
+    <t>08/03/26 16:59 EDT</t>
+  </si>
+  <si>
+    <t>29.502413, -98.183330</t>
+  </si>
+  <si>
+    <t>08/04/26 12:27 EDT</t>
+  </si>
+  <si>
+    <t>7.8mi NW of Fredericksburg TX</t>
+  </si>
+  <si>
+    <t>30.364586, -98.939190</t>
+  </si>
+  <si>
+    <t>08/04/26 12:53 EDT</t>
+  </si>
+  <si>
+    <t>31.5mi S of Brady TX</t>
+  </si>
+  <si>
+    <t>30.704916, -99.184570</t>
+  </si>
+  <si>
+    <t>08/04/26 13:59 EDT</t>
+  </si>
+  <si>
+    <t>13mi NW of Fredericksburg TX</t>
+  </si>
+  <si>
+    <t>30.433535, -98.973076</t>
+  </si>
+  <si>
+    <t>08/04/26 15:42 EDT</t>
+  </si>
+  <si>
+    <t>6.6mi S of Timberwood Park TX</t>
+  </si>
+  <si>
+    <t>29.606453, -98.458760</t>
+  </si>
+  <si>
+    <t>08/04/26 15:49 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi W of Selma TX</t>
+  </si>
+  <si>
+    <t>29.602657, -98.368996</t>
+  </si>
+  <si>
+    <t>08/05/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>15.3mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.363966, -98.100950</t>
+  </si>
+  <si>
+    <t>08/06/26 07:52 EDT</t>
+  </si>
+  <si>
+    <t>08/05/26 09:33 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi NW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.627094, -98.023550</t>
+  </si>
+  <si>
+    <t>08/05/26 10:53 EDT</t>
+  </si>
+  <si>
+    <t>29.492538, -98.121060</t>
+  </si>
+  <si>
+    <t>08/05/26 11:18 EDT</t>
+  </si>
+  <si>
+    <t>08/05/26 13:27 EDT</t>
+  </si>
+  <si>
+    <t>5.2mi N of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.639088, -98.213610</t>
+  </si>
+  <si>
+    <t>08/05/26 16:59 EDT</t>
+  </si>
+  <si>
+    <t>41.4mi NW of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.416855, -99.671570</t>
+  </si>
+  <si>
+    <t>08/05/26 20:02 EDT</t>
+  </si>
+  <si>
+    <t>2mi NW of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.486227, -98.402860</t>
+  </si>
+  <si>
+    <t>08/06/26 08:44 EDT</t>
+  </si>
+  <si>
+    <t>8.3mi S of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.272161, -98.574120</t>
+  </si>
+  <si>
+    <t>08/06/26 12:55 EDT</t>
+  </si>
+  <si>
+    <t>7.5mi SE of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.292131, -98.557970</t>
+  </si>
+  <si>
+    <t>08/06/26 14:02 EDT</t>
+  </si>
+  <si>
+    <t>3.5mi NE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.733608, -98.072540</t>
+  </si>
+  <si>
+    <t>08/07/26 07:43 EDT</t>
+  </si>
+  <si>
+    <t>08/06/26 14:10 EDT</t>
+  </si>
+  <si>
+    <t>4mi SW of San Marcos TX</t>
+  </si>
+  <si>
+    <t>29.831070, -97.981720</t>
+  </si>
+  <si>
+    <t>08/07/26 07:46 EDT</t>
+  </si>
+  <si>
+    <t>08/06/26 19:29 EDT</t>
+  </si>
+  <si>
+    <t>3mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>29.567762, -98.162280</t>
+  </si>
+  <si>
+    <t>08/06/26 21:15 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.569626, -98.018814</t>
+  </si>
+  <si>
+    <t>08/06/26 21:18 EDT</t>
+  </si>
+  <si>
+    <t>6.3mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>29.545012, -98.058846</t>
+  </si>
+  <si>
+    <t>08/07/26 08:53 EDT</t>
+  </si>
+  <si>
+    <t>08/07/26 10:22 EDT</t>
+  </si>
+  <si>
+    <t>28mi SE of Floresville TX</t>
+  </si>
+  <si>
+    <t>28.834064, -97.867850</t>
+  </si>
+  <si>
+    <t>08/07/26 15:29 EDT</t>
+  </si>
+  <si>
+    <t>17.1mi S of Pearsall TX</t>
+  </si>
+  <si>
+    <t>28.655476, -99.180374</t>
+  </si>
+  <si>
+    <t>08/07/26 15:59 EDT</t>
+  </si>
+  <si>
+    <t>16.2mi NE of Pearsall TX</t>
+  </si>
+  <si>
+    <t>29.090797, -98.955086</t>
+  </si>
+  <si>
+    <t>08/07/26 17:00 EDT</t>
+  </si>
+  <si>
+    <t>28.790812, -97.773094</t>
+  </si>
+  <si>
+    <t>08/07/26 21:34 EDT</t>
+  </si>
+  <si>
+    <t>08/08/26 10:33 EDT</t>
+  </si>
+  <si>
+    <t>26.4mi N of Beeville TX</t>
+  </si>
+  <si>
+    <t>28.787094, -97.766130</t>
+  </si>
+  <si>
+    <t>08/08/26 11:47 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi NW of Floresville TX</t>
+  </si>
+  <si>
+    <t>29.198547, -98.206930</t>
   </si>
 </sst>
 </file>
@@ -11517,7 +11778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1317"/>
+  <dimension ref="A1:N1345"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -35270,7 +35531,7 @@
         <v>112</v>
       </c>
       <c r="D742" s="3">
-        <v>5622402770</v>
+        <v>5622271458</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>53</v>
@@ -35300,7 +35561,7 @@
         <v>112</v>
       </c>
       <c r="D743" s="3">
-        <v>5622271458</v>
+        <v>5622402770</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>53</v>
@@ -46728,16 +46989,16 @@
         <v>112</v>
       </c>
       <c r="D1095" s="3">
-        <v>5982274613</v>
+        <v>5982274614</v>
       </c>
       <c r="E1095" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1095" s="3" t="s">
         <v>3075</v>
       </c>
-      <c r="F1095" s="3" t="s">
+      <c r="G1095" s="3" t="s">
         <v>3076</v>
-      </c>
-      <c r="G1095" s="3" t="s">
-        <v>3077</v>
       </c>
       <c r="H1095" s="3" t="s">
         <v>110</v>
@@ -46751,7 +47012,7 @@
         <v>39</v>
       </c>
       <c r="M1095" s="3" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="N1095" s="3"/>
     </row>
@@ -46764,16 +47025,16 @@
         <v>112</v>
       </c>
       <c r="D1096" s="3">
-        <v>5982274614</v>
+        <v>5982274613</v>
       </c>
       <c r="E1096" s="3" t="s">
-        <v>428</v>
+        <v>3078</v>
       </c>
       <c r="F1096" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="G1096" s="3" t="s">
         <v>3076</v>
-      </c>
-      <c r="G1096" s="3" t="s">
-        <v>3077</v>
       </c>
       <c r="H1096" s="3" t="s">
         <v>110</v>
@@ -49904,7 +50165,7 @@
         <v>71</v>
       </c>
       <c r="F1194" s="3" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="G1194" s="3" t="s">
         <v>3351</v>
@@ -53164,7 +53425,7 @@
         <v>3649</v>
       </c>
       <c r="H1295" s="3" t="s">
-        <v>110</v>
+        <v>1678</v>
       </c>
       <c r="I1295" s="3"/>
       <c r="J1295" s="3"/>
@@ -53290,7 +53551,7 @@
         <v>3658</v>
       </c>
       <c r="H1299" s="3" t="s">
-        <v>110</v>
+        <v>1678</v>
       </c>
       <c r="I1299" s="3"/>
       <c r="J1299" s="3"/>
@@ -53301,13 +53562,13 @@
         <v>39</v>
       </c>
       <c r="M1299" s="3" t="s">
-        <v>3659</v>
+        <v>3650</v>
       </c>
       <c r="N1299" s="3"/>
     </row>
     <row r="1300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1300" s="3" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="B1300" s="3"/>
       <c r="C1300" s="3">
@@ -53323,10 +53584,10 @@
         <v>47</v>
       </c>
       <c r="G1300" s="3" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="H1300" s="3" t="s">
-        <v>110</v>
+        <v>1678</v>
       </c>
       <c r="I1300" s="3"/>
       <c r="J1300" s="3"/>
@@ -53337,13 +53598,13 @@
         <v>39</v>
       </c>
       <c r="M1300" s="3" t="s">
-        <v>3659</v>
+        <v>3650</v>
       </c>
       <c r="N1300" s="3"/>
     </row>
     <row r="1301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1301" s="3" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="B1301" s="3"/>
       <c r="C1301" s="3">
@@ -53359,7 +53620,7 @@
         <v>869</v>
       </c>
       <c r="G1301" s="3" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="H1301" s="3"/>
       <c r="I1301" s="3"/>
@@ -53373,7 +53634,7 @@
     </row>
     <row r="1302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1302" s="3" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="B1302" s="3"/>
       <c r="C1302" s="3">
@@ -53389,7 +53650,7 @@
         <v>230</v>
       </c>
       <c r="G1302" s="3" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="H1302" s="3"/>
       <c r="I1302" s="3"/>
@@ -53403,7 +53664,7 @@
     </row>
     <row r="1303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1303" s="3" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="B1303" s="3"/>
       <c r="C1303" s="3">
@@ -53416,10 +53677,10 @@
         <v>80</v>
       </c>
       <c r="F1303" s="3" t="s">
+        <v>3666</v>
+      </c>
+      <c r="G1303" s="3" t="s">
         <v>3667</v>
-      </c>
-      <c r="G1303" s="3" t="s">
-        <v>3668</v>
       </c>
       <c r="H1303" s="3" t="s">
         <v>110</v>
@@ -53433,13 +53694,13 @@
         <v>39</v>
       </c>
       <c r="M1303" s="3" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="N1303" s="3"/>
     </row>
     <row r="1304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1304" s="3" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="B1304" s="3"/>
       <c r="C1304" s="3">
@@ -53455,7 +53716,7 @@
         <v>1832</v>
       </c>
       <c r="G1304" s="3" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="H1304" s="3"/>
       <c r="I1304" s="3"/>
@@ -53469,7 +53730,7 @@
     </row>
     <row r="1305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1305" s="3" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="B1305" s="3"/>
       <c r="C1305" s="3">
@@ -53485,7 +53746,7 @@
         <v>230</v>
       </c>
       <c r="G1305" s="3" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="H1305" s="3" t="s">
         <v>110</v>
@@ -53499,13 +53760,13 @@
         <v>39</v>
       </c>
       <c r="M1305" s="3" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="N1305" s="3"/>
     </row>
     <row r="1306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1306" s="3" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="B1306" s="3"/>
       <c r="C1306" s="3">
@@ -53518,10 +53779,10 @@
         <v>53</v>
       </c>
       <c r="F1306" s="3" t="s">
+        <v>3675</v>
+      </c>
+      <c r="G1306" s="3" t="s">
         <v>3676</v>
-      </c>
-      <c r="G1306" s="3" t="s">
-        <v>3677</v>
       </c>
       <c r="H1306" s="3"/>
       <c r="I1306" s="3"/>
@@ -53535,7 +53796,7 @@
     </row>
     <row r="1307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1307" s="3" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="B1307" s="3"/>
       <c r="C1307" s="3">
@@ -53551,7 +53812,7 @@
         <v>990</v>
       </c>
       <c r="G1307" s="3" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="H1307" s="3" t="s">
         <v>110</v>
@@ -53565,13 +53826,13 @@
         <v>39</v>
       </c>
       <c r="M1307" s="3" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="N1307" s="3"/>
     </row>
     <row r="1308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1308" s="3" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="B1308" s="3"/>
       <c r="C1308" s="3">
@@ -53587,7 +53848,7 @@
         <v>557</v>
       </c>
       <c r="G1308" s="3" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
       <c r="H1308" s="3" t="s">
         <v>110</v>
@@ -53601,13 +53862,13 @@
         <v>39</v>
       </c>
       <c r="M1308" s="3" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="N1308" s="3"/>
     </row>
     <row r="1309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1309" s="3" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="B1309" s="3"/>
       <c r="C1309" s="3">
@@ -53623,7 +53884,7 @@
         <v>230</v>
       </c>
       <c r="G1309" s="3" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
       <c r="H1309" s="3"/>
       <c r="I1309" s="3"/>
@@ -53637,7 +53898,7 @@
     </row>
     <row r="1310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1310" s="3" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="B1310" s="3" t="s">
         <v>62</v>
@@ -53652,10 +53913,10 @@
         <v>80</v>
       </c>
       <c r="F1310" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="G1310" s="3" t="s">
         <v>3685</v>
-      </c>
-      <c r="G1310" s="3" t="s">
-        <v>3686</v>
       </c>
       <c r="H1310" s="3" t="s">
         <v>37</v>
@@ -53669,15 +53930,15 @@
         <v>39</v>
       </c>
       <c r="M1310" s="3" t="s">
+        <v>3686</v>
+      </c>
+      <c r="N1310" s="3" t="s">
         <v>3687</v>
-      </c>
-      <c r="N1310" s="3" t="s">
-        <v>3688</v>
       </c>
     </row>
     <row r="1311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1311" s="3" t="s">
-        <v>3689</v>
+        <v>3688</v>
       </c>
       <c r="B1311" s="3"/>
       <c r="C1311" s="3">
@@ -53690,10 +53951,10 @@
         <v>80</v>
       </c>
       <c r="F1311" s="3" t="s">
+        <v>3689</v>
+      </c>
+      <c r="G1311" s="3" t="s">
         <v>3690</v>
-      </c>
-      <c r="G1311" s="3" t="s">
-        <v>3691</v>
       </c>
       <c r="H1311" s="3"/>
       <c r="I1311" s="3"/>
@@ -53705,15 +53966,17 @@
         <v>39</v>
       </c>
       <c r="M1311" s="3" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="N1311" s="3"/>
     </row>
     <row r="1312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1312" s="3" t="s">
-        <v>3693</v>
-      </c>
-      <c r="B1312" s="3"/>
+        <v>3692</v>
+      </c>
+      <c r="B1312" s="3" t="s">
+        <v>3456</v>
+      </c>
       <c r="C1312" s="3">
         <v>111</v>
       </c>
@@ -53724,13 +53987,13 @@
         <v>80</v>
       </c>
       <c r="F1312" s="3" t="s">
+        <v>3693</v>
+      </c>
+      <c r="G1312" s="3" t="s">
         <v>3694</v>
       </c>
-      <c r="G1312" s="3" t="s">
-        <v>3695</v>
-      </c>
       <c r="H1312" s="3" t="s">
-        <v>1678</v>
+        <v>37</v>
       </c>
       <c r="I1312" s="3"/>
       <c r="J1312" s="3"/>
@@ -53741,9 +54004,11 @@
         <v>39</v>
       </c>
       <c r="M1312" s="3" t="s">
+        <v>3695</v>
+      </c>
+      <c r="N1312" s="3" t="s">
         <v>3696</v>
       </c>
-      <c r="N1312" s="3"/>
     </row>
     <row r="1313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1313" s="3" t="s">
@@ -53895,6 +54160,898 @@
       <c r="M1317" s="3"/>
       <c r="N1317" s="3"/>
     </row>
+    <row r="1318" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1318" s="3" t="s">
+        <v>3712</v>
+      </c>
+      <c r="B1318" s="3"/>
+      <c r="C1318" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1318" s="3">
+        <v>6252427157</v>
+      </c>
+      <c r="E1318" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1318" s="3" t="s">
+        <v>3713</v>
+      </c>
+      <c r="G1318" s="3" t="s">
+        <v>3714</v>
+      </c>
+      <c r="H1318" s="3"/>
+      <c r="I1318" s="3"/>
+      <c r="J1318" s="3"/>
+      <c r="K1318" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1318" s="3"/>
+      <c r="M1318" s="3"/>
+      <c r="N1318" s="3"/>
+    </row>
+    <row r="1319" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1319" s="3" t="s">
+        <v>3715</v>
+      </c>
+      <c r="B1319" s="3"/>
+      <c r="C1319" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1319" s="3">
+        <v>6252909778</v>
+      </c>
+      <c r="E1319" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1319" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G1319" s="3" t="s">
+        <v>3716</v>
+      </c>
+      <c r="H1319" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1319" s="3"/>
+      <c r="J1319" s="3"/>
+      <c r="K1319" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1319" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1319" s="3" t="s">
+        <v>3717</v>
+      </c>
+      <c r="N1319" s="3"/>
+    </row>
+    <row r="1320" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1320" s="3" t="s">
+        <v>3718</v>
+      </c>
+      <c r="B1320" s="3"/>
+      <c r="C1320" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1320" s="3">
+        <v>6263491722</v>
+      </c>
+      <c r="E1320" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1320" s="3" t="s">
+        <v>3719</v>
+      </c>
+      <c r="G1320" s="3" t="s">
+        <v>3720</v>
+      </c>
+      <c r="H1320" s="3"/>
+      <c r="I1320" s="3"/>
+      <c r="J1320" s="3"/>
+      <c r="K1320" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1320" s="3"/>
+      <c r="M1320" s="3"/>
+      <c r="N1320" s="3"/>
+    </row>
+    <row r="1321" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1321" s="3" t="s">
+        <v>3721</v>
+      </c>
+      <c r="B1321" s="3"/>
+      <c r="C1321" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1321" s="3">
+        <v>6263775709</v>
+      </c>
+      <c r="E1321" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1321" s="3" t="s">
+        <v>2146</v>
+      </c>
+      <c r="G1321" s="3" t="s">
+        <v>3722</v>
+      </c>
+      <c r="H1321" s="3"/>
+      <c r="I1321" s="3"/>
+      <c r="J1321" s="3"/>
+      <c r="K1321" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1321" s="3"/>
+      <c r="M1321" s="3"/>
+      <c r="N1321" s="3"/>
+    </row>
+    <row r="1322" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1322" s="3" t="s">
+        <v>3723</v>
+      </c>
+      <c r="B1322" s="3"/>
+      <c r="C1322" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1322" s="3">
+        <v>6259132121</v>
+      </c>
+      <c r="E1322" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1322" s="3" t="s">
+        <v>3724</v>
+      </c>
+      <c r="G1322" s="3" t="s">
+        <v>3725</v>
+      </c>
+      <c r="H1322" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1322" s="3"/>
+      <c r="J1322" s="3"/>
+      <c r="K1322" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1322" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1322" s="3" t="s">
+        <v>3650</v>
+      </c>
+      <c r="N1322" s="3"/>
+    </row>
+    <row r="1323" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1323" s="3" t="s">
+        <v>3726</v>
+      </c>
+      <c r="B1323" s="3"/>
+      <c r="C1323" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1323" s="3">
+        <v>6259362876</v>
+      </c>
+      <c r="E1323" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1323" s="3" t="s">
+        <v>3727</v>
+      </c>
+      <c r="G1323" s="3" t="s">
+        <v>3728</v>
+      </c>
+      <c r="H1323" s="3"/>
+      <c r="I1323" s="3"/>
+      <c r="J1323" s="3"/>
+      <c r="K1323" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1323" s="3"/>
+      <c r="M1323" s="3"/>
+      <c r="N1323" s="3"/>
+    </row>
+    <row r="1324" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1324" s="3" t="s">
+        <v>3729</v>
+      </c>
+      <c r="B1324" s="3"/>
+      <c r="C1324" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1324" s="3">
+        <v>6270898497</v>
+      </c>
+      <c r="E1324" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1324" s="3" t="s">
+        <v>3730</v>
+      </c>
+      <c r="G1324" s="3" t="s">
+        <v>3731</v>
+      </c>
+      <c r="H1324" s="3"/>
+      <c r="I1324" s="3"/>
+      <c r="J1324" s="3"/>
+      <c r="K1324" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1324" s="3"/>
+      <c r="M1324" s="3"/>
+      <c r="N1324" s="3"/>
+    </row>
+    <row r="1325" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1325" s="3" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B1325" s="3"/>
+      <c r="C1325" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1325" s="3">
+        <v>6260883890</v>
+      </c>
+      <c r="E1325" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1325" s="3" t="s">
+        <v>3733</v>
+      </c>
+      <c r="G1325" s="3" t="s">
+        <v>3734</v>
+      </c>
+      <c r="H1325" s="3"/>
+      <c r="I1325" s="3"/>
+      <c r="J1325" s="3"/>
+      <c r="K1325" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1325" s="3"/>
+      <c r="M1325" s="3"/>
+      <c r="N1325" s="3"/>
+    </row>
+    <row r="1326" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1326" s="3" t="s">
+        <v>3735</v>
+      </c>
+      <c r="B1326" s="3"/>
+      <c r="C1326" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1326" s="3">
+        <v>6260934691</v>
+      </c>
+      <c r="E1326" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1326" s="3" t="s">
+        <v>3736</v>
+      </c>
+      <c r="G1326" s="3" t="s">
+        <v>3737</v>
+      </c>
+      <c r="H1326" s="3"/>
+      <c r="I1326" s="3"/>
+      <c r="J1326" s="3"/>
+      <c r="K1326" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1326" s="3"/>
+      <c r="M1326" s="3"/>
+      <c r="N1326" s="3"/>
+    </row>
+    <row r="1327" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1327" s="3" t="s">
+        <v>3738</v>
+      </c>
+      <c r="B1327" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1327" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1327" s="3">
+        <v>6265025587</v>
+      </c>
+      <c r="E1327" s="3" t="s">
+        <v>2371</v>
+      </c>
+      <c r="F1327" s="3" t="s">
+        <v>3739</v>
+      </c>
+      <c r="G1327" s="3" t="s">
+        <v>3740</v>
+      </c>
+      <c r="H1327" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1327" s="3"/>
+      <c r="J1327" s="3"/>
+      <c r="K1327" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1327" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1327" s="3" t="s">
+        <v>3741</v>
+      </c>
+      <c r="N1327" s="3"/>
+    </row>
+    <row r="1328" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1328" s="3" t="s">
+        <v>3742</v>
+      </c>
+      <c r="B1328" s="3"/>
+      <c r="C1328" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1328" s="3">
+        <v>6265080307</v>
+      </c>
+      <c r="E1328" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1328" s="3" t="s">
+        <v>3743</v>
+      </c>
+      <c r="G1328" s="3" t="s">
+        <v>3744</v>
+      </c>
+      <c r="H1328" s="3"/>
+      <c r="I1328" s="3"/>
+      <c r="J1328" s="3"/>
+      <c r="K1328" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1328" s="3"/>
+      <c r="M1328" s="3"/>
+      <c r="N1328" s="3"/>
+    </row>
+    <row r="1329" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1329" s="3" t="s">
+        <v>3745</v>
+      </c>
+      <c r="B1329" s="3"/>
+      <c r="C1329" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1329" s="3">
+        <v>6265580906</v>
+      </c>
+      <c r="E1329" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1329" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G1329" s="3" t="s">
+        <v>3746</v>
+      </c>
+      <c r="H1329" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1329" s="3"/>
+      <c r="J1329" s="3"/>
+      <c r="K1329" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1329" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1329" s="3" t="s">
+        <v>3747</v>
+      </c>
+      <c r="N1329" s="3"/>
+    </row>
+    <row r="1330" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1330" s="3" t="s">
+        <v>3748</v>
+      </c>
+      <c r="B1330" s="3"/>
+      <c r="C1330" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1330" s="3">
+        <v>6266882286</v>
+      </c>
+      <c r="E1330" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1330" s="3" t="s">
+        <v>3749</v>
+      </c>
+      <c r="G1330" s="3" t="s">
+        <v>3750</v>
+      </c>
+      <c r="H1330" s="3"/>
+      <c r="I1330" s="3"/>
+      <c r="J1330" s="3"/>
+      <c r="K1330" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1330" s="3"/>
+      <c r="M1330" s="3"/>
+      <c r="N1330" s="3"/>
+    </row>
+    <row r="1331" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1331" s="3" t="s">
+        <v>3751</v>
+      </c>
+      <c r="B1331" s="3"/>
+      <c r="C1331" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1331" s="3">
+        <v>6277977155</v>
+      </c>
+      <c r="E1331" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1331" s="3" t="s">
+        <v>3752</v>
+      </c>
+      <c r="G1331" s="3" t="s">
+        <v>3753</v>
+      </c>
+      <c r="H1331" s="3"/>
+      <c r="I1331" s="3"/>
+      <c r="J1331" s="3"/>
+      <c r="K1331" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1331" s="3"/>
+      <c r="M1331" s="3"/>
+      <c r="N1331" s="3"/>
+    </row>
+    <row r="1332" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1332" s="3" t="s">
+        <v>3754</v>
+      </c>
+      <c r="B1332" s="3"/>
+      <c r="C1332" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1332" s="3">
+        <v>6269974762</v>
+      </c>
+      <c r="E1332" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1332" s="3" t="s">
+        <v>3755</v>
+      </c>
+      <c r="G1332" s="3" t="s">
+        <v>3756</v>
+      </c>
+      <c r="H1332" s="3"/>
+      <c r="I1332" s="3"/>
+      <c r="J1332" s="3"/>
+      <c r="K1332" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1332" s="3"/>
+      <c r="M1332" s="3"/>
+      <c r="N1332" s="3"/>
+    </row>
+    <row r="1333" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1333" s="3" t="s">
+        <v>3757</v>
+      </c>
+      <c r="B1333" s="3"/>
+      <c r="C1333" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1333" s="3">
+        <v>6272071925</v>
+      </c>
+      <c r="E1333" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1333" s="3" t="s">
+        <v>3758</v>
+      </c>
+      <c r="G1333" s="3" t="s">
+        <v>3759</v>
+      </c>
+      <c r="H1333" s="3"/>
+      <c r="I1333" s="3"/>
+      <c r="J1333" s="3"/>
+      <c r="K1333" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1333" s="3"/>
+      <c r="M1333" s="3"/>
+      <c r="N1333" s="3"/>
+    </row>
+    <row r="1334" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1334" s="3" t="s">
+        <v>3760</v>
+      </c>
+      <c r="B1334" s="3"/>
+      <c r="C1334" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1334" s="3">
+        <v>6273858561</v>
+      </c>
+      <c r="E1334" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1334" s="3" t="s">
+        <v>3761</v>
+      </c>
+      <c r="G1334" s="3" t="s">
+        <v>3762</v>
+      </c>
+      <c r="H1334" s="3"/>
+      <c r="I1334" s="3"/>
+      <c r="J1334" s="3"/>
+      <c r="K1334" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1334" s="3"/>
+      <c r="M1334" s="3"/>
+      <c r="N1334" s="3"/>
+    </row>
+    <row r="1335" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1335" s="3" t="s">
+        <v>3763</v>
+      </c>
+      <c r="B1335" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1335" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1335" s="3">
+        <v>6274453367</v>
+      </c>
+      <c r="E1335" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1335" s="3" t="s">
+        <v>3764</v>
+      </c>
+      <c r="G1335" s="3" t="s">
+        <v>3765</v>
+      </c>
+      <c r="H1335" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1335" s="3"/>
+      <c r="J1335" s="3"/>
+      <c r="K1335" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1335" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1335" s="3" t="s">
+        <v>3766</v>
+      </c>
+      <c r="N1335" s="3"/>
+    </row>
+    <row r="1336" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1336" s="3" t="s">
+        <v>3767</v>
+      </c>
+      <c r="B1336" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1336" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1336" s="3">
+        <v>6274525700</v>
+      </c>
+      <c r="E1336" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1336" s="3" t="s">
+        <v>3768</v>
+      </c>
+      <c r="G1336" s="3" t="s">
+        <v>3769</v>
+      </c>
+      <c r="H1336" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1336" s="3"/>
+      <c r="J1336" s="3"/>
+      <c r="K1336" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1336" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1336" s="3" t="s">
+        <v>3770</v>
+      </c>
+      <c r="N1336" s="3"/>
+    </row>
+    <row r="1337" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1337" s="3" t="s">
+        <v>3771</v>
+      </c>
+      <c r="B1337" s="3"/>
+      <c r="C1337" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1337" s="3">
+        <v>6284567772</v>
+      </c>
+      <c r="E1337" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1337" s="3" t="s">
+        <v>3772</v>
+      </c>
+      <c r="G1337" s="3" t="s">
+        <v>3773</v>
+      </c>
+      <c r="H1337" s="3"/>
+      <c r="I1337" s="3"/>
+      <c r="J1337" s="3"/>
+      <c r="K1337" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1337" s="3"/>
+      <c r="M1337" s="3"/>
+      <c r="N1337" s="3"/>
+    </row>
+    <row r="1338" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1338" s="3" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B1338" s="3"/>
+      <c r="C1338" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1338" s="3">
+        <v>6277432874</v>
+      </c>
+      <c r="E1338" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1338" s="3" t="s">
+        <v>3775</v>
+      </c>
+      <c r="G1338" s="3" t="s">
+        <v>3776</v>
+      </c>
+      <c r="H1338" s="3"/>
+      <c r="I1338" s="3"/>
+      <c r="J1338" s="3"/>
+      <c r="K1338" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1338" s="3"/>
+      <c r="M1338" s="3"/>
+      <c r="N1338" s="3"/>
+    </row>
+    <row r="1339" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1339" s="3" t="s">
+        <v>3777</v>
+      </c>
+      <c r="B1339" s="3"/>
+      <c r="C1339" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1339" s="3">
+        <v>6277442024</v>
+      </c>
+      <c r="E1339" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1339" s="3" t="s">
+        <v>3778</v>
+      </c>
+      <c r="G1339" s="3" t="s">
+        <v>3779</v>
+      </c>
+      <c r="H1339" s="3"/>
+      <c r="I1339" s="3"/>
+      <c r="J1339" s="3"/>
+      <c r="K1339" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1339" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1339" s="3" t="s">
+        <v>3780</v>
+      </c>
+      <c r="N1339" s="3"/>
+    </row>
+    <row r="1340" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1340" s="3" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B1340" s="3"/>
+      <c r="C1340" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1340" s="3">
+        <v>6279742775</v>
+      </c>
+      <c r="E1340" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1340" s="3" t="s">
+        <v>3782</v>
+      </c>
+      <c r="G1340" s="3" t="s">
+        <v>3783</v>
+      </c>
+      <c r="H1340" s="3"/>
+      <c r="I1340" s="3"/>
+      <c r="J1340" s="3"/>
+      <c r="K1340" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1340" s="3"/>
+      <c r="M1340" s="3"/>
+      <c r="N1340" s="3"/>
+    </row>
+    <row r="1341" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1341" s="3" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B1341" s="3"/>
+      <c r="C1341" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1341" s="3">
+        <v>6289278890</v>
+      </c>
+      <c r="E1341" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1341" s="3" t="s">
+        <v>3785</v>
+      </c>
+      <c r="G1341" s="3" t="s">
+        <v>3786</v>
+      </c>
+      <c r="H1341" s="3"/>
+      <c r="I1341" s="3"/>
+      <c r="J1341" s="3"/>
+      <c r="K1341" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1341" s="3"/>
+      <c r="M1341" s="3"/>
+      <c r="N1341" s="3"/>
+    </row>
+    <row r="1342" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1342" s="3" t="s">
+        <v>3787</v>
+      </c>
+      <c r="B1342" s="3"/>
+      <c r="C1342" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1342" s="3">
+        <v>6289116067</v>
+      </c>
+      <c r="E1342" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1342" s="3" t="s">
+        <v>3788</v>
+      </c>
+      <c r="G1342" s="3" t="s">
+        <v>3789</v>
+      </c>
+      <c r="H1342" s="3"/>
+      <c r="I1342" s="3"/>
+      <c r="J1342" s="3"/>
+      <c r="K1342" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1342" s="3"/>
+      <c r="M1342" s="3"/>
+      <c r="N1342" s="3"/>
+    </row>
+    <row r="1343" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1343" s="3" t="s">
+        <v>3790</v>
+      </c>
+      <c r="B1343" s="3"/>
+      <c r="C1343" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1343" s="3">
+        <v>6282853132</v>
+      </c>
+      <c r="E1343" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1343" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G1343" s="3" t="s">
+        <v>3791</v>
+      </c>
+      <c r="H1343" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1343" s="3"/>
+      <c r="J1343" s="3"/>
+      <c r="K1343" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1343" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1343" s="3" t="s">
+        <v>3792</v>
+      </c>
+      <c r="N1343" s="3"/>
+    </row>
+    <row r="1344" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1344" s="3" t="s">
+        <v>3793</v>
+      </c>
+      <c r="B1344" s="3"/>
+      <c r="C1344" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1344" s="3">
+        <v>6285690638</v>
+      </c>
+      <c r="E1344" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1344" s="3" t="s">
+        <v>3794</v>
+      </c>
+      <c r="G1344" s="3" t="s">
+        <v>3795</v>
+      </c>
+      <c r="H1344" s="3"/>
+      <c r="I1344" s="3"/>
+      <c r="J1344" s="3"/>
+      <c r="K1344" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1344" s="3"/>
+      <c r="M1344" s="3"/>
+      <c r="N1344" s="3"/>
+    </row>
+    <row r="1345" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1345" s="3" t="s">
+        <v>3796</v>
+      </c>
+      <c r="B1345" s="3"/>
+      <c r="C1345" s="3">
+        <v>111</v>
+      </c>
+      <c r="D1345" s="3">
+        <v>6286015689</v>
+      </c>
+      <c r="E1345" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1345" s="3" t="s">
+        <v>3797</v>
+      </c>
+      <c r="G1345" s="3" t="s">
+        <v>3798</v>
+      </c>
+      <c r="H1345" s="3"/>
+      <c r="I1345" s="3"/>
+      <c r="J1345" s="3"/>
+      <c r="K1345" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1345" s="3"/>
+      <c r="M1345" s="3"/>
+      <c r="N1345" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E80DF06-B633-4BDE-9E3E-B13C81126AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DA56798-0BD5-41F3-A6D4-25544361CE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8421" uniqueCount="3899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8534" uniqueCount="3955">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
   <si>
-    <t>Period: 01/01/26 00:00 CST - 12/31/26 23:59 CST</t>
+    <t>Period: 01/01/26 02:00 CST - 01/01/27 23:59 CST</t>
   </si>
   <si>
     <t>Datetime</t>
@@ -9247,21 +9247,21 @@
     <t>06/19/26 15:32 CDT</t>
   </si>
   <si>
+    <t>1.9mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.433548, -98.390060</t>
+  </si>
+  <si>
+    <t>06/21/26 20:00 CDT</t>
+  </si>
+  <si>
     <t>COLLISION-WARNING</t>
   </si>
   <si>
-    <t>1.9mi S of Kirby TX</t>
-  </si>
-  <si>
-    <t>29.433548, -98.390060</t>
-  </si>
-  <si>
     <t>06/22/26 12:05 CDT</t>
   </si>
   <si>
-    <t>06/21/26 20:00 CDT</t>
-  </si>
-  <si>
     <t>06/19/26 15:36 CDT</t>
   </si>
   <si>
@@ -11717,6 +11717,174 @@
   </si>
   <si>
     <t>29.525301, -98.393654</t>
+  </si>
+  <si>
+    <t>08/24/26 18:20 CDT</t>
+  </si>
+  <si>
+    <t>5.2mi SE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.635450, -98.069980</t>
+  </si>
+  <si>
+    <t>08/25/26 13:59 CDT</t>
+  </si>
+  <si>
+    <t>29.427385, -98.418144</t>
+  </si>
+  <si>
+    <t>08/25/26 16:07 CDT</t>
+  </si>
+  <si>
+    <t>1.8mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.444784, -98.362206</t>
+  </si>
+  <si>
+    <t>08/25/26 18:01 CDT</t>
+  </si>
+  <si>
+    <t>12.5mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>29.358002, -98.194145</t>
+  </si>
+  <si>
+    <t>08/25/26 22:47 CDT</t>
+  </si>
+  <si>
+    <t>08/25/26 18:28 CDT</t>
+  </si>
+  <si>
+    <t>7.9mi SE of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.320340, -98.511870</t>
+  </si>
+  <si>
+    <t>08/25/26 18:29 CDT</t>
+  </si>
+  <si>
+    <t>7.6mi SW of Sinton TX</t>
+  </si>
+  <si>
+    <t>27.949638, -97.586820</t>
+  </si>
+  <si>
+    <t>08/25/26 18:45 CDT</t>
+  </si>
+  <si>
+    <t>27.949144, -97.587860</t>
+  </si>
+  <si>
+    <t>08/25/26 20:29 CDT</t>
+  </si>
+  <si>
+    <t>12.6mi N of Pleasanton TX</t>
+  </si>
+  <si>
+    <t>29.137370, -98.429160</t>
+  </si>
+  <si>
+    <t>08/27/26 17:16 CDT</t>
+  </si>
+  <si>
+    <t>29.539783, -98.072220</t>
+  </si>
+  <si>
+    <t>08/27/26 17:35 CDT</t>
+  </si>
+  <si>
+    <t>29.482447, -98.239870</t>
+  </si>
+  <si>
+    <t>08/27/26 20:49 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 08:06 CDT</t>
+  </si>
+  <si>
+    <t>29.652890, -98.149320</t>
+  </si>
+  <si>
+    <t>08/28/26 10:33 CDT</t>
+  </si>
+  <si>
+    <t>0.9mi SE of Boerne TX</t>
+  </si>
+  <si>
+    <t>29.777071, -98.717340</t>
+  </si>
+  <si>
+    <t>08/28/26 10:34 CDT</t>
+  </si>
+  <si>
+    <t>3.5mi SE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.678326, -98.061080</t>
+  </si>
+  <si>
+    <t>08/28/26 23:31 CDT</t>
+  </si>
+  <si>
+    <t>08/28/26 11:48 CDT</t>
+  </si>
+  <si>
+    <t>6.4mi S of Timberwood Park TX</t>
+  </si>
+  <si>
+    <t>29.608395, -98.500220</t>
+  </si>
+  <si>
+    <t>08/28/26 12:59 CDT</t>
+  </si>
+  <si>
+    <t>2.9mi NE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.728724, -98.079570</t>
+  </si>
+  <si>
+    <t>08/28/26 14:58 CDT</t>
+  </si>
+  <si>
+    <t>29.444738, -98.360790</t>
+  </si>
+  <si>
+    <t>08/28/26 15:33 CDT</t>
+  </si>
+  <si>
+    <t>29.491102, -98.290380</t>
+  </si>
+  <si>
+    <t>08/29/26 10:17 CDT</t>
+  </si>
+  <si>
+    <t>5.2mi SE of San Antonio TX</t>
+  </si>
+  <si>
+    <t>29.395082, -98.488850</t>
+  </si>
+  <si>
+    <t>08/30/26 10:04 CDT</t>
+  </si>
+  <si>
+    <t>2.7mi S of Terrell Hills TX</t>
+  </si>
+  <si>
+    <t>29.438778, -98.457500</t>
+  </si>
+  <si>
+    <t>08/30/26 10:25 CDT</t>
+  </si>
+  <si>
+    <t>3.3mi SE of Scenic Oaks TX</t>
+  </si>
+  <si>
+    <t>29.666096, -98.637110</t>
   </si>
 </sst>
 </file>
@@ -12078,7 +12246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1380"/>
+  <dimension ref="A1:N1400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -35831,7 +35999,7 @@
         <v>112</v>
       </c>
       <c r="D742" s="3">
-        <v>5622271458</v>
+        <v>5622402770</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>53</v>
@@ -35861,7 +36029,7 @@
         <v>112</v>
       </c>
       <c r="D743" s="3">
-        <v>5622402770</v>
+        <v>5622271458</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>53</v>
@@ -47289,16 +47457,16 @@
         <v>112</v>
       </c>
       <c r="D1095" s="3">
-        <v>5982274613</v>
+        <v>5982274614</v>
       </c>
       <c r="E1095" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1095" s="3" t="s">
         <v>3075</v>
       </c>
-      <c r="F1095" s="3" t="s">
+      <c r="G1095" s="3" t="s">
         <v>3076</v>
-      </c>
-      <c r="G1095" s="3" t="s">
-        <v>3077</v>
       </c>
       <c r="H1095" s="3" t="s">
         <v>110</v>
@@ -47312,7 +47480,7 @@
         <v>39</v>
       </c>
       <c r="M1095" s="3" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="N1095" s="3"/>
     </row>
@@ -47325,16 +47493,16 @@
         <v>112</v>
       </c>
       <c r="D1096" s="3">
-        <v>5982274614</v>
+        <v>5982274613</v>
       </c>
       <c r="E1096" s="3" t="s">
-        <v>428</v>
+        <v>3078</v>
       </c>
       <c r="F1096" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="G1096" s="3" t="s">
         <v>3076</v>
-      </c>
-      <c r="G1096" s="3" t="s">
-        <v>3077</v>
       </c>
       <c r="H1096" s="3" t="s">
         <v>110</v>
@@ -50465,7 +50633,7 @@
         <v>71</v>
       </c>
       <c r="F1194" s="3" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="G1194" s="3" t="s">
         <v>3351</v>
@@ -56520,6 +56688,640 @@
       <c r="M1380" s="3"/>
       <c r="N1380" s="3"/>
     </row>
+    <row r="1381" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1381" s="3" t="s">
+        <v>3899</v>
+      </c>
+      <c r="B1381" s="3"/>
+      <c r="C1381" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1381" s="3">
+        <v>6385968848</v>
+      </c>
+      <c r="E1381" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F1381" s="3" t="s">
+        <v>3900</v>
+      </c>
+      <c r="G1381" s="3" t="s">
+        <v>3901</v>
+      </c>
+      <c r="H1381" s="3"/>
+      <c r="I1381" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1381" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1381" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1381" s="3"/>
+      <c r="M1381" s="3"/>
+      <c r="N1381" s="3"/>
+    </row>
+    <row r="1382" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1382" s="3" t="s">
+        <v>3902</v>
+      </c>
+      <c r="B1382" s="3"/>
+      <c r="C1382" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1382" s="3">
+        <v>6401486598</v>
+      </c>
+      <c r="E1382" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1382" s="3" t="s">
+        <v>2140</v>
+      </c>
+      <c r="G1382" s="3" t="s">
+        <v>3903</v>
+      </c>
+      <c r="H1382" s="3"/>
+      <c r="I1382" s="3"/>
+      <c r="J1382" s="3"/>
+      <c r="K1382" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1382" s="3"/>
+      <c r="M1382" s="3"/>
+      <c r="N1382" s="3"/>
+    </row>
+    <row r="1383" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1383" s="3" t="s">
+        <v>3904</v>
+      </c>
+      <c r="B1383" s="3"/>
+      <c r="C1383" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1383" s="3">
+        <v>6392189080</v>
+      </c>
+      <c r="E1383" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1383" s="3" t="s">
+        <v>3905</v>
+      </c>
+      <c r="G1383" s="3" t="s">
+        <v>3906</v>
+      </c>
+      <c r="H1383" s="3"/>
+      <c r="I1383" s="3"/>
+      <c r="J1383" s="3"/>
+      <c r="K1383" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1383" s="3"/>
+      <c r="M1383" s="3"/>
+      <c r="N1383" s="3"/>
+    </row>
+    <row r="1384" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1384" s="3" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B1384" s="3"/>
+      <c r="C1384" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1384" s="3">
+        <v>6392979984</v>
+      </c>
+      <c r="E1384" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1384" s="3" t="s">
+        <v>3908</v>
+      </c>
+      <c r="G1384" s="3" t="s">
+        <v>3909</v>
+      </c>
+      <c r="H1384" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1384" s="3"/>
+      <c r="J1384" s="3"/>
+      <c r="K1384" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1384" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1384" s="3" t="s">
+        <v>3910</v>
+      </c>
+      <c r="N1384" s="3"/>
+    </row>
+    <row r="1385" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1385" s="3" t="s">
+        <v>3911</v>
+      </c>
+      <c r="B1385" s="3"/>
+      <c r="C1385" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1385" s="3">
+        <v>6393148228</v>
+      </c>
+      <c r="E1385" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1385" s="3" t="s">
+        <v>3912</v>
+      </c>
+      <c r="G1385" s="3" t="s">
+        <v>3913</v>
+      </c>
+      <c r="H1385" s="3"/>
+      <c r="I1385" s="3"/>
+      <c r="J1385" s="3"/>
+      <c r="K1385" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1385" s="3"/>
+      <c r="M1385" s="3"/>
+      <c r="N1385" s="3"/>
+    </row>
+    <row r="1386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1386" s="3" t="s">
+        <v>3914</v>
+      </c>
+      <c r="B1386" s="3"/>
+      <c r="C1386" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1386" s="3">
+        <v>6401365014</v>
+      </c>
+      <c r="E1386" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1386" s="3" t="s">
+        <v>3915</v>
+      </c>
+      <c r="G1386" s="3" t="s">
+        <v>3916</v>
+      </c>
+      <c r="H1386" s="3"/>
+      <c r="I1386" s="3"/>
+      <c r="J1386" s="3"/>
+      <c r="K1386" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1386" s="3"/>
+      <c r="M1386" s="3"/>
+      <c r="N1386" s="3"/>
+    </row>
+    <row r="1387" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1387" s="3" t="s">
+        <v>3917</v>
+      </c>
+      <c r="B1387" s="3"/>
+      <c r="C1387" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1387" s="3">
+        <v>6393235306</v>
+      </c>
+      <c r="E1387" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1387" s="3" t="s">
+        <v>3915</v>
+      </c>
+      <c r="G1387" s="3" t="s">
+        <v>3918</v>
+      </c>
+      <c r="H1387" s="3"/>
+      <c r="I1387" s="3"/>
+      <c r="J1387" s="3"/>
+      <c r="K1387" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1387" s="3"/>
+      <c r="M1387" s="3"/>
+      <c r="N1387" s="3"/>
+    </row>
+    <row r="1388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1388" s="3" t="s">
+        <v>3919</v>
+      </c>
+      <c r="B1388" s="3"/>
+      <c r="C1388" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1388" s="3">
+        <v>6401569211</v>
+      </c>
+      <c r="E1388" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1388" s="3" t="s">
+        <v>3920</v>
+      </c>
+      <c r="G1388" s="3" t="s">
+        <v>3921</v>
+      </c>
+      <c r="H1388" s="3"/>
+      <c r="I1388" s="3"/>
+      <c r="J1388" s="3"/>
+      <c r="K1388" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1388" s="3"/>
+      <c r="M1388" s="3"/>
+      <c r="N1388" s="3"/>
+    </row>
+    <row r="1389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1389" s="3" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B1389" s="3"/>
+      <c r="C1389" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1389" s="3">
+        <v>6407436213</v>
+      </c>
+      <c r="E1389" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1389" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="G1389" s="3" t="s">
+        <v>3923</v>
+      </c>
+      <c r="H1389" s="3"/>
+      <c r="I1389" s="3"/>
+      <c r="J1389" s="3"/>
+      <c r="K1389" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1389" s="3"/>
+      <c r="M1389" s="3"/>
+      <c r="N1389" s="3"/>
+    </row>
+    <row r="1390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1390" s="3" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B1390" s="3" t="s">
+        <v>3456</v>
+      </c>
+      <c r="C1390" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1390" s="3">
+        <v>6407571856</v>
+      </c>
+      <c r="E1390" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1390" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="G1390" s="3" t="s">
+        <v>3925</v>
+      </c>
+      <c r="H1390" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1390" s="3"/>
+      <c r="J1390" s="3"/>
+      <c r="K1390" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1390" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1390" s="3" t="s">
+        <v>3926</v>
+      </c>
+      <c r="N1390" s="3"/>
+    </row>
+    <row r="1391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1391" s="3" t="s">
+        <v>3927</v>
+      </c>
+      <c r="B1391" s="3"/>
+      <c r="C1391" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1391" s="3">
+        <v>6410240693</v>
+      </c>
+      <c r="E1391" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F1391" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1391" s="3" t="s">
+        <v>3928</v>
+      </c>
+      <c r="H1391" s="3"/>
+      <c r="I1391" s="3">
+        <v>43</v>
+      </c>
+      <c r="J1391" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1391" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1391" s="3"/>
+      <c r="M1391" s="3"/>
+      <c r="N1391" s="3"/>
+    </row>
+    <row r="1392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1392" s="3" t="s">
+        <v>3929</v>
+      </c>
+      <c r="B1392" s="3"/>
+      <c r="C1392" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1392" s="3">
+        <v>6411199130</v>
+      </c>
+      <c r="E1392" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1392" s="3" t="s">
+        <v>3930</v>
+      </c>
+      <c r="G1392" s="3" t="s">
+        <v>3931</v>
+      </c>
+      <c r="H1392" s="3"/>
+      <c r="I1392" s="3"/>
+      <c r="J1392" s="3"/>
+      <c r="K1392" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1392" s="3"/>
+      <c r="M1392" s="3"/>
+      <c r="N1392" s="3"/>
+    </row>
+    <row r="1393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1393" s="3" t="s">
+        <v>3932</v>
+      </c>
+      <c r="B1393" s="3"/>
+      <c r="C1393" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1393" s="3">
+        <v>6411205718</v>
+      </c>
+      <c r="E1393" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1393" s="3" t="s">
+        <v>3933</v>
+      </c>
+      <c r="G1393" s="3" t="s">
+        <v>3934</v>
+      </c>
+      <c r="H1393" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1393" s="3"/>
+      <c r="J1393" s="3"/>
+      <c r="K1393" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1393" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1393" s="3" t="s">
+        <v>3935</v>
+      </c>
+      <c r="N1393" s="3"/>
+    </row>
+    <row r="1394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1394" s="3" t="s">
+        <v>3936</v>
+      </c>
+      <c r="B1394" s="3"/>
+      <c r="C1394" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1394" s="3">
+        <v>6411851506</v>
+      </c>
+      <c r="E1394" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1394" s="3" t="s">
+        <v>3937</v>
+      </c>
+      <c r="G1394" s="3" t="s">
+        <v>3938</v>
+      </c>
+      <c r="H1394" s="3"/>
+      <c r="I1394" s="3"/>
+      <c r="J1394" s="3"/>
+      <c r="K1394" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1394" s="3"/>
+      <c r="M1394" s="3"/>
+      <c r="N1394" s="3"/>
+    </row>
+    <row r="1395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1395" s="3" t="s">
+        <v>3939</v>
+      </c>
+      <c r="B1395" s="3"/>
+      <c r="C1395" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1395" s="3">
+        <v>6420573690</v>
+      </c>
+      <c r="E1395" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1395" s="3" t="s">
+        <v>3940</v>
+      </c>
+      <c r="G1395" s="3" t="s">
+        <v>3941</v>
+      </c>
+      <c r="H1395" s="3"/>
+      <c r="I1395" s="3"/>
+      <c r="J1395" s="3"/>
+      <c r="K1395" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1395" s="3"/>
+      <c r="M1395" s="3"/>
+      <c r="N1395" s="3"/>
+    </row>
+    <row r="1396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1396" s="3" t="s">
+        <v>3942</v>
+      </c>
+      <c r="B1396" s="3"/>
+      <c r="C1396" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1396" s="3">
+        <v>6413547384</v>
+      </c>
+      <c r="E1396" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1396" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G1396" s="3" t="s">
+        <v>3943</v>
+      </c>
+      <c r="H1396" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1396" s="3"/>
+      <c r="J1396" s="3"/>
+      <c r="K1396" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1396" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1396" s="3" t="s">
+        <v>3935</v>
+      </c>
+      <c r="N1396" s="3"/>
+    </row>
+    <row r="1397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1397" s="3" t="s">
+        <v>3944</v>
+      </c>
+      <c r="B1397" s="3"/>
+      <c r="C1397" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1397" s="3">
+        <v>6413829206</v>
+      </c>
+      <c r="E1397" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1397" s="3" t="s">
+        <v>2328</v>
+      </c>
+      <c r="G1397" s="3" t="s">
+        <v>3945</v>
+      </c>
+      <c r="H1397" s="3"/>
+      <c r="I1397" s="3"/>
+      <c r="J1397" s="3"/>
+      <c r="K1397" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1397" s="3"/>
+      <c r="M1397" s="3"/>
+      <c r="N1397" s="3"/>
+    </row>
+    <row r="1398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1398" s="3" t="s">
+        <v>3946</v>
+      </c>
+      <c r="B1398" s="3"/>
+      <c r="C1398" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1398" s="3">
+        <v>6417279173</v>
+      </c>
+      <c r="E1398" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1398" s="3" t="s">
+        <v>3947</v>
+      </c>
+      <c r="G1398" s="3" t="s">
+        <v>3948</v>
+      </c>
+      <c r="H1398" s="3"/>
+      <c r="I1398" s="3"/>
+      <c r="J1398" s="3"/>
+      <c r="K1398" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1398" s="3"/>
+      <c r="M1398" s="3"/>
+      <c r="N1398" s="3"/>
+    </row>
+    <row r="1399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1399" s="3" t="s">
+        <v>3949</v>
+      </c>
+      <c r="B1399" s="3"/>
+      <c r="C1399" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1399" s="3">
+        <v>6421568932</v>
+      </c>
+      <c r="E1399" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1399" s="3" t="s">
+        <v>3950</v>
+      </c>
+      <c r="G1399" s="3" t="s">
+        <v>3951</v>
+      </c>
+      <c r="H1399" s="3"/>
+      <c r="I1399" s="3"/>
+      <c r="J1399" s="3"/>
+      <c r="K1399" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1399" s="3"/>
+      <c r="M1399" s="3"/>
+      <c r="N1399" s="3"/>
+    </row>
+    <row r="1400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1400" s="3" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B1400" s="3"/>
+      <c r="C1400" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1400" s="3">
+        <v>6421652092</v>
+      </c>
+      <c r="E1400" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1400" s="3" t="s">
+        <v>3953</v>
+      </c>
+      <c r="G1400" s="3" t="s">
+        <v>3954</v>
+      </c>
+      <c r="H1400" s="3"/>
+      <c r="I1400" s="3"/>
+      <c r="J1400" s="3"/>
+      <c r="K1400" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1400" s="3"/>
+      <c r="M1400" s="3"/>
+      <c r="N1400" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mott-s-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DA56798-0BD5-41F3-A6D4-25544361CE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BB1B032-698E-42EA-ACD6-68EBDC5237F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8534" uniqueCount="3955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8661" uniqueCount="4013">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
   <si>
-    <t>Period: 01/01/26 02:00 CST - 01/01/27 23:59 CST</t>
+    <t>Period: 01/01/26 00:00 CST - 12/31/26 23:59 CST</t>
   </si>
   <si>
     <t>Datetime</t>
@@ -9247,21 +9247,21 @@
     <t>06/19/26 15:32 CDT</t>
   </si>
   <si>
+    <t>COLLISION-WARNING</t>
+  </si>
+  <si>
     <t>1.9mi S of Kirby TX</t>
   </si>
   <si>
     <t>29.433548, -98.390060</t>
   </si>
   <si>
+    <t>06/22/26 12:05 CDT</t>
+  </si>
+  <si>
     <t>06/21/26 20:00 CDT</t>
   </si>
   <si>
-    <t>COLLISION-WARNING</t>
-  </si>
-  <si>
-    <t>06/22/26 12:05 CDT</t>
-  </si>
-  <si>
     <t>06/19/26 15:36 CDT</t>
   </si>
   <si>
@@ -11885,6 +11885,180 @@
   </si>
   <si>
     <t>29.666096, -98.637110</t>
+  </si>
+  <si>
+    <t>08/31/26 09:58 CDT</t>
+  </si>
+  <si>
+    <t>29.497162, -98.195330</t>
+  </si>
+  <si>
+    <t>08/31/26 18:09 CDT</t>
+  </si>
+  <si>
+    <t>08/31/26 16:59 CDT</t>
+  </si>
+  <si>
+    <t>14mi SE of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.217123, -98.489560</t>
+  </si>
+  <si>
+    <t>09/01/26 10:52 CDT</t>
+  </si>
+  <si>
+    <t>5.4mi NE of Hondo TX</t>
+  </si>
+  <si>
+    <t>29.422579, -99.119460</t>
+  </si>
+  <si>
+    <t>09/01/26 18:23 CDT</t>
+  </si>
+  <si>
+    <t>09/01/26 10:55 CDT</t>
+  </si>
+  <si>
+    <t>5.3mi NE of Hondo TX</t>
+  </si>
+  <si>
+    <t>29.422575, -99.125084</t>
+  </si>
+  <si>
+    <t>09/01/26 12:24 CDT</t>
+  </si>
+  <si>
+    <t>29.401562, -98.459170</t>
+  </si>
+  <si>
+    <t>09/01/26 12:26 CDT</t>
+  </si>
+  <si>
+    <t>4.7mi SW of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.409971, -98.435370</t>
+  </si>
+  <si>
+    <t>09/02/26 06:51 CDT</t>
+  </si>
+  <si>
+    <t>4.7mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>29.395079, -98.368010</t>
+  </si>
+  <si>
+    <t>09/02/26 09:28 CDT</t>
+  </si>
+  <si>
+    <t>4.8mi NE of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>29.747492, -98.057920</t>
+  </si>
+  <si>
+    <t>09/02/26 18:28 CDT</t>
+  </si>
+  <si>
+    <t>09/02/26 13:23 CDT</t>
+  </si>
+  <si>
+    <t>7.3mi E of Helotes TX</t>
+  </si>
+  <si>
+    <t>29.603870, -98.581150</t>
+  </si>
+  <si>
+    <t>09/02/26 14:29 CDT</t>
+  </si>
+  <si>
+    <t>1.8mi NE of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.407484, -98.600670</t>
+  </si>
+  <si>
+    <t>09/02/26 14:30 CDT</t>
+  </si>
+  <si>
+    <t>1.2mi N of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.403625, -98.622700</t>
+  </si>
+  <si>
+    <t>09/03/26 05:59 CDT</t>
+  </si>
+  <si>
+    <t>16.3mi SW of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>29.214745, -98.804220</t>
+  </si>
+  <si>
+    <t>09/03/26 08:34 CDT</t>
+  </si>
+  <si>
+    <t>29.495039, -98.203880</t>
+  </si>
+  <si>
+    <t>09/03/26 22:00 CDT</t>
+  </si>
+  <si>
+    <t>09/03/26 10:14 CDT</t>
+  </si>
+  <si>
+    <t>12.1mi N of Floresville TX</t>
+  </si>
+  <si>
+    <t>29.319944, -98.155460</t>
+  </si>
+  <si>
+    <t>09/03/26 12:06 CDT</t>
+  </si>
+  <si>
+    <t>15.2mi NW of Boerne TX</t>
+  </si>
+  <si>
+    <t>29.956223, -98.886830</t>
+  </si>
+  <si>
+    <t>09/03/26 14:36 CDT</t>
+  </si>
+  <si>
+    <t>0.8mi E of Kyle TX</t>
+  </si>
+  <si>
+    <t>29.988993, -97.872160</t>
+  </si>
+  <si>
+    <t>09/03/26 16:09 CDT</t>
+  </si>
+  <si>
+    <t>29.519653, -98.137730</t>
+  </si>
+  <si>
+    <t>09/03/26 17:44 CDT</t>
+  </si>
+  <si>
+    <t>29.582254, -97.999530</t>
+  </si>
+  <si>
+    <t>09/04/26 08:56 CDT</t>
+  </si>
+  <si>
+    <t>29.669832, -98.151250</t>
+  </si>
+  <si>
+    <t>09/04/26 23:56 CDT</t>
+  </si>
+  <si>
+    <t>09/04/26 16:30 CDT</t>
+  </si>
+  <si>
+    <t>29.450418, -98.341810</t>
   </si>
 </sst>
 </file>
@@ -12246,7 +12420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1400"/>
+  <dimension ref="A1:N1420"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -35999,7 +36173,7 @@
         <v>112</v>
       </c>
       <c r="D742" s="3">
-        <v>5622402770</v>
+        <v>5622271458</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>53</v>
@@ -36029,7 +36203,7 @@
         <v>112</v>
       </c>
       <c r="D743" s="3">
-        <v>5622271458</v>
+        <v>5622402770</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>53</v>
@@ -47457,16 +47631,16 @@
         <v>112</v>
       </c>
       <c r="D1095" s="3">
-        <v>5982274614</v>
+        <v>5982274613</v>
       </c>
       <c r="E1095" s="3" t="s">
-        <v>428</v>
+        <v>3075</v>
       </c>
       <c r="F1095" s="3" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="G1095" s="3" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="H1095" s="3" t="s">
         <v>110</v>
@@ -47480,7 +47654,7 @@
         <v>39</v>
       </c>
       <c r="M1095" s="3" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="N1095" s="3"/>
     </row>
@@ -47493,16 +47667,16 @@
         <v>112</v>
       </c>
       <c r="D1096" s="3">
-        <v>5982274613</v>
+        <v>5982274614</v>
       </c>
       <c r="E1096" s="3" t="s">
-        <v>3078</v>
+        <v>428</v>
       </c>
       <c r="F1096" s="3" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="G1096" s="3" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="H1096" s="3" t="s">
         <v>110</v>
@@ -50633,7 +50807,7 @@
         <v>71</v>
       </c>
       <c r="F1194" s="3" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="G1194" s="3" t="s">
         <v>3351</v>
@@ -57322,6 +57496,660 @@
       <c r="M1400" s="3"/>
       <c r="N1400" s="3"/>
     </row>
+    <row r="1401" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1401" s="3" t="s">
+        <v>3955</v>
+      </c>
+      <c r="B1401" s="3"/>
+      <c r="C1401" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1401" s="3">
+        <v>6426822713</v>
+      </c>
+      <c r="E1401" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1401" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1401" s="3" t="s">
+        <v>3956</v>
+      </c>
+      <c r="H1401" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1401" s="3"/>
+      <c r="J1401" s="3"/>
+      <c r="K1401" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1401" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1401" s="3" t="s">
+        <v>3957</v>
+      </c>
+      <c r="N1401" s="3"/>
+    </row>
+    <row r="1402" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1402" s="3" t="s">
+        <v>3958</v>
+      </c>
+      <c r="B1402" s="3"/>
+      <c r="C1402" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1402" s="3">
+        <v>6439810338</v>
+      </c>
+      <c r="E1402" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1402" s="3" t="s">
+        <v>3959</v>
+      </c>
+      <c r="G1402" s="3" t="s">
+        <v>3960</v>
+      </c>
+      <c r="H1402" s="3"/>
+      <c r="I1402" s="3"/>
+      <c r="J1402" s="3"/>
+      <c r="K1402" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1402" s="3"/>
+      <c r="M1402" s="3"/>
+      <c r="N1402" s="3"/>
+    </row>
+    <row r="1403" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1403" s="3" t="s">
+        <v>3961</v>
+      </c>
+      <c r="B1403" s="3"/>
+      <c r="C1403" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1403" s="3">
+        <v>6434650529</v>
+      </c>
+      <c r="E1403" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1403" s="3" t="s">
+        <v>3962</v>
+      </c>
+      <c r="G1403" s="3" t="s">
+        <v>3963</v>
+      </c>
+      <c r="H1403" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1403" s="3"/>
+      <c r="J1403" s="3"/>
+      <c r="K1403" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1403" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1403" s="3" t="s">
+        <v>3964</v>
+      </c>
+      <c r="N1403" s="3"/>
+    </row>
+    <row r="1404" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1404" s="3" t="s">
+        <v>3965</v>
+      </c>
+      <c r="B1404" s="3"/>
+      <c r="C1404" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1404" s="3">
+        <v>6434677619</v>
+      </c>
+      <c r="E1404" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1404" s="3" t="s">
+        <v>3966</v>
+      </c>
+      <c r="G1404" s="3" t="s">
+        <v>3967</v>
+      </c>
+      <c r="H1404" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1404" s="3"/>
+      <c r="J1404" s="3"/>
+      <c r="K1404" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1404" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1404" s="3" t="s">
+        <v>3964</v>
+      </c>
+      <c r="N1404" s="3"/>
+    </row>
+    <row r="1405" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1405" s="3" t="s">
+        <v>3968</v>
+      </c>
+      <c r="B1405" s="3"/>
+      <c r="C1405" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1405" s="3">
+        <v>6435519337</v>
+      </c>
+      <c r="E1405" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1405" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G1405" s="3" t="s">
+        <v>3969</v>
+      </c>
+      <c r="H1405" s="3"/>
+      <c r="I1405" s="3"/>
+      <c r="J1405" s="3"/>
+      <c r="K1405" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1405" s="3"/>
+      <c r="M1405" s="3"/>
+      <c r="N1405" s="3"/>
+    </row>
+    <row r="1406" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1406" s="3" t="s">
+        <v>3970</v>
+      </c>
+      <c r="B1406" s="3"/>
+      <c r="C1406" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1406" s="3">
+        <v>6435529007</v>
+      </c>
+      <c r="E1406" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1406" s="3" t="s">
+        <v>3971</v>
+      </c>
+      <c r="G1406" s="3" t="s">
+        <v>3972</v>
+      </c>
+      <c r="H1406" s="3"/>
+      <c r="I1406" s="3"/>
+      <c r="J1406" s="3"/>
+      <c r="K1406" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1406" s="3"/>
+      <c r="M1406" s="3"/>
+      <c r="N1406" s="3"/>
+    </row>
+    <row r="1407" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1407" s="3" t="s">
+        <v>3973</v>
+      </c>
+      <c r="B1407" s="3"/>
+      <c r="C1407" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1407" s="3">
+        <v>6440591986</v>
+      </c>
+      <c r="E1407" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1407" s="3" t="s">
+        <v>3974</v>
+      </c>
+      <c r="G1407" s="3" t="s">
+        <v>3975</v>
+      </c>
+      <c r="H1407" s="3"/>
+      <c r="I1407" s="3"/>
+      <c r="J1407" s="3"/>
+      <c r="K1407" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1407" s="3"/>
+      <c r="M1407" s="3"/>
+      <c r="N1407" s="3"/>
+    </row>
+    <row r="1408" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1408" s="3" t="s">
+        <v>3976</v>
+      </c>
+      <c r="B1408" s="3"/>
+      <c r="C1408" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1408" s="3">
+        <v>6441525429</v>
+      </c>
+      <c r="E1408" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1408" s="3" t="s">
+        <v>3977</v>
+      </c>
+      <c r="G1408" s="3" t="s">
+        <v>3978</v>
+      </c>
+      <c r="H1408" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1408" s="3"/>
+      <c r="J1408" s="3"/>
+      <c r="K1408" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1408" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1408" s="3" t="s">
+        <v>3979</v>
+      </c>
+      <c r="N1408" s="3"/>
+    </row>
+    <row r="1409" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1409" s="3" t="s">
+        <v>3980</v>
+      </c>
+      <c r="B1409" s="3"/>
+      <c r="C1409" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1409" s="3">
+        <v>6443620376</v>
+      </c>
+      <c r="E1409" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1409" s="3" t="s">
+        <v>3981</v>
+      </c>
+      <c r="G1409" s="3" t="s">
+        <v>3982</v>
+      </c>
+      <c r="H1409" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1409" s="3"/>
+      <c r="J1409" s="3"/>
+      <c r="K1409" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1409" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1409" s="3" t="s">
+        <v>3979</v>
+      </c>
+      <c r="N1409" s="3"/>
+    </row>
+    <row r="1410" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1410" s="3" t="s">
+        <v>3983</v>
+      </c>
+      <c r="B1410" s="3"/>
+      <c r="C1410" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1410" s="3">
+        <v>6454674684</v>
+      </c>
+      <c r="E1410" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1410" s="3" t="s">
+        <v>3984</v>
+      </c>
+      <c r="G1410" s="3" t="s">
+        <v>3985</v>
+      </c>
+      <c r="H1410" s="3"/>
+      <c r="I1410" s="3"/>
+      <c r="J1410" s="3"/>
+      <c r="K1410" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1410" s="3"/>
+      <c r="M1410" s="3"/>
+      <c r="N1410" s="3"/>
+    </row>
+    <row r="1411" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1411" s="3" t="s">
+        <v>3986</v>
+      </c>
+      <c r="B1411" s="3"/>
+      <c r="C1411" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1411" s="3">
+        <v>6444254490</v>
+      </c>
+      <c r="E1411" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1411" s="3" t="s">
+        <v>3987</v>
+      </c>
+      <c r="G1411" s="3" t="s">
+        <v>3988</v>
+      </c>
+      <c r="H1411" s="3"/>
+      <c r="I1411" s="3"/>
+      <c r="J1411" s="3"/>
+      <c r="K1411" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1411" s="3"/>
+      <c r="M1411" s="3"/>
+      <c r="N1411" s="3"/>
+    </row>
+    <row r="1412" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1412" s="3" t="s">
+        <v>3989</v>
+      </c>
+      <c r="B1412" s="3"/>
+      <c r="C1412" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1412" s="3">
+        <v>6461186751</v>
+      </c>
+      <c r="E1412" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1412" s="3" t="s">
+        <v>3990</v>
+      </c>
+      <c r="G1412" s="3" t="s">
+        <v>3991</v>
+      </c>
+      <c r="H1412" s="3"/>
+      <c r="I1412" s="3"/>
+      <c r="J1412" s="3"/>
+      <c r="K1412" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1412" s="3"/>
+      <c r="M1412" s="3"/>
+      <c r="N1412" s="3"/>
+    </row>
+    <row r="1413" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1413" s="3" t="s">
+        <v>3992</v>
+      </c>
+      <c r="B1413" s="3"/>
+      <c r="C1413" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1413" s="3">
+        <v>6448733994</v>
+      </c>
+      <c r="E1413" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1413" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1413" s="3" t="s">
+        <v>3993</v>
+      </c>
+      <c r="H1413" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1413" s="3"/>
+      <c r="J1413" s="3"/>
+      <c r="K1413" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1413" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1413" s="3" t="s">
+        <v>3994</v>
+      </c>
+      <c r="N1413" s="3"/>
+    </row>
+    <row r="1414" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1414" s="3" t="s">
+        <v>3995</v>
+      </c>
+      <c r="B1414" s="3"/>
+      <c r="C1414" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1414" s="3">
+        <v>6449429578</v>
+      </c>
+      <c r="E1414" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1414" s="3" t="s">
+        <v>3996</v>
+      </c>
+      <c r="G1414" s="3" t="s">
+        <v>3997</v>
+      </c>
+      <c r="H1414" s="3"/>
+      <c r="I1414" s="3"/>
+      <c r="J1414" s="3"/>
+      <c r="K1414" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1414" s="3"/>
+      <c r="M1414" s="3"/>
+      <c r="N1414" s="3"/>
+    </row>
+    <row r="1415" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1415" s="3" t="s">
+        <v>3998</v>
+      </c>
+      <c r="B1415" s="3"/>
+      <c r="C1415" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1415" s="3">
+        <v>6450427192</v>
+      </c>
+      <c r="E1415" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1415" s="3" t="s">
+        <v>3999</v>
+      </c>
+      <c r="G1415" s="3" t="s">
+        <v>4000</v>
+      </c>
+      <c r="H1415" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1415" s="3"/>
+      <c r="J1415" s="3"/>
+      <c r="K1415" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1415" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1415" s="3" t="s">
+        <v>3994</v>
+      </c>
+      <c r="N1415" s="3"/>
+    </row>
+    <row r="1416" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1416" s="3" t="s">
+        <v>4001</v>
+      </c>
+      <c r="B1416" s="3"/>
+      <c r="C1416" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1416" s="3">
+        <v>6451816351</v>
+      </c>
+      <c r="E1416" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1416" s="3" t="s">
+        <v>4002</v>
+      </c>
+      <c r="G1416" s="3" t="s">
+        <v>4003</v>
+      </c>
+      <c r="H1416" s="3"/>
+      <c r="I1416" s="3"/>
+      <c r="J1416" s="3"/>
+      <c r="K1416" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1416" s="3"/>
+      <c r="M1416" s="3"/>
+      <c r="N1416" s="3"/>
+    </row>
+    <row r="1417" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1417" s="3" t="s">
+        <v>4004</v>
+      </c>
+      <c r="B1417" s="3"/>
+      <c r="C1417" s="3">
+        <v>113</v>
+      </c>
+      <c r="D1417" s="3">
+        <v>6452637891</v>
+      </c>
+      <c r="E1417" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1417" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1417" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="H1417" s="3"/>
+      <c r="I1417" s="3"/>
+      <c r="J1417" s="3"/>
+      <c r="K1417" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1417" s="3"/>
+      <c r="M1417" s="3"/>
+      <c r="N1417" s="3"/>
+    </row>
+    <row r="1418" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1418" s="3" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B1418" s="3"/>
+      <c r="C1418" s="3">
+        <v>112</v>
+      </c>
+      <c r="D1418" s="3">
+        <v>6453336054</v>
+      </c>
+      <c r="E1418" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1418" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1418" s="3" t="s">
+        <v>4007</v>
+      </c>
+      <c r="H1418" s="3"/>
+      <c r="I1418" s="3"/>
+      <c r="J1418" s="3"/>
+      <c r="K1418" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1418" s="3"/>
+      <c r="M1418" s="3"/>
+      <c r="N1418" s="3"/>
+    </row>
+    <row r="1419" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1419" s="3" t="s">
+        <v>4008</v>
+      </c>
+      <c r="B1419" s="3"/>
+      <c r="C1419" s="3">
+        <v>301</v>
+      </c>
+      <c r="D1419" s="3">
+        <v>6456144316</v>
+      </c>
+      <c r="E1419" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1419" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G1419" s="3" t="s">
+        <v>4009</v>
+      </c>
+      <c r="H1419" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1419" s="3"/>
+      <c r="J1419" s="3"/>
+      <c r="K1419" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1419" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1419" s="3" t="s">
+        <v>4010</v>
+      </c>
+      <c r="N1419" s="3"/>
+    </row>
+    <row r="1420" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1420" s="3" t="s">
+        <v>4011</v>
+      </c>
+      <c r="B1420" s="3"/>
+      <c r="C1420" s="3">
+        <v>110</v>
+      </c>
+      <c r="D1420" s="3">
+        <v>6459778660</v>
+      </c>
+      <c r="E1420" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1420" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G1420" s="3" t="s">
+        <v>4012</v>
+      </c>
+      <c r="H1420" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1420" s="3"/>
+      <c r="J1420" s="3"/>
+      <c r="K1420" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1420" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1420" s="3" t="s">
+        <v>4010</v>
+      </c>
+      <c r="N1420" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
